--- a/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-groups.xlsx
+++ b/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-groups.xlsx
@@ -107,7 +107,7 @@
     <t>,,</t>
   </si>
   <si>
-    <t>(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010)</t>
+    <t>(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Хроника первой российской войны в Чечне 2026)</t>
   </si>
   <si>
     <t>source ID</t>

--- a/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-groups.xlsx
+++ b/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-groups.xlsx
@@ -107,7 +107,7 @@
     <t>,,</t>
   </si>
   <si>
-    <t>(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Хроника первой российской войны в Чечне 2026)</t>
+    <t>(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010)</t>
   </si>
   <si>
     <t>source ID</t>

--- a/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-groups.xlsx
+++ b/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-groups.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4450" uniqueCount="1343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4469" uniqueCount="1354">
   <si>
     <t>ID</t>
   </si>
@@ -68,22 +68,22 @@
     <t>G0013</t>
   </si>
   <si>
-    <t>intrusion-set--764cac65-3338-4105-9501-152d67a8fc5b</t>
-  </si>
-  <si>
-    <t>intrusion-set--d02a2528-4983-49ba-9958-e3dca5f57c1a</t>
-  </si>
-  <si>
-    <t>intrusion-set--7077cfc8-f533-42d0-bc5a-a2bbebf847e1</t>
-  </si>
-  <si>
-    <t>intrusion-set--8837e6ef-c6bb-4b41-b8c6-c0588be2db1c</t>
-  </si>
-  <si>
-    <t>intrusion-set--a6148444-d09e-4aa5-8c32-50da2bd25525</t>
-  </si>
-  <si>
-    <t>intrusion-set--43830a9b-2a24-4049-8b19-d210028de96e</t>
+    <t>intrusion-set--6bb397ce-d257-45ef-9a68-fd682239dc91</t>
+  </si>
+  <si>
+    <t>intrusion-set--080fc39f-be32-4bdf-aa6b-d86e3dcd4f81</t>
+  </si>
+  <si>
+    <t>intrusion-set--6fcf2657-4840-4754-a318-5cee4b91d670</t>
+  </si>
+  <si>
+    <t>intrusion-set--4f0187aa-3964-42bb-8185-827fd9232dcb</t>
+  </si>
+  <si>
+    <t>intrusion-set--1e2aa43d-a27c-407c-b94a-405123ec52f9</t>
+  </si>
+  <si>
+    <t>intrusion-set--701ece7a-3998-432c-ab53-b4496887b072</t>
   </si>
   <si>
     <t>Белое движение (ВСЮР)</t>
@@ -149,22 +149,22 @@
     <t>1.0</t>
   </si>
   <si>
-    <t>(Citation: Україна й українці в постімперську добу (1917–1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917–1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.)</t>
-  </si>
-  <si>
-    <t>(Citation: Русифікація України — Вікіпедія 2026),(Citation: Московсько-українська війна (1658—1659),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Руїна — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Решетилівські статті — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Мазепа 2007),(Citation: Московсько-українська війна (1658—1659),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Малоросійський приказ — Вікіпедія 2026),(Citation: Запорозька Січ — Вікіпедія 2026),(Citation: Переяславська рада — Вікіпедія 2026),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Киевский синопсис — Википедия 2026),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Північна війна (1700—1721),(Citation: Руїна — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Переяславські статті (1659),(Citation: Ліквідація козацтва на Правобережній Україні (1699),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Конотопські статті — Вікіпедія 2026),(Citation: Решетилівські статті — Вікіпедія 2026),(Citation: Киевский синопсис — Википедия 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Переяславські статті (1659),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Мазепа 2007),(Citation: Запорозька Січ — Вікіпедія 2026),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Руїна — Вікіпедія 2026),(Citation: Азовські походи (1695—1696),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Андрусовское перемирие - Википедия 2026),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Малоросійський приказ — Вікіпедія 2026),(Citation: Переяславська рада — Вікіпедія 2026),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Московські статті (1665)</t>
-  </si>
-  <si>
-    <t>(Citation: Ліквідація Запорозької Січі (1775),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Друга Малоросійська колегія — Вікіпедія 2026),(Citation: Листопадове повстання (1830—1831),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Чорносотенці — Вікіпедія 2026),(Citation: Історія Донецької області — Вікіпедія 2026),(Citation: Столипінська реформа — Вікіпедія 2026),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Повстання бузьких козаків (1817),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Україна у війнах Наполеона — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Повстання бузьких козаків (1817),(Citation: Російсько-турецька війна (1806—1812),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026),(Citation: Антикріпосницький рух в Україні (1789-1861),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Польское восстание (1863—1864),(Citation: Столипінська реформа — Вікіпедія 2026),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Правління гетьманського уряду — Вікіпедія 2026),(Citation: Чорносотенці — Вікіпедія 2026),(Citation: Малоросійське генерал-губернаторство — Вікіпедія 2026),(Citation: Листопадове повстання (1830—1831),(Citation: Русско-турецкая война (1768—1774),(Citation: Перепис населення Російської імперії (1897),(Citation: Смуга осілості — Вікіпедія 2026),(Citation: Крымская война — Википедия 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Кирило-Мефодіївське товариство — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026)</t>
-  </si>
-  <si>
-    <t>(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Российские удары по украинской энергосистеме — Википедия 2026),(Citation: Дезінформація під час російсько-української війни — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Російсько-українська війна (з 2014),(Citation: 2015 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023),(Citation: 2016 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Рашизм: Звір з безодні 2023),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Хроника первой российской войны в Чечне 2026)</t>
-  </si>
-  <si>
-    <t>(Citation: Карательная психиатрия в России: назад в СССР? 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Україна й українці в постімперську добу (1917–1939),(Citation: Карательная психиатрия в России: назад в СССР? 2026),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: РАШИЗМ ЗВІР З БЕЗОДНІ 2023),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Котлета по-київськи (промова),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Кенгирское восстание заключённых - Википедия 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Україна й українці в постімперську добу (1917–1939),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: В ТЕНИ «БОЛЬШОГО БРАТА» ЗАПАДНЫЕ НАЦИОНАЛЬНЫЕ МЕНЬШИНСТВА В СССР 1917-1938 ГГ . 2011),(Citation: РАШИЗМ ЗВІР З БЕЗОДНІ 2023),(Citation: ДИССИДЕНТСКОЕ ДВИЖЕНИЕ В УКРАИНЕ (1954 – 1987),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Всесоюзний референдум про збереження СРСР — Вікіпедія 2026),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.)</t>
-  </si>
-  <si>
-    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Україна й українці в постімперську добу (1917–1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Україна й українці в постімперську добу (1917–1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917–1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.)</t>
+    <t>(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.)</t>
+  </si>
+  <si>
+    <t>(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Руїна — Вікіпедія 2026),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Московсько-українська війна (1658—1659),(Citation: Русифікація України — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Руїна — Вікіпедія 2026),(Citation: Переяславські статті (1659),(Citation: Малоросійський приказ — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Мазепа 2007),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Переяславська рада — Вікіпедія 2026),(Citation: Решетилівські статті — Вікіпедія 2026),(Citation: Московсько-українська війна (1658—1659),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Киевский синопсис — Википедия 2026),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Північна війна (1700—1721),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Запорозька Січ — Вікіпедія 2026),(Citation: Руїна — Вікіпедія 2026),(Citation: Переяславська рада — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Московські статті (1665),(Citation: Переяславські статті (1659),(Citation: Мазепа 2007),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Малоросійський приказ — Вікіпедія 2026),(Citation: Решетилівські статті — Вікіпедія 2026),(Citation: Андрусовское перемирие - Википедия 2026),(Citation: Ліквідація козацтва на Правобережній Україні (1699),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Конотопські статті — Вікіпедія 2026),(Citation: Киевский синопсис — Википедия 2026),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Азовські походи (1695—1696),(Citation: Запорозька Січ — Вікіпедія 2026)</t>
+  </si>
+  <si>
+    <t>(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: Чорносотенці — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Листопадове повстання (1830—1831),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Історія Донецької області — Вікіпедія 2026),(Citation: Столипінська реформа — Вікіпедія 2026),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Друга Малоросійська колегія — Вікіпедія 2026),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Повстання бузьких козаків (1817),(Citation: Історія України — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026),(Citation: Перепис населення Російської імперії (1897),(Citation: Правління гетьманського уряду — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Крымская война — Википедия 2026),(Citation: Столипінська реформа — Вікіпедія 2026),(Citation: Повстання бузьких козаків (1817),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Кирило-Мефодіївське товариство — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Антикріпосницький рух в Україні (1789-1861),(Citation: Листопадове повстання (1830—1831),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Русско-турецкая война (1768—1774),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Малоросійське генерал-губернаторство — Вікіпедія 2026),(Citation: Чорносотенці — Вікіпедія 2026),(Citation: Польское восстание (1863—1864),(Citation: Україна у війнах Наполеона — Вікіпедія 2026),(Citation: Смуга осілості — Вікіпедія 2026),(Citation: Російсько-турецька війна (1806—1812),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026)</t>
+  </si>
+  <si>
+    <t>(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: 2016 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Рашизм: Звір з безодні 2023),(Citation: Российские удары по украинской энергосистеме — Википедия 2026),(Citation: 2015 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Російсько-українська війна (з 2014),(Citation: Дезінформація під час російсько-української війни — Вікіпедія 2026),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010)</t>
+  </si>
+  <si>
+    <t>(Citation: Карательная психиатрия в России: назад в СССР? 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Рашизм: Звір з безодні 2023),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Карательная психиатрия в России: назад в СССР? 2026),(Citation: Котлета по-київськи (промова),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Історія України — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Кенгирское восстание заключённых - Википедия 2026),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Рашизм: Звір з безодні 2023),(Citation: В ТЕНИ «БОЛЬШОГО БРАТА» ЗАПАДНЫЕ НАЦИОНАЛЬНЫЕ МЕНЬШИНСТВА В СССР 1917-1938 ГГ . 2011),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: ДИССИДЕНТСКОЕ ДВИЖЕНИЕ В УКРАИНЕ (1954 – 1987),(Citation: Всесоюзний референдум про збереження СРСР — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026)</t>
+  </si>
+  <si>
+    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939)</t>
   </si>
   <si>
     <t>source ID</t>
@@ -281,49 +281,49 @@
     <t>Подконтрольная оппозиция</t>
   </si>
   <si>
-    <t>tool--f772df95-d66e-4e57-8645-b8020a451f65</t>
-  </si>
-  <si>
-    <t>tool--72e7409f-63c7-43bd-9414-02a61e50b0b2</t>
-  </si>
-  <si>
-    <t>tool--88321b03-b598-459c-b69c-53b4cb0ebb20</t>
-  </si>
-  <si>
-    <t>tool--4556118e-edf6-43e4-9cee-24e270ae451e</t>
-  </si>
-  <si>
-    <t>tool--f74fade6-c2ba-4cbc-8833-3daf6cc482ae</t>
-  </si>
-  <si>
-    <t>tool--f889d8a2-0000-47c9-b8b3-1a12089eec06</t>
-  </si>
-  <si>
-    <t>tool--cdc507d7-2b86-4fd9-9a01-b0172cfc5205</t>
-  </si>
-  <si>
-    <t>tool--f92083ef-3b0a-455a-a6ca-fc137cb4a6c0</t>
-  </si>
-  <si>
-    <t>tool--f69553b2-8023-4d84-b754-92e67a665955</t>
-  </si>
-  <si>
-    <t>tool--ea14cd7b-585a-494b-88e8-d9f8da2455eb</t>
-  </si>
-  <si>
-    <t>tool--60e274fe-60d9-44b4-b2e2-19ab1948bd5e</t>
-  </si>
-  <si>
-    <t>tool--229ccd55-af8b-4954-9d37-c01c7b007daf</t>
-  </si>
-  <si>
-    <t>tool--29369b13-242b-4f23-92f0-f8c810bc8cd4</t>
+    <t>tool--6fd47d4c-bac8-4dcd-b582-e6a42bb51313</t>
+  </si>
+  <si>
+    <t>tool--4a55efd1-b775-4318-8adc-ebb029729960</t>
+  </si>
+  <si>
+    <t>tool--78806636-7cbc-4a54-9f61-2a5a98a33f13</t>
+  </si>
+  <si>
+    <t>tool--4d2e439d-9619-4447-8a41-1af8960acc55</t>
+  </si>
+  <si>
+    <t>tool--60f65bd4-46b3-4eed-9418-254cf51965fd</t>
+  </si>
+  <si>
+    <t>tool--17849785-49e2-4f22-9488-618cbc11cec9</t>
+  </si>
+  <si>
+    <t>tool--b8bf442f-c688-4983-bc89-7fc0e5a2d70f</t>
+  </si>
+  <si>
+    <t>tool--6faacf93-e3f5-43f6-8d94-9d2c7c6382a9</t>
+  </si>
+  <si>
+    <t>tool--1652bd4f-c611-4f10-aedc-6581590e2df2</t>
+  </si>
+  <si>
+    <t>tool--03b1e023-5469-49ea-9988-c7118a91b725</t>
+  </si>
+  <si>
+    <t>tool--ed0808d4-111e-4057-a345-7d951b669eb5</t>
+  </si>
+  <si>
+    <t>tool--43db716c-e55e-4798-8810-4606ebb81e52</t>
+  </si>
+  <si>
+    <t>tool--b591e96e-6cd5-4b20-9c6f-aa7dc5747255</t>
   </si>
   <si>
     <t>software</t>
   </si>
   <si>
-    <t>Ультимативный отказ белогвардейского командования (генерал Бредов) признавать украинскую армию и государственность, сопровождавшийся заявлением, что «Киев никогда не был украинским и не будет». (Citation: Україна й українці в постімперську добу (1917–1939) 2021)</t>
+    <t>Ультимативный отказ белогвардейского командования (генерал Бредов) признавать украинскую армию и государственность, сопровождавшийся заявлением, что «Киев никогда не был украинским и не будет». (Citation: Україна й українці в постімперську добу (1917—1939) 2021)</t>
   </si>
   <si>
     <t>Оккупационная политика генерала Деникина, направленная на уничтожение украинской культуры путем ликвидации права обучаться на родном языке и прямого закрытия украинских школ. (Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.) 2013)</t>
@@ -410,10 +410,10 @@
     <t>Целенаправленное физическое уничтожение (массовые казни) национальной культурной элиты — трагедия, вошедшая в историю как [«Расстрелянное возрождение»](https://ru.wikipedia.org/wiki/Расстрелянное_возрождение). «Телеграма Сталіна про припинення українізації і знищення більшості українських письменників» (Citation: Русифікація України — Вікіпедія 2026). Эти репрессии уничтожили целое поколение выдающихся украинских писателей, поэтов и интеллигенции (Citation: Война и наказание: Как Россия уничтожала Украину 2023).</t>
   </si>
   <si>
-    <t>Использование Советом народных комиссаров местных большевистских ячеек в качестве легальной политической силы, которая должна была выступить от имени украинского пролетариата против Центральной Рады. (Citation: Україна й українці в постімперську добу (1917–1939) 2021)</t>
-  </si>
-  <si>
-    <t>Проведение фейкового альтернативного съезда в Харькове и создание подконтрольного Москве «Народного секретариата» для имитации внутренней борьбы. (Citation: Україна й українці в постімперську добу (1917–1939) 2021)</t>
+    <t>Использование Советом народных комиссаров местных большевистских ячеек в качестве легальной политической силы, которая должна была выступить от имени украинского пролетариата против Центральной Рады. (Citation: Україна й українці в постімперську добу (1917—1939) 2021)</t>
+  </si>
+  <si>
+    <t>Проведение фейкового альтернативного съезда в Харькове и создание подконтрольного Москве «Народного секретариата» для имитации внутренней борьбы. (Citation: Україна й українці в постімперську добу (1917—1939) 2021)</t>
   </si>
   <si>
     <t>Целенаправленная переброска лояльных делегатов и политических агитаторов на Всеукраинский съезд советов в Киеве для перехвата повестки изнутри. (Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.) 2013)</t>
@@ -425,106 +425,106 @@
     <t>Провоцирование большевиками восстания рабочих завода «Арсенал» в самом Киеве для оттягивания резервов украинских властей прямо во время наступления красных войск. (Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
   </si>
   <si>
-    <t>relationship--07ff3bf1-da85-48ff-a7f1-092087360a4b</t>
-  </si>
-  <si>
-    <t>relationship--a568902c-2781-4c02-9561-daa3cd389fdd</t>
-  </si>
-  <si>
-    <t>relationship--7fc72472-9b9e-4c55-b0f6-b594a238d151</t>
-  </si>
-  <si>
-    <t>relationship--6adb2573-0b76-4a78-814e-f1065642ca10</t>
-  </si>
-  <si>
-    <t>relationship--d18a5e90-6666-473b-a5d4-61e0229c1b0c</t>
-  </si>
-  <si>
-    <t>relationship--5147f80b-0d35-4fb9-b077-7e4edb6625b7</t>
-  </si>
-  <si>
-    <t>relationship--755b810b-2223-4724-8f71-7b5b131558ad</t>
-  </si>
-  <si>
-    <t>relationship--e37f82fa-879e-4232-b4e6-cbb67afc4eed</t>
-  </si>
-  <si>
-    <t>relationship--73c719f0-ddaa-4188-8ee1-0a2d1d18072c</t>
-  </si>
-  <si>
-    <t>relationship--1ff820f2-be59-4c12-bfa9-d93a821cabff</t>
-  </si>
-  <si>
-    <t>relationship--bb015f20-2518-43a7-83d6-c248c75697d9</t>
-  </si>
-  <si>
-    <t>relationship--f2117157-5739-4fb7-ba0e-b8755049c60c</t>
-  </si>
-  <si>
-    <t>relationship--3c6e4570-df11-4a98-880a-bf4b2b08c35e</t>
-  </si>
-  <si>
-    <t>relationship--9d83a076-25c0-4350-a631-2d2d8e92c550</t>
-  </si>
-  <si>
-    <t>relationship--cf5e11df-ba9e-44b4-af92-9bd3834541a3</t>
-  </si>
-  <si>
-    <t>relationship--9fbf80bb-c4c6-4ae9-8210-bac7d061d88c</t>
-  </si>
-  <si>
-    <t>relationship--f28dec40-aeef-4066-baf1-a4503f18169d</t>
-  </si>
-  <si>
-    <t>relationship--17e09586-8594-4ad7-b94d-e29a9543f19b</t>
-  </si>
-  <si>
-    <t>relationship--4d20a15e-ffdf-4500-9ab7-1f578cad1263</t>
-  </si>
-  <si>
-    <t>relationship--5a177542-b091-4817-b666-f322dcb7ed63</t>
-  </si>
-  <si>
-    <t>relationship--f7b12560-78ed-4f92-a296-151ccd80b9f0</t>
-  </si>
-  <si>
-    <t>relationship--08a05095-e51f-45a7-b895-568a10262260</t>
-  </si>
-  <si>
-    <t>relationship--cec33e7a-2cda-46f4-8a37-90a991776503</t>
-  </si>
-  <si>
-    <t>relationship--078c6efe-8978-4f8f-95ce-4d632f3c68d7</t>
-  </si>
-  <si>
-    <t>relationship--5083da2c-53cc-44ff-b31d-af6bc2ec1075</t>
-  </si>
-  <si>
-    <t>relationship--c2ba08ea-f1d1-492d-9287-fb0f293fbbbc</t>
-  </si>
-  <si>
-    <t>relationship--f6ea15aa-1bac-42ac-8f0b-abf92500a9cf</t>
-  </si>
-  <si>
-    <t>relationship--5f605d53-64c0-4be6-9bb1-aa9ecbdb4041</t>
-  </si>
-  <si>
-    <t>relationship--b27d1694-379e-4dc8-9a89-6c8f149fcb4b</t>
-  </si>
-  <si>
-    <t>relationship--154a4f4b-614f-4e7a-afc2-a72aabf44daa</t>
-  </si>
-  <si>
-    <t>relationship--4627ab63-1c88-4c31-8390-c649f58d53e4</t>
-  </si>
-  <si>
-    <t>relationship--256ea25f-fba9-4b0c-93c1-f19726910d48</t>
-  </si>
-  <si>
-    <t>relationship--6c4b53a7-4999-421a-bef6-7f49392b9aa2</t>
-  </si>
-  <si>
-    <t>relationship--4b52815f-e22e-41e1-824e-e531749f5f65</t>
+    <t>relationship--748adbe7-f59c-4bc0-97f4-de3ec43934c9</t>
+  </si>
+  <si>
+    <t>relationship--223dcaad-ae78-43af-86c8-5494371b1d37</t>
+  </si>
+  <si>
+    <t>relationship--54823f51-aa85-4d2f-ba24-5f50309914c7</t>
+  </si>
+  <si>
+    <t>relationship--ac746805-7a46-4ae9-8b34-a32e9a11c539</t>
+  </si>
+  <si>
+    <t>relationship--4964717a-b221-499a-927d-39dcb9db33a2</t>
+  </si>
+  <si>
+    <t>relationship--7c711dce-6dd9-45f8-8bc2-7343d77afe0f</t>
+  </si>
+  <si>
+    <t>relationship--6b10a528-82da-42f7-9cdc-1aa588fab481</t>
+  </si>
+  <si>
+    <t>relationship--bc8eb603-4feb-4413-bf43-80cb97d78378</t>
+  </si>
+  <si>
+    <t>relationship--6156c3c7-b5ba-49fd-b912-528c84e7a683</t>
+  </si>
+  <si>
+    <t>relationship--addd0ef0-894f-455c-8180-38cd60e04c37</t>
+  </si>
+  <si>
+    <t>relationship--ffc52e98-63f1-4ff9-9e6c-0ecf73c132a4</t>
+  </si>
+  <si>
+    <t>relationship--5e3dfb1e-eacc-43fe-ab72-12a4adcd0e10</t>
+  </si>
+  <si>
+    <t>relationship--b13a8a02-0a0e-461c-bb4b-4a4376ff35c6</t>
+  </si>
+  <si>
+    <t>relationship--6a268ffe-5e34-4dff-86c0-07aa08dcb5a2</t>
+  </si>
+  <si>
+    <t>relationship--be640a50-5ff4-4b10-ba98-384c9b0d55c8</t>
+  </si>
+  <si>
+    <t>relationship--7776534d-2830-47ec-a5f7-3cfce9bb3d44</t>
+  </si>
+  <si>
+    <t>relationship--374dc1bc-6679-4a55-9b31-fb16e91b7f00</t>
+  </si>
+  <si>
+    <t>relationship--c8637b07-3a35-46c8-aa81-13619be9953e</t>
+  </si>
+  <si>
+    <t>relationship--8dd4ccd1-6e48-4e5c-9b30-f06ab1d93521</t>
+  </si>
+  <si>
+    <t>relationship--5dcc9361-437b-4a59-a451-3d954258d94d</t>
+  </si>
+  <si>
+    <t>relationship--9d98aef8-2024-4ee4-84cc-07e3af7e47c5</t>
+  </si>
+  <si>
+    <t>relationship--856984be-eae4-4f32-b090-8ed806b87c1e</t>
+  </si>
+  <si>
+    <t>relationship--df3c4fca-1b31-4f57-a805-f4f74a87dfe7</t>
+  </si>
+  <si>
+    <t>relationship--014fda40-f5c3-47ed-a2ed-3b6b46c55878</t>
+  </si>
+  <si>
+    <t>relationship--f85f034d-6561-4988-abaa-ac7172a7bd76</t>
+  </si>
+  <si>
+    <t>relationship--55964349-3162-4e27-bb1e-abf01bb55215</t>
+  </si>
+  <si>
+    <t>relationship--4534db45-fe9b-4f0e-aedc-98ad60b13128</t>
+  </si>
+  <si>
+    <t>relationship--4330ffb9-d8ff-4288-ac43-6a065a313900</t>
+  </si>
+  <si>
+    <t>relationship--3d908446-973f-47fc-a39e-3789efe97ff3</t>
+  </si>
+  <si>
+    <t>relationship--232d9c6f-6ad7-4312-a2d8-c607f9ee0276</t>
+  </si>
+  <si>
+    <t>relationship--e642c95f-3e56-4c24-a977-d86cc4c20ba3</t>
+  </si>
+  <si>
+    <t>relationship--8227572b-82be-4c2c-861b-5113f97dfddd</t>
+  </si>
+  <si>
+    <t>relationship--f7a0de34-a733-435a-9ec1-62e98780f91a</t>
+  </si>
+  <si>
+    <t>relationship--06fe07f5-9a2f-47f1-b0a5-6e296fb85588</t>
   </si>
   <si>
     <t>T0019</t>
@@ -1025,259 +1025,259 @@
     <t>Поддержка подконтрольной оппозиции</t>
   </si>
   <si>
-    <t>attack-pattern--972bf47e-c0f5-4dae-97cd-9451c7bc4603</t>
-  </si>
-  <si>
-    <t>attack-pattern--ff63c265-0310-4574-82ad-3dc8a99c3488</t>
-  </si>
-  <si>
-    <t>attack-pattern--f7e4beb6-0682-47aa-acf9-03c1ca5d415a</t>
-  </si>
-  <si>
-    <t>attack-pattern--9336c78d-5a9f-4d5b-b674-0e344c73b809</t>
-  </si>
-  <si>
-    <t>attack-pattern--55fed0eb-37e3-4ce6-b9a3-a924f2578368</t>
-  </si>
-  <si>
-    <t>attack-pattern--9f3fdc90-cca7-485e-b78b-eefe2753dc95</t>
-  </si>
-  <si>
-    <t>attack-pattern--cd8bb5ae-5aff-4b70-8d6f-31ac36eadbde</t>
-  </si>
-  <si>
-    <t>attack-pattern--0d84c262-0100-44cc-9fd7-a698ee3776dc</t>
-  </si>
-  <si>
-    <t>attack-pattern--eb3aa6f0-74f5-4e0a-861e-a2c82ffc0798</t>
-  </si>
-  <si>
-    <t>attack-pattern--5a357495-f376-4a5e-a3f7-0066f362328b</t>
-  </si>
-  <si>
-    <t>attack-pattern--af2dabb3-15cb-4c7a-87ae-6953c2686480</t>
-  </si>
-  <si>
-    <t>attack-pattern--20693395-073f-458c-b2a1-7be782d97354</t>
-  </si>
-  <si>
-    <t>attack-pattern--281579e8-e28f-4e62-9971-a18fab84e0af</t>
-  </si>
-  <si>
-    <t>attack-pattern--cffadcf5-6a6b-4e1f-8b87-85adf27c9f9c</t>
-  </si>
-  <si>
-    <t>attack-pattern--57e6c6c4-a591-4903-9985-4d284b4eaf64</t>
-  </si>
-  <si>
-    <t>attack-pattern--3cb79497-d461-4586-860f-71737528f775</t>
-  </si>
-  <si>
-    <t>attack-pattern--22a5b731-e091-4444-bc84-5e60eba2a2bb</t>
-  </si>
-  <si>
-    <t>attack-pattern--a83e27a1-55ce-4327-8003-590d22630ae9</t>
-  </si>
-  <si>
-    <t>attack-pattern--ae2812e0-2ac6-48c0-aaf1-8a649e218bd7</t>
-  </si>
-  <si>
-    <t>attack-pattern--c9e6ccf7-a8ae-4556-bede-76dbb5670f16</t>
-  </si>
-  <si>
-    <t>attack-pattern--952c089f-d14e-4e35-a31d-95ebc0496362</t>
-  </si>
-  <si>
-    <t>attack-pattern--f09d31c3-1ef9-4f13-9587-c5645517cfe0</t>
-  </si>
-  <si>
-    <t>attack-pattern--61b8a224-eb09-443f-822a-8009280fcdc5</t>
-  </si>
-  <si>
-    <t>attack-pattern--d080b90a-f3a6-4503-8b13-e422b7a47265</t>
-  </si>
-  <si>
-    <t>attack-pattern--69a3d9fe-d220-4cc1-ac9e-0eb3c8da7a10</t>
-  </si>
-  <si>
-    <t>attack-pattern--25092de4-9a0b-4dbc-8b23-6d1a000a5f42</t>
-  </si>
-  <si>
-    <t>attack-pattern--d7da24f0-8fe5-4136-85ff-12c3f911587f</t>
-  </si>
-  <si>
-    <t>attack-pattern--a903cd8c-c914-4408-ae0a-c915df961d3b</t>
-  </si>
-  <si>
-    <t>attack-pattern--f98477fa-369f-4d0d-8064-a2180d75714c</t>
-  </si>
-  <si>
-    <t>attack-pattern--ba2aee33-7edc-416e-921b-2aece2032428</t>
-  </si>
-  <si>
-    <t>attack-pattern--91f8404d-6987-41b7-b7a9-df79fe77afe5</t>
-  </si>
-  <si>
-    <t>attack-pattern--09a18447-c729-43f1-8ceb-2d48687eac97</t>
-  </si>
-  <si>
-    <t>attack-pattern--154481f0-8068-45c2-9e46-31ae7dc6853a</t>
-  </si>
-  <si>
-    <t>attack-pattern--a46ec1d7-5bdd-4e55-a04f-a6f259b5e12e</t>
-  </si>
-  <si>
-    <t>attack-pattern--0ef67418-f9c5-4e0f-9e36-0747bc8f210c</t>
-  </si>
-  <si>
-    <t>attack-pattern--024d1d49-921a-479d-b8c4-90d4f7f94d35</t>
-  </si>
-  <si>
-    <t>attack-pattern--5111de41-6dbf-4ce2-ab89-beaa810e1cf7</t>
-  </si>
-  <si>
-    <t>attack-pattern--262ba99b-f4f8-41cb-b5cd-5b08f6bb8bd3</t>
-  </si>
-  <si>
-    <t>attack-pattern--8209784f-cde9-413a-bc2b-2ad5da2f0bba</t>
-  </si>
-  <si>
-    <t>attack-pattern--e0246bcc-9820-45fa-bfea-862bed9dd573</t>
-  </si>
-  <si>
-    <t>attack-pattern--e236beed-9135-4388-92da-004919b6e1c8</t>
-  </si>
-  <si>
-    <t>attack-pattern--f7c2ef21-3827-4a2e-91f2-e658ba4e6fa5</t>
-  </si>
-  <si>
-    <t>attack-pattern--cc247977-b994-472a-a92f-a82cf26cbbe2</t>
-  </si>
-  <si>
-    <t>attack-pattern--4de692cb-753a-45d3-ac80-34255162bcaf</t>
-  </si>
-  <si>
-    <t>attack-pattern--c0383ad6-d98f-4336-963f-37398fe3c9a3</t>
-  </si>
-  <si>
-    <t>attack-pattern--d5f1412a-2885-40f5-a71f-f39ad84178c0</t>
-  </si>
-  <si>
-    <t>attack-pattern--4a7ebe15-e0c5-424d-8581-ba13a207baf0</t>
-  </si>
-  <si>
-    <t>attack-pattern--48d4b99e-6c35-41df-9bca-54744d0eb5bd</t>
-  </si>
-  <si>
-    <t>attack-pattern--7aa1b36a-86ff-4f8b-b158-ee648a9ef31a</t>
-  </si>
-  <si>
-    <t>attack-pattern--ecf3feb7-137c-4f53-9e1c-2e1181947f3c</t>
-  </si>
-  <si>
-    <t>attack-pattern--3fb03caa-0900-45aa-b166-8e7282b52a60</t>
-  </si>
-  <si>
-    <t>attack-pattern--e5c43fec-3847-47e6-aad1-56f38d6c0723</t>
-  </si>
-  <si>
-    <t>attack-pattern--f4ee8a5d-0fb9-42f8-8046-04b5e02d18be</t>
-  </si>
-  <si>
-    <t>attack-pattern--e99f7a3a-594c-4175-9d82-5b5c75db890d</t>
-  </si>
-  <si>
-    <t>attack-pattern--c3384966-9c95-434d-bcf2-3be46383e578</t>
-  </si>
-  <si>
-    <t>attack-pattern--7b14e908-93a7-43b6-a8d4-ef9881f7b070</t>
-  </si>
-  <si>
-    <t>attack-pattern--65b7c386-1376-4ee1-a83e-d9a77c643142</t>
-  </si>
-  <si>
-    <t>attack-pattern--1d927ea8-3d2b-413f-8459-9786ccf5b725</t>
-  </si>
-  <si>
-    <t>attack-pattern--7d791de3-2e04-431d-ba88-dbdde6add3f4</t>
-  </si>
-  <si>
-    <t>attack-pattern--b66ac526-6f64-4e32-9922-2d68e51631b1</t>
-  </si>
-  <si>
-    <t>attack-pattern--dba55821-e44f-42a3-b519-056650fee6a3</t>
-  </si>
-  <si>
-    <t>attack-pattern--85ac27b3-8e0a-481a-8960-03146d6387b9</t>
-  </si>
-  <si>
-    <t>attack-pattern--ea0a04c0-9769-475c-8c33-4f5c369808b9</t>
-  </si>
-  <si>
-    <t>attack-pattern--49a44b3e-87a2-4cf6-a4f0-fd58d82d63ea</t>
-  </si>
-  <si>
-    <t>attack-pattern--53cb5b45-acd8-45ad-8e44-a1db86632a2d</t>
-  </si>
-  <si>
-    <t>attack-pattern--50d263b4-e04e-4942-a7d4-026ee3dd7f03</t>
-  </si>
-  <si>
-    <t>attack-pattern--8a9a83e5-2d69-4928-8efc-9a84de5d0373</t>
-  </si>
-  <si>
-    <t>attack-pattern--816d2931-33e2-4dde-a98f-1bdcd38931b3</t>
-  </si>
-  <si>
-    <t>attack-pattern--a4deb5e5-f8da-46dc-91ed-17f22df9d9f1</t>
-  </si>
-  <si>
-    <t>attack-pattern--e64e3ca3-6b6e-482c-bdb2-3d3a64794457</t>
-  </si>
-  <si>
-    <t>attack-pattern--953bf0ac-d5ae-4b33-a124-4c223463b0fa</t>
-  </si>
-  <si>
-    <t>attack-pattern--46228d06-6a20-4748-9cdb-8155982fdceb</t>
-  </si>
-  <si>
-    <t>attack-pattern--896791e3-5b2d-426b-a067-e6e79c492c4a</t>
-  </si>
-  <si>
-    <t>attack-pattern--069c328b-ad93-472b-bf2f-08db21002615</t>
-  </si>
-  <si>
-    <t>attack-pattern--e27e053b-85f7-4f3b-9caa-70ba91cc3a44</t>
-  </si>
-  <si>
-    <t>attack-pattern--404cbad7-d4cf-4dfa-a2d5-f7e771b4c804</t>
-  </si>
-  <si>
-    <t>attack-pattern--8056b7be-c173-4a65-8710-6ea8194a3741</t>
-  </si>
-  <si>
-    <t>attack-pattern--a0d79fcb-de29-4b04-ab91-078640aa7942</t>
-  </si>
-  <si>
-    <t>attack-pattern--9dfb75d7-34d0-4b59-a463-4300cf5493a6</t>
-  </si>
-  <si>
-    <t>attack-pattern--bf051bf8-cc3b-4bed-921d-d093e17d11b6</t>
-  </si>
-  <si>
-    <t>attack-pattern--f3ce3c11-3e28-4d6e-b4f2-426f987041f8</t>
-  </si>
-  <si>
-    <t>attack-pattern--ecc01b5f-5093-4549-972c-ff73588df011</t>
-  </si>
-  <si>
-    <t>attack-pattern--a45e2a90-8a79-47a9-ad3e-2c1f33b089f3</t>
+    <t>attack-pattern--563b0db6-14f7-4b63-8256-95de0ef5cf8c</t>
+  </si>
+  <si>
+    <t>attack-pattern--ca41993a-f62d-477b-802f-e63f4c050380</t>
+  </si>
+  <si>
+    <t>attack-pattern--8accb141-a1ff-471e-9a3a-988919bcceb6</t>
+  </si>
+  <si>
+    <t>attack-pattern--8feebaca-97cf-4478-b1d3-8e0a8ed2edc0</t>
+  </si>
+  <si>
+    <t>attack-pattern--e49e8037-4bae-447d-86e6-23b275db8d96</t>
+  </si>
+  <si>
+    <t>attack-pattern--8623a36b-99de-4dfb-ba46-b2b5e9cf0d85</t>
+  </si>
+  <si>
+    <t>attack-pattern--37759b81-258f-4d71-9703-9654ac67cab0</t>
+  </si>
+  <si>
+    <t>attack-pattern--95138ada-459f-440e-a79a-7fcf8874b584</t>
+  </si>
+  <si>
+    <t>attack-pattern--fe23fd12-ed27-416d-a891-53fd0945c418</t>
+  </si>
+  <si>
+    <t>attack-pattern--7f745905-530b-4294-9eda-f8dafe9f0edd</t>
+  </si>
+  <si>
+    <t>attack-pattern--fe33bd0c-bd06-451b-92ea-b2f65444329b</t>
+  </si>
+  <si>
+    <t>attack-pattern--a6684ef1-fa45-4bf7-9ec1-db7ebe4dec10</t>
+  </si>
+  <si>
+    <t>attack-pattern--91bd2ac0-d39a-4a37-b4ba-3b7d9cc48480</t>
+  </si>
+  <si>
+    <t>attack-pattern--cf3d899a-e96c-4063-bf08-65e437c19c7f</t>
+  </si>
+  <si>
+    <t>attack-pattern--575a4091-4083-4c93-8862-74543ad2f94c</t>
+  </si>
+  <si>
+    <t>attack-pattern--3d97cbb0-3c4c-4fd3-9b5e-679517b777f3</t>
+  </si>
+  <si>
+    <t>attack-pattern--aa11cd7e-92e7-43ec-af19-193b81bdb604</t>
+  </si>
+  <si>
+    <t>attack-pattern--08292bee-5177-4f79-bfa6-4f0345a5a446</t>
+  </si>
+  <si>
+    <t>attack-pattern--60d5bdf7-06c3-4a53-b2d3-36b02a2230e3</t>
+  </si>
+  <si>
+    <t>attack-pattern--0fa8defa-fb0b-4599-9491-7d725883c3fd</t>
+  </si>
+  <si>
+    <t>attack-pattern--60a4cda8-8154-4a3f-9826-f9d39155d257</t>
+  </si>
+  <si>
+    <t>attack-pattern--0ffd53d6-5fd6-43e5-aff6-4e1d50a00743</t>
+  </si>
+  <si>
+    <t>attack-pattern--9fb6f979-a54f-46ce-9d0b-ce0c5db37e7a</t>
+  </si>
+  <si>
+    <t>attack-pattern--3a36e7b8-ad04-4cb0-8ffc-9b6502c66d77</t>
+  </si>
+  <si>
+    <t>attack-pattern--c8e73b27-78c5-4634-93ec-287a7cd80529</t>
+  </si>
+  <si>
+    <t>attack-pattern--e1c8faff-7670-454e-a4f0-3da445f53ac9</t>
+  </si>
+  <si>
+    <t>attack-pattern--8f5deb62-ed66-4518-9b21-c1557815cce5</t>
+  </si>
+  <si>
+    <t>attack-pattern--019504d9-9143-4762-b36e-729108653789</t>
+  </si>
+  <si>
+    <t>attack-pattern--22e649d9-36b0-4f1f-88e9-e34fd12441c4</t>
+  </si>
+  <si>
+    <t>attack-pattern--624b5cee-3da2-4c18-906b-d1f1aca11306</t>
+  </si>
+  <si>
+    <t>attack-pattern--286b8cda-f24d-4dde-a188-c0b140491a96</t>
+  </si>
+  <si>
+    <t>attack-pattern--3c93037a-c467-4137-81e2-c058a9d90107</t>
+  </si>
+  <si>
+    <t>attack-pattern--229f46aa-5a77-41ce-a34b-4d978b1164ea</t>
+  </si>
+  <si>
+    <t>attack-pattern--1a2eea19-fa56-4b46-b746-af741b0fbe4a</t>
+  </si>
+  <si>
+    <t>attack-pattern--2001e1d6-3887-44fe-892d-ce873833b382</t>
+  </si>
+  <si>
+    <t>attack-pattern--37844351-6c24-42d8-99ba-2eb178febd3c</t>
+  </si>
+  <si>
+    <t>attack-pattern--aeca9532-ecda-49fc-9915-fe9b53956bf8</t>
+  </si>
+  <si>
+    <t>attack-pattern--dc37deb9-2659-4fc2-b801-127690502a1e</t>
+  </si>
+  <si>
+    <t>attack-pattern--595ddc1a-2efe-4154-a6d7-880fb2fe280f</t>
+  </si>
+  <si>
+    <t>attack-pattern--8f5f6323-a749-4b89-a8ae-36633f183b54</t>
+  </si>
+  <si>
+    <t>attack-pattern--bf3afc82-5403-4ae9-9f69-3d9ef357c6c8</t>
+  </si>
+  <si>
+    <t>attack-pattern--fd99f80b-0f34-4288-bc79-c0f3cf18e846</t>
+  </si>
+  <si>
+    <t>attack-pattern--2421e2f6-4b1f-4f1e-8faa-69e9b14cbbe8</t>
+  </si>
+  <si>
+    <t>attack-pattern--fe1389e1-23dc-4f41-b2e1-15ed665a5840</t>
+  </si>
+  <si>
+    <t>attack-pattern--f69b9809-b9e2-4a3e-b8d9-cf3f74af4335</t>
+  </si>
+  <si>
+    <t>attack-pattern--9f1e418c-f7d0-4526-9824-f880b69b0dc8</t>
+  </si>
+  <si>
+    <t>attack-pattern--709b796b-4c14-4219-8b7d-848ccf3df33f</t>
+  </si>
+  <si>
+    <t>attack-pattern--7be66db5-2484-4f82-9c02-2c658aba5534</t>
+  </si>
+  <si>
+    <t>attack-pattern--503486f3-22d3-4ed3-a8fb-f63db2718af0</t>
+  </si>
+  <si>
+    <t>attack-pattern--a92eb244-48f1-4d36-91b8-9ff6404bc66d</t>
+  </si>
+  <si>
+    <t>attack-pattern--b516107a-c248-4465-aa68-d5e20f3bf635</t>
+  </si>
+  <si>
+    <t>attack-pattern--062669ed-dadc-446f-992c-3425ac24dd1e</t>
+  </si>
+  <si>
+    <t>attack-pattern--e745fb62-c9c2-41af-affe-cac608952241</t>
+  </si>
+  <si>
+    <t>attack-pattern--ac8f6735-f593-4862-b036-039679f6825d</t>
+  </si>
+  <si>
+    <t>attack-pattern--fef93f62-3fe5-4d86-bad7-82607554a597</t>
+  </si>
+  <si>
+    <t>attack-pattern--dac8d747-5bf3-47af-9f54-b010ae92ccea</t>
+  </si>
+  <si>
+    <t>attack-pattern--8fa70d63-cbe1-4ba7-b1a5-2573911cf454</t>
+  </si>
+  <si>
+    <t>attack-pattern--0813df13-c30d-4a9c-badc-bf8ff641b717</t>
+  </si>
+  <si>
+    <t>attack-pattern--ae7d996b-f766-44ab-a46b-60abdd2b3ef6</t>
+  </si>
+  <si>
+    <t>attack-pattern--b8f0d38d-8111-4ef2-87ab-d970fb6f6d04</t>
+  </si>
+  <si>
+    <t>attack-pattern--73c181fd-e569-4225-9bfb-045b64df9b0c</t>
+  </si>
+  <si>
+    <t>attack-pattern--85208eb7-09ab-4287-a298-87298178d6c7</t>
+  </si>
+  <si>
+    <t>attack-pattern--fd811343-f4f3-4812-ad57-477da21a7e8d</t>
+  </si>
+  <si>
+    <t>attack-pattern--72323e0d-b098-4e42-8cd1-544258dc8973</t>
+  </si>
+  <si>
+    <t>attack-pattern--d4b577cd-5a76-46f7-8c39-b96213fc4263</t>
+  </si>
+  <si>
+    <t>attack-pattern--14d57931-21d5-4fd1-bf37-f26ce432a5ca</t>
+  </si>
+  <si>
+    <t>attack-pattern--71797db1-dffd-44dd-8bfa-53446c0091df</t>
+  </si>
+  <si>
+    <t>attack-pattern--ed09b02f-1bf8-4c07-859e-b28e828825d5</t>
+  </si>
+  <si>
+    <t>attack-pattern--880b414d-a823-4193-b270-c0a7de9e6d12</t>
+  </si>
+  <si>
+    <t>attack-pattern--4c4ac28a-0504-4efc-b7bb-a81682cab9ef</t>
+  </si>
+  <si>
+    <t>attack-pattern--a8e7461e-9164-42e7-a275-578694585803</t>
+  </si>
+  <si>
+    <t>attack-pattern--3fff8702-55b8-4c84-a528-2b14b7b980da</t>
+  </si>
+  <si>
+    <t>attack-pattern--c0c59602-b27b-4b66-b864-82a05ff862db</t>
+  </si>
+  <si>
+    <t>attack-pattern--a08a6f55-9930-4233-8df3-cf86e10008ca</t>
+  </si>
+  <si>
+    <t>attack-pattern--a26ee77d-cf1a-4687-988f-932ccc9542bf</t>
+  </si>
+  <si>
+    <t>attack-pattern--81623f2c-c724-43fa-bbab-429f8575f921</t>
+  </si>
+  <si>
+    <t>attack-pattern--b8fc16d6-7f03-4404-9d8d-f9782a0d4b3e</t>
+  </si>
+  <si>
+    <t>attack-pattern--b041117e-4c21-419b-a1ad-f357fd63741f</t>
+  </si>
+  <si>
+    <t>attack-pattern--61fccaa6-3ad9-4372-8b42-682b13577269</t>
+  </si>
+  <si>
+    <t>attack-pattern--52c17a9d-8e67-4b7c-bddd-a0111496a6f5</t>
+  </si>
+  <si>
+    <t>attack-pattern--3b132a9a-ecc8-4b8b-b93c-77771f5dc46c</t>
+  </si>
+  <si>
+    <t>attack-pattern--99619131-579e-49d3-aa32-d9ba015ed29a</t>
+  </si>
+  <si>
+    <t>attack-pattern--242eeb83-aeba-4f79-a3ae-2f62a5bc3706</t>
   </si>
   <si>
     <t>technique</t>
   </si>
   <si>
-    <t>Запрет белогвардейским командованием печати и распространения украинских книг на захваченных территориях. (Citation: Україна й українці в постімперську добу (1917–1939) 2021)</t>
+    <t>Запрет белогвардейским командованием печати и распространения украинских книг на захваченных территориях. (Citation: Україна й українці в постімперську добу (1917—1939) 2021)</t>
   </si>
   <si>
     <t>Принудительное закрытие белогвардейской администрацией украинских культурных и просветительских учреждений. (Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.) 2013)</t>
@@ -1610,7 +1610,7 @@
     <t>Прямое вооруженное вторжение Красной армии 17 сентября 1939 года на территорию Польши для военной оккупации западноукраинских земель. (Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
   </si>
   <si>
-    <t>Официальное обвинение всего крымскотатарского народа в коллективном «предательстве» для идеологического оправдания репрессий и выселения. (Citation: РАШИЗМ ЗВІР З БЕЗОДНІ 2023)</t>
+    <t>Официальное обвинение всего крымскотатарского народа в коллективном «предательстве» для идеологического оправдания репрессий и выселения. (Citation: Рашизм: Звір з безодні 2023)</t>
   </si>
   <si>
     <t>Массовое выселение сотен тысяч украинских крестьян («кулаков») и членов их семей в Сибирь и отдаленные северные регионы СССР. (Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.) 2013)</t>
@@ -1682,7 +1682,7 @@
     <t>Секретные протоколы к Пакту Молотова — Риббентропа с нацистской Германией по разделу сфер влияния в Восточной Европе и легализации вторжения. (Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
   </si>
   <si>
-    <t>Массовое переименование крымских населенных пунктов с целью замещения исторической тюркской топонимики русскими названиями. (Citation: РАШИЗМ ЗВІР З БЕЗОДНІ 2023)</t>
+    <t>Массовое переименование крымских населенных пунктов с целью замещения исторической тюркской топонимики русскими названиями. (Citation: Рашизм: Звір з безодні 2023)</t>
   </si>
   <si>
     <t>Системное психологическое подавление через публичные показательные суды над «саботажниками» и введение карательного закона об охране социалистической собственности («закон о пяти колосках»). (Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.) 2013)</t>
@@ -1694,7 +1694,7 @@
     <t>Институциональный разгром национальной исторической науки, закрытие исследовательских школ и изъятие трудов украинских историков из научного оборота. (Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.) 2013)</t>
   </si>
   <si>
-    <t>Использование Договора об образовании СССР (декабрь 1922 г.) для формального декларирования союза равноправных республик, маскирующего окончательную централизацию власти в Москве. (Citation: Україна й українці в постімперську добу (1917–1939) 2021)</t>
+    <t>Использование Договора об образовании СССР (декабрь 1922 г.) для формального декларирования союза равноправных республик, маскирующего окончательную централизацию власти в Москве. (Citation: Україна й українці в постімперську добу (1917—1939) 2021)</t>
   </si>
   <si>
     <t>Создание искусственных финансовых стимулов для вытеснения родного языка: «Доплата за російську мову викладання 15 % та поділ класів» (Citation: Русифікація України — Вікіпедія 2026).</t>
@@ -1709,7 +1709,7 @@
     <t>Использование раскулаченных крестьян, отправленных в систему зарождающегося ГУЛАГа, в качестве принудительной бесплатной рабочей силы на тяжелых государственных работах. (Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.) 2013)</t>
   </si>
   <si>
-    <t>Попытка бюрократического переподчинения территорий — объявление Донбасса автономной частью, напрямую связанной с Россией, в обход любых украинских властей. (Citation: Україна й українці в постімперську добу (1917–1939) 2021)</t>
+    <t>Попытка бюрократического переподчинения территорий — объявление Донбасса автономной частью, напрямую связанной с Россией, в обход любых украинских властей. (Citation: Україна й українці в постімперську добу (1917—1939) 2021)</t>
   </si>
   <si>
     <t>Попытка через фальсификацию квот и мандатов превратить свое электоральное меньшинство (около 10%) в процедурное большинство на съезде, чтобы легитимно проголосовать за роспуск Центральной Рады и подчинение Петрограду. (Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.) 2013)</t>
@@ -1718,7 +1718,7 @@
     <t>Принудительное изъятие («продразверстка») и безостановочный вывоз зерна, угля и сырья в РСФСР без экономического возмещения, что спровоцировало бунты и восстание Григорьева. (Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.) 2013)</t>
   </si>
   <si>
-    <t>Использование военных частей и продотрядов для силовых рейдов в украинские села с целью конфискации хлеба. (Citation: Україна й українці в постімперську добу (1917–1939) 2021)</t>
+    <t>Использование военных частей и продотрядов для силовых рейдов в украинские села с целью конфискации хлеба. (Citation: Україна й українці в постімперську добу (1917—1939) 2021)</t>
   </si>
   <si>
     <t>Фактическая ликвидация украинской армии (расформирование Украинского фронта) и превращение правительства УССР в номинальный придаток российской административной машины. (Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.) 2013)</t>
@@ -1736,13 +1736,13 @@
     <t>Политическая и военная поддержка местных радикалов (группа Артема) в провозглашении неподконтрольной Киеву республики. (Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.) 2013)</t>
   </si>
   <si>
-    <t>Использование харьковского правительства для формального прикрытия внешней агрессии, чтобы представить военное вторжение как гражданскую войну внутри Украины. (Citation: Україна й українці в постімперську добу (1917–1939) 2021)</t>
-  </si>
-  <si>
-    <t>Подписание Рижского мирного договора в марте 1921 года: кулуарный раздел сфер влияния и территорий Украины с Польшей за спиной украинского народа, легализованный формальным участием марионеточной УССР. (Citation: Україна й українці в постімперську добу (1917–1939) 2021)</t>
-  </si>
-  <si>
-    <t>Системное, демонстративное насилие и запугивание силами ЧК (ВУЧК) для создания атмосферы тотального страха и принуждения крестьянства к сдаче продовольствия. (Citation: Україна й українці в постімперську добу (1917–1939) 2021)</t>
+    <t>Использование харьковского правительства для формального прикрытия внешней агрессии, чтобы представить военное вторжение как гражданскую войну внутри Украины. (Citation: Україна й українці в постімперську добу (1917—1939) 2021)</t>
+  </si>
+  <si>
+    <t>Подписание Рижского мирного договора в марте 1921 года: кулуарный раздел сфер влияния и территорий Украины с Польшей за спиной украинского народа, легализованный формальным участием марионеточной УССР. (Citation: Україна й українці в постімперську добу (1917—1939) 2021)</t>
+  </si>
+  <si>
+    <t>Системное, демонстративное насилие и запугивание силами ЧК (ВУЧК) для создания атмосферы тотального страха и принуждения крестьянства к сдаче продовольствия. (Citation: Україна й українці в постімперську добу (1917—1939) 2021)</t>
   </si>
   <si>
     <t>Перехват Москвой прямого контроля над карательным аппаратом путем решения о ликвидации самостоятельной Всеукраинской ЧК (ВУЧК) в августе 1919 года и назначения своего спецкомиссара Я. Петерса. (Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.) 2013)</t>
@@ -1754,571 +1754,571 @@
     <t>Введение государственной монополии на торговлю хлебом и централизованный контроль над распределением товаров. (Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.) 2013)</t>
   </si>
   <si>
-    <t>relationship--4f3fa1fa-287a-44b6-b100-335be069d3b5</t>
-  </si>
-  <si>
-    <t>relationship--e33ccdbc-868b-41cf-9046-f3de807ed0bb</t>
-  </si>
-  <si>
-    <t>relationship--70a6669a-9870-4504-a3de-4692012746c8</t>
-  </si>
-  <si>
-    <t>relationship--079fddde-0eaa-4350-a37d-df57aa1f56d1</t>
-  </si>
-  <si>
-    <t>relationship--ecf3b0bc-3deb-452a-8bf3-3ce21d2f01b9</t>
-  </si>
-  <si>
-    <t>relationship--03c647f6-f164-445f-a325-429dfa105ff2</t>
-  </si>
-  <si>
-    <t>relationship--2f8c6f3f-c425-4bcb-b826-fa0f7436bf28</t>
-  </si>
-  <si>
-    <t>relationship--c6476241-6537-4c86-87c7-24e1ad7928cc</t>
-  </si>
-  <si>
-    <t>relationship--9b741086-ea5d-45c6-b5f5-ce87986711db</t>
-  </si>
-  <si>
-    <t>relationship--c021e7fe-233c-44b3-bebe-1e1055e9ea14</t>
-  </si>
-  <si>
-    <t>relationship--9497dcb6-b563-420f-8b30-bce8b1674b9c</t>
-  </si>
-  <si>
-    <t>relationship--e355eee2-5f61-4e21-8bf9-82a7b0cc0865</t>
-  </si>
-  <si>
-    <t>relationship--d4e394b0-543d-402d-a15c-6b160659dbf8</t>
-  </si>
-  <si>
-    <t>relationship--722d3c1c-9cba-4280-985b-05ac50432a69</t>
-  </si>
-  <si>
-    <t>relationship--1cc26cc8-75d6-41f4-bcd5-ac6d12cc06e9</t>
-  </si>
-  <si>
-    <t>relationship--af66a04a-f9c8-4f01-8d3a-fb88bfe5f787</t>
-  </si>
-  <si>
-    <t>relationship--7d591097-606a-4f73-8334-60e04ca2e40e</t>
-  </si>
-  <si>
-    <t>relationship--e21d400f-b4e0-4dd1-9c32-0fa1e47df2fe</t>
-  </si>
-  <si>
-    <t>relationship--ccfaa2b4-45f5-4be9-bfe0-c5151ea13fc6</t>
-  </si>
-  <si>
-    <t>relationship--af5746ad-f103-4d98-96b6-401fa9cae9a5</t>
-  </si>
-  <si>
-    <t>relationship--c6246f0a-2a31-40ea-b156-e75b64bea3a4</t>
-  </si>
-  <si>
-    <t>relationship--01ef36e1-ae48-4056-a7ea-df05e06aa9d6</t>
-  </si>
-  <si>
-    <t>relationship--faca8014-9060-4ae6-a775-6aae15af1c0f</t>
-  </si>
-  <si>
-    <t>relationship--9adaeffd-d5de-4bd9-bac5-3399c22f54dc</t>
-  </si>
-  <si>
-    <t>relationship--e8acbd3b-1a21-4fbc-9e45-3d0910d466d5</t>
-  </si>
-  <si>
-    <t>relationship--1279a9b6-14c3-48b4-8755-421b930ab253</t>
-  </si>
-  <si>
-    <t>relationship--1f4f9066-60de-4ba7-a7f7-c1ce2ba0255a</t>
-  </si>
-  <si>
-    <t>relationship--df67ce2b-78c1-4dc3-a8c9-d0d03c5934e5</t>
-  </si>
-  <si>
-    <t>relationship--29fb8e8c-dbaa-4860-b8c7-c56e833ed334</t>
-  </si>
-  <si>
-    <t>relationship--9ce4b463-7b1a-4d92-8409-56906055099d</t>
-  </si>
-  <si>
-    <t>relationship--125e0120-c9e4-4fa5-8160-afe7baa438e2</t>
-  </si>
-  <si>
-    <t>relationship--a9ec61fc-b0cd-4943-87fc-c57d3f500ee4</t>
-  </si>
-  <si>
-    <t>relationship--0ed1c86e-4186-4f29-b13e-cbcc72a7f536</t>
-  </si>
-  <si>
-    <t>relationship--2a482899-f97b-49cb-9a24-4c7dd98feff4</t>
-  </si>
-  <si>
-    <t>relationship--7aef5c8c-70c0-4cc4-a8e6-cf35f8a2083f</t>
-  </si>
-  <si>
-    <t>relationship--7f3704ec-6f99-4516-8987-8690a7f9fcc2</t>
-  </si>
-  <si>
-    <t>relationship--b2a753eb-eae8-48cd-aa31-18f82f3747f6</t>
-  </si>
-  <si>
-    <t>relationship--f0600427-e698-4a5a-a80c-401a9d391b89</t>
-  </si>
-  <si>
-    <t>relationship--7b73eebb-f333-4a5f-9634-68049026e5c6</t>
-  </si>
-  <si>
-    <t>relationship--c9fd6fb4-88ed-4b62-9a9c-f1935fabebd4</t>
-  </si>
-  <si>
-    <t>relationship--d5041b35-f879-417e-994f-1f99ea336d16</t>
-  </si>
-  <si>
-    <t>relationship--1d975d20-036a-4a7d-85ac-1ab9dc425701</t>
-  </si>
-  <si>
-    <t>relationship--5a494507-bc90-44de-b355-df7adc06712a</t>
-  </si>
-  <si>
-    <t>relationship--78a088e2-a30c-4f93-8704-879fb3391df8</t>
-  </si>
-  <si>
-    <t>relationship--1b511638-c664-49aa-83d3-9333853bcd0d</t>
-  </si>
-  <si>
-    <t>relationship--d1854feb-2283-4172-995a-382146d3b0b9</t>
-  </si>
-  <si>
-    <t>relationship--f57d4ee2-fa09-4d56-a3c9-973e7d0abe84</t>
-  </si>
-  <si>
-    <t>relationship--3fbb5188-860e-4100-b981-cebe09faaaca</t>
-  </si>
-  <si>
-    <t>relationship--1c650db7-e34b-4069-a9b8-64e92b408aa5</t>
-  </si>
-  <si>
-    <t>relationship--860b4713-39b2-4b87-93bb-fff03c067ec7</t>
-  </si>
-  <si>
-    <t>relationship--83697eb4-fa98-43b6-8e2f-a840755838da</t>
-  </si>
-  <si>
-    <t>relationship--5262db74-5511-4c3d-b5db-64f54ce49d46</t>
-  </si>
-  <si>
-    <t>relationship--793452d6-f2b7-4ce2-a55f-249616688fe7</t>
-  </si>
-  <si>
-    <t>relationship--b7940711-5bf0-4e1c-970e-ef3de2b53e5e</t>
-  </si>
-  <si>
-    <t>relationship--7be2ec48-3faf-4bb5-a2b2-aa551ecc6f75</t>
-  </si>
-  <si>
-    <t>relationship--eaded384-6bc2-49e2-b8e4-98ec6eb72759</t>
-  </si>
-  <si>
-    <t>relationship--06d632cb-902a-46c6-8fc7-fe5b15734f3e</t>
-  </si>
-  <si>
-    <t>relationship--83a53801-7893-4168-a870-1236ee2ef844</t>
-  </si>
-  <si>
-    <t>relationship--2fd28196-db27-4a9c-92a3-1c15b50f4106</t>
-  </si>
-  <si>
-    <t>relationship--9edd6805-70b0-400c-8db7-71149bf1cdab</t>
-  </si>
-  <si>
-    <t>relationship--5b4ac1b1-ed0a-4988-8b58-3c70887d83e4</t>
-  </si>
-  <si>
-    <t>relationship--a72684b3-cb3d-4efc-943f-b0dfc6773c12</t>
-  </si>
-  <si>
-    <t>relationship--c9533064-df6d-4104-8ea0-ab1e4ca53184</t>
-  </si>
-  <si>
-    <t>relationship--2540bec0-dd51-44d2-a61d-29662cd8d4d4</t>
-  </si>
-  <si>
-    <t>relationship--15dfa149-83f5-4dd6-a39c-de16905e4249</t>
-  </si>
-  <si>
-    <t>relationship--dde0207a-5255-42c3-9cf2-c16e0b11857b</t>
-  </si>
-  <si>
-    <t>relationship--179efd74-e4d7-4e3a-8fa8-23428097b5d1</t>
-  </si>
-  <si>
-    <t>relationship--7114f6fd-2ca9-4828-84c8-7c88333bc52a</t>
-  </si>
-  <si>
-    <t>relationship--c26847c4-2c4d-4efa-b330-552f8196e36e</t>
-  </si>
-  <si>
-    <t>relationship--e11feae6-bcaa-483d-ba69-5d9539b3f2e1</t>
-  </si>
-  <si>
-    <t>relationship--ca2018a2-2975-4d14-81cb-25f350ebeb46</t>
-  </si>
-  <si>
-    <t>relationship--dd2dc3e4-7c1f-411d-9a5b-dfc6c4f6065d</t>
-  </si>
-  <si>
-    <t>relationship--11c3da83-064f-4a26-a2ba-249eb04767e4</t>
-  </si>
-  <si>
-    <t>relationship--1466d6c3-6b9b-4adf-9c56-63789f74b265</t>
-  </si>
-  <si>
-    <t>relationship--8d99ca43-0dbe-4052-9250-efe80ed77285</t>
-  </si>
-  <si>
-    <t>relationship--c18d4dd3-1235-4f01-b89b-e9de4b2da645</t>
-  </si>
-  <si>
-    <t>relationship--125570be-1463-4895-8fe8-4053f1cbfb33</t>
-  </si>
-  <si>
-    <t>relationship--546dcee6-0a01-496a-b78d-4a930c87b0b4</t>
-  </si>
-  <si>
-    <t>relationship--b03cf540-cfc8-42fd-a3eb-2f976d1349c7</t>
-  </si>
-  <si>
-    <t>relationship--eb336200-3603-4b4b-a7c8-a321dfa6537d</t>
-  </si>
-  <si>
-    <t>relationship--a642cddb-d8ca-4ee9-be42-efd2f24bdfa4</t>
-  </si>
-  <si>
-    <t>relationship--bb1065f4-561d-45b1-b907-99630dfd1b14</t>
-  </si>
-  <si>
-    <t>relationship--750e9ad2-c3ca-4392-9842-af946de377fc</t>
-  </si>
-  <si>
-    <t>relationship--3831f81c-1ff8-46f1-825a-7b540acc560e</t>
-  </si>
-  <si>
-    <t>relationship--5fce500b-eba8-4e6a-9e60-ee1d7b1490b0</t>
-  </si>
-  <si>
-    <t>relationship--0ac2d69b-6471-4a61-a97b-784de4de596a</t>
-  </si>
-  <si>
-    <t>relationship--7349033a-878b-4563-b45d-4dd19b8571f7</t>
-  </si>
-  <si>
-    <t>relationship--4d896093-b812-4dd5-ab70-b7c96186132d</t>
-  </si>
-  <si>
-    <t>relationship--18c03684-fb7b-419a-a437-3a71c12c89ec</t>
-  </si>
-  <si>
-    <t>relationship--e215907b-a098-4425-a41c-645b3f38f730</t>
-  </si>
-  <si>
-    <t>relationship--27f0e5eb-2bc6-466c-836c-37e2dcaf7f77</t>
-  </si>
-  <si>
-    <t>relationship--17c4485d-32de-438a-9a0a-e6c5e8da4123</t>
-  </si>
-  <si>
-    <t>relationship--5450ea32-a2c9-4396-82bf-026ce9906ada</t>
-  </si>
-  <si>
-    <t>relationship--98f00d5e-aa82-4385-b84c-e8070701b2e4</t>
-  </si>
-  <si>
-    <t>relationship--ddbdd552-c891-4545-839d-d6cebf659298</t>
-  </si>
-  <si>
-    <t>relationship--0af480c6-3d6c-4c8e-9c31-e1634b96502d</t>
-  </si>
-  <si>
-    <t>relationship--c22aaa51-65f6-4102-ad6c-fe8ecf96eeab</t>
-  </si>
-  <si>
-    <t>relationship--cfcc4ded-29a5-4683-8b45-21d7f9d3a1d2</t>
-  </si>
-  <si>
-    <t>relationship--595d481e-7a80-4e33-8127-667c5bbd6b7d</t>
-  </si>
-  <si>
-    <t>relationship--32bb8976-53c6-4d62-a1f4-77da7274b47b</t>
-  </si>
-  <si>
-    <t>relationship--7a34b295-1d4c-425e-ba58-89cda1ce6c13</t>
-  </si>
-  <si>
-    <t>relationship--9a934078-9d7e-454d-bb6e-7ffd300b34f9</t>
-  </si>
-  <si>
-    <t>relationship--2b59b5ab-67fe-48dd-827a-a5b24b0ffd39</t>
-  </si>
-  <si>
-    <t>relationship--19a5d88a-abef-4c3e-b2f1-4518833fca22</t>
-  </si>
-  <si>
-    <t>relationship--d5496d24-8214-4bdf-9dbf-04b89937b7c8</t>
-  </si>
-  <si>
-    <t>relationship--6ab17e0b-994d-41e3-92e6-52c1948f95de</t>
-  </si>
-  <si>
-    <t>relationship--7c10dff9-413b-4b6e-af47-bc23cd7772f1</t>
-  </si>
-  <si>
-    <t>relationship--26613c81-0f8c-4686-89c1-7ce5a1bbc50c</t>
-  </si>
-  <si>
-    <t>relationship--d98c3c8a-51a8-444d-acd9-b21a5022085d</t>
-  </si>
-  <si>
-    <t>relationship--46068bd4-ea91-473c-9364-85377d4399ca</t>
-  </si>
-  <si>
-    <t>relationship--5069347e-3173-4037-8a62-ee1e3aaf58b1</t>
-  </si>
-  <si>
-    <t>relationship--b3ef5bad-60a5-418a-9e3f-b14bca45c365</t>
-  </si>
-  <si>
-    <t>relationship--e1184011-bc09-4616-8b3d-3bb3c6eff98c</t>
-  </si>
-  <si>
-    <t>relationship--7f0d1060-5052-409c-a6b5-a16e6b3a4997</t>
-  </si>
-  <si>
-    <t>relationship--800560f2-b502-4fd7-aa56-56cb6afbcdc1</t>
-  </si>
-  <si>
-    <t>relationship--3882b000-08b0-41e1-8a63-ba31a819d522</t>
-  </si>
-  <si>
-    <t>relationship--bf7bf5a4-e1a2-43c7-a688-2b2c88c668fe</t>
-  </si>
-  <si>
-    <t>relationship--cb0247d3-4a7f-4d28-82c3-d988b0bb285a</t>
-  </si>
-  <si>
-    <t>relationship--a1fa679b-b15b-4525-bcc4-f9a98a83351a</t>
-  </si>
-  <si>
-    <t>relationship--0aea2a48-2807-43ce-8423-14cae84e1cfd</t>
-  </si>
-  <si>
-    <t>relationship--1906be5d-6b76-438d-99d5-7c6a96de53dc</t>
-  </si>
-  <si>
-    <t>relationship--f8711783-3a8c-47e6-be9d-6c853250ee44</t>
-  </si>
-  <si>
-    <t>relationship--a7b69b05-c7f2-4ec6-a47f-1935fbb514c3</t>
-  </si>
-  <si>
-    <t>relationship--14f7d419-b22d-4708-81f2-763afb017cef</t>
-  </si>
-  <si>
-    <t>relationship--6cfe3322-09e0-4d96-a680-b75143355c75</t>
-  </si>
-  <si>
-    <t>relationship--fb94b656-310e-4c00-9e8d-bf1a467b63da</t>
-  </si>
-  <si>
-    <t>relationship--519d3618-3f0d-4afe-8867-c3e2b578a77a</t>
-  </si>
-  <si>
-    <t>relationship--0ca98bc5-351d-4a8e-93c3-6af2dac701a4</t>
-  </si>
-  <si>
-    <t>relationship--6b44a6be-700e-4f1d-8254-7f0e62b55e6f</t>
-  </si>
-  <si>
-    <t>relationship--d7f234cc-e336-4707-9417-c13170cb1877</t>
-  </si>
-  <si>
-    <t>relationship--20e26477-764c-4d13-a18f-f28e9a81a7a6</t>
-  </si>
-  <si>
-    <t>relationship--41479d62-a031-4a0d-9251-66f01781f833</t>
-  </si>
-  <si>
-    <t>relationship--87cd70c9-77bd-42c4-829d-0402fe469e0b</t>
-  </si>
-  <si>
-    <t>relationship--7b07abd4-10ea-40f6-83d8-dfaacb489ca3</t>
-  </si>
-  <si>
-    <t>relationship--5c7af1e7-91f8-41a2-8e62-116008f721e2</t>
-  </si>
-  <si>
-    <t>relationship--d06237bc-8ad7-464c-acaa-656af70f5ad0</t>
-  </si>
-  <si>
-    <t>relationship--d1548913-3b09-43b7-92ca-6857b26be9de</t>
-  </si>
-  <si>
-    <t>relationship--ef809645-1c30-4b02-9946-437bc1dd82e3</t>
-  </si>
-  <si>
-    <t>relationship--3aa5db81-1a80-411b-9069-8b93ce348bf4</t>
-  </si>
-  <si>
-    <t>relationship--9aecf354-421c-4a57-83a3-03bde0ba31d3</t>
-  </si>
-  <si>
-    <t>relationship--f793f30f-7454-4c2c-a31f-b79794d27625</t>
-  </si>
-  <si>
-    <t>relationship--58c41bf8-36db-4132-95c3-2775710502f8</t>
-  </si>
-  <si>
-    <t>relationship--468aebcb-96ac-4e00-8592-9f38e1122c73</t>
-  </si>
-  <si>
-    <t>relationship--461bb135-6023-40aa-88da-65da96385e72</t>
-  </si>
-  <si>
-    <t>relationship--f5b70ed6-7b77-4012-8ed1-173ace64d9f4</t>
-  </si>
-  <si>
-    <t>relationship--1cc00acd-691e-4a33-9ade-47e3445493c9</t>
-  </si>
-  <si>
-    <t>relationship--7a26b20f-db1c-484d-acc1-b2ef56c456a3</t>
-  </si>
-  <si>
-    <t>relationship--df0d52a6-1f7e-4f80-9785-24eb77052414</t>
-  </si>
-  <si>
-    <t>relationship--157e6808-d7a3-4e02-887b-50690db1ab33</t>
-  </si>
-  <si>
-    <t>relationship--ef8c9861-5196-4bf1-ab94-d103458d7196</t>
-  </si>
-  <si>
-    <t>relationship--b9ee5321-1802-4a05-9102-cc76caa3182b</t>
-  </si>
-  <si>
-    <t>relationship--6232ff46-b3a8-4fec-9fa4-cff35c2d913b</t>
-  </si>
-  <si>
-    <t>relationship--63bf1c53-89f8-4080-8859-68ada2a4c31b</t>
-  </si>
-  <si>
-    <t>relationship--4018bd79-5db9-4f80-af74-68211b3318d2</t>
-  </si>
-  <si>
-    <t>relationship--5992e9af-5676-498d-bf16-af69c13042d0</t>
-  </si>
-  <si>
-    <t>relationship--149206aa-e7f1-44fd-9962-c6e0eddc6076</t>
-  </si>
-  <si>
-    <t>relationship--b3cebae2-5fc1-41e5-92b2-51cb5b479d45</t>
-  </si>
-  <si>
-    <t>relationship--057d1042-0869-4eb0-bfa9-eef31c812d08</t>
-  </si>
-  <si>
-    <t>relationship--d1ecd420-ed57-4baf-a151-1337f5a684aa</t>
-  </si>
-  <si>
-    <t>relationship--9e49bf1d-e3be-4265-a494-1043f2045d68</t>
-  </si>
-  <si>
-    <t>relationship--e857a567-0272-4c8a-aac4-039647ce5453</t>
-  </si>
-  <si>
-    <t>relationship--e6599b2f-8bac-4155-80c3-d43b6a7c6e62</t>
-  </si>
-  <si>
-    <t>relationship--7538124d-e512-4b31-ac33-2bcf54a938bb</t>
-  </si>
-  <si>
-    <t>relationship--0b0e5fd3-f4bc-4dc1-a29e-7f4b26c3e6ae</t>
-  </si>
-  <si>
-    <t>relationship--1d48d4c2-aaa9-4097-9eb0-2b639bfe88c6</t>
-  </si>
-  <si>
-    <t>relationship--8a2e251c-b566-4bf3-9ef8-c8a34ebe6962</t>
-  </si>
-  <si>
-    <t>relationship--4eeed991-ca85-413a-b9d5-b78f99429fd3</t>
-  </si>
-  <si>
-    <t>relationship--c6d6fc9b-a3a1-429e-9883-c77f98d0bd98</t>
-  </si>
-  <si>
-    <t>relationship--f85cf51f-07f3-4981-864e-ba9b6ad821ad</t>
-  </si>
-  <si>
-    <t>relationship--26e3714c-625a-46ba-909a-d64280228f10</t>
-  </si>
-  <si>
-    <t>relationship--fd4ee52a-564b-4a47-9176-0c61be498174</t>
-  </si>
-  <si>
-    <t>relationship--27adaa9b-b9c3-4ca1-9bc7-d4cbc96c18e7</t>
-  </si>
-  <si>
-    <t>relationship--ef3e4e92-ca0f-4ebe-b05c-46b721ef1421</t>
-  </si>
-  <si>
-    <t>relationship--ed6c1a2d-4486-4e3b-b9b9-c20536d8a11f</t>
-  </si>
-  <si>
-    <t>relationship--9701080c-8ae3-4de0-bc5d-95111225cd0c</t>
-  </si>
-  <si>
-    <t>relationship--7e2815fa-f3c1-4070-a6d9-9230ea12779c</t>
-  </si>
-  <si>
-    <t>relationship--3192c239-d1fc-4d41-bb6c-8f9b0f985792</t>
-  </si>
-  <si>
-    <t>relationship--a22dd250-f35e-4cc2-ae95-2209ff5efb95</t>
-  </si>
-  <si>
-    <t>relationship--809d4dba-32be-48ab-b703-88e06a5599be</t>
-  </si>
-  <si>
-    <t>relationship--59632cd5-09a9-4592-bc7e-f421369e5530</t>
-  </si>
-  <si>
-    <t>relationship--f2907bd2-82a7-4755-ac21-5641c33796be</t>
-  </si>
-  <si>
-    <t>relationship--0aebd150-2acd-4ee8-a8ae-bc838ace41af</t>
-  </si>
-  <si>
-    <t>relationship--355e885f-56b5-45dc-af5e-560babfd7eb5</t>
-  </si>
-  <si>
-    <t>relationship--b23ee932-dd71-401b-98f0-2de0e672fcbd</t>
-  </si>
-  <si>
-    <t>relationship--11f20020-b589-4bf9-9f77-939f3f32acbb</t>
-  </si>
-  <si>
-    <t>relationship--92573660-6ec7-48f3-b145-443397e56cc8</t>
-  </si>
-  <si>
-    <t>relationship--8041970c-3d90-4b19-b855-fd7a2193e7de</t>
-  </si>
-  <si>
-    <t>relationship--ac54d383-c301-4118-84c7-ffdb55dfcd0d</t>
-  </si>
-  <si>
-    <t>relationship--5a4bc9fa-1384-4679-8651-558ec4b05aa7</t>
+    <t>relationship--19f5ae4f-6f55-4234-8e02-b7849d67cb3e</t>
+  </si>
+  <si>
+    <t>relationship--a8c565aa-1b03-445d-ad0a-cfa9b9774625</t>
+  </si>
+  <si>
+    <t>relationship--1200f03f-0995-4007-bba8-9b9104523678</t>
+  </si>
+  <si>
+    <t>relationship--27c6c544-dbd7-447d-b13b-dd7cf18d09bd</t>
+  </si>
+  <si>
+    <t>relationship--745a6e9f-ae84-4c45-8455-dfaf312b5fdc</t>
+  </si>
+  <si>
+    <t>relationship--37839205-46ec-4e2f-8123-a85d91fe5d32</t>
+  </si>
+  <si>
+    <t>relationship--c04707e2-dee7-4657-b31b-5319724b0be3</t>
+  </si>
+  <si>
+    <t>relationship--7f12e6bd-3864-44df-9d27-9e79fd2cda83</t>
+  </si>
+  <si>
+    <t>relationship--65257f7e-4d5c-490a-a72b-c0e1abf828a7</t>
+  </si>
+  <si>
+    <t>relationship--fbf0263d-c0d7-405f-b574-c66a4956efe8</t>
+  </si>
+  <si>
+    <t>relationship--2e23a33f-3d39-41cc-befb-bbb2bec46212</t>
+  </si>
+  <si>
+    <t>relationship--115eb83d-7c72-4d69-9c7a-0a7dfb16567f</t>
+  </si>
+  <si>
+    <t>relationship--1cb5a9bc-28f5-4eaa-8c53-1ab0603b1115</t>
+  </si>
+  <si>
+    <t>relationship--c8051db6-217b-4b3c-a077-bc2246f2ca5d</t>
+  </si>
+  <si>
+    <t>relationship--69097e44-b340-41fb-b71b-a9e4bb5bdf34</t>
+  </si>
+  <si>
+    <t>relationship--da778b0c-13fe-4c8b-b58a-37a6413f985d</t>
+  </si>
+  <si>
+    <t>relationship--c6d2e80f-8b05-4297-a133-b19cc7359f40</t>
+  </si>
+  <si>
+    <t>relationship--fc016907-a6b1-4ccf-9aa3-0e5134d2efbb</t>
+  </si>
+  <si>
+    <t>relationship--303f721d-3aa6-4707-a40a-622fff9209ed</t>
+  </si>
+  <si>
+    <t>relationship--98a4a0fd-ffbd-4ae0-b54c-356cd63b6fe9</t>
+  </si>
+  <si>
+    <t>relationship--2ae8fd5a-8463-4519-b1a7-144cff5caae3</t>
+  </si>
+  <si>
+    <t>relationship--c7f93fbc-e3f5-4fc6-bd06-1d5f0ef8b534</t>
+  </si>
+  <si>
+    <t>relationship--829bbe12-1433-4ddc-86fe-a9f1576358d6</t>
+  </si>
+  <si>
+    <t>relationship--380f0ba5-40d6-4b11-8f4d-532071f0f8fc</t>
+  </si>
+  <si>
+    <t>relationship--5720eeb6-cb68-4aec-a169-61af53093498</t>
+  </si>
+  <si>
+    <t>relationship--2c53304b-a8ab-4cd6-96f9-47d007a41437</t>
+  </si>
+  <si>
+    <t>relationship--f5330dcf-6ea7-4953-86d3-afd38052cec3</t>
+  </si>
+  <si>
+    <t>relationship--4f973e78-494d-4faf-af03-628495b9e2e2</t>
+  </si>
+  <si>
+    <t>relationship--a8477547-160e-4f85-93b6-0dd8e8998c16</t>
+  </si>
+  <si>
+    <t>relationship--b1cf70e4-2ceb-44ee-b30e-ae14d097b02a</t>
+  </si>
+  <si>
+    <t>relationship--e55fd8fc-48c9-4389-9653-bb0460d9a8e6</t>
+  </si>
+  <si>
+    <t>relationship--b2f59554-4941-4365-81e1-9d9088a01b1d</t>
+  </si>
+  <si>
+    <t>relationship--ebb09495-6544-4894-98c1-d61731361695</t>
+  </si>
+  <si>
+    <t>relationship--5d027595-85a0-41f3-af88-51ea8d13445b</t>
+  </si>
+  <si>
+    <t>relationship--9ca3e2d3-e98d-42ad-a196-306d91954152</t>
+  </si>
+  <si>
+    <t>relationship--0dfe3dec-a7b5-46f6-91f7-d7f7d04cee19</t>
+  </si>
+  <si>
+    <t>relationship--44b60aea-8e56-49cc-ba63-c25d52d6b064</t>
+  </si>
+  <si>
+    <t>relationship--6922e89d-789c-4920-9971-c9e0aec8abef</t>
+  </si>
+  <si>
+    <t>relationship--643726f0-6b49-4ff0-bf27-524106570628</t>
+  </si>
+  <si>
+    <t>relationship--99750379-0991-49d2-845a-38e0534bb2b9</t>
+  </si>
+  <si>
+    <t>relationship--17af9190-ed2c-4d9c-bc94-fde195349df0</t>
+  </si>
+  <si>
+    <t>relationship--7813f1f2-b6fd-40fb-af15-dd9a2ca04a90</t>
+  </si>
+  <si>
+    <t>relationship--fecccdd6-4dba-4297-ae6b-860f0d654d51</t>
+  </si>
+  <si>
+    <t>relationship--247c1400-d20a-4f06-9958-75c299197f0d</t>
+  </si>
+  <si>
+    <t>relationship--ccc3baee-92ba-4d65-a274-591c4eca4754</t>
+  </si>
+  <si>
+    <t>relationship--c525349f-f773-4156-9f8b-9539d939dce0</t>
+  </si>
+  <si>
+    <t>relationship--5291ce1a-3273-4000-8902-06bb255bf8af</t>
+  </si>
+  <si>
+    <t>relationship--e319ff58-0abb-4c3d-a306-b795663ff85e</t>
+  </si>
+  <si>
+    <t>relationship--52f3ee40-6928-4e92-8645-10821b4fb24c</t>
+  </si>
+  <si>
+    <t>relationship--578721a1-f1b0-4860-b1b0-e6ec697710f3</t>
+  </si>
+  <si>
+    <t>relationship--157cc1c4-fb87-4900-98ac-90a0c2bee8c6</t>
+  </si>
+  <si>
+    <t>relationship--ef982e88-c329-463a-8244-7b373320d856</t>
+  </si>
+  <si>
+    <t>relationship--0ebf4f68-0ae0-48cb-b8e1-064f3cf37f14</t>
+  </si>
+  <si>
+    <t>relationship--422a69fb-b923-4fe2-b6f9-5cf222bff621</t>
+  </si>
+  <si>
+    <t>relationship--7f665ce4-c8c2-4fa5-a183-cf888b37dfad</t>
+  </si>
+  <si>
+    <t>relationship--97d8db77-03f1-4510-af5d-d57136d85cc4</t>
+  </si>
+  <si>
+    <t>relationship--66f6c6bb-f86c-4d70-98c4-a20458570037</t>
+  </si>
+  <si>
+    <t>relationship--4278dd17-e79a-4b66-991d-5b36d1301c23</t>
+  </si>
+  <si>
+    <t>relationship--cb4fc774-fa24-4943-8d13-193a0dcc00a9</t>
+  </si>
+  <si>
+    <t>relationship--83e456d4-226f-4816-ac4d-685c06c8b5d1</t>
+  </si>
+  <si>
+    <t>relationship--cf0446a2-000f-4ac1-8051-cb41f7571f94</t>
+  </si>
+  <si>
+    <t>relationship--70f0a8fc-c11f-4e8a-ab22-0b57ed0243fd</t>
+  </si>
+  <si>
+    <t>relationship--fde26adc-952e-4eae-8c32-90f8e2c289f1</t>
+  </si>
+  <si>
+    <t>relationship--ef96ae40-c63a-483c-af98-eb120db0d729</t>
+  </si>
+  <si>
+    <t>relationship--7e73fe42-7c64-47f3-98ed-490e5879d6cb</t>
+  </si>
+  <si>
+    <t>relationship--e495833b-e7fc-4a45-a3b0-088de55613ab</t>
+  </si>
+  <si>
+    <t>relationship--87b59acc-3517-4ef4-a487-ff0cb738d26b</t>
+  </si>
+  <si>
+    <t>relationship--5199a200-76f5-4226-a15c-2edff1f1dd8f</t>
+  </si>
+  <si>
+    <t>relationship--979dd474-a489-4302-820f-6b0fe99ac0b8</t>
+  </si>
+  <si>
+    <t>relationship--95be85f6-ea3f-49c7-8176-47fb2b14acc3</t>
+  </si>
+  <si>
+    <t>relationship--c5f89a37-f7ea-4fc3-8d53-44385be766c0</t>
+  </si>
+  <si>
+    <t>relationship--2460c04f-37b2-4b3b-986b-ca71811d32d2</t>
+  </si>
+  <si>
+    <t>relationship--b76c4f0c-9e86-405c-885c-2a6a1e03aacb</t>
+  </si>
+  <si>
+    <t>relationship--90d5f2c3-21ed-4495-a244-515610ebd773</t>
+  </si>
+  <si>
+    <t>relationship--04c02d46-fbe1-4ad2-9fb3-cb301cc21db0</t>
+  </si>
+  <si>
+    <t>relationship--14da342c-de4d-4fa0-9852-1822f2915a15</t>
+  </si>
+  <si>
+    <t>relationship--1a003ba2-1a44-4896-85a2-46ac6ed81310</t>
+  </si>
+  <si>
+    <t>relationship--ef90f573-128f-4d2a-8626-4d9b0a981ad1</t>
+  </si>
+  <si>
+    <t>relationship--4e429355-42b0-4de6-aa4f-6f3ebe099a86</t>
+  </si>
+  <si>
+    <t>relationship--deacdc42-71b6-4dd8-8aaf-69b66e210301</t>
+  </si>
+  <si>
+    <t>relationship--64b3a5f9-b367-4eed-81cd-808883bd7563</t>
+  </si>
+  <si>
+    <t>relationship--5beba3b0-257f-42ae-937c-76502cc6e4d6</t>
+  </si>
+  <si>
+    <t>relationship--6852c501-da52-4547-9314-82638d0cae16</t>
+  </si>
+  <si>
+    <t>relationship--d06c83c0-473d-44af-b216-94609b2ae705</t>
+  </si>
+  <si>
+    <t>relationship--38198316-4d10-46d4-8667-986f6ab7425b</t>
+  </si>
+  <si>
+    <t>relationship--80dee8f1-1b29-420d-9c15-fecf53ee3229</t>
+  </si>
+  <si>
+    <t>relationship--20d9dd2b-1d77-4b5f-b0a3-8edbdd544be6</t>
+  </si>
+  <si>
+    <t>relationship--b59a2993-5458-4be6-a1be-fc61ae3e2225</t>
+  </si>
+  <si>
+    <t>relationship--b0df84c2-ffdb-42c0-9d0a-04e4e769ff16</t>
+  </si>
+  <si>
+    <t>relationship--3db00a0a-a50a-4399-8d23-cbc942f47e7a</t>
+  </si>
+  <si>
+    <t>relationship--71d87ecd-a71b-4b1b-95a1-0b26f86e8f98</t>
+  </si>
+  <si>
+    <t>relationship--9bbeaaef-abf9-434e-b308-d523c2070af7</t>
+  </si>
+  <si>
+    <t>relationship--f68e21ae-6621-4ffc-9a90-70affdec2c77</t>
+  </si>
+  <si>
+    <t>relationship--d192470f-32da-438c-a680-713ad35a66ff</t>
+  </si>
+  <si>
+    <t>relationship--c9a4f0a0-2fb1-48db-96bb-9f4d75f5183c</t>
+  </si>
+  <si>
+    <t>relationship--d438fc28-b978-4835-a52b-9de40988fce1</t>
+  </si>
+  <si>
+    <t>relationship--c2bf44c9-7582-473c-92bf-6200c6e2b97d</t>
+  </si>
+  <si>
+    <t>relationship--6c4ab8b6-93db-4163-9f82-ef7f84d805f8</t>
+  </si>
+  <si>
+    <t>relationship--369a4d9b-8b07-4672-a7a4-bef505202f2d</t>
+  </si>
+  <si>
+    <t>relationship--be1d9a30-5d9f-48d6-94c6-4146b7a038ff</t>
+  </si>
+  <si>
+    <t>relationship--6e6c1595-7a47-4b2c-8b88-04b9af47eba6</t>
+  </si>
+  <si>
+    <t>relationship--3c95514f-4ea4-47eb-a08a-5cc3989990e3</t>
+  </si>
+  <si>
+    <t>relationship--058e246d-cf7c-4957-9fac-45022e7c46dd</t>
+  </si>
+  <si>
+    <t>relationship--59519324-c28f-47e3-a28e-6833ee4ef511</t>
+  </si>
+  <si>
+    <t>relationship--29300e50-6531-4e7e-8695-0e9aa52a44c5</t>
+  </si>
+  <si>
+    <t>relationship--eeef4c23-15df-4135-8d66-37934eedba06</t>
+  </si>
+  <si>
+    <t>relationship--747eaf17-b939-49d0-94c9-26d9e039c287</t>
+  </si>
+  <si>
+    <t>relationship--36e8d7e1-4708-44a6-bc91-8fc9d1960db7</t>
+  </si>
+  <si>
+    <t>relationship--7897de01-e8e3-439c-937f-58471ac53ad1</t>
+  </si>
+  <si>
+    <t>relationship--458e1dca-67b7-48d8-9f8d-ba4fba34172d</t>
+  </si>
+  <si>
+    <t>relationship--69db264e-cfb6-4084-8699-74a3451b8d89</t>
+  </si>
+  <si>
+    <t>relationship--f266400a-d882-49da-8cd0-94d53a8440a7</t>
+  </si>
+  <si>
+    <t>relationship--6dd81fb8-1b0f-414a-b66d-249f578281dc</t>
+  </si>
+  <si>
+    <t>relationship--dfc8a5c6-887e-4c06-a6af-96d5f0a70c71</t>
+  </si>
+  <si>
+    <t>relationship--4a66513f-b03c-404c-8229-00ed0ba5d2bb</t>
+  </si>
+  <si>
+    <t>relationship--bfa2a6bc-d95e-4a9e-bdce-eb211b1b05f0</t>
+  </si>
+  <si>
+    <t>relationship--97b5a942-0c74-4429-b75e-a5f56986e4bc</t>
+  </si>
+  <si>
+    <t>relationship--2be93575-1965-4fb8-9e27-cff22794a83c</t>
+  </si>
+  <si>
+    <t>relationship--30536913-ff45-40b4-97bc-cc83c2842a6c</t>
+  </si>
+  <si>
+    <t>relationship--7c3da382-c3aa-497e-b9e8-34b57f50a40c</t>
+  </si>
+  <si>
+    <t>relationship--9ccfb40e-3145-4cef-8c25-541a85085a7a</t>
+  </si>
+  <si>
+    <t>relationship--48d3bd6c-6d67-427a-a918-a229472348fe</t>
+  </si>
+  <si>
+    <t>relationship--aa3ffd81-87db-4dc1-acbe-7ab2b835c1da</t>
+  </si>
+  <si>
+    <t>relationship--b5aaa679-ad3f-4bb1-aeab-3f280c7fb972</t>
+  </si>
+  <si>
+    <t>relationship--975197fc-2168-4040-a841-c3cb46d1da64</t>
+  </si>
+  <si>
+    <t>relationship--c6a49cec-51e2-42e4-8944-71a297fff307</t>
+  </si>
+  <si>
+    <t>relationship--bf415a60-02ac-4937-b134-7ab28b8f509a</t>
+  </si>
+  <si>
+    <t>relationship--08409ba1-6544-46cf-82d3-ab57b733c2c0</t>
+  </si>
+  <si>
+    <t>relationship--2e9e7a4d-97ef-4b84-9422-8bd0e3408640</t>
+  </si>
+  <si>
+    <t>relationship--d888712b-f1f0-4a72-9def-9f80bf399441</t>
+  </si>
+  <si>
+    <t>relationship--6920c644-8f01-4504-bd46-0f8cb4d9c03b</t>
+  </si>
+  <si>
+    <t>relationship--8fce6d91-96be-4a36-95f0-d9129add2414</t>
+  </si>
+  <si>
+    <t>relationship--f2d26557-8399-4687-b41a-7a9d7d2d6991</t>
+  </si>
+  <si>
+    <t>relationship--7e5d14c5-eee2-4516-a591-6ab114b39616</t>
+  </si>
+  <si>
+    <t>relationship--4aedfcbf-0b21-4cc4-bbc3-5fcd7133e96b</t>
+  </si>
+  <si>
+    <t>relationship--91505aef-64b8-4c19-a36b-00572428daae</t>
+  </si>
+  <si>
+    <t>relationship--27f0c620-33ac-4941-ad34-8ad92fb951bb</t>
+  </si>
+  <si>
+    <t>relationship--12987ed8-ae41-4a2b-9119-048b0d1c2a29</t>
+  </si>
+  <si>
+    <t>relationship--8761c9a9-1bca-43d7-b73b-063e2ccb5892</t>
+  </si>
+  <si>
+    <t>relationship--9859d030-c359-4277-a7c0-f4c0dc8ebea0</t>
+  </si>
+  <si>
+    <t>relationship--c6621408-c216-4632-8830-2cb368b491b2</t>
+  </si>
+  <si>
+    <t>relationship--cb149f6a-70ff-44d6-a7a4-dc7705413b7e</t>
+  </si>
+  <si>
+    <t>relationship--ffeec6db-89d9-44b8-a2d8-03c873161126</t>
+  </si>
+  <si>
+    <t>relationship--926fc305-439f-4e90-9d7e-fe20ee9f3b42</t>
+  </si>
+  <si>
+    <t>relationship--01ca3970-7a1f-46c5-8382-cfd35f0c730e</t>
+  </si>
+  <si>
+    <t>relationship--3980e6e6-b81b-4dec-b045-4241533377f8</t>
+  </si>
+  <si>
+    <t>relationship--53f62f92-2229-4f2d-b5e2-1bae14576a8d</t>
+  </si>
+  <si>
+    <t>relationship--10d7e27d-7a6e-4ea2-becb-b09ff7f5c73b</t>
+  </si>
+  <si>
+    <t>relationship--cd8fa868-85aa-4da3-9741-8badb8968112</t>
+  </si>
+  <si>
+    <t>relationship--3c08beb3-52a0-40d1-9c57-534aedd48ebf</t>
+  </si>
+  <si>
+    <t>relationship--bb007e67-caa9-4d3d-ac1f-3d618ab1de0d</t>
+  </si>
+  <si>
+    <t>relationship--84e048ac-fa44-4dce-bd05-e7825e346f5a</t>
+  </si>
+  <si>
+    <t>relationship--328bebba-f51c-42c7-bb3b-3002b8200a7b</t>
+  </si>
+  <si>
+    <t>relationship--2c64d9ce-762f-4b0a-a028-e35551463e03</t>
+  </si>
+  <si>
+    <t>relationship--8c3d77ea-8756-400d-b154-ec811df67412</t>
+  </si>
+  <si>
+    <t>relationship--f5168c16-e698-4bb4-9f50-7debdd5a3630</t>
+  </si>
+  <si>
+    <t>relationship--533afae2-4c7e-47a9-8ba3-ed82137df35a</t>
+  </si>
+  <si>
+    <t>relationship--90ca0b3c-4c3b-4a5b-8af9-4be8770d1bc1</t>
+  </si>
+  <si>
+    <t>relationship--86f0d89f-5cfb-4aa1-89c5-ca829fb54f0f</t>
+  </si>
+  <si>
+    <t>relationship--7e401d36-2524-4677-8cfb-b91674c12d2c</t>
+  </si>
+  <si>
+    <t>relationship--c166204b-0ede-4ddc-b15f-79b040bac7c1</t>
+  </si>
+  <si>
+    <t>relationship--f11f9b9b-57c5-4847-a328-fb70b2c9538c</t>
+  </si>
+  <si>
+    <t>relationship--a9f8de35-3128-45a4-b1cb-eee7174b014b</t>
+  </si>
+  <si>
+    <t>relationship--3db39e09-580e-44b3-8524-bbedcbddbad8</t>
+  </si>
+  <si>
+    <t>relationship--473e0e90-0dd6-42a5-9db8-860333d080e7</t>
+  </si>
+  <si>
+    <t>relationship--4ed2adee-2957-48f2-b787-771ff24842cc</t>
+  </si>
+  <si>
+    <t>relationship--f9253b57-b541-4864-ae70-84fdb5a9a009</t>
+  </si>
+  <si>
+    <t>relationship--ae77458f-2e73-44af-a4fe-568ac150a084</t>
+  </si>
+  <si>
+    <t>relationship--68f8ab90-d155-4302-b323-62f169f8e2f5</t>
+  </si>
+  <si>
+    <t>relationship--4d8fe415-5ba3-4218-b152-93400c0c05c9</t>
+  </si>
+  <si>
+    <t>relationship--328b830e-5848-4d69-aa54-9b9a9d0d71bd</t>
+  </si>
+  <si>
+    <t>relationship--fe1bb675-0c5e-4443-92e1-5e6cb50b2638</t>
+  </si>
+  <si>
+    <t>relationship--852935b0-0e77-4146-a270-7209b4dc693b</t>
+  </si>
+  <si>
+    <t>relationship--aeb32c7a-6284-4a47-b399-d8e136b116e6</t>
+  </si>
+  <si>
+    <t>relationship--5538f8fc-0291-4895-be52-13f6c2a31d03</t>
+  </si>
+  <si>
+    <t>relationship--bef9e71a-f7c1-4419-a5c3-d23d0b7a621d</t>
+  </si>
+  <si>
+    <t>relationship--4d72ad95-a4af-4a8b-832d-c862c922f58e</t>
+  </si>
+  <si>
+    <t>relationship--994616e8-ab99-4e2e-865f-e85308ffbf78</t>
+  </si>
+  <si>
+    <t>relationship--229019bf-8e78-44c5-88aa-d8c0061872c8</t>
+  </si>
+  <si>
+    <t>relationship--a30dfd3f-6cc1-4757-9d3b-910225e77dee</t>
+  </si>
+  <si>
+    <t>relationship--a2282a7f-2ea9-4f73-a79e-ec48d1f5818c</t>
+  </si>
+  <si>
+    <t>relationship--1766db0b-cecf-47d3-a1a1-5b57b20aa5f8</t>
+  </si>
+  <si>
+    <t>relationship--ee97460c-7ddc-4504-b619-a0fd72e0021b</t>
+  </si>
+  <si>
+    <t>relationship--58cc72d7-9597-4352-ace7-99cfbc5bf722</t>
+  </si>
+  <si>
+    <t>relationship--2e5b2622-ab7f-47cf-a1b8-4bc7ecad202c</t>
+  </si>
+  <si>
+    <t>relationship--75adf5f2-87ce-491b-84e6-41803005c30e</t>
+  </si>
+  <si>
+    <t>relationship--f7b6576c-0180-4f1c-af20-95a63a684aaa</t>
+  </si>
+  <si>
+    <t>relationship--bfddeccc-d818-4e1b-986e-a84e6fc111f4</t>
+  </si>
+  <si>
+    <t>relationship--dc7c1483-8d89-4e6a-a8dc-a2ea9f38e025</t>
   </si>
   <si>
     <t>C0009</t>
@@ -2510,6 +2510,9 @@
     <t>C0084</t>
   </si>
   <si>
+    <t>C0103</t>
+  </si>
+  <si>
     <t>C0015</t>
   </si>
   <si>
@@ -2813,6 +2816,9 @@
     <t>Подавление сопротивления УПА и операция «Висла» (1944–1951)</t>
   </si>
   <si>
+    <t>Полномасштабное вторжение (с 24 февраля 2022)</t>
+  </si>
+  <si>
     <t>Полтавская битва и окончательный разгром Гетманщины (1709)</t>
   </si>
   <si>
@@ -2927,307 +2933,310 @@
     <t>Юридическое поглощение через создание СССР (1922–1924)</t>
   </si>
   <si>
-    <t>campaign--6cb77d0a-3451-4de8-87da-b018068dfb90</t>
-  </si>
-  <si>
-    <t>campaign--8b42609d-df97-4863-be72-6956976733bf</t>
-  </si>
-  <si>
-    <t>campaign--9a411991-5759-4401-bf8b-1d035755a82e</t>
-  </si>
-  <si>
-    <t>campaign--87f90c81-65f7-408a-869c-13c15763058d</t>
-  </si>
-  <si>
-    <t>campaign--79792109-8930-4868-a0d5-c36b7e4d35d2</t>
-  </si>
-  <si>
-    <t>campaign--a2a50721-74ad-4a1b-8f10-4729fe218d77</t>
-  </si>
-  <si>
-    <t>campaign--e0b2ee1f-02d9-420b-95ec-c5e69e7683ba</t>
-  </si>
-  <si>
-    <t>campaign--f1f99961-521b-4e4c-ad7b-41a7f7fbb47d</t>
-  </si>
-  <si>
-    <t>campaign--b00634c3-5732-436e-b8ac-a379eb11a3a5</t>
-  </si>
-  <si>
-    <t>campaign--79f52559-e2ab-4202-825d-6c93ef0450f8</t>
-  </si>
-  <si>
-    <t>campaign--946006e7-080a-4089-846c-570e294df9de</t>
-  </si>
-  <si>
-    <t>campaign--120e2810-9671-4bbd-89dd-fdd5e5664bd8</t>
-  </si>
-  <si>
-    <t>campaign--e31eeb50-d21f-4f54-94fc-7a1265e3f422</t>
-  </si>
-  <si>
-    <t>campaign--4b4c6c32-adfd-4839-a189-784041b133e3</t>
-  </si>
-  <si>
-    <t>campaign--bbf4f7b4-df46-40fb-9560-91bbccaa69dd</t>
-  </si>
-  <si>
-    <t>campaign--d71c0044-37aa-487b-a348-d665b548d364</t>
-  </si>
-  <si>
-    <t>campaign--db3cd6c5-fdee-4f60-a49a-78a6842a0bdd</t>
-  </si>
-  <si>
-    <t>campaign--76bb2459-6ee0-4d14-9d96-4608d7fb554f</t>
-  </si>
-  <si>
-    <t>campaign--6763e8dc-524b-4121-9c95-1badc8d4ac5e</t>
-  </si>
-  <si>
-    <t>campaign--f7092c6b-af00-4ffc-bbc9-d41fdc3d22c0</t>
-  </si>
-  <si>
-    <t>campaign--02c01b67-1582-41d8-9cb8-89286d93e772</t>
-  </si>
-  <si>
-    <t>campaign--aedfaa2b-061a-4e70-8824-e88b30dbe4c4</t>
-  </si>
-  <si>
-    <t>campaign--452ec2f1-3adb-4883-a2a6-240c40bc70bc</t>
-  </si>
-  <si>
-    <t>campaign--467c7d12-8c86-49b3-accf-f377d0d7d0cc</t>
-  </si>
-  <si>
-    <t>campaign--a124adf3-a386-46f5-ab54-3b856f8a8bad</t>
-  </si>
-  <si>
-    <t>campaign--b25b509c-ab0c-4256-8f81-968d821c5915</t>
-  </si>
-  <si>
-    <t>campaign--18b1943c-1241-40fe-aae3-033c9ffa418c</t>
-  </si>
-  <si>
-    <t>campaign--50f07b8d-3a52-4520-9e5a-1f1eb1e83dea</t>
-  </si>
-  <si>
-    <t>campaign--05ca5326-ae3e-481b-ad1b-07a246c88714</t>
-  </si>
-  <si>
-    <t>campaign--5263d574-5eed-4573-a592-aff86805b317</t>
-  </si>
-  <si>
-    <t>campaign--87b0aff4-b9bb-4edb-b847-a3eb826f374e</t>
-  </si>
-  <si>
-    <t>campaign--4b8f603c-2beb-40c6-9db9-d9823f6e0437</t>
-  </si>
-  <si>
-    <t>campaign--45fafe35-cd3c-444a-a268-46b6a7370a63</t>
-  </si>
-  <si>
-    <t>campaign--4f403031-7401-483e-8eed-57761453596d</t>
-  </si>
-  <si>
-    <t>campaign--8cae9b2b-74d5-4ad1-9fea-e453ecc7f425</t>
-  </si>
-  <si>
-    <t>campaign--040c2b9c-df77-4197-bd95-495a7034b4c1</t>
-  </si>
-  <si>
-    <t>campaign--c7253f1e-c38d-4816-aa0b-fcd9f8dbbc27</t>
-  </si>
-  <si>
-    <t>campaign--d706a65d-715e-48ed-967a-3f237212463e</t>
-  </si>
-  <si>
-    <t>campaign--c3ef8acc-0599-468f-8956-3b91f3f30511</t>
-  </si>
-  <si>
-    <t>campaign--9a4f57ab-6a5e-462f-9d19-5421174ca868</t>
-  </si>
-  <si>
-    <t>campaign--3eab6e53-2449-478f-bf55-dd8afe89a40f</t>
-  </si>
-  <si>
-    <t>campaign--66baf89b-527e-4143-b19f-5621e74abb52</t>
-  </si>
-  <si>
-    <t>campaign--d33f72f9-20ea-4c43-a97d-85d6b536eda0</t>
-  </si>
-  <si>
-    <t>campaign--bebaab35-7783-4d15-b58b-ad2b0da41e64</t>
-  </si>
-  <si>
-    <t>campaign--1d62a197-4c67-4f24-8a41-5890204c4c85</t>
-  </si>
-  <si>
-    <t>campaign--ab5f7d10-2bd1-4ecb-b899-e478c9e2bedd</t>
-  </si>
-  <si>
-    <t>campaign--f9faba2b-2963-4108-975a-2425bcf557ff</t>
-  </si>
-  <si>
-    <t>campaign--d99a23fc-75f2-454e-a013-ef34ceee1c09</t>
-  </si>
-  <si>
-    <t>campaign--f36b045a-dea2-4a27-9a7e-dd439efff501</t>
-  </si>
-  <si>
-    <t>campaign--b93d1b44-3dc6-4818-b008-6748d0af33e9</t>
-  </si>
-  <si>
-    <t>campaign--2152c27e-8fb6-4d17-9545-ece61b0abb3d</t>
-  </si>
-  <si>
-    <t>campaign--da5bc58c-582e-4e35-83a7-a7616031ccf5</t>
-  </si>
-  <si>
-    <t>campaign--25d28320-21cd-47c2-8697-a1311d1d96f7</t>
-  </si>
-  <si>
-    <t>campaign--9232f8d3-d677-410c-9237-89f745f0288d</t>
-  </si>
-  <si>
-    <t>campaign--4b2262cd-ff27-411a-979d-6212f210b82d</t>
-  </si>
-  <si>
-    <t>campaign--9b0bbb08-af99-4a34-b75d-4014845f167d</t>
-  </si>
-  <si>
-    <t>campaign--29d1bd6c-71fb-4d83-862b-cbd6746a86b0</t>
-  </si>
-  <si>
-    <t>campaign--8d7e51bc-58cf-4cf3-891f-e30a45c03432</t>
-  </si>
-  <si>
-    <t>campaign--767abf96-8a3c-4500-9ec1-0d0a1fb32a88</t>
-  </si>
-  <si>
-    <t>campaign--009b3fbb-eb3e-4dd6-a04c-a439731c1854</t>
-  </si>
-  <si>
-    <t>campaign--210bd249-aeb2-4415-8206-e60090b574d1</t>
-  </si>
-  <si>
-    <t>campaign--142059e7-8457-48d4-8716-7aa6b587ab1b</t>
-  </si>
-  <si>
-    <t>campaign--6bb7b821-0e8b-4422-ad1b-764fff0a37e9</t>
-  </si>
-  <si>
-    <t>campaign--a7570eea-ac8a-4869-a00b-367790a7b200</t>
-  </si>
-  <si>
-    <t>campaign--9d9fbae1-5595-4a19-bd8c-7ddd1e2168ec</t>
-  </si>
-  <si>
-    <t>campaign--08748419-8e5d-40dc-aaff-c88e0fff5983</t>
-  </si>
-  <si>
-    <t>campaign--bbc072e6-4905-4dc0-a250-6a9d2dc9d66b</t>
-  </si>
-  <si>
-    <t>campaign--e30cc2e9-1add-4397-876e-067e0ede49ff</t>
-  </si>
-  <si>
-    <t>campaign--d787d857-4e39-4e4a-8103-3f6a4562de40</t>
-  </si>
-  <si>
-    <t>campaign--3c84c661-3fb6-44a6-ab75-7b4399e54925</t>
-  </si>
-  <si>
-    <t>campaign--33b91be6-6f1e-4aa6-ae4b-0099423adbf4</t>
-  </si>
-  <si>
-    <t>campaign--c8a3e3e3-0e8c-491a-b935-3ee30c72989d</t>
-  </si>
-  <si>
-    <t>campaign--9ed45ec0-7d71-4336-ba95-741c9cb1c4ad</t>
-  </si>
-  <si>
-    <t>campaign--c655b524-c56f-484c-b29f-132f99d873d6</t>
-  </si>
-  <si>
-    <t>campaign--256cf231-0b45-47ef-8398-143a78d0dbbf</t>
-  </si>
-  <si>
-    <t>campaign--ee36ce57-051f-4c20-8a09-69d43a2c1de6</t>
-  </si>
-  <si>
-    <t>campaign--b7e2e05a-2a56-49bf-af17-f86e431bece0</t>
-  </si>
-  <si>
-    <t>campaign--5cb4ced0-dedd-48cf-82cb-86724811997b</t>
-  </si>
-  <si>
-    <t>campaign--22649a71-e98f-4dce-a1cc-ed19d9c75cee</t>
-  </si>
-  <si>
-    <t>campaign--b3642930-149d-4b8d-ad0d-64d9d7c22e31</t>
-  </si>
-  <si>
-    <t>campaign--41303f5c-3cb5-48f0-afe0-1b97bae4f54b</t>
-  </si>
-  <si>
-    <t>campaign--2d672617-e7ff-4186-b99a-6c0e59b2069d</t>
-  </si>
-  <si>
-    <t>campaign--065b7c0a-b8f7-4351-9b58-96cb67b5bacb</t>
-  </si>
-  <si>
-    <t>campaign--4929ab8d-cac2-4c99-a2b4-d3012a155cfd</t>
-  </si>
-  <si>
-    <t>campaign--168b36b5-425a-4f37-8a93-b1b55d5a1da7</t>
-  </si>
-  <si>
-    <t>campaign--144ec9d9-444e-43fe-9d0e-3a2394ee8b53</t>
-  </si>
-  <si>
-    <t>campaign--65523a6a-2868-4b87-be5d-4ae9b29134b1</t>
-  </si>
-  <si>
-    <t>campaign--fe715480-d6ee-406e-ac1c-97428a212e65</t>
-  </si>
-  <si>
-    <t>campaign--88abdeab-1534-4131-aa37-73e84eb546ae</t>
-  </si>
-  <si>
-    <t>campaign--1c35fcdc-a6e6-4112-aa74-de7560d1bba3</t>
-  </si>
-  <si>
-    <t>campaign--ee0f26e4-d128-460c-9682-7492020544fb</t>
-  </si>
-  <si>
-    <t>campaign--0e177b96-42bc-49d8-a7a4-87d001a7b97d</t>
-  </si>
-  <si>
-    <t>campaign--09aa5cdd-2b55-4270-9ede-505fce974966</t>
-  </si>
-  <si>
-    <t>campaign--4a354ca0-b612-41ae-a22d-d5c6fb7a028a</t>
-  </si>
-  <si>
-    <t>campaign--01263d76-7a3e-4516-b993-39c444830762</t>
-  </si>
-  <si>
-    <t>campaign--513a8978-9c37-43cb-852f-88eaf99d3f6d</t>
-  </si>
-  <si>
-    <t>campaign--e667332a-68bc-4c3b-8f13-e19634de4d9f</t>
-  </si>
-  <si>
-    <t>campaign--65767352-3a24-4af7-a88e-481714d18d9c</t>
-  </si>
-  <si>
-    <t>campaign--54b232b3-84e1-4abc-a84d-f4855390eec4</t>
-  </si>
-  <si>
-    <t>campaign--2750145d-cbe0-49fc-b789-75f9234b1e96</t>
-  </si>
-  <si>
-    <t>campaign--8f92c47c-028b-41e2-b632-00565ffce2c8</t>
+    <t>campaign--84bc21e9-f278-45cd-8acb-817742dcff21</t>
+  </si>
+  <si>
+    <t>campaign--4bf56bd2-d5ca-438b-a3aa-5cbc36381133</t>
+  </si>
+  <si>
+    <t>campaign--3bd127a5-73b3-4aac-8fd7-982a95669434</t>
+  </si>
+  <si>
+    <t>campaign--1b611c93-e848-4ee1-8527-8bbbdf2e62a5</t>
+  </si>
+  <si>
+    <t>campaign--09a157f6-2eda-4e89-85e1-0705374ca9ee</t>
+  </si>
+  <si>
+    <t>campaign--d2e92b25-7923-452d-8885-6245a64315da</t>
+  </si>
+  <si>
+    <t>campaign--20b4d9b6-86c9-414d-b7c2-ba45639bfae6</t>
+  </si>
+  <si>
+    <t>campaign--dbcf8329-be72-43a6-9503-bd3b5f80e167</t>
+  </si>
+  <si>
+    <t>campaign--06e4cf4f-1d7a-4669-bfe2-46cf114cf71f</t>
+  </si>
+  <si>
+    <t>campaign--21b1b148-99e1-447f-863e-5f179ec7aac7</t>
+  </si>
+  <si>
+    <t>campaign--d1a75343-e6bc-456b-af9c-67abfebd8778</t>
+  </si>
+  <si>
+    <t>campaign--a1253a3a-9d62-49e1-acc7-7430a198b8bc</t>
+  </si>
+  <si>
+    <t>campaign--7c61ae27-c860-4b7d-9dbc-12b393680025</t>
+  </si>
+  <si>
+    <t>campaign--0c5ea36b-4e12-47ff-8d99-a4a35e4327b0</t>
+  </si>
+  <si>
+    <t>campaign--8ba7050c-642b-4ab9-9ce1-6ca4a4676ab5</t>
+  </si>
+  <si>
+    <t>campaign--6232bf9b-bb63-402d-b03e-9a0515ee09d8</t>
+  </si>
+  <si>
+    <t>campaign--9f962768-2e42-4c2e-a172-9291db92461b</t>
+  </si>
+  <si>
+    <t>campaign--2e0766ba-2d5c-4bab-a68b-5fe011747831</t>
+  </si>
+  <si>
+    <t>campaign--4a0448c0-0001-4134-acd4-941aa1379172</t>
+  </si>
+  <si>
+    <t>campaign--eedf404e-3e21-4116-be4d-0d7601599b91</t>
+  </si>
+  <si>
+    <t>campaign--e62f4c80-a205-4fe1-91c4-85256ac37f31</t>
+  </si>
+  <si>
+    <t>campaign--6ceef077-03f6-482f-8e76-a98491db2913</t>
+  </si>
+  <si>
+    <t>campaign--2248df9e-ba27-43a8-98d8-9026a6b9de03</t>
+  </si>
+  <si>
+    <t>campaign--05daf063-815a-43c4-bdef-868e86a89149</t>
+  </si>
+  <si>
+    <t>campaign--584843e9-c5e0-4087-a142-c385deeb2bdf</t>
+  </si>
+  <si>
+    <t>campaign--a657f3f9-0df3-4ed7-a7a4-a5412ea7ecb6</t>
+  </si>
+  <si>
+    <t>campaign--8f323bf8-3b9b-4bf4-97ad-3d61fc33fd82</t>
+  </si>
+  <si>
+    <t>campaign--6e5202d1-fbbe-422b-84d5-246cb35c0b2d</t>
+  </si>
+  <si>
+    <t>campaign--8ba3d669-f614-429f-9b77-a9cf527ff71d</t>
+  </si>
+  <si>
+    <t>campaign--7ce1e89d-a9af-4fb3-81ee-15ea23718846</t>
+  </si>
+  <si>
+    <t>campaign--6c24cbbb-4ce2-45a1-981a-cf0fd9c34d97</t>
+  </si>
+  <si>
+    <t>campaign--b9baf1bc-a3fa-4050-8722-e4ac1d29b0aa</t>
+  </si>
+  <si>
+    <t>campaign--eb1f4e4b-b946-449e-8752-60b5a41d8094</t>
+  </si>
+  <si>
+    <t>campaign--fa1c9409-7b35-48bb-8f3f-1de992f2a9fe</t>
+  </si>
+  <si>
+    <t>campaign--485bc4b1-d6a0-4262-b92b-de60846a3cc2</t>
+  </si>
+  <si>
+    <t>campaign--f98d27b7-b9b2-4ee5-968d-2242b9fed57d</t>
+  </si>
+  <si>
+    <t>campaign--d9246b40-5b51-4294-bcd6-dba876074271</t>
+  </si>
+  <si>
+    <t>campaign--c084e1db-0f03-44c2-8697-12757be14ecf</t>
+  </si>
+  <si>
+    <t>campaign--78366146-c147-4bca-adbc-91cf59affa19</t>
+  </si>
+  <si>
+    <t>campaign--c4b1a1bd-5808-4f82-8404-cb671321f0b8</t>
+  </si>
+  <si>
+    <t>campaign--4cb4ba5f-3257-4a64-99a7-89c1c8584ea3</t>
+  </si>
+  <si>
+    <t>campaign--bb5621a4-0317-4a72-9557-a3309369a148</t>
+  </si>
+  <si>
+    <t>campaign--c00efded-d911-444c-8743-89ddb7c2a25b</t>
+  </si>
+  <si>
+    <t>campaign--33e7df73-0ba4-4031-911d-d9a34f23381e</t>
+  </si>
+  <si>
+    <t>campaign--398bbef2-59b4-4eae-b7fb-2ddb4325a3db</t>
+  </si>
+  <si>
+    <t>campaign--5e9e3ee9-0edc-47b8-b51f-27d825c93ba6</t>
+  </si>
+  <si>
+    <t>campaign--a928c5b5-bd92-4716-bd4b-8e2e42e22ee8</t>
+  </si>
+  <si>
+    <t>campaign--13a5e084-1143-4c42-82a1-97c7cc060f9c</t>
+  </si>
+  <si>
+    <t>campaign--2f03ada1-afc9-4e6a-b822-aa65414b1b02</t>
+  </si>
+  <si>
+    <t>campaign--6d1a46e6-ac73-4930-aabd-a8f533a687cf</t>
+  </si>
+  <si>
+    <t>campaign--5f6c1d2e-8b43-49f7-9d3f-f3a0c3ae48b1</t>
+  </si>
+  <si>
+    <t>campaign--2e2bed38-682c-4d2f-ad6c-e2bb4c4cfdd0</t>
+  </si>
+  <si>
+    <t>campaign--fcb45d3f-14e8-4834-8b2c-d18b4c8f5273</t>
+  </si>
+  <si>
+    <t>campaign--c86c2f91-e10d-4e8b-b767-78378e15121e</t>
+  </si>
+  <si>
+    <t>campaign--0ba3a916-5b43-4183-b453-0927882dba85</t>
+  </si>
+  <si>
+    <t>campaign--e0cc83b8-2a5f-42f8-8537-a7a3e72ee650</t>
+  </si>
+  <si>
+    <t>campaign--4fa7d988-4c1c-4971-84cf-ca0467775997</t>
+  </si>
+  <si>
+    <t>campaign--49d099af-a6dc-4afe-8188-c064ef26fde7</t>
+  </si>
+  <si>
+    <t>campaign--007f466b-7682-4d8a-b195-22c21ff3e565</t>
+  </si>
+  <si>
+    <t>campaign--8f1d796b-636c-4cd1-86b4-37c3ece5165a</t>
+  </si>
+  <si>
+    <t>campaign--3d806c36-94c1-487f-b65e-9ff91c2a9abb</t>
+  </si>
+  <si>
+    <t>campaign--f2ebdc18-4134-4740-9f13-2c482064e83a</t>
+  </si>
+  <si>
+    <t>campaign--c4507383-caba-4152-b825-48578038d866</t>
+  </si>
+  <si>
+    <t>campaign--127d73b7-ad29-4bc6-bae2-aec0c43bad66</t>
+  </si>
+  <si>
+    <t>campaign--b67d3570-8e41-417e-8f8e-7d5ecb7e1d31</t>
+  </si>
+  <si>
+    <t>campaign--7b0b746d-42c4-4b10-aa04-8bfec1343821</t>
+  </si>
+  <si>
+    <t>campaign--d00c3e48-4826-4f1e-bfb7-118f00d84861</t>
+  </si>
+  <si>
+    <t>campaign--51b9d6b1-568b-4d68-8f9c-19a0b548272b</t>
+  </si>
+  <si>
+    <t>campaign--ce760399-e985-4e95-bb41-7d3b796dd18b</t>
+  </si>
+  <si>
+    <t>campaign--4e66eed7-56a9-48ac-8a18-99a559927eb6</t>
+  </si>
+  <si>
+    <t>campaign--152cca2d-a341-45fd-a306-6690c012f021</t>
+  </si>
+  <si>
+    <t>campaign--387e09ec-bf7a-447c-a918-bcff0ee9da8b</t>
+  </si>
+  <si>
+    <t>campaign--beeb4667-4ab9-4028-94c4-b6b19eefabeb</t>
+  </si>
+  <si>
+    <t>campaign--40524974-ff86-4741-bc58-ccfb35d10bc7</t>
+  </si>
+  <si>
+    <t>campaign--d5059819-4fb3-4b0e-9e0a-5784b854386c</t>
+  </si>
+  <si>
+    <t>campaign--0dca3871-e3fd-47d7-a07f-e9ea15919c0d</t>
+  </si>
+  <si>
+    <t>campaign--d6da9526-4dd6-4eb9-abfd-44a5e1879d41</t>
+  </si>
+  <si>
+    <t>campaign--b1e8059c-3914-414e-8a6d-0fb74549bec8</t>
+  </si>
+  <si>
+    <t>campaign--2660323c-96cd-4d12-920b-3ca598fbdb74</t>
+  </si>
+  <si>
+    <t>campaign--a51dfeb5-c6ce-44b2-9bc5-c4c6687bd2f0</t>
+  </si>
+  <si>
+    <t>campaign--f3a217be-13bd-488e-b046-33d4a55b2cf3</t>
+  </si>
+  <si>
+    <t>campaign--5424b97c-0790-47c0-bc6a-99fda22a8e9d</t>
+  </si>
+  <si>
+    <t>campaign--6733da7e-2f67-4c13-97a6-00b05a549f10</t>
+  </si>
+  <si>
+    <t>campaign--ce5cc518-cbce-4e92-b8ff-30e504c15c2c</t>
+  </si>
+  <si>
+    <t>campaign--2907649b-fd94-42fa-8784-f18f4584d71a</t>
+  </si>
+  <si>
+    <t>campaign--dddb4201-585e-47c1-95e9-425b0730fb90</t>
+  </si>
+  <si>
+    <t>campaign--cf6632c9-6e3d-4cbc-9dce-724891b573c7</t>
+  </si>
+  <si>
+    <t>campaign--e7ee89b0-2cb6-4b84-948c-7057dd523852</t>
+  </si>
+  <si>
+    <t>campaign--eddd1738-28fd-4da0-b6f4-7c44a32152b7</t>
+  </si>
+  <si>
+    <t>campaign--5fa57ffc-7b8e-49c1-82da-60712fe1a716</t>
+  </si>
+  <si>
+    <t>campaign--466f1dd3-c4d2-4076-b0d7-d52a41e7bc83</t>
+  </si>
+  <si>
+    <t>campaign--11dce568-2d19-4c59-bdfd-64ec6fced3e6</t>
+  </si>
+  <si>
+    <t>campaign--0356e86e-0974-45cf-b41d-6997de20ba10</t>
+  </si>
+  <si>
+    <t>campaign--0956db31-89c5-43f3-aaa6-f6d9b3b7ff12</t>
+  </si>
+  <si>
+    <t>campaign--5177f321-68a6-4d63-a678-c5265f63243b</t>
+  </si>
+  <si>
+    <t>campaign--7402cc4a-618b-4851-8075-cb883379e3c0</t>
+  </si>
+  <si>
+    <t>campaign--b5ce00ca-7682-4ce8-9c4c-8be0c65df490</t>
+  </si>
+  <si>
+    <t>campaign--af98cd78-ddfd-4a73-8ab2-5b920e8221ac</t>
+  </si>
+  <si>
+    <t>campaign--9f187028-927d-4536-ba2f-3f2177c0e164</t>
+  </si>
+  <si>
+    <t>campaign--66970f35-4e71-491e-932e-1fee6b188e71</t>
+  </si>
+  <si>
+    <t>campaign--d419efc6-e0ba-4f5e-83a2-46e1d38cd231</t>
+  </si>
+  <si>
+    <t>campaign--09ffe87c-9f1c-4a9e-9879-3648aa2d3535</t>
   </si>
   <si>
     <t>campaign</t>
@@ -3341,6 +3350,9 @@
     <t>Многолетняя силовая кампания Российской империи против масштабного восстания бесправных украинских крестьян под предводительством [Устима Кармалюка](https://uk.wikipedia.org/wiki/Кармалюк_Устим_Якимович) на Подолье (Citation: Історія України — Вікіпедія 2026).</t>
   </si>
   <si>
+    <t>Вторжение регулярной армии РФ и нанесение массированных ракетно-авиационных ударов по Киеву, Днепру, Харькову и другим украинским городам ранним утром 24 февраля 2022 года. (Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
+  </si>
+  <si>
     <t>Физическое уничтожение вооруженных сил сторонников независимости в ходе генерального сражения для ликвидации военного потенциала сопротивления (Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011).</t>
   </si>
   <si>
@@ -3398,310 +3410,313 @@
     <t>Указ Александра II: «Заборона ввозити українські книги з-за кордону, заборона підписувати українські тексти під нотами, заборона українських вистав» (Citation: Русифікація України — Вікіпедія 2026).</t>
   </si>
   <si>
-    <t>relationship--382fcb97-4f41-46e4-bb60-34c2ae61e243</t>
-  </si>
-  <si>
-    <t>relationship--4495adfe-a3e7-45bd-8dd4-3592a6569138</t>
-  </si>
-  <si>
-    <t>relationship--9225e21e-7c93-49c2-8027-237b8e463ac1</t>
-  </si>
-  <si>
-    <t>relationship--eb953dbb-8e6f-40d4-be23-9cda1f740475</t>
-  </si>
-  <si>
-    <t>relationship--dd066db1-d38e-40a6-a63e-ac40ea62ccf8</t>
-  </si>
-  <si>
-    <t>relationship--61b8e545-b323-4b47-ab5a-7a9a3bcac4f1</t>
-  </si>
-  <si>
-    <t>relationship--d1126afd-11e5-4fd8-9ca4-aef38e5474ee</t>
-  </si>
-  <si>
-    <t>relationship--36fdff9f-fc5c-482e-9de7-6da2088cb90d</t>
-  </si>
-  <si>
-    <t>relationship--7483aed6-f3af-415b-8a8d-2c3c5df83162</t>
-  </si>
-  <si>
-    <t>relationship--55707eee-feda-43e1-9663-98427e22c425</t>
-  </si>
-  <si>
-    <t>relationship--8d1f50e8-5d19-401b-8f5f-e546f4f06f4b</t>
-  </si>
-  <si>
-    <t>relationship--d66ec916-3d0c-4de2-b7be-5df665df503f</t>
-  </si>
-  <si>
-    <t>relationship--da504b5e-7045-48b4-86e9-79c5ca91c4ed</t>
-  </si>
-  <si>
-    <t>relationship--8a2151b1-85a2-4de8-8404-b5359eee6472</t>
-  </si>
-  <si>
-    <t>relationship--8768eabd-8d6b-4420-aeea-54339ed9baf0</t>
-  </si>
-  <si>
-    <t>relationship--49274bca-c396-4e35-9bac-8a77e42bbe37</t>
-  </si>
-  <si>
-    <t>relationship--8856c1b0-3c97-4a08-8129-1ca06a9aa77e</t>
-  </si>
-  <si>
-    <t>relationship--e45bcd17-fc61-4997-ba9d-dd9350c19fcf</t>
-  </si>
-  <si>
-    <t>relationship--a681f9c6-75fb-48b1-a518-4ae4693469cf</t>
-  </si>
-  <si>
-    <t>relationship--a2ae0fcd-d5a3-48f2-9648-94c6a578996b</t>
-  </si>
-  <si>
-    <t>relationship--2169d14e-dccd-4fcb-8089-596e31f992be</t>
-  </si>
-  <si>
-    <t>relationship--85c2a1ef-0476-4dc7-b04b-c7ab04d1551d</t>
-  </si>
-  <si>
-    <t>relationship--2e69f83c-b3d0-428e-8e0e-83f2622be4fe</t>
-  </si>
-  <si>
-    <t>relationship--6196146c-172f-40bd-939e-a3e86f47fccc</t>
-  </si>
-  <si>
-    <t>relationship--bdf151f8-928d-4d5e-9c05-e3d5db94fc73</t>
-  </si>
-  <si>
-    <t>relationship--28d66b03-24f5-4e5c-97e4-02822aa8ccf7</t>
-  </si>
-  <si>
-    <t>relationship--c4d58b25-d138-401b-a8f1-7b6c3070c24f</t>
-  </si>
-  <si>
-    <t>relationship--e63320e3-64b9-476c-8ffd-9b697bbdd1ca</t>
-  </si>
-  <si>
-    <t>relationship--5db7d86a-c6c2-4edf-976f-a8b386b7c52f</t>
-  </si>
-  <si>
-    <t>relationship--88bdfc29-6fee-47c4-8531-4dd2c50addc3</t>
-  </si>
-  <si>
-    <t>relationship--c1bc7a48-1f0d-4b5d-95e3-d41a262fdcb3</t>
-  </si>
-  <si>
-    <t>relationship--8499a70c-630a-494f-9336-2f1763b1bbdc</t>
-  </si>
-  <si>
-    <t>relationship--23806f4b-ec1d-457f-9917-6db807392b7d</t>
-  </si>
-  <si>
-    <t>relationship--efa0724d-5137-40f1-8b31-515732cdb62a</t>
-  </si>
-  <si>
-    <t>relationship--77aab65f-58a4-4e9d-a54d-83a8ee32c799</t>
-  </si>
-  <si>
-    <t>relationship--044095aa-fae1-49c3-b301-5342abc40196</t>
-  </si>
-  <si>
-    <t>relationship--1cbd029d-e0d4-48d3-9d4b-6728e01611c9</t>
-  </si>
-  <si>
-    <t>relationship--49c17912-3b07-4b38-bf9b-a72bd56dc4ca</t>
-  </si>
-  <si>
-    <t>relationship--b5279e93-6c2d-4ef7-b0a2-abee935c2f67</t>
-  </si>
-  <si>
-    <t>relationship--2873c7d0-b4e5-46e7-a4eb-237fb5ab2d86</t>
-  </si>
-  <si>
-    <t>relationship--4e4832dc-e64f-412d-8a26-0e93f91c542c</t>
-  </si>
-  <si>
-    <t>relationship--dc690243-0da4-4460-82ad-9965ac7c3f9e</t>
-  </si>
-  <si>
-    <t>relationship--1589557c-674b-42a6-9d79-140dd54c57a9</t>
-  </si>
-  <si>
-    <t>relationship--23aedab9-87d8-4155-950b-80af2f045330</t>
-  </si>
-  <si>
-    <t>relationship--101c7f49-2c04-4b8a-9556-b4c26783bfe2</t>
-  </si>
-  <si>
-    <t>relationship--1aca5862-5cf0-4da7-be63-d773e5b14e6c</t>
-  </si>
-  <si>
-    <t>relationship--1734101c-ef7a-4948-8a3b-0a0905ca1f1d</t>
-  </si>
-  <si>
-    <t>relationship--db41c035-7acc-4a92-9eac-aead465c5a2c</t>
-  </si>
-  <si>
-    <t>relationship--07f6f446-cb45-4775-bc19-4ca62911421c</t>
-  </si>
-  <si>
-    <t>relationship--23635f40-42e0-4aab-93e5-7839900aa645</t>
-  </si>
-  <si>
-    <t>relationship--e9fd6b3f-16bf-4479-92ec-5caab1d1e0e9</t>
-  </si>
-  <si>
-    <t>relationship--18910b2c-ba23-486c-985b-b109124d1b3e</t>
-  </si>
-  <si>
-    <t>relationship--0ccfc730-fb82-4744-8e1d-322140f19e9a</t>
-  </si>
-  <si>
-    <t>relationship--eee05d7c-ae7b-4053-8875-afcf211b76ed</t>
-  </si>
-  <si>
-    <t>relationship--8aa0ca1b-3f7c-4c32-8a7c-45b31ce910ae</t>
-  </si>
-  <si>
-    <t>relationship--b7259905-9d80-494f-b98c-475f9626877c</t>
-  </si>
-  <si>
-    <t>relationship--94fdda67-bf68-47b8-8de2-34e48e939fc1</t>
-  </si>
-  <si>
-    <t>relationship--590a6244-8e58-46d8-b696-1c5d8e0625b3</t>
-  </si>
-  <si>
-    <t>relationship--bbb202d4-6a82-4e71-820a-a7a10f749fa8</t>
-  </si>
-  <si>
-    <t>relationship--e082139a-4d63-42e3-a9ab-22704289063c</t>
-  </si>
-  <si>
-    <t>relationship--3b287c44-edb0-493f-b089-4c8e9b742c1e</t>
-  </si>
-  <si>
-    <t>relationship--af6c11a0-1a81-4476-9133-418e237512ff</t>
-  </si>
-  <si>
-    <t>relationship--4765f79a-41a8-48a0-9df1-2008ca7b0f99</t>
-  </si>
-  <si>
-    <t>relationship--cb521445-1143-4d52-8855-527fd205f9f8</t>
-  </si>
-  <si>
-    <t>relationship--fdf48b58-3ad9-4551-9e50-af554a5b42ad</t>
-  </si>
-  <si>
-    <t>relationship--ffb95292-95f1-4871-991d-7c92aa317f0b</t>
-  </si>
-  <si>
-    <t>relationship--505e1362-9b73-4bb0-b4c2-e6d1b039e4e4</t>
-  </si>
-  <si>
-    <t>relationship--20298c0f-6237-45dc-af9d-f56d893f7259</t>
-  </si>
-  <si>
-    <t>relationship--9a23d323-20c6-4635-aadb-67dd78a2f01a</t>
-  </si>
-  <si>
-    <t>relationship--61a7038d-63a6-4b13-8a2d-0caca2bc8325</t>
-  </si>
-  <si>
-    <t>relationship--aeb42ea0-3a92-4e4a-8b4b-7f232833f401</t>
-  </si>
-  <si>
-    <t>relationship--da2a7062-df67-4afa-8567-858795e0c382</t>
-  </si>
-  <si>
-    <t>relationship--14f872e6-ada3-4196-ad9c-211a9ce327bb</t>
-  </si>
-  <si>
-    <t>relationship--7b9cbfa7-d262-4ff2-b520-b459f9b562f9</t>
-  </si>
-  <si>
-    <t>relationship--c46aab24-4e0f-41b8-9b97-46505ddae0ae</t>
-  </si>
-  <si>
-    <t>relationship--9a947244-79a8-4ed8-b542-832c9c926e6d</t>
-  </si>
-  <si>
-    <t>relationship--6d836384-f648-4400-8095-c213d21fda1d</t>
-  </si>
-  <si>
-    <t>relationship--e2e535e7-756f-4444-b330-8001d5906d93</t>
-  </si>
-  <si>
-    <t>relationship--d6a4f28f-89a5-4b6e-8bdb-50c6acb9ea4b</t>
-  </si>
-  <si>
-    <t>relationship--d75b0862-802b-4770-9fd6-3426a5d767c7</t>
-  </si>
-  <si>
-    <t>relationship--0350c612-d784-4b91-99a7-cbaac48b11cf</t>
-  </si>
-  <si>
-    <t>relationship--7189b336-e5d2-491b-b8f8-e94a9b52a4e5</t>
-  </si>
-  <si>
-    <t>relationship--c12be137-9cae-44dd-8092-aeee8a1963f4</t>
-  </si>
-  <si>
-    <t>relationship--24b777c8-f739-463f-b8ef-a86cf6aa4f34</t>
-  </si>
-  <si>
-    <t>relationship--05decf97-2ade-44f2-96b0-30b40a6246cf</t>
-  </si>
-  <si>
-    <t>relationship--e7216d3e-de30-4410-9c3f-c022eed6a6d2</t>
-  </si>
-  <si>
-    <t>relationship--e5771421-67f9-443e-873a-3472d1f67ef0</t>
-  </si>
-  <si>
-    <t>relationship--08caa687-cc83-4bc5-8fc3-e2ac19d8c83e</t>
-  </si>
-  <si>
-    <t>relationship--e0ca1f77-bd5b-411a-b57f-6813c65a46ac</t>
-  </si>
-  <si>
-    <t>relationship--62d3fe94-11cc-4584-ad49-257cae10cd2c</t>
-  </si>
-  <si>
-    <t>relationship--f5c60d72-2433-4f5f-b65e-aca6af57ad7e</t>
-  </si>
-  <si>
-    <t>relationship--bdd5cf36-5fe9-40eb-9590-e32ec89eac25</t>
-  </si>
-  <si>
-    <t>relationship--677a1907-f669-4245-89a3-2afbc2911210</t>
-  </si>
-  <si>
-    <t>relationship--5cb58ec3-0569-4768-b0e0-afa765845d2f</t>
-  </si>
-  <si>
-    <t>relationship--ee63d5d7-bc76-42a4-ae67-cea3bfe1cc8d</t>
-  </si>
-  <si>
-    <t>relationship--4e768b23-0fe0-4104-b97e-f19cf0a96cc3</t>
-  </si>
-  <si>
-    <t>relationship--2a5e61b4-05d8-4d14-9de4-2b9c61d56326</t>
-  </si>
-  <si>
-    <t>relationship--7a5abd80-9d01-4a4d-8206-9b79ba60a02d</t>
-  </si>
-  <si>
-    <t>relationship--23bab217-d7a8-4ba9-b0cd-2d38801cfc47</t>
-  </si>
-  <si>
-    <t>relationship--bbbd33ce-ba16-49d8-908c-9d2fc8c86474</t>
-  </si>
-  <si>
-    <t>relationship--764bbf19-51ca-465d-81a9-f43abc274c3e</t>
-  </si>
-  <si>
-    <t>relationship--d11a6c57-9820-4859-a256-286d04380747</t>
+    <t>relationship--12bc8904-99bc-4a55-a768-c6d397e1a829</t>
+  </si>
+  <si>
+    <t>relationship--f69b368a-adad-48c6-8f60-0c29f400c102</t>
+  </si>
+  <si>
+    <t>relationship--18c6088c-8841-4ec9-aac2-46a007ebcc21</t>
+  </si>
+  <si>
+    <t>relationship--a963ff2b-070c-4db6-a06d-e5e88f4f3325</t>
+  </si>
+  <si>
+    <t>relationship--797f6d6f-ef9f-4e5e-ae50-0adf72381d8d</t>
+  </si>
+  <si>
+    <t>relationship--aac285db-9b35-40f3-850d-3879630f39b0</t>
+  </si>
+  <si>
+    <t>relationship--01b73e42-a773-4c1d-ae11-0261602aa1d5</t>
+  </si>
+  <si>
+    <t>relationship--fd3683f7-5961-46fb-a76a-82b65e3a5b73</t>
+  </si>
+  <si>
+    <t>relationship--70eb29ba-2799-438a-823e-c446df6bb1c3</t>
+  </si>
+  <si>
+    <t>relationship--3034bb38-cc9e-4fe3-9842-ae672d1b5536</t>
+  </si>
+  <si>
+    <t>relationship--386bf42f-4150-4986-9814-edbe336dfe55</t>
+  </si>
+  <si>
+    <t>relationship--284bb962-aeb3-442f-b754-228c2dd8867e</t>
+  </si>
+  <si>
+    <t>relationship--d05d0b21-357b-4498-bc88-e7c4cc4f9f9f</t>
+  </si>
+  <si>
+    <t>relationship--d2022ffe-3862-4f2c-9b89-19cb8f674ff3</t>
+  </si>
+  <si>
+    <t>relationship--44935fe7-597d-4305-8969-7d4193d4937e</t>
+  </si>
+  <si>
+    <t>relationship--b237bf26-ef58-44ce-884b-12d24cef4ebc</t>
+  </si>
+  <si>
+    <t>relationship--78f059a7-2d33-49be-9c65-b63c987a69e8</t>
+  </si>
+  <si>
+    <t>relationship--6cd0cf96-c86f-49ec-8146-9ffbe9e15ab1</t>
+  </si>
+  <si>
+    <t>relationship--eb81fea3-4753-4b73-893f-16fd43321646</t>
+  </si>
+  <si>
+    <t>relationship--170c807a-1fe8-4130-977a-13bd8e119f56</t>
+  </si>
+  <si>
+    <t>relationship--cdf4555b-3027-4c26-8582-bdb5ea5f869a</t>
+  </si>
+  <si>
+    <t>relationship--53131930-c0c4-4d4b-9c82-ee16de54ce19</t>
+  </si>
+  <si>
+    <t>relationship--4821fa4d-5f4d-4bfb-8bd6-4a0299575b5b</t>
+  </si>
+  <si>
+    <t>relationship--37cfc5df-0284-43b0-8c9f-621300de40cb</t>
+  </si>
+  <si>
+    <t>relationship--31c52698-3b14-4ed3-b949-6f20a9f44ea9</t>
+  </si>
+  <si>
+    <t>relationship--b392a5a2-6f29-4155-b30e-c35d6e81164a</t>
+  </si>
+  <si>
+    <t>relationship--10b967cf-5d22-49ba-9593-7586cfb25d57</t>
+  </si>
+  <si>
+    <t>relationship--9a4cfe1d-243b-4da7-8f85-a5a234c0de46</t>
+  </si>
+  <si>
+    <t>relationship--229bc6e3-bd6e-4f00-920a-bf0b75aeb3ce</t>
+  </si>
+  <si>
+    <t>relationship--3b64a530-ee75-43af-ad56-3f7be087f2b6</t>
+  </si>
+  <si>
+    <t>relationship--24417c43-3986-4157-a47b-138ce21c1586</t>
+  </si>
+  <si>
+    <t>relationship--d2f3847c-ea68-485c-9b5c-5489b3c02399</t>
+  </si>
+  <si>
+    <t>relationship--243e8e41-8775-4d04-8cf5-4270b8f00b87</t>
+  </si>
+  <si>
+    <t>relationship--1e9db859-18a1-4b08-bbd4-9c8cb097729b</t>
+  </si>
+  <si>
+    <t>relationship--05eb80d0-303e-4b3d-8974-3be40c5a6cdc</t>
+  </si>
+  <si>
+    <t>relationship--c1b7dbad-95fa-4b86-aa0b-f4847943206f</t>
+  </si>
+  <si>
+    <t>relationship--712355d5-0423-4efa-910b-56b77ad545fa</t>
+  </si>
+  <si>
+    <t>relationship--5fbfc696-714c-42dc-a387-89d2a7bb4132</t>
+  </si>
+  <si>
+    <t>relationship--9179dcc8-fd36-43e7-8ebc-45c9b2d0c555</t>
+  </si>
+  <si>
+    <t>relationship--e179b84d-4d95-4dce-a854-38c32b638bc9</t>
+  </si>
+  <si>
+    <t>relationship--d019a938-c6f0-42a3-b4c7-00fc1eac691c</t>
+  </si>
+  <si>
+    <t>relationship--fc05427b-b7ed-4a94-b62c-2bb9ef30d7ad</t>
+  </si>
+  <si>
+    <t>relationship--c5355ea4-9dd7-41b9-a281-58dfe58bacd2</t>
+  </si>
+  <si>
+    <t>relationship--e322551c-b3c2-40e8-9efa-d9fe5c984aab</t>
+  </si>
+  <si>
+    <t>relationship--6fabfad7-778f-461e-9d87-7d2f8192ddc4</t>
+  </si>
+  <si>
+    <t>relationship--1cada7a0-7e70-4c74-85aa-54969bd99f6d</t>
+  </si>
+  <si>
+    <t>relationship--464ccc93-dc4f-4050-bb8b-07a28cef790e</t>
+  </si>
+  <si>
+    <t>relationship--b6b6b49c-9491-4e42-a665-09884c32fa52</t>
+  </si>
+  <si>
+    <t>relationship--0e9d2f82-e202-4317-94cf-8932067cdd33</t>
+  </si>
+  <si>
+    <t>relationship--5b7b09b3-9a51-4d65-a86c-4befe3ab7fbc</t>
+  </si>
+  <si>
+    <t>relationship--f30be867-5cae-40b0-8c91-06f5c306ff2b</t>
+  </si>
+  <si>
+    <t>relationship--ca78e3f5-edc4-46ff-86f6-89fb3c35288e</t>
+  </si>
+  <si>
+    <t>relationship--7752b90a-82a7-4e9c-b827-c26959415840</t>
+  </si>
+  <si>
+    <t>relationship--ffa36b52-804f-4e4a-a467-aff1ccaeb8b2</t>
+  </si>
+  <si>
+    <t>relationship--b1dd4bc9-7ef5-4050-b0f8-f5fb9c2019e0</t>
+  </si>
+  <si>
+    <t>relationship--2ee3efa5-74c8-4255-94b2-ce1b5ff81142</t>
+  </si>
+  <si>
+    <t>relationship--fe6278dd-37ff-4ae0-aaa2-15e5deec1bad</t>
+  </si>
+  <si>
+    <t>relationship--e6bf0e77-c31d-42b9-8cd6-f52b8fb3d2db</t>
+  </si>
+  <si>
+    <t>relationship--5e841f9c-b382-44fc-b069-31d7ed86d613</t>
+  </si>
+  <si>
+    <t>relationship--26b24ed3-bab4-48b5-af20-473d37df73a1</t>
+  </si>
+  <si>
+    <t>relationship--5dc7f800-2702-41e3-a999-ec18d12bdb0b</t>
+  </si>
+  <si>
+    <t>relationship--bb205bd8-3105-49e8-a966-8a5a4b80ce4b</t>
+  </si>
+  <si>
+    <t>relationship--066eb730-edbb-4eb7-be95-30ee7a67bbad</t>
+  </si>
+  <si>
+    <t>relationship--997ffb23-24f9-4bf6-ae61-1773c568c2d6</t>
+  </si>
+  <si>
+    <t>relationship--90927691-a826-45b1-aa61-4b0253556a02</t>
+  </si>
+  <si>
+    <t>relationship--da285461-ab09-48e4-bac7-6e4b7f5c2e1d</t>
+  </si>
+  <si>
+    <t>relationship--ae5ce0c4-d70d-40a0-891a-6472f31c7fa3</t>
+  </si>
+  <si>
+    <t>relationship--a16aa153-ab2d-49f9-96bf-61989c058b71</t>
+  </si>
+  <si>
+    <t>relationship--64487f17-db95-46e3-adff-3d3d2629772b</t>
+  </si>
+  <si>
+    <t>relationship--5c1bd692-3e7e-43aa-907a-435464271bc7</t>
+  </si>
+  <si>
+    <t>relationship--c2595a81-92d7-404b-ad9f-1b290af8866b</t>
+  </si>
+  <si>
+    <t>relationship--bd9c2824-ba1b-4fc6-b7be-815d4341d76c</t>
+  </si>
+  <si>
+    <t>relationship--13d8371a-bd47-4e2d-9833-64256ea7236e</t>
+  </si>
+  <si>
+    <t>relationship--d4f3bacb-f6e3-44e1-948e-fb11cc9afcdb</t>
+  </si>
+  <si>
+    <t>relationship--c561afa2-ce06-447a-8c4c-be71f21480c7</t>
+  </si>
+  <si>
+    <t>relationship--28cf8d5f-6d6f-453c-a201-317c04dee34d</t>
+  </si>
+  <si>
+    <t>relationship--769341f9-ee3b-42c3-b2ab-3398313428ec</t>
+  </si>
+  <si>
+    <t>relationship--2d753309-a85e-415c-a222-0301ec963f66</t>
+  </si>
+  <si>
+    <t>relationship--cc65d3dc-fb26-4e54-b54f-9d2c812c7cff</t>
+  </si>
+  <si>
+    <t>relationship--1eb1a282-23cc-43ab-b857-0d11d636e2a5</t>
+  </si>
+  <si>
+    <t>relationship--2bbbd285-77d1-4fd6-91c9-5d028c72f098</t>
+  </si>
+  <si>
+    <t>relationship--a1492f55-f3d8-429c-8ec4-384c57f58821</t>
+  </si>
+  <si>
+    <t>relationship--c63d2783-b3b7-47a3-9be9-d1677fa6945c</t>
+  </si>
+  <si>
+    <t>relationship--0b4d5b99-7039-4ab0-a99d-094ceaa1cd91</t>
+  </si>
+  <si>
+    <t>relationship--c3b294ff-66a0-4e31-a6b4-12d7a648a472</t>
+  </si>
+  <si>
+    <t>relationship--4eef5b22-d5ab-478f-8fcc-018f34f58e25</t>
+  </si>
+  <si>
+    <t>relationship--40042475-a205-4c1b-97e7-7c76c7865cbb</t>
+  </si>
+  <si>
+    <t>relationship--c67c90d0-effd-43e6-84de-05d750e98fe0</t>
+  </si>
+  <si>
+    <t>relationship--b12bd32f-d8c0-47c2-a1f0-cfddf25000c1</t>
+  </si>
+  <si>
+    <t>relationship--ba3fd383-b77d-4c48-9eb4-506a4833f1f2</t>
+  </si>
+  <si>
+    <t>relationship--15c27931-d7a9-4b5c-9058-bf081b37a8a3</t>
+  </si>
+  <si>
+    <t>relationship--1ad4791e-261a-4512-8123-89fc26e12b25</t>
+  </si>
+  <si>
+    <t>relationship--17997574-a161-4f2d-81d7-a8ffc9343dcf</t>
+  </si>
+  <si>
+    <t>relationship--39edf99e-7601-4a47-ad39-8e3d080fba7d</t>
+  </si>
+  <si>
+    <t>relationship--5173a2ce-e76a-4bb7-8685-3d30657cf7bb</t>
+  </si>
+  <si>
+    <t>relationship--36eb1714-2670-44e7-b9cb-96d0eb426b72</t>
+  </si>
+  <si>
+    <t>relationship--3d4c10fe-6943-48fd-b897-e90c3158744f</t>
+  </si>
+  <si>
+    <t>relationship--78c6f40f-c64c-4681-9061-63acf50a4bd6</t>
+  </si>
+  <si>
+    <t>relationship--b24d5aea-09e9-41bc-85a0-240a7b69a591</t>
+  </si>
+  <si>
+    <t>relationship--2bb139e8-1edc-4db2-b8c1-482176975ad4</t>
+  </si>
+  <si>
+    <t>relationship--ca8c42ef-8ef1-4ccb-8237-f9206f58f733</t>
+  </si>
+  <si>
+    <t>relationship--fd974d03-b680-4744-85c5-8e1ac2ce7c31</t>
+  </si>
+  <si>
+    <t>relationship--d88929a7-dc71-49ce-b9a1-bfedc801e8a8</t>
   </si>
   <si>
     <t>reference</t>
@@ -3716,15 +3731,24 @@
     <t>2016 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023</t>
   </si>
   <si>
+    <t>Іван Мазепа — Вікіпедія 2026</t>
+  </si>
+  <si>
     <t>Історія України — Вікіпедія 2026</t>
   </si>
   <si>
+    <t>Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026</t>
+  </si>
+  <si>
     <t>Война и наказание: Как Россия уничтожала Украину 2023</t>
   </si>
   <si>
     <t>Всесоюзний референдум про збереження СРСР — Вікіпедія 2026</t>
   </si>
   <si>
+    <t>Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026</t>
+  </si>
+  <si>
     <t>Дезінформація під час російсько-української війни — Вікіпедія 2026</t>
   </si>
   <si>
@@ -3740,9 +3764,6 @@
     <t>ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011</t>
   </si>
   <si>
-    <t>Карательная психиатрия в России: назад в СССР? 2026</t>
-  </si>
-  <si>
     <t>Кенгирское восстание заключённых - Википедия 2026</t>
   </si>
   <si>
@@ -3833,15 +3854,24 @@
     <t>MITRE ATT&amp;CK®. (2023). 2016 Ukraine Electric Power Attack | MITRE ATT&amp;CK®.</t>
   </si>
   <si>
+    <t>Вікіпедія. (2026). Іван Мазепа — Вікіпедія.</t>
+  </si>
+  <si>
     <t>Вікіпедія. (2026). Історія України — Вікіпедія.</t>
   </si>
   <si>
+    <t>Вікіпедія. (2026). Анексія Київської митрополії Московським патріархатом — Вікіпедія.</t>
+  </si>
+  <si>
     <t>Михаил Зыгарь. (2023). Война и наказание: Как Россия уничтожала Украину.</t>
   </si>
   <si>
     <t>Википедия. (2026). Всесоюзний референдум про збереження СРСР — Вікіпедія.</t>
   </si>
   <si>
+    <t>Obozrevatel. (2026). Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу.</t>
+  </si>
+  <si>
     <t>Вікіпедія. (2026). Дезінформація під час російсько-української війни — Вікіпедія.</t>
   </si>
   <si>
@@ -3857,9 +3887,6 @@
     <t>Татьяна Таирова-Яковлева. (2011). ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА».</t>
   </si>
   <si>
-    <t>Riddle Russia. (2026). Карательная психиатрия в России: назад в СССР?.</t>
-  </si>
-  <si>
     <t>Википедия. (2026). Кенгирское восстание заключённых - Википедия.</t>
   </si>
   <si>
@@ -3950,12 +3977,21 @@
     <t>https://attack.mitre.org/campaigns/C0025/</t>
   </si>
   <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%2586%25D0%25B2%25D0%25B0%25D0%25BD_%25D0%259C%25D0%25B0%25D0%25B7%25D0%25B5%25D0%25BF%25D0%25B0</t>
+  </si>
+  <si>
     <t>https://uk.wikipedia.org/wiki/%25D0%2586%25D1%2581%25D1%2582%25D0%25BE%25D1%2580%25D1%2596%25D1%258F_%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D0%25B8</t>
   </si>
   <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%2590%25D0%25BD%25D0%25B5%25D0%25BA%25D1%2581%25D1%2596%25D1%258F_%25D0%259A%25D0%25B8%25D1%2597%25D0%25B2%25D1%2581%25D1%258C%25D0%25BA%25D0%25BE%25D1%2597_%25D0%25BC%25D0%25B8%25D1%2582%25D1%2580%25D0%25BE%25D0%25BF%25D0%25BE%25D0%25BB%25D1%2596%25D1%2597_%25D0%259C%25D0%25BE%25D1%2581%25D0%25BA%25D0%25BE%25D0%25B2%25D1%2581%25D1%258C%25D0%25BA%25D0%25B8%25D0%25BC_%25D0%25BF%25D0%25B0%25D1%2582%25D1%2580%25D1%2596%25D0%25B0%25D1%2580%25D1%2585%25D0%25B0%25D1%2582%25D0%25BE%25D0%25BC</t>
+  </si>
+  <si>
     <t>https://uk.wikipedia.org/wiki/%25D0%2592%25D1%2581%25D0%25B5%25D1%2581%25D0%25BE%25D1%258E%25D0%25B7%25D0%25BD%25D0%25B8%25D0%25B9_%25D1%2580%25D0%25B5%25D1%2584%25D0%25B5%25D1%2580%25D0%25B5%25D0%25BD%25D0%25B4%25D1%2583%25D0%25BC_%25D0%25BF%25D1%2580%25D0%25BE_%25D0%25B7%25D0%25B1%25D0%25B5%25D1%2580%25D0%25B5%25D0%25B6%25D0%25B5%25D0%25BD%25D0%25BD%25D1%258F_%25D0%25A1%25D0%25A0%25D0%25A1%25D0%25A0</t>
   </si>
   <si>
+    <t>https://www.obozrevatel.com/novosti-obschestvo/dvojnoe-prestuplenie-sssr-kak-sovetyi-skryivali-chernobyilskuyu-katastrofu.htm</t>
+  </si>
+  <si>
     <t>https://uk.wikipedia.org/wiki/%25D0%25A0%25D0%25BE%25D1%2581%25D1%2596%25D0%25B9%25D1%2581%25D1%258C%25D0%25BA%25D0%25B0_%25D0%25B4%25D0%25B5%25D0%25B7%25D1%2596%25D0%25BD%25D1%2584%25D0%25BE%25D1%2580%25D0%25BC%25D0%25B0%25D1%2586%25D1%2596%25D1%258F_%25D0%25BF%25D1%2596%25D0%25B4_%25D1%2587%25D0%25B0%25D1%2581_%25D1%2580%25D0%25BE%25D1%2581%25D1%2596%25D0%25B9%25D1%2581%25D1%258C%25D0%25BA%25D0%25BE-%25D1%2583%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D1%2581%25D1%258C%25D0%25BA%25D0%25BE%25D1%2597_%25D0%25B2%25D1%2596%25D0%25B9%25D0%25BD%25D0%25B8</t>
   </si>
   <si>
@@ -3966,9 +4002,6 @@
   </si>
   <si>
     <t>https://uk.wikipedia.org/wiki/%25D0%2597%25D0%25B0%25D0%25BF%25D0%25BE%25D1%2580%25D0%25BE%25D0%25B7%25D1%258C%25D0%25BA%25D0%25B0_%25D0%25A1%25D1%2596%25D1%2587</t>
-  </si>
-  <si>
-    <t>https://ridl.io/ru/karatelnaja-psihiatrija-v-rossii-nazad-v-sssr/</t>
   </si>
   <si>
     <t>https://ru.wikipedia.org/wiki/%25D0%259A%25D0%25B5%25D0%25BD%25D0%25B3%25D0%25B8%25D1%2580%25D1%2581%25D0%25BA%25D0%25BE%25D0%25B5_%25D0%25B2%25D0%25BE%25D1%2581%25D1%2581%25D1%2582%25D0%25B0%25D0%25BD%25D0%25B8%25D0%25B5_%25D0%25B7%25D0%25B0%25D0%25BA%25D0%25BB%25D1%258E%25D1%2587%25D1%2591%25D0%25BD%25D0%25BD%25D1%258B%25D1%2585</t>
@@ -13878,7 +13911,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M103"/>
+  <dimension ref="A1:M104"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -13927,16 +13960,16 @@
         <v>767</v>
       </c>
       <c r="B2" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C2" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="D2" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E2" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F2" t="s">
         <v>11</v>
@@ -13951,10 +13984,10 @@
         <v>59</v>
       </c>
       <c r="J2" t="s">
-        <v>1072</v>
+        <v>1075</v>
       </c>
       <c r="K2" t="s">
-        <v>1126</v>
+        <v>1130</v>
       </c>
       <c r="L2" t="s">
         <v>40</v>
@@ -13968,16 +14001,16 @@
         <v>768</v>
       </c>
       <c r="B3" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="C3" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="D3" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E3" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F3" t="s">
         <v>14</v>
@@ -13992,10 +14025,10 @@
         <v>59</v>
       </c>
       <c r="J3" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
       <c r="K3" t="s">
-        <v>1127</v>
+        <v>1131</v>
       </c>
       <c r="L3" t="s">
         <v>40</v>
@@ -14009,16 +14042,16 @@
         <v>769</v>
       </c>
       <c r="B4" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="C4" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="D4" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E4" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F4" t="s">
         <v>12</v>
@@ -14033,10 +14066,10 @@
         <v>59</v>
       </c>
       <c r="J4" t="s">
-        <v>1074</v>
+        <v>1077</v>
       </c>
       <c r="K4" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="L4" t="s">
         <v>40</v>
@@ -14050,16 +14083,16 @@
         <v>770</v>
       </c>
       <c r="B5" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="C5" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="D5" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E5" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F5" t="s">
         <v>11</v>
@@ -14074,10 +14107,10 @@
         <v>59</v>
       </c>
       <c r="J5" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
       <c r="K5" t="s">
-        <v>1129</v>
+        <v>1133</v>
       </c>
       <c r="L5" t="s">
         <v>40</v>
@@ -14091,16 +14124,16 @@
         <v>771</v>
       </c>
       <c r="B6" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C6" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="D6" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E6" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F6" t="s">
         <v>11</v>
@@ -14115,10 +14148,10 @@
         <v>59</v>
       </c>
       <c r="J6" t="s">
-        <v>1076</v>
+        <v>1079</v>
       </c>
       <c r="K6" t="s">
-        <v>1130</v>
+        <v>1134</v>
       </c>
       <c r="L6" t="s">
         <v>40</v>
@@ -14132,16 +14165,16 @@
         <v>772</v>
       </c>
       <c r="B7" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="C7" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="D7" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E7" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F7" t="s">
         <v>11</v>
@@ -14156,10 +14189,10 @@
         <v>59</v>
       </c>
       <c r="J7" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="K7" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="L7" t="s">
         <v>40</v>
@@ -14173,16 +14206,16 @@
         <v>773</v>
       </c>
       <c r="B8" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C8" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="D8" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E8" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F8" t="s">
         <v>14</v>
@@ -14200,7 +14233,7 @@
         <v>553</v>
       </c>
       <c r="K8" t="s">
-        <v>1132</v>
+        <v>1136</v>
       </c>
       <c r="L8" t="s">
         <v>40</v>
@@ -14214,16 +14247,16 @@
         <v>774</v>
       </c>
       <c r="B9" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="C9" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="D9" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E9" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F9" t="s">
         <v>12</v>
@@ -14238,10 +14271,10 @@
         <v>59</v>
       </c>
       <c r="J9" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
       <c r="K9" t="s">
-        <v>1133</v>
+        <v>1137</v>
       </c>
       <c r="L9" t="s">
         <v>40</v>
@@ -14255,16 +14288,16 @@
         <v>775</v>
       </c>
       <c r="B10" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="C10" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="D10" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E10" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F10" t="s">
         <v>12</v>
@@ -14282,7 +14315,7 @@
         <v>489</v>
       </c>
       <c r="K10" t="s">
-        <v>1134</v>
+        <v>1138</v>
       </c>
       <c r="L10" t="s">
         <v>40</v>
@@ -14296,16 +14329,16 @@
         <v>776</v>
       </c>
       <c r="B11" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="C11" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="D11" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E11" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F11" t="s">
         <v>11</v>
@@ -14323,7 +14356,7 @@
         <v>445</v>
       </c>
       <c r="K11" t="s">
-        <v>1135</v>
+        <v>1139</v>
       </c>
       <c r="L11" t="s">
         <v>40</v>
@@ -14337,16 +14370,16 @@
         <v>777</v>
       </c>
       <c r="B12" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="C12" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="D12" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E12" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F12" t="s">
         <v>13</v>
@@ -14364,7 +14397,7 @@
         <v>123</v>
       </c>
       <c r="K12" t="s">
-        <v>1136</v>
+        <v>1140</v>
       </c>
       <c r="L12" t="s">
         <v>40</v>
@@ -14378,16 +14411,16 @@
         <v>778</v>
       </c>
       <c r="B13" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="C13" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="D13" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E13" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F13" t="s">
         <v>12</v>
@@ -14402,10 +14435,10 @@
         <v>59</v>
       </c>
       <c r="J13" t="s">
-        <v>1079</v>
+        <v>1082</v>
       </c>
       <c r="K13" t="s">
-        <v>1137</v>
+        <v>1141</v>
       </c>
       <c r="L13" t="s">
         <v>40</v>
@@ -14419,16 +14452,16 @@
         <v>779</v>
       </c>
       <c r="B14" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="C14" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="D14" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E14" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F14" t="s">
         <v>13</v>
@@ -14443,10 +14476,10 @@
         <v>59</v>
       </c>
       <c r="J14" t="s">
-        <v>1080</v>
+        <v>1083</v>
       </c>
       <c r="K14" t="s">
-        <v>1138</v>
+        <v>1142</v>
       </c>
       <c r="L14" t="s">
         <v>40</v>
@@ -14460,16 +14493,16 @@
         <v>780</v>
       </c>
       <c r="B15" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="C15" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="D15" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E15" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F15" t="s">
         <v>12</v>
@@ -14487,7 +14520,7 @@
         <v>466</v>
       </c>
       <c r="K15" t="s">
-        <v>1139</v>
+        <v>1143</v>
       </c>
       <c r="L15" t="s">
         <v>40</v>
@@ -14501,16 +14534,16 @@
         <v>781</v>
       </c>
       <c r="B16" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="C16" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="D16" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E16" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F16" t="s">
         <v>12</v>
@@ -14525,10 +14558,10 @@
         <v>59</v>
       </c>
       <c r="J16" t="s">
-        <v>1081</v>
+        <v>1084</v>
       </c>
       <c r="K16" t="s">
-        <v>1140</v>
+        <v>1144</v>
       </c>
       <c r="L16" t="s">
         <v>40</v>
@@ -14542,16 +14575,16 @@
         <v>782</v>
       </c>
       <c r="B17" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="C17" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="D17" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E17" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F17" t="s">
         <v>12</v>
@@ -14566,10 +14599,10 @@
         <v>59</v>
       </c>
       <c r="J17" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
       <c r="K17" t="s">
-        <v>1141</v>
+        <v>1145</v>
       </c>
       <c r="L17" t="s">
         <v>40</v>
@@ -14583,16 +14616,16 @@
         <v>783</v>
       </c>
       <c r="B18" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="C18" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="D18" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E18" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F18" t="s">
         <v>10</v>
@@ -14610,7 +14643,7 @@
         <v>103</v>
       </c>
       <c r="K18" t="s">
-        <v>1142</v>
+        <v>1146</v>
       </c>
       <c r="L18" t="s">
         <v>40</v>
@@ -14624,16 +14657,16 @@
         <v>783</v>
       </c>
       <c r="B19" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="C19" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="D19" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E19" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F19" t="s">
         <v>15</v>
@@ -14648,10 +14681,10 @@
         <v>59</v>
       </c>
       <c r="J19" t="s">
-        <v>1083</v>
+        <v>1086</v>
       </c>
       <c r="K19" t="s">
-        <v>1143</v>
+        <v>1147</v>
       </c>
       <c r="L19" t="s">
         <v>40</v>
@@ -14665,16 +14698,16 @@
         <v>784</v>
       </c>
       <c r="B20" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="C20" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="D20" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E20" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F20" t="s">
         <v>12</v>
@@ -14689,10 +14722,10 @@
         <v>59</v>
       </c>
       <c r="J20" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
       <c r="K20" t="s">
-        <v>1144</v>
+        <v>1148</v>
       </c>
       <c r="L20" t="s">
         <v>40</v>
@@ -14706,16 +14739,16 @@
         <v>785</v>
       </c>
       <c r="B21" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="C21" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="D21" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E21" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F21" t="s">
         <v>13</v>
@@ -14733,7 +14766,7 @@
         <v>525</v>
       </c>
       <c r="K21" t="s">
-        <v>1145</v>
+        <v>1149</v>
       </c>
       <c r="L21" t="s">
         <v>40</v>
@@ -14747,16 +14780,16 @@
         <v>786</v>
       </c>
       <c r="B22" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="C22" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="D22" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E22" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F22" t="s">
         <v>14</v>
@@ -14774,7 +14807,7 @@
         <v>530</v>
       </c>
       <c r="K22" t="s">
-        <v>1146</v>
+        <v>1150</v>
       </c>
       <c r="L22" t="s">
         <v>40</v>
@@ -14788,16 +14821,16 @@
         <v>787</v>
       </c>
       <c r="B23" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="C23" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="D23" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E23" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F23" t="s">
         <v>13</v>
@@ -14815,7 +14848,7 @@
         <v>514</v>
       </c>
       <c r="K23" t="s">
-        <v>1147</v>
+        <v>1151</v>
       </c>
       <c r="L23" t="s">
         <v>40</v>
@@ -14829,16 +14862,16 @@
         <v>788</v>
       </c>
       <c r="B24" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C24" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="D24" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E24" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F24" t="s">
         <v>13</v>
@@ -14856,7 +14889,7 @@
         <v>120</v>
       </c>
       <c r="K24" t="s">
-        <v>1148</v>
+        <v>1152</v>
       </c>
       <c r="L24" t="s">
         <v>40</v>
@@ -14870,16 +14903,16 @@
         <v>789</v>
       </c>
       <c r="B25" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C25" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="D25" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E25" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F25" t="s">
         <v>12</v>
@@ -14894,10 +14927,10 @@
         <v>59</v>
       </c>
       <c r="J25" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
       <c r="K25" t="s">
-        <v>1149</v>
+        <v>1153</v>
       </c>
       <c r="L25" t="s">
         <v>40</v>
@@ -14911,16 +14944,16 @@
         <v>790</v>
       </c>
       <c r="B26" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C26" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="D26" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E26" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F26" t="s">
         <v>11</v>
@@ -14938,7 +14971,7 @@
         <v>106</v>
       </c>
       <c r="K26" t="s">
-        <v>1150</v>
+        <v>1154</v>
       </c>
       <c r="L26" t="s">
         <v>40</v>
@@ -14952,16 +14985,16 @@
         <v>791</v>
       </c>
       <c r="B27" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C27" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="D27" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E27" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F27" t="s">
         <v>12</v>
@@ -14976,10 +15009,10 @@
         <v>59</v>
       </c>
       <c r="J27" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
       <c r="K27" t="s">
-        <v>1151</v>
+        <v>1155</v>
       </c>
       <c r="L27" t="s">
         <v>40</v>
@@ -14993,16 +15026,16 @@
         <v>792</v>
       </c>
       <c r="B28" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="C28" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="D28" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E28" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F28" t="s">
         <v>14</v>
@@ -15017,10 +15050,10 @@
         <v>59</v>
       </c>
       <c r="J28" t="s">
-        <v>1087</v>
+        <v>1090</v>
       </c>
       <c r="K28" t="s">
-        <v>1152</v>
+        <v>1156</v>
       </c>
       <c r="L28" t="s">
         <v>40</v>
@@ -15034,16 +15067,16 @@
         <v>793</v>
       </c>
       <c r="B29" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="C29" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="D29" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E29" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F29" t="s">
         <v>13</v>
@@ -15061,7 +15094,7 @@
         <v>507</v>
       </c>
       <c r="K29" t="s">
-        <v>1153</v>
+        <v>1157</v>
       </c>
       <c r="L29" t="s">
         <v>40</v>
@@ -15075,16 +15108,16 @@
         <v>794</v>
       </c>
       <c r="B30" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="C30" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="D30" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E30" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F30" t="s">
         <v>11</v>
@@ -15102,7 +15135,7 @@
         <v>438</v>
       </c>
       <c r="K30" t="s">
-        <v>1154</v>
+        <v>1158</v>
       </c>
       <c r="L30" t="s">
         <v>40</v>
@@ -15116,16 +15149,16 @@
         <v>795</v>
       </c>
       <c r="B31" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="C31" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="D31" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E31" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F31" t="s">
         <v>15</v>
@@ -15143,7 +15176,7 @@
         <v>576</v>
       </c>
       <c r="K31" t="s">
-        <v>1155</v>
+        <v>1159</v>
       </c>
       <c r="L31" t="s">
         <v>40</v>
@@ -15157,16 +15190,16 @@
         <v>796</v>
       </c>
       <c r="B32" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="C32" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="D32" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E32" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F32" t="s">
         <v>13</v>
@@ -15181,10 +15214,10 @@
         <v>59</v>
       </c>
       <c r="J32" t="s">
-        <v>1088</v>
+        <v>1091</v>
       </c>
       <c r="K32" t="s">
-        <v>1156</v>
+        <v>1160</v>
       </c>
       <c r="L32" t="s">
         <v>40</v>
@@ -15198,16 +15231,16 @@
         <v>797</v>
       </c>
       <c r="B33" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="C33" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="D33" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E33" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F33" t="s">
         <v>11</v>
@@ -15225,7 +15258,7 @@
         <v>442</v>
       </c>
       <c r="K33" t="s">
-        <v>1157</v>
+        <v>1161</v>
       </c>
       <c r="L33" t="s">
         <v>40</v>
@@ -15239,16 +15272,16 @@
         <v>798</v>
       </c>
       <c r="B34" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="C34" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="D34" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E34" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F34" t="s">
         <v>14</v>
@@ -15266,7 +15299,7 @@
         <v>534</v>
       </c>
       <c r="K34" t="s">
-        <v>1158</v>
+        <v>1162</v>
       </c>
       <c r="L34" t="s">
         <v>40</v>
@@ -15280,16 +15313,16 @@
         <v>799</v>
       </c>
       <c r="B35" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="C35" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="D35" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E35" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F35" t="s">
         <v>15</v>
@@ -15307,7 +15340,7 @@
         <v>571</v>
       </c>
       <c r="K35" t="s">
-        <v>1159</v>
+        <v>1163</v>
       </c>
       <c r="L35" t="s">
         <v>40</v>
@@ -15321,16 +15354,16 @@
         <v>800</v>
       </c>
       <c r="B36" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="C36" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="D36" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E36" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F36" t="s">
         <v>13</v>
@@ -15348,7 +15381,7 @@
         <v>493</v>
       </c>
       <c r="K36" t="s">
-        <v>1160</v>
+        <v>1164</v>
       </c>
       <c r="L36" t="s">
         <v>40</v>
@@ -15362,16 +15395,16 @@
         <v>801</v>
       </c>
       <c r="B37" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="C37" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="D37" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E37" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F37" t="s">
         <v>11</v>
@@ -15386,10 +15419,10 @@
         <v>59</v>
       </c>
       <c r="J37" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
       <c r="K37" t="s">
-        <v>1161</v>
+        <v>1165</v>
       </c>
       <c r="L37" t="s">
         <v>40</v>
@@ -15403,16 +15436,16 @@
         <v>802</v>
       </c>
       <c r="B38" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="C38" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="D38" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E38" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F38" t="s">
         <v>11</v>
@@ -15427,10 +15460,10 @@
         <v>59</v>
       </c>
       <c r="J38" t="s">
-        <v>1090</v>
+        <v>1093</v>
       </c>
       <c r="K38" t="s">
-        <v>1162</v>
+        <v>1166</v>
       </c>
       <c r="L38" t="s">
         <v>40</v>
@@ -15444,16 +15477,16 @@
         <v>803</v>
       </c>
       <c r="B39" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="C39" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="D39" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E39" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F39" t="s">
         <v>12</v>
@@ -15468,10 +15501,10 @@
         <v>59</v>
       </c>
       <c r="J39" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
       <c r="K39" t="s">
-        <v>1163</v>
+        <v>1167</v>
       </c>
       <c r="L39" t="s">
         <v>40</v>
@@ -15485,16 +15518,16 @@
         <v>804</v>
       </c>
       <c r="B40" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="C40" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="D40" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E40" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F40" t="s">
         <v>14</v>
@@ -15509,10 +15542,10 @@
         <v>59</v>
       </c>
       <c r="J40" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
       <c r="K40" t="s">
-        <v>1164</v>
+        <v>1168</v>
       </c>
       <c r="L40" t="s">
         <v>40</v>
@@ -15526,16 +15559,16 @@
         <v>805</v>
       </c>
       <c r="B41" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="C41" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="D41" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E41" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F41" t="s">
         <v>11</v>
@@ -15553,7 +15586,7 @@
         <v>435</v>
       </c>
       <c r="K41" t="s">
-        <v>1165</v>
+        <v>1169</v>
       </c>
       <c r="L41" t="s">
         <v>40</v>
@@ -15567,16 +15600,16 @@
         <v>806</v>
       </c>
       <c r="B42" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="C42" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="D42" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E42" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F42" t="s">
         <v>11</v>
@@ -15591,10 +15624,10 @@
         <v>59</v>
       </c>
       <c r="J42" t="s">
-        <v>1093</v>
+        <v>1096</v>
       </c>
       <c r="K42" t="s">
-        <v>1166</v>
+        <v>1170</v>
       </c>
       <c r="L42" t="s">
         <v>40</v>
@@ -15608,16 +15641,16 @@
         <v>807</v>
       </c>
       <c r="B43" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="C43" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="D43" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E43" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F43" t="s">
         <v>12</v>
@@ -15635,7 +15668,7 @@
         <v>463</v>
       </c>
       <c r="K43" t="s">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="L43" t="s">
         <v>40</v>
@@ -15649,16 +15682,16 @@
         <v>808</v>
       </c>
       <c r="B44" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="C44" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="D44" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E44" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F44" t="s">
         <v>12</v>
@@ -15673,10 +15706,10 @@
         <v>59</v>
       </c>
       <c r="J44" t="s">
-        <v>1094</v>
+        <v>1097</v>
       </c>
       <c r="K44" t="s">
-        <v>1168</v>
+        <v>1172</v>
       </c>
       <c r="L44" t="s">
         <v>40</v>
@@ -15690,16 +15723,16 @@
         <v>809</v>
       </c>
       <c r="B45" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="C45" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="D45" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E45" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F45" t="s">
         <v>11</v>
@@ -15714,10 +15747,10 @@
         <v>59</v>
       </c>
       <c r="J45" t="s">
-        <v>1095</v>
+        <v>1098</v>
       </c>
       <c r="K45" t="s">
-        <v>1169</v>
+        <v>1173</v>
       </c>
       <c r="L45" t="s">
         <v>40</v>
@@ -15731,16 +15764,16 @@
         <v>810</v>
       </c>
       <c r="B46" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="C46" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="D46" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E46" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F46" t="s">
         <v>14</v>
@@ -15755,10 +15788,10 @@
         <v>59</v>
       </c>
       <c r="J46" t="s">
-        <v>1096</v>
+        <v>1099</v>
       </c>
       <c r="K46" t="s">
-        <v>1170</v>
+        <v>1174</v>
       </c>
       <c r="L46" t="s">
         <v>40</v>
@@ -15772,16 +15805,16 @@
         <v>811</v>
       </c>
       <c r="B47" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="C47" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="D47" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E47" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F47" t="s">
         <v>12</v>
@@ -15796,10 +15829,10 @@
         <v>59</v>
       </c>
       <c r="J47" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
       <c r="K47" t="s">
-        <v>1171</v>
+        <v>1175</v>
       </c>
       <c r="L47" t="s">
         <v>40</v>
@@ -15813,16 +15846,16 @@
         <v>812</v>
       </c>
       <c r="B48" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="C48" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="D48" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E48" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F48" t="s">
         <v>11</v>
@@ -15837,10 +15870,10 @@
         <v>59</v>
       </c>
       <c r="J48" t="s">
-        <v>1098</v>
+        <v>1101</v>
       </c>
       <c r="K48" t="s">
-        <v>1172</v>
+        <v>1176</v>
       </c>
       <c r="L48" t="s">
         <v>40</v>
@@ -15854,16 +15887,16 @@
         <v>813</v>
       </c>
       <c r="B49" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C49" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="D49" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E49" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F49" t="s">
         <v>11</v>
@@ -15881,7 +15914,7 @@
         <v>108</v>
       </c>
       <c r="K49" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="L49" t="s">
         <v>40</v>
@@ -15895,16 +15928,16 @@
         <v>814</v>
       </c>
       <c r="B50" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="C50" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="D50" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E50" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F50" t="s">
         <v>14</v>
@@ -15922,7 +15955,7 @@
         <v>561</v>
       </c>
       <c r="K50" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="L50" t="s">
         <v>40</v>
@@ -15936,16 +15969,16 @@
         <v>815</v>
       </c>
       <c r="B51" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="C51" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="D51" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E51" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F51" t="s">
         <v>14</v>
@@ -15960,10 +15993,10 @@
         <v>59</v>
       </c>
       <c r="J51" t="s">
-        <v>1099</v>
+        <v>1102</v>
       </c>
       <c r="K51" t="s">
-        <v>1175</v>
+        <v>1179</v>
       </c>
       <c r="L51" t="s">
         <v>40</v>
@@ -15977,16 +16010,16 @@
         <v>816</v>
       </c>
       <c r="B52" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="C52" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="D52" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E52" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F52" t="s">
         <v>13</v>
@@ -16004,7 +16037,7 @@
         <v>122</v>
       </c>
       <c r="K52" t="s">
-        <v>1176</v>
+        <v>1180</v>
       </c>
       <c r="L52" t="s">
         <v>40</v>
@@ -16018,16 +16051,16 @@
         <v>817</v>
       </c>
       <c r="B53" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="C53" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="D53" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E53" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F53" t="s">
         <v>12</v>
@@ -16042,10 +16075,10 @@
         <v>59</v>
       </c>
       <c r="J53" t="s">
-        <v>1100</v>
+        <v>1103</v>
       </c>
       <c r="K53" t="s">
-        <v>1177</v>
+        <v>1181</v>
       </c>
       <c r="L53" t="s">
         <v>40</v>
@@ -16059,16 +16092,16 @@
         <v>818</v>
       </c>
       <c r="B54" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="C54" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="D54" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E54" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F54" t="s">
         <v>12</v>
@@ -16086,7 +16119,7 @@
         <v>455</v>
       </c>
       <c r="K54" t="s">
-        <v>1178</v>
+        <v>1182</v>
       </c>
       <c r="L54" t="s">
         <v>40</v>
@@ -16100,16 +16133,16 @@
         <v>819</v>
       </c>
       <c r="B55" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="C55" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="D55" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E55" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F55" t="s">
         <v>14</v>
@@ -16124,10 +16157,10 @@
         <v>59</v>
       </c>
       <c r="J55" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="K55" t="s">
-        <v>1179</v>
+        <v>1183</v>
       </c>
       <c r="L55" t="s">
         <v>40</v>
@@ -16141,16 +16174,16 @@
         <v>820</v>
       </c>
       <c r="B56" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="C56" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="D56" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E56" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F56" t="s">
         <v>12</v>
@@ -16165,10 +16198,10 @@
         <v>59</v>
       </c>
       <c r="J56" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
       <c r="K56" t="s">
-        <v>1180</v>
+        <v>1184</v>
       </c>
       <c r="L56" t="s">
         <v>40</v>
@@ -16182,16 +16215,16 @@
         <v>821</v>
       </c>
       <c r="B57" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="C57" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="D57" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E57" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F57" t="s">
         <v>11</v>
@@ -16209,7 +16242,7 @@
         <v>428</v>
       </c>
       <c r="K57" t="s">
-        <v>1181</v>
+        <v>1185</v>
       </c>
       <c r="L57" t="s">
         <v>40</v>
@@ -16223,16 +16256,16 @@
         <v>822</v>
       </c>
       <c r="B58" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="C58" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="D58" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E58" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F58" t="s">
         <v>11</v>
@@ -16250,7 +16283,7 @@
         <v>451</v>
       </c>
       <c r="K58" t="s">
-        <v>1182</v>
+        <v>1186</v>
       </c>
       <c r="L58" t="s">
         <v>40</v>
@@ -16264,16 +16297,16 @@
         <v>823</v>
       </c>
       <c r="B59" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="C59" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="D59" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E59" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F59" t="s">
         <v>11</v>
@@ -16291,7 +16324,7 @@
         <v>436</v>
       </c>
       <c r="K59" t="s">
-        <v>1183</v>
+        <v>1187</v>
       </c>
       <c r="L59" t="s">
         <v>40</v>
@@ -16305,16 +16338,16 @@
         <v>824</v>
       </c>
       <c r="B60" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="C60" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="D60" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E60" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F60" t="s">
         <v>12</v>
@@ -16332,7 +16365,7 @@
         <v>457</v>
       </c>
       <c r="K60" t="s">
-        <v>1184</v>
+        <v>1188</v>
       </c>
       <c r="L60" t="s">
         <v>40</v>
@@ -16346,16 +16379,16 @@
         <v>825</v>
       </c>
       <c r="B61" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="C61" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="D61" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E61" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F61" t="s">
         <v>12</v>
@@ -16370,10 +16403,10 @@
         <v>59</v>
       </c>
       <c r="J61" t="s">
-        <v>1103</v>
+        <v>1106</v>
       </c>
       <c r="K61" t="s">
-        <v>1185</v>
+        <v>1189</v>
       </c>
       <c r="L61" t="s">
         <v>40</v>
@@ -16387,16 +16420,16 @@
         <v>826</v>
       </c>
       <c r="B62" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="C62" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="D62" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E62" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F62" t="s">
         <v>12</v>
@@ -16411,10 +16444,10 @@
         <v>59</v>
       </c>
       <c r="J62" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
       <c r="K62" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="L62" t="s">
         <v>40</v>
@@ -16428,16 +16461,16 @@
         <v>827</v>
       </c>
       <c r="B63" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="C63" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="D63" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E63" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F63" t="s">
         <v>14</v>
@@ -16452,10 +16485,10 @@
         <v>59</v>
       </c>
       <c r="J63" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="K63" t="s">
-        <v>1187</v>
+        <v>1191</v>
       </c>
       <c r="L63" t="s">
         <v>40</v>
@@ -16469,16 +16502,16 @@
         <v>828</v>
       </c>
       <c r="B64" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="C64" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="D64" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E64" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F64" t="s">
         <v>12</v>
@@ -16493,10 +16526,10 @@
         <v>59</v>
       </c>
       <c r="J64" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="K64" t="s">
-        <v>1188</v>
+        <v>1192</v>
       </c>
       <c r="L64" t="s">
         <v>40</v>
@@ -16510,16 +16543,16 @@
         <v>829</v>
       </c>
       <c r="B65" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="C65" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="D65" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E65" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F65" t="s">
         <v>14</v>
@@ -16537,7 +16570,7 @@
         <v>538</v>
       </c>
       <c r="K65" t="s">
-        <v>1189</v>
+        <v>1193</v>
       </c>
       <c r="L65" t="s">
         <v>40</v>
@@ -16551,34 +16584,34 @@
         <v>830</v>
       </c>
       <c r="B66" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="C66" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="D66" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E66" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F66" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G66" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H66" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I66" t="s">
         <v>59</v>
       </c>
       <c r="J66" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
       <c r="K66" t="s">
-        <v>1190</v>
+        <v>1194</v>
       </c>
       <c r="L66" t="s">
         <v>40</v>
@@ -16592,34 +16625,34 @@
         <v>831</v>
       </c>
       <c r="B67" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C67" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="D67" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E67" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F67" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G67" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H67" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I67" t="s">
         <v>59</v>
       </c>
       <c r="J67" t="s">
-        <v>547</v>
+        <v>1111</v>
       </c>
       <c r="K67" t="s">
-        <v>1191</v>
+        <v>1195</v>
       </c>
       <c r="L67" t="s">
         <v>40</v>
@@ -16633,16 +16666,16 @@
         <v>832</v>
       </c>
       <c r="B68" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="C68" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="D68" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E68" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F68" t="s">
         <v>14</v>
@@ -16657,10 +16690,10 @@
         <v>59</v>
       </c>
       <c r="J68" t="s">
-        <v>1108</v>
+        <v>547</v>
       </c>
       <c r="K68" t="s">
-        <v>1192</v>
+        <v>1196</v>
       </c>
       <c r="L68" t="s">
         <v>40</v>
@@ -16674,34 +16707,34 @@
         <v>833</v>
       </c>
       <c r="B69" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="C69" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="D69" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E69" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F69" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G69" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H69" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I69" t="s">
         <v>59</v>
       </c>
       <c r="J69" t="s">
-        <v>104</v>
+        <v>1112</v>
       </c>
       <c r="K69" t="s">
-        <v>1193</v>
+        <v>1197</v>
       </c>
       <c r="L69" t="s">
         <v>40</v>
@@ -16715,34 +16748,34 @@
         <v>834</v>
       </c>
       <c r="B70" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="C70" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="D70" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E70" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F70" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G70" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H70" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I70" t="s">
         <v>59</v>
       </c>
       <c r="J70" t="s">
-        <v>1109</v>
+        <v>104</v>
       </c>
       <c r="K70" t="s">
-        <v>1194</v>
+        <v>1198</v>
       </c>
       <c r="L70" t="s">
         <v>40</v>
@@ -16756,34 +16789,34 @@
         <v>835</v>
       </c>
       <c r="B71" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="C71" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="D71" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E71" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F71" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G71" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H71" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="I71" t="s">
         <v>59</v>
       </c>
       <c r="J71" t="s">
-        <v>130</v>
+        <v>1113</v>
       </c>
       <c r="K71" t="s">
-        <v>1195</v>
+        <v>1199</v>
       </c>
       <c r="L71" t="s">
         <v>40</v>
@@ -16797,34 +16830,34 @@
         <v>836</v>
       </c>
       <c r="B72" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="C72" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="D72" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E72" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F72" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H72" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I72" t="s">
         <v>59</v>
       </c>
       <c r="J72" t="s">
-        <v>512</v>
+        <v>130</v>
       </c>
       <c r="K72" t="s">
-        <v>1196</v>
+        <v>1200</v>
       </c>
       <c r="L72" t="s">
         <v>40</v>
@@ -16838,16 +16871,16 @@
         <v>837</v>
       </c>
       <c r="B73" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="C73" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="D73" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E73" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F73" t="s">
         <v>13</v>
@@ -16862,10 +16895,10 @@
         <v>59</v>
       </c>
       <c r="J73" t="s">
-        <v>1110</v>
+        <v>512</v>
       </c>
       <c r="K73" t="s">
-        <v>1197</v>
+        <v>1201</v>
       </c>
       <c r="L73" t="s">
         <v>40</v>
@@ -16879,34 +16912,34 @@
         <v>838</v>
       </c>
       <c r="B74" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="C74" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="D74" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E74" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F74" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G74" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H74" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I74" t="s">
         <v>59</v>
       </c>
       <c r="J74" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="K74" t="s">
-        <v>1198</v>
+        <v>1202</v>
       </c>
       <c r="L74" t="s">
         <v>40</v>
@@ -16920,34 +16953,34 @@
         <v>839</v>
       </c>
       <c r="B75" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="C75" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="D75" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E75" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F75" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G75" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H75" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I75" t="s">
         <v>59</v>
       </c>
       <c r="J75" t="s">
-        <v>1112</v>
+        <v>1115</v>
       </c>
       <c r="K75" t="s">
-        <v>1199</v>
+        <v>1203</v>
       </c>
       <c r="L75" t="s">
         <v>40</v>
@@ -16961,34 +16994,34 @@
         <v>840</v>
       </c>
       <c r="B76" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="C76" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="D76" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E76" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F76" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G76" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H76" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I76" t="s">
         <v>59</v>
       </c>
       <c r="J76" t="s">
-        <v>115</v>
+        <v>1116</v>
       </c>
       <c r="K76" t="s">
-        <v>1200</v>
+        <v>1204</v>
       </c>
       <c r="L76" t="s">
         <v>40</v>
@@ -17002,16 +17035,16 @@
         <v>841</v>
       </c>
       <c r="B77" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="C77" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="D77" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E77" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F77" t="s">
         <v>12</v>
@@ -17026,10 +17059,10 @@
         <v>59</v>
       </c>
       <c r="J77" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="K77" t="s">
-        <v>1201</v>
+        <v>1205</v>
       </c>
       <c r="L77" t="s">
         <v>40</v>
@@ -17043,16 +17076,16 @@
         <v>842</v>
       </c>
       <c r="B78" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="C78" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="D78" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E78" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F78" t="s">
         <v>12</v>
@@ -17067,10 +17100,10 @@
         <v>59</v>
       </c>
       <c r="J78" t="s">
-        <v>1113</v>
+        <v>113</v>
       </c>
       <c r="K78" t="s">
-        <v>1202</v>
+        <v>1206</v>
       </c>
       <c r="L78" t="s">
         <v>40</v>
@@ -17084,16 +17117,16 @@
         <v>843</v>
       </c>
       <c r="B79" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="C79" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="D79" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E79" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F79" t="s">
         <v>12</v>
@@ -17108,10 +17141,10 @@
         <v>59</v>
       </c>
       <c r="J79" t="s">
-        <v>1114</v>
+        <v>1117</v>
       </c>
       <c r="K79" t="s">
-        <v>1203</v>
+        <v>1207</v>
       </c>
       <c r="L79" t="s">
         <v>40</v>
@@ -17125,16 +17158,16 @@
         <v>844</v>
       </c>
       <c r="B80" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="C80" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="D80" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E80" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F80" t="s">
         <v>12</v>
@@ -17149,10 +17182,10 @@
         <v>59</v>
       </c>
       <c r="J80" t="s">
-        <v>475</v>
+        <v>1118</v>
       </c>
       <c r="K80" t="s">
-        <v>1204</v>
+        <v>1208</v>
       </c>
       <c r="L80" t="s">
         <v>40</v>
@@ -17166,16 +17199,16 @@
         <v>845</v>
       </c>
       <c r="B81" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="C81" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="D81" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E81" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F81" t="s">
         <v>12</v>
@@ -17190,10 +17223,10 @@
         <v>59</v>
       </c>
       <c r="J81" t="s">
-        <v>1115</v>
+        <v>475</v>
       </c>
       <c r="K81" t="s">
-        <v>1205</v>
+        <v>1209</v>
       </c>
       <c r="L81" t="s">
         <v>40</v>
@@ -17207,34 +17240,34 @@
         <v>846</v>
       </c>
       <c r="B82" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="C82" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="D82" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E82" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F82" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G82" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H82" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I82" t="s">
         <v>59</v>
       </c>
       <c r="J82" t="s">
-        <v>450</v>
+        <v>1119</v>
       </c>
       <c r="K82" t="s">
-        <v>1206</v>
+        <v>1210</v>
       </c>
       <c r="L82" t="s">
         <v>40</v>
@@ -17248,34 +17281,34 @@
         <v>847</v>
       </c>
       <c r="B83" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="C83" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="D83" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E83" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F83" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G83" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H83" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I83" t="s">
         <v>59</v>
       </c>
       <c r="J83" t="s">
-        <v>1116</v>
+        <v>450</v>
       </c>
       <c r="K83" t="s">
-        <v>1207</v>
+        <v>1211</v>
       </c>
       <c r="L83" t="s">
         <v>40</v>
@@ -17289,34 +17322,34 @@
         <v>848</v>
       </c>
       <c r="B84" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C84" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="D84" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E84" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F84" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G84" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H84" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I84" t="s">
         <v>59</v>
       </c>
       <c r="J84" t="s">
-        <v>131</v>
+        <v>1120</v>
       </c>
       <c r="K84" t="s">
-        <v>1208</v>
+        <v>1212</v>
       </c>
       <c r="L84" t="s">
         <v>40</v>
@@ -17330,34 +17363,34 @@
         <v>849</v>
       </c>
       <c r="B85" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="C85" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="D85" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E85" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F85" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G85" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H85" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I85" t="s">
         <v>59</v>
       </c>
       <c r="J85" t="s">
-        <v>517</v>
+        <v>131</v>
       </c>
       <c r="K85" t="s">
-        <v>1209</v>
+        <v>1213</v>
       </c>
       <c r="L85" t="s">
         <v>40</v>
@@ -17371,34 +17404,34 @@
         <v>850</v>
       </c>
       <c r="B86" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="C86" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="D86" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E86" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F86" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G86" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H86" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I86" t="s">
         <v>59</v>
       </c>
       <c r="J86" t="s">
-        <v>124</v>
+        <v>517</v>
       </c>
       <c r="K86" t="s">
-        <v>1210</v>
+        <v>1214</v>
       </c>
       <c r="L86" t="s">
         <v>40</v>
@@ -17412,34 +17445,34 @@
         <v>851</v>
       </c>
       <c r="B87" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="C87" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="D87" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E87" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F87" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G87" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H87" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I87" t="s">
         <v>59</v>
       </c>
       <c r="J87" t="s">
-        <v>459</v>
+        <v>124</v>
       </c>
       <c r="K87" t="s">
-        <v>1211</v>
+        <v>1215</v>
       </c>
       <c r="L87" t="s">
         <v>40</v>
@@ -17453,34 +17486,34 @@
         <v>852</v>
       </c>
       <c r="B88" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="C88" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="D88" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E88" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F88" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G88" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H88" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I88" t="s">
         <v>59</v>
       </c>
       <c r="J88" t="s">
-        <v>1117</v>
+        <v>459</v>
       </c>
       <c r="K88" t="s">
-        <v>1212</v>
+        <v>1216</v>
       </c>
       <c r="L88" t="s">
         <v>40</v>
@@ -17494,34 +17527,34 @@
         <v>853</v>
       </c>
       <c r="B89" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="C89" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="D89" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E89" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F89" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G89" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H89" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I89" t="s">
         <v>59</v>
       </c>
       <c r="J89" t="s">
-        <v>556</v>
+        <v>1121</v>
       </c>
       <c r="K89" t="s">
-        <v>1213</v>
+        <v>1217</v>
       </c>
       <c r="L89" t="s">
         <v>40</v>
@@ -17535,16 +17568,16 @@
         <v>854</v>
       </c>
       <c r="B90" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="C90" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="D90" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E90" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F90" t="s">
         <v>14</v>
@@ -17559,10 +17592,10 @@
         <v>59</v>
       </c>
       <c r="J90" t="s">
-        <v>536</v>
+        <v>556</v>
       </c>
       <c r="K90" t="s">
-        <v>1214</v>
+        <v>1218</v>
       </c>
       <c r="L90" t="s">
         <v>40</v>
@@ -17576,16 +17609,16 @@
         <v>855</v>
       </c>
       <c r="B91" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="C91" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="D91" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E91" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F91" t="s">
         <v>14</v>
@@ -17600,10 +17633,10 @@
         <v>59</v>
       </c>
       <c r="J91" t="s">
-        <v>1118</v>
+        <v>536</v>
       </c>
       <c r="K91" t="s">
-        <v>1215</v>
+        <v>1219</v>
       </c>
       <c r="L91" t="s">
         <v>40</v>
@@ -17617,34 +17650,34 @@
         <v>856</v>
       </c>
       <c r="B92" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="C92" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="D92" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E92" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F92" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G92" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H92" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I92" t="s">
         <v>59</v>
       </c>
       <c r="J92" t="s">
-        <v>1119</v>
+        <v>1122</v>
       </c>
       <c r="K92" t="s">
-        <v>1216</v>
+        <v>1220</v>
       </c>
       <c r="L92" t="s">
         <v>40</v>
@@ -17658,34 +17691,34 @@
         <v>857</v>
       </c>
       <c r="B93" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="C93" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="D93" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E93" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F93" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G93" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H93" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I93" t="s">
         <v>59</v>
       </c>
       <c r="J93" t="s">
-        <v>1120</v>
+        <v>1123</v>
       </c>
       <c r="K93" t="s">
-        <v>1217</v>
+        <v>1221</v>
       </c>
       <c r="L93" t="s">
         <v>40</v>
@@ -17699,34 +17732,34 @@
         <v>858</v>
       </c>
       <c r="B94" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="C94" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="D94" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E94" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F94" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G94" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H94" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I94" t="s">
         <v>59</v>
       </c>
       <c r="J94" t="s">
-        <v>523</v>
+        <v>1124</v>
       </c>
       <c r="K94" t="s">
-        <v>1218</v>
+        <v>1222</v>
       </c>
       <c r="L94" t="s">
         <v>40</v>
@@ -17740,34 +17773,34 @@
         <v>859</v>
       </c>
       <c r="B95" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="C95" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="D95" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E95" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F95" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G95" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H95" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I95" t="s">
         <v>59</v>
       </c>
       <c r="J95" t="s">
-        <v>469</v>
+        <v>523</v>
       </c>
       <c r="K95" t="s">
-        <v>1219</v>
+        <v>1223</v>
       </c>
       <c r="L95" t="s">
         <v>40</v>
@@ -17781,34 +17814,34 @@
         <v>860</v>
       </c>
       <c r="B96" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="C96" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="D96" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E96" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F96" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G96" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H96" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I96" t="s">
         <v>59</v>
       </c>
       <c r="J96" t="s">
-        <v>1121</v>
+        <v>469</v>
       </c>
       <c r="K96" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="L96" t="s">
         <v>40</v>
@@ -17822,34 +17855,34 @@
         <v>861</v>
       </c>
       <c r="B97" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="C97" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="D97" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E97" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F97" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G97" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H97" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I97" t="s">
         <v>59</v>
       </c>
       <c r="J97" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="K97" t="s">
-        <v>1221</v>
+        <v>1225</v>
       </c>
       <c r="L97" t="s">
         <v>40</v>
@@ -17863,34 +17896,34 @@
         <v>862</v>
       </c>
       <c r="B98" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="C98" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="D98" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E98" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F98" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G98" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H98" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I98" t="s">
         <v>59</v>
       </c>
       <c r="J98" t="s">
-        <v>1123</v>
+        <v>1126</v>
       </c>
       <c r="K98" t="s">
-        <v>1222</v>
+        <v>1226</v>
       </c>
       <c r="L98" t="s">
         <v>40</v>
@@ -17904,34 +17937,34 @@
         <v>863</v>
       </c>
       <c r="B99" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="C99" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="D99" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E99" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F99" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G99" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H99" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I99" t="s">
         <v>59</v>
       </c>
       <c r="J99" t="s">
-        <v>458</v>
+        <v>1127</v>
       </c>
       <c r="K99" t="s">
-        <v>1223</v>
+        <v>1227</v>
       </c>
       <c r="L99" t="s">
         <v>40</v>
@@ -17945,16 +17978,16 @@
         <v>864</v>
       </c>
       <c r="B100" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="C100" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="D100" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E100" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F100" t="s">
         <v>12</v>
@@ -17969,10 +18002,10 @@
         <v>59</v>
       </c>
       <c r="J100" t="s">
-        <v>484</v>
+        <v>458</v>
       </c>
       <c r="K100" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
       <c r="L100" t="s">
         <v>40</v>
@@ -17986,34 +18019,34 @@
         <v>865</v>
       </c>
       <c r="B101" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="C101" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="D101" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E101" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F101" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G101" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H101" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I101" t="s">
         <v>59</v>
       </c>
       <c r="J101" t="s">
-        <v>1124</v>
+        <v>484</v>
       </c>
       <c r="K101" t="s">
-        <v>1225</v>
+        <v>1229</v>
       </c>
       <c r="L101" t="s">
         <v>40</v>
@@ -18027,34 +18060,34 @@
         <v>866</v>
       </c>
       <c r="B102" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="C102" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="D102" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E102" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F102" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G102" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H102" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I102" t="s">
         <v>59</v>
       </c>
       <c r="J102" t="s">
-        <v>1125</v>
+        <v>1128</v>
       </c>
       <c r="K102" t="s">
-        <v>1226</v>
+        <v>1230</v>
       </c>
       <c r="L102" t="s">
         <v>40</v>
@@ -18068,39 +18101,80 @@
         <v>867</v>
       </c>
       <c r="B103" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C103" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="D103" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E103" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F103" t="s">
+        <v>12</v>
+      </c>
+      <c r="G103" t="s">
+        <v>24</v>
+      </c>
+      <c r="H103" t="s">
+        <v>18</v>
+      </c>
+      <c r="I103" t="s">
+        <v>59</v>
+      </c>
+      <c r="J103" t="s">
+        <v>1129</v>
+      </c>
+      <c r="K103" t="s">
+        <v>1231</v>
+      </c>
+      <c r="L103" t="s">
+        <v>40</v>
+      </c>
+      <c r="M103" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13">
+      <c r="A104" t="s">
+        <v>868</v>
+      </c>
+      <c r="B104" t="s">
+        <v>970</v>
+      </c>
+      <c r="C104" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D104" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E104" t="s">
+        <v>1074</v>
+      </c>
+      <c r="F104" t="s">
         <v>14</v>
       </c>
-      <c r="G103" t="s">
+      <c r="G104" t="s">
         <v>26</v>
       </c>
-      <c r="H103" t="s">
+      <c r="H104" t="s">
         <v>20</v>
       </c>
-      <c r="I103" t="s">
-        <v>59</v>
-      </c>
-      <c r="J103" t="s">
+      <c r="I104" t="s">
+        <v>59</v>
+      </c>
+      <c r="J104" t="s">
         <v>558</v>
       </c>
-      <c r="K103" t="s">
-        <v>1227</v>
-      </c>
-      <c r="L103" t="s">
-        <v>40</v>
-      </c>
-      <c r="M103" t="s">
+      <c r="K104" t="s">
+        <v>1232</v>
+      </c>
+      <c r="L104" t="s">
+        <v>40</v>
+      </c>
+      <c r="M104" t="s">
         <v>40</v>
       </c>
     </row>
@@ -18111,15 +18185,15 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>1228</v>
+        <v>1233</v>
       </c>
       <c r="B1" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
       <c r="C1" t="s">
         <v>4</v>
@@ -18127,419 +18201,441 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>1230</v>
+        <v>1235</v>
       </c>
       <c r="B2" t="s">
-        <v>1269</v>
+        <v>1276</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1308</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>1231</v>
+        <v>1236</v>
       </c>
       <c r="B3" t="s">
-        <v>1270</v>
+        <v>1277</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1309</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>1232</v>
+        <v>1237</v>
       </c>
       <c r="B4" t="s">
-        <v>1271</v>
+        <v>1278</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>1310</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>1233</v>
+        <v>1238</v>
       </c>
       <c r="B5" t="s">
-        <v>1272</v>
+        <v>1279</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>1320</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>1234</v>
+        <v>1239</v>
       </c>
       <c r="B6" t="s">
-        <v>1273</v>
+        <v>1280</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1311</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>1235</v>
+        <v>1240</v>
       </c>
       <c r="B7" t="s">
-        <v>1274</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>1312</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>1236</v>
+        <v>1241</v>
       </c>
       <c r="B8" t="s">
-        <v>1275</v>
+        <v>1282</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1313</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>1237</v>
+        <v>1242</v>
       </c>
       <c r="B9" t="s">
-        <v>1276</v>
+        <v>1283</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>1314</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>1238</v>
+        <v>1243</v>
       </c>
       <c r="B10" t="s">
-        <v>1277</v>
+        <v>1284</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>1315</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>1239</v>
+        <v>1244</v>
       </c>
       <c r="B11" t="s">
-        <v>1278</v>
+        <v>1285</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>1325</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>1240</v>
+        <v>1245</v>
       </c>
       <c r="B12" t="s">
-        <v>1279</v>
+        <v>1286</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>1316</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>1241</v>
+        <v>1246</v>
       </c>
       <c r="B13" t="s">
-        <v>1280</v>
+        <v>1287</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>1317</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>1242</v>
+        <v>1247</v>
       </c>
       <c r="B14" t="s">
-        <v>1281</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>1318</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>1243</v>
+        <v>1248</v>
       </c>
       <c r="B15" t="s">
-        <v>1282</v>
+        <v>1289</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>1319</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>1244</v>
+        <v>1249</v>
       </c>
       <c r="B16" t="s">
-        <v>1283</v>
+        <v>1290</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>1320</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>1245</v>
+        <v>1250</v>
       </c>
       <c r="B17" t="s">
-        <v>1284</v>
+        <v>1291</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>1321</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>1246</v>
+        <v>1251</v>
       </c>
       <c r="B18" t="s">
-        <v>1285</v>
+        <v>1292</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>1322</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>1247</v>
+        <v>1252</v>
       </c>
       <c r="B19" t="s">
-        <v>1286</v>
+        <v>1293</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>1332</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>1248</v>
+        <v>1253</v>
       </c>
       <c r="B20" t="s">
-        <v>1287</v>
+        <v>1294</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>1323</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>1249</v>
+        <v>1254</v>
       </c>
       <c r="B21" t="s">
-        <v>1288</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>1324</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>1250</v>
+        <v>1255</v>
       </c>
       <c r="B22" t="s">
-        <v>1289</v>
+        <v>1296</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>1325</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>1251</v>
+        <v>1256</v>
       </c>
       <c r="B23" t="s">
-        <v>1290</v>
+        <v>1297</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>1326</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>1252</v>
+        <v>1257</v>
       </c>
       <c r="B24" t="s">
-        <v>1291</v>
+        <v>1298</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>1327</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>1253</v>
+        <v>1258</v>
       </c>
       <c r="B25" t="s">
-        <v>1292</v>
+        <v>1299</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>1328</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>1254</v>
+        <v>1259</v>
       </c>
       <c r="B26" t="s">
-        <v>1293</v>
+        <v>1300</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>1338</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>1255</v>
+        <v>1260</v>
       </c>
       <c r="B27" t="s">
-        <v>1294</v>
+        <v>1301</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>1329</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>1256</v>
+        <v>1261</v>
       </c>
       <c r="B28" t="s">
-        <v>1295</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>1330</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>1257</v>
+        <v>1262</v>
       </c>
       <c r="B29" t="s">
-        <v>1296</v>
+        <v>1303</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>1331</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>1258</v>
+        <v>1263</v>
       </c>
       <c r="B30" t="s">
-        <v>1297</v>
+        <v>1304</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>1332</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>1259</v>
+        <v>1264</v>
       </c>
       <c r="B31" t="s">
-        <v>1298</v>
+        <v>1305</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>1260</v>
+        <v>1265</v>
       </c>
       <c r="B32" t="s">
-        <v>1299</v>
+        <v>1306</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>1334</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>1261</v>
+        <v>1266</v>
       </c>
       <c r="B33" t="s">
-        <v>1300</v>
+        <v>1307</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>1335</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>1262</v>
+        <v>1267</v>
       </c>
       <c r="B34" t="s">
-        <v>1301</v>
+        <v>1308</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>1336</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>1263</v>
+        <v>1268</v>
       </c>
       <c r="B35" t="s">
-        <v>1302</v>
+        <v>1309</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>1337</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>1264</v>
+        <v>1269</v>
       </c>
       <c r="B36" t="s">
-        <v>1303</v>
+        <v>1310</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>1338</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>1265</v>
+        <v>1270</v>
       </c>
       <c r="B37" t="s">
-        <v>1304</v>
+        <v>1311</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>1339</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>1266</v>
+        <v>1271</v>
       </c>
       <c r="B38" t="s">
-        <v>1305</v>
+        <v>1312</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>1340</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>1267</v>
+        <v>1272</v>
       </c>
       <c r="B39" t="s">
-        <v>1306</v>
+        <v>1313</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>1341</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>1268</v>
+        <v>1273</v>
       </c>
       <c r="B40" t="s">
-        <v>1307</v>
+        <v>1314</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>1342</v>
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B41" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B42" t="s">
+        <v>1316</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>1353</v>
       </c>
     </row>
   </sheetData>
@@ -18547,26 +18643,26 @@
     <hyperlink ref="C2" r:id="rId1"/>
     <hyperlink ref="C3" r:id="rId2"/>
     <hyperlink ref="C4" r:id="rId3"/>
-    <hyperlink ref="C6" r:id="rId4"/>
-    <hyperlink ref="C7" r:id="rId5"/>
+    <hyperlink ref="C5" r:id="rId4"/>
+    <hyperlink ref="C6" r:id="rId5"/>
     <hyperlink ref="C8" r:id="rId6"/>
     <hyperlink ref="C9" r:id="rId7"/>
     <hyperlink ref="C10" r:id="rId8"/>
-    <hyperlink ref="C12" r:id="rId9"/>
-    <hyperlink ref="C13" r:id="rId10"/>
-    <hyperlink ref="C14" r:id="rId11"/>
+    <hyperlink ref="C11" r:id="rId9"/>
+    <hyperlink ref="C12" r:id="rId10"/>
+    <hyperlink ref="C13" r:id="rId11"/>
     <hyperlink ref="C15" r:id="rId12"/>
     <hyperlink ref="C16" r:id="rId13"/>
     <hyperlink ref="C17" r:id="rId14"/>
     <hyperlink ref="C18" r:id="rId15"/>
-    <hyperlink ref="C20" r:id="rId16"/>
-    <hyperlink ref="C21" r:id="rId17"/>
+    <hyperlink ref="C19" r:id="rId16"/>
+    <hyperlink ref="C20" r:id="rId17"/>
     <hyperlink ref="C22" r:id="rId18"/>
     <hyperlink ref="C23" r:id="rId19"/>
     <hyperlink ref="C24" r:id="rId20"/>
     <hyperlink ref="C25" r:id="rId21"/>
-    <hyperlink ref="C27" r:id="rId22"/>
-    <hyperlink ref="C28" r:id="rId23"/>
+    <hyperlink ref="C26" r:id="rId22"/>
+    <hyperlink ref="C27" r:id="rId23"/>
     <hyperlink ref="C29" r:id="rId24"/>
     <hyperlink ref="C30" r:id="rId25"/>
     <hyperlink ref="C31" r:id="rId26"/>
@@ -18579,6 +18675,8 @@
     <hyperlink ref="C38" r:id="rId33"/>
     <hyperlink ref="C39" r:id="rId34"/>
     <hyperlink ref="C40" r:id="rId35"/>
+    <hyperlink ref="C41" r:id="rId36"/>
+    <hyperlink ref="C42" r:id="rId37"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-groups.xlsx
+++ b/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-groups.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4469" uniqueCount="1354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4486" uniqueCount="1371">
   <si>
     <t>ID</t>
   </si>
@@ -68,22 +68,22 @@
     <t>G0013</t>
   </si>
   <si>
-    <t>intrusion-set--6bb397ce-d257-45ef-9a68-fd682239dc91</t>
-  </si>
-  <si>
-    <t>intrusion-set--080fc39f-be32-4bdf-aa6b-d86e3dcd4f81</t>
-  </si>
-  <si>
-    <t>intrusion-set--6fcf2657-4840-4754-a318-5cee4b91d670</t>
-  </si>
-  <si>
-    <t>intrusion-set--4f0187aa-3964-42bb-8185-827fd9232dcb</t>
-  </si>
-  <si>
-    <t>intrusion-set--1e2aa43d-a27c-407c-b94a-405123ec52f9</t>
-  </si>
-  <si>
-    <t>intrusion-set--701ece7a-3998-432c-ab53-b4496887b072</t>
+    <t>intrusion-set--3642f171-4667-4b82-b3c5-73f7f518396b</t>
+  </si>
+  <si>
+    <t>intrusion-set--224aa639-ced9-4891-bc3c-72ee1592cf05</t>
+  </si>
+  <si>
+    <t>intrusion-set--e3bc6b24-7eb3-408b-af74-b5924d08cd07</t>
+  </si>
+  <si>
+    <t>intrusion-set--1be81b91-037a-46a1-8e5e-b282c40ea297</t>
+  </si>
+  <si>
+    <t>intrusion-set--243887eb-e4f8-4b0e-a6d2-843e9676f671</t>
+  </si>
+  <si>
+    <t>intrusion-set--8b5f0098-75af-4fcd-9c7f-88149768cd8b</t>
   </si>
   <si>
     <t>Белое движение (ВСЮР)</t>
@@ -152,19 +152,19 @@
     <t>(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.)</t>
   </si>
   <si>
-    <t>(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Руїна — Вікіпедія 2026),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Московсько-українська війна (1658—1659),(Citation: Русифікація України — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Руїна — Вікіпедія 2026),(Citation: Переяславські статті (1659),(Citation: Малоросійський приказ — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Мазепа 2007),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Переяславська рада — Вікіпедія 2026),(Citation: Решетилівські статті — Вікіпедія 2026),(Citation: Московсько-українська війна (1658—1659),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Киевский синопсис — Википедия 2026),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Північна війна (1700—1721),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Запорозька Січ — Вікіпедія 2026),(Citation: Руїна — Вікіпедія 2026),(Citation: Переяславська рада — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Московські статті (1665),(Citation: Переяславські статті (1659),(Citation: Мазепа 2007),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Малоросійський приказ — Вікіпедія 2026),(Citation: Решетилівські статті — Вікіпедія 2026),(Citation: Андрусовское перемирие - Википедия 2026),(Citation: Ліквідація козацтва на Правобережній Україні (1699),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Конотопські статті — Вікіпедія 2026),(Citation: Киевский синопсис — Википедия 2026),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Азовські походи (1695—1696),(Citation: Запорозька Січ — Вікіпедія 2026)</t>
-  </si>
-  <si>
-    <t>(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: Чорносотенці — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Листопадове повстання (1830—1831),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Історія Донецької області — Вікіпедія 2026),(Citation: Столипінська реформа — Вікіпедія 2026),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Друга Малоросійська колегія — Вікіпедія 2026),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Повстання бузьких козаків (1817),(Citation: Історія України — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026),(Citation: Перепис населення Російської імперії (1897),(Citation: Правління гетьманського уряду — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Крымская война — Википедия 2026),(Citation: Столипінська реформа — Вікіпедія 2026),(Citation: Повстання бузьких козаків (1817),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Кирило-Мефодіївське товариство — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Антикріпосницький рух в Україні (1789-1861),(Citation: Листопадове повстання (1830—1831),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Русско-турецкая война (1768—1774),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Малоросійське генерал-губернаторство — Вікіпедія 2026),(Citation: Чорносотенці — Вікіпедія 2026),(Citation: Польское восстание (1863—1864),(Citation: Україна у війнах Наполеона — Вікіпедія 2026),(Citation: Смуга осілості — Вікіпедія 2026),(Citation: Російсько-турецька війна (1806—1812),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026)</t>
-  </si>
-  <si>
-    <t>(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: 2016 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Рашизм: Звір з безодні 2023),(Citation: Российские удары по украинской энергосистеме — Википедия 2026),(Citation: 2015 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Російсько-українська війна (з 2014),(Citation: Дезінформація під час російсько-української війни — Вікіпедія 2026),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010)</t>
-  </si>
-  <si>
-    <t>(Citation: Карательная психиатрия в России: назад в СССР? 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Рашизм: Звір з безодні 2023),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Карательная психиатрия в России: назад в СССР? 2026),(Citation: Котлета по-київськи (промова),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Історія України — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Кенгирское восстание заключённых - Википедия 2026),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Рашизм: Звір з безодні 2023),(Citation: В ТЕНИ «БОЛЬШОГО БРАТА» ЗАПАДНЫЕ НАЦИОНАЛЬНЫЕ МЕНЬШИНСТВА В СССР 1917-1938 ГГ . 2011),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: ДИССИДЕНТСКОЕ ДВИЖЕНИЕ В УКРАИНЕ (1954 – 1987),(Citation: Всесоюзний референдум про збереження СРСР — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026)</t>
-  </si>
-  <si>
-    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939)</t>
+    <t>(Citation: Руїна — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Московсько-українська війна (1658—1659),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Руїна — Вікіпедія 2026),(Citation: Запорозька Січ — Вікіпедія 2026),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Московсько-українська війна (1658—1659),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Киевский синопсис — Википедия 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Переяславська рада — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Мазепа 2007),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Переяславські статті (1659),(Citation: Північна війна (1700—1721),(Citation: Малоросійський приказ — Вікіпедія 2026),(Citation: Решетилівські статті — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Запорозька Січ — Вікіпедія 2026),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Азовські походи (1695—1696),(Citation: Андрусовское перемирие - Википедия 2026),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Ліквідація козацтва на Правобережній Україні (1699),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Переяславська рада — Вікіпедія 2026),(Citation: Решетилівські статті — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Киевский синопсис — Википедия 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Московські статті (1665),(Citation: Мазепа 2007),(Citation: Малоросійський приказ — Вікіпедія 2026),(Citation: Переяславські статті (1659),(Citation: Конотопські статті — Вікіпедія 2026),(Citation: Руїна — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711)</t>
+  </si>
+  <si>
+    <t>(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Історія Донецької області — Вікіпедія 2026),(Citation: Чорносотенці — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Столипінська реформа — Вікіпедія 2026),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Друга Малоросійська колегія — Вікіпедія 2026),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026),(Citation: Повстання бузьких козаків (1817),(Citation: Історія України — Вікіпедія 2026),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: Листопадове повстання (1830—1831),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026),(Citation: Листопадове повстання (1830—1831),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Чорносотенці — Вікіпедія 2026),(Citation: Крымская война — Википедия 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Україна у війнах Наполеона — Вікіпедія 2026),(Citation: Російсько-турецька війна (1806—1812),(Citation: Русско-турецкая война (1768—1774),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Повстання бузьких козаків (1817),(Citation: Перепис населення Російської імперії (1897),(Citation: Смуга осілості — Вікіпедія 2026),(Citation: Польское восстание (1863—1864),(Citation: Правління гетьманського уряду — Вікіпедія 2026),(Citation: Малоросійське генерал-губернаторство — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Столипінська реформа — Вікіпедія 2026),(Citation: Антикріпосницький рух в Україні (1789-1861),(Citation: Кирило-Мефодіївське товариство — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026)</t>
+  </si>
+  <si>
+    <t>(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Рашизм: Звір з безодні 2023),(Citation: Дезінформація під час російсько-української війни — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: 2016 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Російсько-українська війна (з 2014),(Citation: Історія України — Вікіпедія 2026),(Citation: 2015 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023),(Citation: Российские удары по украинской энергосистеме — Википедия 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Хроника первой российской войны в Чечне 2026)</t>
+  </si>
+  <si>
+    <t>(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Карательная психиатрия в России: назад в СССР? 2020),(Citation: Історія України — Вікіпедія 2026),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Рашизм: Звір з безодні 2023),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Карательная психиатрия в России: назад в СССР? 2020),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: Котлета по-київськи (промова),(Citation: Історія України — Вікіпедія 2026),(Citation: Рашизм: Звір з безодні 2023),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: В ТЕНИ «БОЛЬШОГО БРАТА» ЗАПАДНЫЕ НАЦИОНАЛЬНЫЕ МЕНЬШИНСТВА В СССР 1917-1938 ГГ . 2011),(Citation: Всесоюзний референдум про збереження СРСР — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: ДИССИДЕНТСКОЕ ДВИЖЕНИЕ В УКРАИНЕ (1954 – 1987),(Citation: Історія України — Вікіпедія 2026),(Citation: Кенгирское восстание заключённых - Википедия 2026)</t>
+  </si>
+  <si>
+    <t>(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939)</t>
   </si>
   <si>
     <t>source ID</t>
@@ -281,43 +281,43 @@
     <t>Подконтрольная оппозиция</t>
   </si>
   <si>
-    <t>tool--6fd47d4c-bac8-4dcd-b582-e6a42bb51313</t>
-  </si>
-  <si>
-    <t>tool--4a55efd1-b775-4318-8adc-ebb029729960</t>
-  </si>
-  <si>
-    <t>tool--78806636-7cbc-4a54-9f61-2a5a98a33f13</t>
-  </si>
-  <si>
-    <t>tool--4d2e439d-9619-4447-8a41-1af8960acc55</t>
-  </si>
-  <si>
-    <t>tool--60f65bd4-46b3-4eed-9418-254cf51965fd</t>
-  </si>
-  <si>
-    <t>tool--17849785-49e2-4f22-9488-618cbc11cec9</t>
-  </si>
-  <si>
-    <t>tool--b8bf442f-c688-4983-bc89-7fc0e5a2d70f</t>
-  </si>
-  <si>
-    <t>tool--6faacf93-e3f5-43f6-8d94-9d2c7c6382a9</t>
-  </si>
-  <si>
-    <t>tool--1652bd4f-c611-4f10-aedc-6581590e2df2</t>
-  </si>
-  <si>
-    <t>tool--03b1e023-5469-49ea-9988-c7118a91b725</t>
-  </si>
-  <si>
-    <t>tool--ed0808d4-111e-4057-a345-7d951b669eb5</t>
-  </si>
-  <si>
-    <t>tool--43db716c-e55e-4798-8810-4606ebb81e52</t>
-  </si>
-  <si>
-    <t>tool--b591e96e-6cd5-4b20-9c6f-aa7dc5747255</t>
+    <t>tool--b4c0d62c-b3f5-4069-a07d-c7e9a48427e5</t>
+  </si>
+  <si>
+    <t>tool--4ba8494b-f590-4308-868c-37a12508f6a3</t>
+  </si>
+  <si>
+    <t>tool--5ceff728-9a89-463d-b71b-79b952d31693</t>
+  </si>
+  <si>
+    <t>tool--d57519cc-1898-4106-8e8b-4798bf53d3b4</t>
+  </si>
+  <si>
+    <t>tool--4ebdeb25-4eb2-43cd-a70b-e019e1a4ef6c</t>
+  </si>
+  <si>
+    <t>tool--ff0e5cd8-b850-4df9-845a-ab14c6ba2104</t>
+  </si>
+  <si>
+    <t>tool--2de74860-9286-45c7-b350-d41ae6685351</t>
+  </si>
+  <si>
+    <t>tool--5c43501c-aa32-48a4-a151-6c6897e3b0dd</t>
+  </si>
+  <si>
+    <t>tool--5dcf4786-4e1a-44f2-8aa0-e4b5fdf1f93f</t>
+  </si>
+  <si>
+    <t>tool--af3c7286-be13-4569-ac9d-c96ebbac6a34</t>
+  </si>
+  <si>
+    <t>tool--413178e7-81d2-4bdd-ab53-c632febad570</t>
+  </si>
+  <si>
+    <t>tool--e5929876-f3ec-466c-90a8-ec4a16cd8ac7</t>
+  </si>
+  <si>
+    <t>tool--fd9d33aa-46ee-48a8-b37c-b5813b8dd7cb</t>
   </si>
   <si>
     <t>software</t>
@@ -395,7 +395,7 @@
     <t>Уничтожение гражданских и просветительских структур в местах компактного проживания диаспоры: «Ліквідація 'Просвіт' на Кубані, в Зеленому Клину» (Citation: Русифікація України — Вікіпедія 2026).</t>
   </si>
   <si>
-    <t>Использование институтов государственного здравоохранения для политически мотивированного диагностирования инакомыслящих (диагноз «вялотекущая шизофрения») и их бессрочной изоляции в психиатрических больницах. (Citation: Карательная психиатрия в России: назад в СССР? 2026)</t>
+    <t>Использование институтов государственного здравоохранения для политически мотивированного диагностирования инакомыслящих (диагноз «вялотекущая шизофрения») и их бессрочной изоляции в психиатрических больницах. (Citation: Карательная психиатрия в России: назад в СССР? 2020)</t>
   </si>
   <si>
     <t>Организация фейковых безальтернативных «Народных сборов» под контролем оккупационных войск для юридического оформления захвата. (Citation: Історія України — Вікіпедія 2026)</t>
@@ -425,106 +425,106 @@
     <t>Провоцирование большевиками восстания рабочих завода «Арсенал» в самом Киеве для оттягивания резервов украинских властей прямо во время наступления красных войск. (Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
   </si>
   <si>
-    <t>relationship--748adbe7-f59c-4bc0-97f4-de3ec43934c9</t>
-  </si>
-  <si>
-    <t>relationship--223dcaad-ae78-43af-86c8-5494371b1d37</t>
-  </si>
-  <si>
-    <t>relationship--54823f51-aa85-4d2f-ba24-5f50309914c7</t>
-  </si>
-  <si>
-    <t>relationship--ac746805-7a46-4ae9-8b34-a32e9a11c539</t>
-  </si>
-  <si>
-    <t>relationship--4964717a-b221-499a-927d-39dcb9db33a2</t>
-  </si>
-  <si>
-    <t>relationship--7c711dce-6dd9-45f8-8bc2-7343d77afe0f</t>
-  </si>
-  <si>
-    <t>relationship--6b10a528-82da-42f7-9cdc-1aa588fab481</t>
-  </si>
-  <si>
-    <t>relationship--bc8eb603-4feb-4413-bf43-80cb97d78378</t>
-  </si>
-  <si>
-    <t>relationship--6156c3c7-b5ba-49fd-b912-528c84e7a683</t>
-  </si>
-  <si>
-    <t>relationship--addd0ef0-894f-455c-8180-38cd60e04c37</t>
-  </si>
-  <si>
-    <t>relationship--ffc52e98-63f1-4ff9-9e6c-0ecf73c132a4</t>
-  </si>
-  <si>
-    <t>relationship--5e3dfb1e-eacc-43fe-ab72-12a4adcd0e10</t>
-  </si>
-  <si>
-    <t>relationship--b13a8a02-0a0e-461c-bb4b-4a4376ff35c6</t>
-  </si>
-  <si>
-    <t>relationship--6a268ffe-5e34-4dff-86c0-07aa08dcb5a2</t>
-  </si>
-  <si>
-    <t>relationship--be640a50-5ff4-4b10-ba98-384c9b0d55c8</t>
-  </si>
-  <si>
-    <t>relationship--7776534d-2830-47ec-a5f7-3cfce9bb3d44</t>
-  </si>
-  <si>
-    <t>relationship--374dc1bc-6679-4a55-9b31-fb16e91b7f00</t>
-  </si>
-  <si>
-    <t>relationship--c8637b07-3a35-46c8-aa81-13619be9953e</t>
-  </si>
-  <si>
-    <t>relationship--8dd4ccd1-6e48-4e5c-9b30-f06ab1d93521</t>
-  </si>
-  <si>
-    <t>relationship--5dcc9361-437b-4a59-a451-3d954258d94d</t>
-  </si>
-  <si>
-    <t>relationship--9d98aef8-2024-4ee4-84cc-07e3af7e47c5</t>
-  </si>
-  <si>
-    <t>relationship--856984be-eae4-4f32-b090-8ed806b87c1e</t>
-  </si>
-  <si>
-    <t>relationship--df3c4fca-1b31-4f57-a805-f4f74a87dfe7</t>
-  </si>
-  <si>
-    <t>relationship--014fda40-f5c3-47ed-a2ed-3b6b46c55878</t>
-  </si>
-  <si>
-    <t>relationship--f85f034d-6561-4988-abaa-ac7172a7bd76</t>
-  </si>
-  <si>
-    <t>relationship--55964349-3162-4e27-bb1e-abf01bb55215</t>
-  </si>
-  <si>
-    <t>relationship--4534db45-fe9b-4f0e-aedc-98ad60b13128</t>
-  </si>
-  <si>
-    <t>relationship--4330ffb9-d8ff-4288-ac43-6a065a313900</t>
-  </si>
-  <si>
-    <t>relationship--3d908446-973f-47fc-a39e-3789efe97ff3</t>
-  </si>
-  <si>
-    <t>relationship--232d9c6f-6ad7-4312-a2d8-c607f9ee0276</t>
-  </si>
-  <si>
-    <t>relationship--e642c95f-3e56-4c24-a977-d86cc4c20ba3</t>
-  </si>
-  <si>
-    <t>relationship--8227572b-82be-4c2c-861b-5113f97dfddd</t>
-  </si>
-  <si>
-    <t>relationship--f7a0de34-a733-435a-9ec1-62e98780f91a</t>
-  </si>
-  <si>
-    <t>relationship--06fe07f5-9a2f-47f1-b0a5-6e296fb85588</t>
+    <t>relationship--ee1770df-945f-4564-9553-b1d84f490dcd</t>
+  </si>
+  <si>
+    <t>relationship--8bc54604-c986-43f2-a701-b12592389a95</t>
+  </si>
+  <si>
+    <t>relationship--653bfee4-8148-4228-b9ad-a0dd9f6fb024</t>
+  </si>
+  <si>
+    <t>relationship--8c5d41d1-9fc6-4849-a964-d4d4cd88d808</t>
+  </si>
+  <si>
+    <t>relationship--5be4de54-a976-41cf-9a3e-801a66dd4ab0</t>
+  </si>
+  <si>
+    <t>relationship--f005b199-111a-4b05-aefa-24a35febc482</t>
+  </si>
+  <si>
+    <t>relationship--0dbf3ce6-19bd-478e-adf9-32c6e80ed0ea</t>
+  </si>
+  <si>
+    <t>relationship--c208739a-827c-4d0e-bf28-61b916f15cfe</t>
+  </si>
+  <si>
+    <t>relationship--614fbc69-8cba-40a0-98f9-936eaac5419e</t>
+  </si>
+  <si>
+    <t>relationship--ca9d96ad-f282-4c8a-a7f1-c49268bc3a88</t>
+  </si>
+  <si>
+    <t>relationship--086b6153-43f4-47de-80df-44693f738943</t>
+  </si>
+  <si>
+    <t>relationship--8a4808c1-777c-40fc-aa35-f6cd68dc33c2</t>
+  </si>
+  <si>
+    <t>relationship--37a411b5-a9ad-4aa3-b275-64db44664d5d</t>
+  </si>
+  <si>
+    <t>relationship--aee80eb9-ab23-4760-8add-e0216bd30a05</t>
+  </si>
+  <si>
+    <t>relationship--ca3971ca-3608-4f4b-ba38-3b8e016ebf03</t>
+  </si>
+  <si>
+    <t>relationship--80974889-50af-4c79-93b8-102362fc0530</t>
+  </si>
+  <si>
+    <t>relationship--e6ca03f6-6ec1-4870-bcb9-a3c507268afb</t>
+  </si>
+  <si>
+    <t>relationship--2a6b0d1a-4fc7-40de-9362-c8eb8abcb9fa</t>
+  </si>
+  <si>
+    <t>relationship--df0ae14a-9167-4c70-bba9-d917ecd1bcbe</t>
+  </si>
+  <si>
+    <t>relationship--38cbf6e2-05be-4c93-9361-7c3355dec29f</t>
+  </si>
+  <si>
+    <t>relationship--eb3986b1-fecd-4d37-92dd-0c8250ef0740</t>
+  </si>
+  <si>
+    <t>relationship--388cb58a-f6b1-432c-aa19-57cc86f8713f</t>
+  </si>
+  <si>
+    <t>relationship--c6850c22-f194-48a1-b786-c5cf857b99cd</t>
+  </si>
+  <si>
+    <t>relationship--917fb287-22e5-452a-9dc2-8c5c8aca7d1b</t>
+  </si>
+  <si>
+    <t>relationship--34cf12dd-b962-4ebe-830a-d8f1c7ff5c4f</t>
+  </si>
+  <si>
+    <t>relationship--94711d8b-0578-438a-9d73-eafd0c1bc983</t>
+  </si>
+  <si>
+    <t>relationship--8045380f-5282-4b2f-ab8f-cb92ffd304a3</t>
+  </si>
+  <si>
+    <t>relationship--3536b790-3098-4639-9c74-ac882b5ab83e</t>
+  </si>
+  <si>
+    <t>relationship--c09a449b-0b73-4e67-abc0-922897a14e61</t>
+  </si>
+  <si>
+    <t>relationship--079404c8-fadc-4028-b464-f31ba21f9514</t>
+  </si>
+  <si>
+    <t>relationship--51aabffe-86e6-4eaa-bf10-1d5525e930ad</t>
+  </si>
+  <si>
+    <t>relationship--49567418-6145-460a-ab69-bcb7861395ac</t>
+  </si>
+  <si>
+    <t>relationship--69dc0331-617e-4089-ac23-257dbeee91a6</t>
+  </si>
+  <si>
+    <t>relationship--57e6a8bb-5b08-4144-8f3d-8b095b08d609</t>
   </si>
   <si>
     <t>T0019</t>
@@ -1025,253 +1025,253 @@
     <t>Поддержка подконтрольной оппозиции</t>
   </si>
   <si>
-    <t>attack-pattern--563b0db6-14f7-4b63-8256-95de0ef5cf8c</t>
-  </si>
-  <si>
-    <t>attack-pattern--ca41993a-f62d-477b-802f-e63f4c050380</t>
-  </si>
-  <si>
-    <t>attack-pattern--8accb141-a1ff-471e-9a3a-988919bcceb6</t>
-  </si>
-  <si>
-    <t>attack-pattern--8feebaca-97cf-4478-b1d3-8e0a8ed2edc0</t>
-  </si>
-  <si>
-    <t>attack-pattern--e49e8037-4bae-447d-86e6-23b275db8d96</t>
-  </si>
-  <si>
-    <t>attack-pattern--8623a36b-99de-4dfb-ba46-b2b5e9cf0d85</t>
-  </si>
-  <si>
-    <t>attack-pattern--37759b81-258f-4d71-9703-9654ac67cab0</t>
-  </si>
-  <si>
-    <t>attack-pattern--95138ada-459f-440e-a79a-7fcf8874b584</t>
-  </si>
-  <si>
-    <t>attack-pattern--fe23fd12-ed27-416d-a891-53fd0945c418</t>
-  </si>
-  <si>
-    <t>attack-pattern--7f745905-530b-4294-9eda-f8dafe9f0edd</t>
-  </si>
-  <si>
-    <t>attack-pattern--fe33bd0c-bd06-451b-92ea-b2f65444329b</t>
-  </si>
-  <si>
-    <t>attack-pattern--a6684ef1-fa45-4bf7-9ec1-db7ebe4dec10</t>
-  </si>
-  <si>
-    <t>attack-pattern--91bd2ac0-d39a-4a37-b4ba-3b7d9cc48480</t>
-  </si>
-  <si>
-    <t>attack-pattern--cf3d899a-e96c-4063-bf08-65e437c19c7f</t>
-  </si>
-  <si>
-    <t>attack-pattern--575a4091-4083-4c93-8862-74543ad2f94c</t>
-  </si>
-  <si>
-    <t>attack-pattern--3d97cbb0-3c4c-4fd3-9b5e-679517b777f3</t>
-  </si>
-  <si>
-    <t>attack-pattern--aa11cd7e-92e7-43ec-af19-193b81bdb604</t>
-  </si>
-  <si>
-    <t>attack-pattern--08292bee-5177-4f79-bfa6-4f0345a5a446</t>
-  </si>
-  <si>
-    <t>attack-pattern--60d5bdf7-06c3-4a53-b2d3-36b02a2230e3</t>
-  </si>
-  <si>
-    <t>attack-pattern--0fa8defa-fb0b-4599-9491-7d725883c3fd</t>
-  </si>
-  <si>
-    <t>attack-pattern--60a4cda8-8154-4a3f-9826-f9d39155d257</t>
-  </si>
-  <si>
-    <t>attack-pattern--0ffd53d6-5fd6-43e5-aff6-4e1d50a00743</t>
-  </si>
-  <si>
-    <t>attack-pattern--9fb6f979-a54f-46ce-9d0b-ce0c5db37e7a</t>
-  </si>
-  <si>
-    <t>attack-pattern--3a36e7b8-ad04-4cb0-8ffc-9b6502c66d77</t>
-  </si>
-  <si>
-    <t>attack-pattern--c8e73b27-78c5-4634-93ec-287a7cd80529</t>
-  </si>
-  <si>
-    <t>attack-pattern--e1c8faff-7670-454e-a4f0-3da445f53ac9</t>
-  </si>
-  <si>
-    <t>attack-pattern--8f5deb62-ed66-4518-9b21-c1557815cce5</t>
-  </si>
-  <si>
-    <t>attack-pattern--019504d9-9143-4762-b36e-729108653789</t>
-  </si>
-  <si>
-    <t>attack-pattern--22e649d9-36b0-4f1f-88e9-e34fd12441c4</t>
-  </si>
-  <si>
-    <t>attack-pattern--624b5cee-3da2-4c18-906b-d1f1aca11306</t>
-  </si>
-  <si>
-    <t>attack-pattern--286b8cda-f24d-4dde-a188-c0b140491a96</t>
-  </si>
-  <si>
-    <t>attack-pattern--3c93037a-c467-4137-81e2-c058a9d90107</t>
-  </si>
-  <si>
-    <t>attack-pattern--229f46aa-5a77-41ce-a34b-4d978b1164ea</t>
-  </si>
-  <si>
-    <t>attack-pattern--1a2eea19-fa56-4b46-b746-af741b0fbe4a</t>
-  </si>
-  <si>
-    <t>attack-pattern--2001e1d6-3887-44fe-892d-ce873833b382</t>
-  </si>
-  <si>
-    <t>attack-pattern--37844351-6c24-42d8-99ba-2eb178febd3c</t>
-  </si>
-  <si>
-    <t>attack-pattern--aeca9532-ecda-49fc-9915-fe9b53956bf8</t>
-  </si>
-  <si>
-    <t>attack-pattern--dc37deb9-2659-4fc2-b801-127690502a1e</t>
-  </si>
-  <si>
-    <t>attack-pattern--595ddc1a-2efe-4154-a6d7-880fb2fe280f</t>
-  </si>
-  <si>
-    <t>attack-pattern--8f5f6323-a749-4b89-a8ae-36633f183b54</t>
-  </si>
-  <si>
-    <t>attack-pattern--bf3afc82-5403-4ae9-9f69-3d9ef357c6c8</t>
-  </si>
-  <si>
-    <t>attack-pattern--fd99f80b-0f34-4288-bc79-c0f3cf18e846</t>
-  </si>
-  <si>
-    <t>attack-pattern--2421e2f6-4b1f-4f1e-8faa-69e9b14cbbe8</t>
-  </si>
-  <si>
-    <t>attack-pattern--fe1389e1-23dc-4f41-b2e1-15ed665a5840</t>
-  </si>
-  <si>
-    <t>attack-pattern--f69b9809-b9e2-4a3e-b8d9-cf3f74af4335</t>
-  </si>
-  <si>
-    <t>attack-pattern--9f1e418c-f7d0-4526-9824-f880b69b0dc8</t>
-  </si>
-  <si>
-    <t>attack-pattern--709b796b-4c14-4219-8b7d-848ccf3df33f</t>
-  </si>
-  <si>
-    <t>attack-pattern--7be66db5-2484-4f82-9c02-2c658aba5534</t>
-  </si>
-  <si>
-    <t>attack-pattern--503486f3-22d3-4ed3-a8fb-f63db2718af0</t>
-  </si>
-  <si>
-    <t>attack-pattern--a92eb244-48f1-4d36-91b8-9ff6404bc66d</t>
-  </si>
-  <si>
-    <t>attack-pattern--b516107a-c248-4465-aa68-d5e20f3bf635</t>
-  </si>
-  <si>
-    <t>attack-pattern--062669ed-dadc-446f-992c-3425ac24dd1e</t>
-  </si>
-  <si>
-    <t>attack-pattern--e745fb62-c9c2-41af-affe-cac608952241</t>
-  </si>
-  <si>
-    <t>attack-pattern--ac8f6735-f593-4862-b036-039679f6825d</t>
-  </si>
-  <si>
-    <t>attack-pattern--fef93f62-3fe5-4d86-bad7-82607554a597</t>
-  </si>
-  <si>
-    <t>attack-pattern--dac8d747-5bf3-47af-9f54-b010ae92ccea</t>
-  </si>
-  <si>
-    <t>attack-pattern--8fa70d63-cbe1-4ba7-b1a5-2573911cf454</t>
-  </si>
-  <si>
-    <t>attack-pattern--0813df13-c30d-4a9c-badc-bf8ff641b717</t>
-  </si>
-  <si>
-    <t>attack-pattern--ae7d996b-f766-44ab-a46b-60abdd2b3ef6</t>
-  </si>
-  <si>
-    <t>attack-pattern--b8f0d38d-8111-4ef2-87ab-d970fb6f6d04</t>
-  </si>
-  <si>
-    <t>attack-pattern--73c181fd-e569-4225-9bfb-045b64df9b0c</t>
-  </si>
-  <si>
-    <t>attack-pattern--85208eb7-09ab-4287-a298-87298178d6c7</t>
-  </si>
-  <si>
-    <t>attack-pattern--fd811343-f4f3-4812-ad57-477da21a7e8d</t>
-  </si>
-  <si>
-    <t>attack-pattern--72323e0d-b098-4e42-8cd1-544258dc8973</t>
-  </si>
-  <si>
-    <t>attack-pattern--d4b577cd-5a76-46f7-8c39-b96213fc4263</t>
-  </si>
-  <si>
-    <t>attack-pattern--14d57931-21d5-4fd1-bf37-f26ce432a5ca</t>
-  </si>
-  <si>
-    <t>attack-pattern--71797db1-dffd-44dd-8bfa-53446c0091df</t>
-  </si>
-  <si>
-    <t>attack-pattern--ed09b02f-1bf8-4c07-859e-b28e828825d5</t>
-  </si>
-  <si>
-    <t>attack-pattern--880b414d-a823-4193-b270-c0a7de9e6d12</t>
-  </si>
-  <si>
-    <t>attack-pattern--4c4ac28a-0504-4efc-b7bb-a81682cab9ef</t>
-  </si>
-  <si>
-    <t>attack-pattern--a8e7461e-9164-42e7-a275-578694585803</t>
-  </si>
-  <si>
-    <t>attack-pattern--3fff8702-55b8-4c84-a528-2b14b7b980da</t>
-  </si>
-  <si>
-    <t>attack-pattern--c0c59602-b27b-4b66-b864-82a05ff862db</t>
-  </si>
-  <si>
-    <t>attack-pattern--a08a6f55-9930-4233-8df3-cf86e10008ca</t>
-  </si>
-  <si>
-    <t>attack-pattern--a26ee77d-cf1a-4687-988f-932ccc9542bf</t>
-  </si>
-  <si>
-    <t>attack-pattern--81623f2c-c724-43fa-bbab-429f8575f921</t>
-  </si>
-  <si>
-    <t>attack-pattern--b8fc16d6-7f03-4404-9d8d-f9782a0d4b3e</t>
-  </si>
-  <si>
-    <t>attack-pattern--b041117e-4c21-419b-a1ad-f357fd63741f</t>
-  </si>
-  <si>
-    <t>attack-pattern--61fccaa6-3ad9-4372-8b42-682b13577269</t>
-  </si>
-  <si>
-    <t>attack-pattern--52c17a9d-8e67-4b7c-bddd-a0111496a6f5</t>
-  </si>
-  <si>
-    <t>attack-pattern--3b132a9a-ecc8-4b8b-b93c-77771f5dc46c</t>
-  </si>
-  <si>
-    <t>attack-pattern--99619131-579e-49d3-aa32-d9ba015ed29a</t>
-  </si>
-  <si>
-    <t>attack-pattern--242eeb83-aeba-4f79-a3ae-2f62a5bc3706</t>
+    <t>attack-pattern--f60c3210-890a-4015-a4a9-e1966101ed5d</t>
+  </si>
+  <si>
+    <t>attack-pattern--c985b114-66f8-43e8-a9d5-09f7dcce76d2</t>
+  </si>
+  <si>
+    <t>attack-pattern--9d3f3422-f494-42ab-9385-bc4e8ef727ca</t>
+  </si>
+  <si>
+    <t>attack-pattern--67fd1251-9ad0-415e-94db-14c6fcda7c8c</t>
+  </si>
+  <si>
+    <t>attack-pattern--6819df95-06a3-4c71-874f-8daea090f07e</t>
+  </si>
+  <si>
+    <t>attack-pattern--22337eab-4ab5-4577-a766-4a514a636fe2</t>
+  </si>
+  <si>
+    <t>attack-pattern--ef5c8e81-c4de-408e-a0bb-eeba03e4ef41</t>
+  </si>
+  <si>
+    <t>attack-pattern--d71852a6-d08a-4937-b2b1-ccf143798754</t>
+  </si>
+  <si>
+    <t>attack-pattern--71b8603d-1b4a-45dd-bdc5-58df6fe6a1cb</t>
+  </si>
+  <si>
+    <t>attack-pattern--3953a646-ca74-4d27-bb4b-801773351821</t>
+  </si>
+  <si>
+    <t>attack-pattern--03024756-3f6a-42b3-b93e-2d31c7ce6b6b</t>
+  </si>
+  <si>
+    <t>attack-pattern--3d1653fe-5ea0-4eb0-8c78-f849ecc43e11</t>
+  </si>
+  <si>
+    <t>attack-pattern--9facc2a5-8243-49aa-96cb-a94ef85b25c9</t>
+  </si>
+  <si>
+    <t>attack-pattern--d38398cd-b820-4626-9510-465d56ba906c</t>
+  </si>
+  <si>
+    <t>attack-pattern--02964caf-d52a-4d68-abcc-cdd1ef5fa69d</t>
+  </si>
+  <si>
+    <t>attack-pattern--d5f24756-885a-43f1-a9f0-b0088651bbc3</t>
+  </si>
+  <si>
+    <t>attack-pattern--9162f78a-1b72-4adc-9f8b-0a6b6410a3a7</t>
+  </si>
+  <si>
+    <t>attack-pattern--0de3e487-7362-4416-91f8-3c71cc10d76d</t>
+  </si>
+  <si>
+    <t>attack-pattern--5e67abdd-9625-497c-8eed-591b2d0091a8</t>
+  </si>
+  <si>
+    <t>attack-pattern--9e90f9e3-ced7-476d-acac-467e8c865ca0</t>
+  </si>
+  <si>
+    <t>attack-pattern--f62f4a3e-70ad-4d66-978f-70460748790e</t>
+  </si>
+  <si>
+    <t>attack-pattern--9861afc3-113a-4f8e-ba90-12d851653a4c</t>
+  </si>
+  <si>
+    <t>attack-pattern--cc782e40-0ae3-4f6d-94cb-2828cb2d5005</t>
+  </si>
+  <si>
+    <t>attack-pattern--36fadd8e-e035-4c50-be0d-258be309a516</t>
+  </si>
+  <si>
+    <t>attack-pattern--9596e8a1-16fa-466f-b16e-b567018e83c6</t>
+  </si>
+  <si>
+    <t>attack-pattern--09059676-291f-4053-a7b5-17d93eb87d30</t>
+  </si>
+  <si>
+    <t>attack-pattern--8a804fba-621a-4868-b128-51cebf0ad2b2</t>
+  </si>
+  <si>
+    <t>attack-pattern--738e1811-a9a5-4407-be43-b726fd7e7589</t>
+  </si>
+  <si>
+    <t>attack-pattern--d4d22a9d-86be-4ed6-bb79-7792aad443f3</t>
+  </si>
+  <si>
+    <t>attack-pattern--63335f7f-c1d8-42d3-bab5-4055c59e6a1e</t>
+  </si>
+  <si>
+    <t>attack-pattern--c55f58f1-faf2-498e-84f2-59993e1ecbcc</t>
+  </si>
+  <si>
+    <t>attack-pattern--c7ccd834-4f08-4829-96ae-45e58d47945f</t>
+  </si>
+  <si>
+    <t>attack-pattern--c93829ec-d90f-41a9-9191-466a6365de51</t>
+  </si>
+  <si>
+    <t>attack-pattern--c671af96-e92c-44ff-820d-00bdb7de4fca</t>
+  </si>
+  <si>
+    <t>attack-pattern--4a811ffb-e200-4e7b-a48d-5dbb2e05d21b</t>
+  </si>
+  <si>
+    <t>attack-pattern--7ee9829e-072b-48f0-b801-b5b627c8bf1a</t>
+  </si>
+  <si>
+    <t>attack-pattern--ea9a2533-0faa-4b9d-bb0e-237ca902e1d7</t>
+  </si>
+  <si>
+    <t>attack-pattern--4b4499c1-7976-4838-ac5f-1b2503e91894</t>
+  </si>
+  <si>
+    <t>attack-pattern--b0851c83-e4d2-41c1-b5de-9115df406339</t>
+  </si>
+  <si>
+    <t>attack-pattern--137a55c1-3751-4f3e-b038-0a8a31ae7b53</t>
+  </si>
+  <si>
+    <t>attack-pattern--2bb142f3-19c9-4d2d-ab6b-e91a6d1eb45d</t>
+  </si>
+  <si>
+    <t>attack-pattern--09c9ca23-10d8-4f0f-a7dd-e99bb022299a</t>
+  </si>
+  <si>
+    <t>attack-pattern--6a388bfd-b3f8-4136-a3d0-3b6c92b62616</t>
+  </si>
+  <si>
+    <t>attack-pattern--e1c78d1f-6f07-4f4b-9220-6d455354bc64</t>
+  </si>
+  <si>
+    <t>attack-pattern--40f36bf9-2850-4992-b47f-4abe909a0e93</t>
+  </si>
+  <si>
+    <t>attack-pattern--b34ebb98-d962-4987-8399-890eef9c69fe</t>
+  </si>
+  <si>
+    <t>attack-pattern--cbff6b3a-8340-4986-9183-3c02b87fd1b2</t>
+  </si>
+  <si>
+    <t>attack-pattern--2f0e072e-5d5e-458e-a5c3-8efbaef46084</t>
+  </si>
+  <si>
+    <t>attack-pattern--41699f0f-f822-4dbc-b201-dca7ac3eddce</t>
+  </si>
+  <si>
+    <t>attack-pattern--07605117-d49e-4edb-b205-a42d341fbafe</t>
+  </si>
+  <si>
+    <t>attack-pattern--77c6e8eb-0074-49c8-90cd-9c830db4859f</t>
+  </si>
+  <si>
+    <t>attack-pattern--ed457228-1fd9-4a65-ac85-388ba6460f94</t>
+  </si>
+  <si>
+    <t>attack-pattern--12023694-fdfd-480d-990d-fefa0cc12655</t>
+  </si>
+  <si>
+    <t>attack-pattern--3eff3cd8-fbaf-4e5d-b38e-c72604acb3ce</t>
+  </si>
+  <si>
+    <t>attack-pattern--d984185b-2502-414b-969d-f165cdeedc31</t>
+  </si>
+  <si>
+    <t>attack-pattern--8a5da3da-67cf-4659-bb91-0b28685766a1</t>
+  </si>
+  <si>
+    <t>attack-pattern--76b6c6fb-ce17-427d-b717-16011ae54b6e</t>
+  </si>
+  <si>
+    <t>attack-pattern--6e962dbe-f818-407b-b5a6-3eec9fbe9ec2</t>
+  </si>
+  <si>
+    <t>attack-pattern--6f08f0ef-8704-4d0e-90f5-ad421918d899</t>
+  </si>
+  <si>
+    <t>attack-pattern--86f1c7c0-561e-4b45-97c0-faad41484e38</t>
+  </si>
+  <si>
+    <t>attack-pattern--36e1d7c1-2f0e-41c6-8aee-177df4bdbc61</t>
+  </si>
+  <si>
+    <t>attack-pattern--0d6e1a1e-2c33-4280-86f2-8a1d0049b089</t>
+  </si>
+  <si>
+    <t>attack-pattern--a882288f-98fe-4c75-859a-17d669c08376</t>
+  </si>
+  <si>
+    <t>attack-pattern--a87aa45d-2118-4e87-af92-e75e367453c9</t>
+  </si>
+  <si>
+    <t>attack-pattern--b3a3b655-dacd-4ee5-bae1-68801c3d15dc</t>
+  </si>
+  <si>
+    <t>attack-pattern--2d723928-4bb8-45b5-86d4-a6f2398ca02f</t>
+  </si>
+  <si>
+    <t>attack-pattern--5df092aa-9e0d-440d-8aa0-5f9988432ae3</t>
+  </si>
+  <si>
+    <t>attack-pattern--3c5f8bcd-ee2b-4396-9e79-3c99fcc96d81</t>
+  </si>
+  <si>
+    <t>attack-pattern--8861e444-81bb-468e-9fc5-8b7e401e8898</t>
+  </si>
+  <si>
+    <t>attack-pattern--da48c22f-a5e2-41e7-97e4-07bfc4156350</t>
+  </si>
+  <si>
+    <t>attack-pattern--c6da22a5-ceb4-4f40-a3bc-bcd6e655d591</t>
+  </si>
+  <si>
+    <t>attack-pattern--fef3fc3b-399c-41e0-8c76-a6eb1d014ada</t>
+  </si>
+  <si>
+    <t>attack-pattern--0b6448a8-18a4-4d48-bfcf-172a74724542</t>
+  </si>
+  <si>
+    <t>attack-pattern--edd49cde-2190-45a8-9277-0fafcda1502c</t>
+  </si>
+  <si>
+    <t>attack-pattern--8f3de97b-1ed5-4594-9889-41cd32d8adf5</t>
+  </si>
+  <si>
+    <t>attack-pattern--f2e939fc-283e-4bea-9fbf-f17acac31435</t>
+  </si>
+  <si>
+    <t>attack-pattern--1f8e90a1-2fa1-4e0c-9de7-2a6b61fc3412</t>
+  </si>
+  <si>
+    <t>attack-pattern--4b8920a8-f486-4065-aff8-4e7b6ee8b829</t>
+  </si>
+  <si>
+    <t>attack-pattern--b2df162e-6cd7-4286-8841-dbeff90a7e20</t>
+  </si>
+  <si>
+    <t>attack-pattern--02c5997b-a7da-48ac-96da-c4daa1aafc35</t>
+  </si>
+  <si>
+    <t>attack-pattern--5f90feb8-5507-456c-9d1d-0e0e3cce55de</t>
+  </si>
+  <si>
+    <t>attack-pattern--d051e585-aa48-4964-b54e-2e08adc472f9</t>
+  </si>
+  <si>
+    <t>attack-pattern--edcb13e5-fbb1-4396-9e8c-1e3fe9dde52c</t>
   </si>
   <si>
     <t>technique</t>
@@ -1676,7 +1676,7 @@
     <t>Массовый насильственный призыв полевыми военкоматами населения только что освобожденных территорий в ряды Красной армии. (Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
   </si>
   <si>
-    <t>Применение разрушительных медикаментозных препаратов (нейролептиков) в качестве средства физического и психологического давления на здоровых правозащитников в закрытых стационарах. (Citation: Карательная психиатрия в России: назад в СССР? 2026)</t>
+    <t>Применение разрушительных медикаментозных препаратов (нейролептиков) в качестве средства физического и психологического давления на здоровых правозащитников в закрытых стационарах. (Citation: Карательная психиатрия в России: назад в СССР? 2020)</t>
   </si>
   <si>
     <t>Секретные протоколы к Пакту Молотова — Риббентропа с нацистской Германией по разделу сфер влияния в Восточной Европе и легализации вторжения. (Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
@@ -1754,571 +1754,571 @@
     <t>Введение государственной монополии на торговлю хлебом и централизованный контроль над распределением товаров. (Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.) 2013)</t>
   </si>
   <si>
-    <t>relationship--19f5ae4f-6f55-4234-8e02-b7849d67cb3e</t>
-  </si>
-  <si>
-    <t>relationship--a8c565aa-1b03-445d-ad0a-cfa9b9774625</t>
-  </si>
-  <si>
-    <t>relationship--1200f03f-0995-4007-bba8-9b9104523678</t>
-  </si>
-  <si>
-    <t>relationship--27c6c544-dbd7-447d-b13b-dd7cf18d09bd</t>
-  </si>
-  <si>
-    <t>relationship--745a6e9f-ae84-4c45-8455-dfaf312b5fdc</t>
-  </si>
-  <si>
-    <t>relationship--37839205-46ec-4e2f-8123-a85d91fe5d32</t>
-  </si>
-  <si>
-    <t>relationship--c04707e2-dee7-4657-b31b-5319724b0be3</t>
-  </si>
-  <si>
-    <t>relationship--7f12e6bd-3864-44df-9d27-9e79fd2cda83</t>
-  </si>
-  <si>
-    <t>relationship--65257f7e-4d5c-490a-a72b-c0e1abf828a7</t>
-  </si>
-  <si>
-    <t>relationship--fbf0263d-c0d7-405f-b574-c66a4956efe8</t>
-  </si>
-  <si>
-    <t>relationship--2e23a33f-3d39-41cc-befb-bbb2bec46212</t>
-  </si>
-  <si>
-    <t>relationship--115eb83d-7c72-4d69-9c7a-0a7dfb16567f</t>
-  </si>
-  <si>
-    <t>relationship--1cb5a9bc-28f5-4eaa-8c53-1ab0603b1115</t>
-  </si>
-  <si>
-    <t>relationship--c8051db6-217b-4b3c-a077-bc2246f2ca5d</t>
-  </si>
-  <si>
-    <t>relationship--69097e44-b340-41fb-b71b-a9e4bb5bdf34</t>
-  </si>
-  <si>
-    <t>relationship--da778b0c-13fe-4c8b-b58a-37a6413f985d</t>
-  </si>
-  <si>
-    <t>relationship--c6d2e80f-8b05-4297-a133-b19cc7359f40</t>
-  </si>
-  <si>
-    <t>relationship--fc016907-a6b1-4ccf-9aa3-0e5134d2efbb</t>
-  </si>
-  <si>
-    <t>relationship--303f721d-3aa6-4707-a40a-622fff9209ed</t>
-  </si>
-  <si>
-    <t>relationship--98a4a0fd-ffbd-4ae0-b54c-356cd63b6fe9</t>
-  </si>
-  <si>
-    <t>relationship--2ae8fd5a-8463-4519-b1a7-144cff5caae3</t>
-  </si>
-  <si>
-    <t>relationship--c7f93fbc-e3f5-4fc6-bd06-1d5f0ef8b534</t>
-  </si>
-  <si>
-    <t>relationship--829bbe12-1433-4ddc-86fe-a9f1576358d6</t>
-  </si>
-  <si>
-    <t>relationship--380f0ba5-40d6-4b11-8f4d-532071f0f8fc</t>
-  </si>
-  <si>
-    <t>relationship--5720eeb6-cb68-4aec-a169-61af53093498</t>
-  </si>
-  <si>
-    <t>relationship--2c53304b-a8ab-4cd6-96f9-47d007a41437</t>
-  </si>
-  <si>
-    <t>relationship--f5330dcf-6ea7-4953-86d3-afd38052cec3</t>
-  </si>
-  <si>
-    <t>relationship--4f973e78-494d-4faf-af03-628495b9e2e2</t>
-  </si>
-  <si>
-    <t>relationship--a8477547-160e-4f85-93b6-0dd8e8998c16</t>
-  </si>
-  <si>
-    <t>relationship--b1cf70e4-2ceb-44ee-b30e-ae14d097b02a</t>
-  </si>
-  <si>
-    <t>relationship--e55fd8fc-48c9-4389-9653-bb0460d9a8e6</t>
-  </si>
-  <si>
-    <t>relationship--b2f59554-4941-4365-81e1-9d9088a01b1d</t>
-  </si>
-  <si>
-    <t>relationship--ebb09495-6544-4894-98c1-d61731361695</t>
-  </si>
-  <si>
-    <t>relationship--5d027595-85a0-41f3-af88-51ea8d13445b</t>
-  </si>
-  <si>
-    <t>relationship--9ca3e2d3-e98d-42ad-a196-306d91954152</t>
-  </si>
-  <si>
-    <t>relationship--0dfe3dec-a7b5-46f6-91f7-d7f7d04cee19</t>
-  </si>
-  <si>
-    <t>relationship--44b60aea-8e56-49cc-ba63-c25d52d6b064</t>
-  </si>
-  <si>
-    <t>relationship--6922e89d-789c-4920-9971-c9e0aec8abef</t>
-  </si>
-  <si>
-    <t>relationship--643726f0-6b49-4ff0-bf27-524106570628</t>
-  </si>
-  <si>
-    <t>relationship--99750379-0991-49d2-845a-38e0534bb2b9</t>
-  </si>
-  <si>
-    <t>relationship--17af9190-ed2c-4d9c-bc94-fde195349df0</t>
-  </si>
-  <si>
-    <t>relationship--7813f1f2-b6fd-40fb-af15-dd9a2ca04a90</t>
-  </si>
-  <si>
-    <t>relationship--fecccdd6-4dba-4297-ae6b-860f0d654d51</t>
-  </si>
-  <si>
-    <t>relationship--247c1400-d20a-4f06-9958-75c299197f0d</t>
-  </si>
-  <si>
-    <t>relationship--ccc3baee-92ba-4d65-a274-591c4eca4754</t>
-  </si>
-  <si>
-    <t>relationship--c525349f-f773-4156-9f8b-9539d939dce0</t>
-  </si>
-  <si>
-    <t>relationship--5291ce1a-3273-4000-8902-06bb255bf8af</t>
-  </si>
-  <si>
-    <t>relationship--e319ff58-0abb-4c3d-a306-b795663ff85e</t>
-  </si>
-  <si>
-    <t>relationship--52f3ee40-6928-4e92-8645-10821b4fb24c</t>
-  </si>
-  <si>
-    <t>relationship--578721a1-f1b0-4860-b1b0-e6ec697710f3</t>
-  </si>
-  <si>
-    <t>relationship--157cc1c4-fb87-4900-98ac-90a0c2bee8c6</t>
-  </si>
-  <si>
-    <t>relationship--ef982e88-c329-463a-8244-7b373320d856</t>
-  </si>
-  <si>
-    <t>relationship--0ebf4f68-0ae0-48cb-b8e1-064f3cf37f14</t>
-  </si>
-  <si>
-    <t>relationship--422a69fb-b923-4fe2-b6f9-5cf222bff621</t>
-  </si>
-  <si>
-    <t>relationship--7f665ce4-c8c2-4fa5-a183-cf888b37dfad</t>
-  </si>
-  <si>
-    <t>relationship--97d8db77-03f1-4510-af5d-d57136d85cc4</t>
-  </si>
-  <si>
-    <t>relationship--66f6c6bb-f86c-4d70-98c4-a20458570037</t>
-  </si>
-  <si>
-    <t>relationship--4278dd17-e79a-4b66-991d-5b36d1301c23</t>
-  </si>
-  <si>
-    <t>relationship--cb4fc774-fa24-4943-8d13-193a0dcc00a9</t>
-  </si>
-  <si>
-    <t>relationship--83e456d4-226f-4816-ac4d-685c06c8b5d1</t>
-  </si>
-  <si>
-    <t>relationship--cf0446a2-000f-4ac1-8051-cb41f7571f94</t>
-  </si>
-  <si>
-    <t>relationship--70f0a8fc-c11f-4e8a-ab22-0b57ed0243fd</t>
-  </si>
-  <si>
-    <t>relationship--fde26adc-952e-4eae-8c32-90f8e2c289f1</t>
-  </si>
-  <si>
-    <t>relationship--ef96ae40-c63a-483c-af98-eb120db0d729</t>
-  </si>
-  <si>
-    <t>relationship--7e73fe42-7c64-47f3-98ed-490e5879d6cb</t>
-  </si>
-  <si>
-    <t>relationship--e495833b-e7fc-4a45-a3b0-088de55613ab</t>
-  </si>
-  <si>
-    <t>relationship--87b59acc-3517-4ef4-a487-ff0cb738d26b</t>
-  </si>
-  <si>
-    <t>relationship--5199a200-76f5-4226-a15c-2edff1f1dd8f</t>
-  </si>
-  <si>
-    <t>relationship--979dd474-a489-4302-820f-6b0fe99ac0b8</t>
-  </si>
-  <si>
-    <t>relationship--95be85f6-ea3f-49c7-8176-47fb2b14acc3</t>
-  </si>
-  <si>
-    <t>relationship--c5f89a37-f7ea-4fc3-8d53-44385be766c0</t>
-  </si>
-  <si>
-    <t>relationship--2460c04f-37b2-4b3b-986b-ca71811d32d2</t>
-  </si>
-  <si>
-    <t>relationship--b76c4f0c-9e86-405c-885c-2a6a1e03aacb</t>
-  </si>
-  <si>
-    <t>relationship--90d5f2c3-21ed-4495-a244-515610ebd773</t>
-  </si>
-  <si>
-    <t>relationship--04c02d46-fbe1-4ad2-9fb3-cb301cc21db0</t>
-  </si>
-  <si>
-    <t>relationship--14da342c-de4d-4fa0-9852-1822f2915a15</t>
-  </si>
-  <si>
-    <t>relationship--1a003ba2-1a44-4896-85a2-46ac6ed81310</t>
-  </si>
-  <si>
-    <t>relationship--ef90f573-128f-4d2a-8626-4d9b0a981ad1</t>
-  </si>
-  <si>
-    <t>relationship--4e429355-42b0-4de6-aa4f-6f3ebe099a86</t>
-  </si>
-  <si>
-    <t>relationship--deacdc42-71b6-4dd8-8aaf-69b66e210301</t>
-  </si>
-  <si>
-    <t>relationship--64b3a5f9-b367-4eed-81cd-808883bd7563</t>
-  </si>
-  <si>
-    <t>relationship--5beba3b0-257f-42ae-937c-76502cc6e4d6</t>
-  </si>
-  <si>
-    <t>relationship--6852c501-da52-4547-9314-82638d0cae16</t>
-  </si>
-  <si>
-    <t>relationship--d06c83c0-473d-44af-b216-94609b2ae705</t>
-  </si>
-  <si>
-    <t>relationship--38198316-4d10-46d4-8667-986f6ab7425b</t>
-  </si>
-  <si>
-    <t>relationship--80dee8f1-1b29-420d-9c15-fecf53ee3229</t>
-  </si>
-  <si>
-    <t>relationship--20d9dd2b-1d77-4b5f-b0a3-8edbdd544be6</t>
-  </si>
-  <si>
-    <t>relationship--b59a2993-5458-4be6-a1be-fc61ae3e2225</t>
-  </si>
-  <si>
-    <t>relationship--b0df84c2-ffdb-42c0-9d0a-04e4e769ff16</t>
-  </si>
-  <si>
-    <t>relationship--3db00a0a-a50a-4399-8d23-cbc942f47e7a</t>
-  </si>
-  <si>
-    <t>relationship--71d87ecd-a71b-4b1b-95a1-0b26f86e8f98</t>
-  </si>
-  <si>
-    <t>relationship--9bbeaaef-abf9-434e-b308-d523c2070af7</t>
-  </si>
-  <si>
-    <t>relationship--f68e21ae-6621-4ffc-9a90-70affdec2c77</t>
-  </si>
-  <si>
-    <t>relationship--d192470f-32da-438c-a680-713ad35a66ff</t>
-  </si>
-  <si>
-    <t>relationship--c9a4f0a0-2fb1-48db-96bb-9f4d75f5183c</t>
-  </si>
-  <si>
-    <t>relationship--d438fc28-b978-4835-a52b-9de40988fce1</t>
-  </si>
-  <si>
-    <t>relationship--c2bf44c9-7582-473c-92bf-6200c6e2b97d</t>
-  </si>
-  <si>
-    <t>relationship--6c4ab8b6-93db-4163-9f82-ef7f84d805f8</t>
-  </si>
-  <si>
-    <t>relationship--369a4d9b-8b07-4672-a7a4-bef505202f2d</t>
-  </si>
-  <si>
-    <t>relationship--be1d9a30-5d9f-48d6-94c6-4146b7a038ff</t>
-  </si>
-  <si>
-    <t>relationship--6e6c1595-7a47-4b2c-8b88-04b9af47eba6</t>
-  </si>
-  <si>
-    <t>relationship--3c95514f-4ea4-47eb-a08a-5cc3989990e3</t>
-  </si>
-  <si>
-    <t>relationship--058e246d-cf7c-4957-9fac-45022e7c46dd</t>
-  </si>
-  <si>
-    <t>relationship--59519324-c28f-47e3-a28e-6833ee4ef511</t>
-  </si>
-  <si>
-    <t>relationship--29300e50-6531-4e7e-8695-0e9aa52a44c5</t>
-  </si>
-  <si>
-    <t>relationship--eeef4c23-15df-4135-8d66-37934eedba06</t>
-  </si>
-  <si>
-    <t>relationship--747eaf17-b939-49d0-94c9-26d9e039c287</t>
-  </si>
-  <si>
-    <t>relationship--36e8d7e1-4708-44a6-bc91-8fc9d1960db7</t>
-  </si>
-  <si>
-    <t>relationship--7897de01-e8e3-439c-937f-58471ac53ad1</t>
-  </si>
-  <si>
-    <t>relationship--458e1dca-67b7-48d8-9f8d-ba4fba34172d</t>
-  </si>
-  <si>
-    <t>relationship--69db264e-cfb6-4084-8699-74a3451b8d89</t>
-  </si>
-  <si>
-    <t>relationship--f266400a-d882-49da-8cd0-94d53a8440a7</t>
-  </si>
-  <si>
-    <t>relationship--6dd81fb8-1b0f-414a-b66d-249f578281dc</t>
-  </si>
-  <si>
-    <t>relationship--dfc8a5c6-887e-4c06-a6af-96d5f0a70c71</t>
-  </si>
-  <si>
-    <t>relationship--4a66513f-b03c-404c-8229-00ed0ba5d2bb</t>
-  </si>
-  <si>
-    <t>relationship--bfa2a6bc-d95e-4a9e-bdce-eb211b1b05f0</t>
-  </si>
-  <si>
-    <t>relationship--97b5a942-0c74-4429-b75e-a5f56986e4bc</t>
-  </si>
-  <si>
-    <t>relationship--2be93575-1965-4fb8-9e27-cff22794a83c</t>
-  </si>
-  <si>
-    <t>relationship--30536913-ff45-40b4-97bc-cc83c2842a6c</t>
-  </si>
-  <si>
-    <t>relationship--7c3da382-c3aa-497e-b9e8-34b57f50a40c</t>
-  </si>
-  <si>
-    <t>relationship--9ccfb40e-3145-4cef-8c25-541a85085a7a</t>
-  </si>
-  <si>
-    <t>relationship--48d3bd6c-6d67-427a-a918-a229472348fe</t>
-  </si>
-  <si>
-    <t>relationship--aa3ffd81-87db-4dc1-acbe-7ab2b835c1da</t>
-  </si>
-  <si>
-    <t>relationship--b5aaa679-ad3f-4bb1-aeab-3f280c7fb972</t>
-  </si>
-  <si>
-    <t>relationship--975197fc-2168-4040-a841-c3cb46d1da64</t>
-  </si>
-  <si>
-    <t>relationship--c6a49cec-51e2-42e4-8944-71a297fff307</t>
-  </si>
-  <si>
-    <t>relationship--bf415a60-02ac-4937-b134-7ab28b8f509a</t>
-  </si>
-  <si>
-    <t>relationship--08409ba1-6544-46cf-82d3-ab57b733c2c0</t>
-  </si>
-  <si>
-    <t>relationship--2e9e7a4d-97ef-4b84-9422-8bd0e3408640</t>
-  </si>
-  <si>
-    <t>relationship--d888712b-f1f0-4a72-9def-9f80bf399441</t>
-  </si>
-  <si>
-    <t>relationship--6920c644-8f01-4504-bd46-0f8cb4d9c03b</t>
-  </si>
-  <si>
-    <t>relationship--8fce6d91-96be-4a36-95f0-d9129add2414</t>
-  </si>
-  <si>
-    <t>relationship--f2d26557-8399-4687-b41a-7a9d7d2d6991</t>
-  </si>
-  <si>
-    <t>relationship--7e5d14c5-eee2-4516-a591-6ab114b39616</t>
-  </si>
-  <si>
-    <t>relationship--4aedfcbf-0b21-4cc4-bbc3-5fcd7133e96b</t>
-  </si>
-  <si>
-    <t>relationship--91505aef-64b8-4c19-a36b-00572428daae</t>
-  </si>
-  <si>
-    <t>relationship--27f0c620-33ac-4941-ad34-8ad92fb951bb</t>
-  </si>
-  <si>
-    <t>relationship--12987ed8-ae41-4a2b-9119-048b0d1c2a29</t>
-  </si>
-  <si>
-    <t>relationship--8761c9a9-1bca-43d7-b73b-063e2ccb5892</t>
-  </si>
-  <si>
-    <t>relationship--9859d030-c359-4277-a7c0-f4c0dc8ebea0</t>
-  </si>
-  <si>
-    <t>relationship--c6621408-c216-4632-8830-2cb368b491b2</t>
-  </si>
-  <si>
-    <t>relationship--cb149f6a-70ff-44d6-a7a4-dc7705413b7e</t>
-  </si>
-  <si>
-    <t>relationship--ffeec6db-89d9-44b8-a2d8-03c873161126</t>
-  </si>
-  <si>
-    <t>relationship--926fc305-439f-4e90-9d7e-fe20ee9f3b42</t>
-  </si>
-  <si>
-    <t>relationship--01ca3970-7a1f-46c5-8382-cfd35f0c730e</t>
-  </si>
-  <si>
-    <t>relationship--3980e6e6-b81b-4dec-b045-4241533377f8</t>
-  </si>
-  <si>
-    <t>relationship--53f62f92-2229-4f2d-b5e2-1bae14576a8d</t>
-  </si>
-  <si>
-    <t>relationship--10d7e27d-7a6e-4ea2-becb-b09ff7f5c73b</t>
-  </si>
-  <si>
-    <t>relationship--cd8fa868-85aa-4da3-9741-8badb8968112</t>
-  </si>
-  <si>
-    <t>relationship--3c08beb3-52a0-40d1-9c57-534aedd48ebf</t>
-  </si>
-  <si>
-    <t>relationship--bb007e67-caa9-4d3d-ac1f-3d618ab1de0d</t>
-  </si>
-  <si>
-    <t>relationship--84e048ac-fa44-4dce-bd05-e7825e346f5a</t>
-  </si>
-  <si>
-    <t>relationship--328bebba-f51c-42c7-bb3b-3002b8200a7b</t>
-  </si>
-  <si>
-    <t>relationship--2c64d9ce-762f-4b0a-a028-e35551463e03</t>
-  </si>
-  <si>
-    <t>relationship--8c3d77ea-8756-400d-b154-ec811df67412</t>
-  </si>
-  <si>
-    <t>relationship--f5168c16-e698-4bb4-9f50-7debdd5a3630</t>
-  </si>
-  <si>
-    <t>relationship--533afae2-4c7e-47a9-8ba3-ed82137df35a</t>
-  </si>
-  <si>
-    <t>relationship--90ca0b3c-4c3b-4a5b-8af9-4be8770d1bc1</t>
-  </si>
-  <si>
-    <t>relationship--86f0d89f-5cfb-4aa1-89c5-ca829fb54f0f</t>
-  </si>
-  <si>
-    <t>relationship--7e401d36-2524-4677-8cfb-b91674c12d2c</t>
-  </si>
-  <si>
-    <t>relationship--c166204b-0ede-4ddc-b15f-79b040bac7c1</t>
-  </si>
-  <si>
-    <t>relationship--f11f9b9b-57c5-4847-a328-fb70b2c9538c</t>
-  </si>
-  <si>
-    <t>relationship--a9f8de35-3128-45a4-b1cb-eee7174b014b</t>
-  </si>
-  <si>
-    <t>relationship--3db39e09-580e-44b3-8524-bbedcbddbad8</t>
-  </si>
-  <si>
-    <t>relationship--473e0e90-0dd6-42a5-9db8-860333d080e7</t>
-  </si>
-  <si>
-    <t>relationship--4ed2adee-2957-48f2-b787-771ff24842cc</t>
-  </si>
-  <si>
-    <t>relationship--f9253b57-b541-4864-ae70-84fdb5a9a009</t>
-  </si>
-  <si>
-    <t>relationship--ae77458f-2e73-44af-a4fe-568ac150a084</t>
-  </si>
-  <si>
-    <t>relationship--68f8ab90-d155-4302-b323-62f169f8e2f5</t>
-  </si>
-  <si>
-    <t>relationship--4d8fe415-5ba3-4218-b152-93400c0c05c9</t>
-  </si>
-  <si>
-    <t>relationship--328b830e-5848-4d69-aa54-9b9a9d0d71bd</t>
-  </si>
-  <si>
-    <t>relationship--fe1bb675-0c5e-4443-92e1-5e6cb50b2638</t>
-  </si>
-  <si>
-    <t>relationship--852935b0-0e77-4146-a270-7209b4dc693b</t>
-  </si>
-  <si>
-    <t>relationship--aeb32c7a-6284-4a47-b399-d8e136b116e6</t>
-  </si>
-  <si>
-    <t>relationship--5538f8fc-0291-4895-be52-13f6c2a31d03</t>
-  </si>
-  <si>
-    <t>relationship--bef9e71a-f7c1-4419-a5c3-d23d0b7a621d</t>
-  </si>
-  <si>
-    <t>relationship--4d72ad95-a4af-4a8b-832d-c862c922f58e</t>
-  </si>
-  <si>
-    <t>relationship--994616e8-ab99-4e2e-865f-e85308ffbf78</t>
-  </si>
-  <si>
-    <t>relationship--229019bf-8e78-44c5-88aa-d8c0061872c8</t>
-  </si>
-  <si>
-    <t>relationship--a30dfd3f-6cc1-4757-9d3b-910225e77dee</t>
-  </si>
-  <si>
-    <t>relationship--a2282a7f-2ea9-4f73-a79e-ec48d1f5818c</t>
-  </si>
-  <si>
-    <t>relationship--1766db0b-cecf-47d3-a1a1-5b57b20aa5f8</t>
-  </si>
-  <si>
-    <t>relationship--ee97460c-7ddc-4504-b619-a0fd72e0021b</t>
-  </si>
-  <si>
-    <t>relationship--58cc72d7-9597-4352-ace7-99cfbc5bf722</t>
-  </si>
-  <si>
-    <t>relationship--2e5b2622-ab7f-47cf-a1b8-4bc7ecad202c</t>
-  </si>
-  <si>
-    <t>relationship--75adf5f2-87ce-491b-84e6-41803005c30e</t>
-  </si>
-  <si>
-    <t>relationship--f7b6576c-0180-4f1c-af20-95a63a684aaa</t>
-  </si>
-  <si>
-    <t>relationship--bfddeccc-d818-4e1b-986e-a84e6fc111f4</t>
-  </si>
-  <si>
-    <t>relationship--dc7c1483-8d89-4e6a-a8dc-a2ea9f38e025</t>
+    <t>relationship--e51c177b-f601-47d5-9ae9-f6adb3dc397d</t>
+  </si>
+  <si>
+    <t>relationship--baecff7e-dc21-44ea-b863-ca8da3c62424</t>
+  </si>
+  <si>
+    <t>relationship--19d3a78f-c438-41f5-a55e-42a419a860ed</t>
+  </si>
+  <si>
+    <t>relationship--1cff25ec-e815-4f02-a656-6f61d9b4302b</t>
+  </si>
+  <si>
+    <t>relationship--574346d1-3eca-43c0-804a-6a49b0fedfbc</t>
+  </si>
+  <si>
+    <t>relationship--e0c46f26-e4dc-44f2-931a-3de7a380d82c</t>
+  </si>
+  <si>
+    <t>relationship--13b93f7a-eceb-4ba1-985b-9f182d1f8959</t>
+  </si>
+  <si>
+    <t>relationship--c094c5e2-4681-47c6-b649-aac2e30ef63e</t>
+  </si>
+  <si>
+    <t>relationship--6b756697-3af1-4921-8afa-de43e8494726</t>
+  </si>
+  <si>
+    <t>relationship--7cd3a274-997e-4fd8-96bd-ed11dbd871ae</t>
+  </si>
+  <si>
+    <t>relationship--e5064444-57d6-4ead-9e9f-a9797549b00a</t>
+  </si>
+  <si>
+    <t>relationship--a977d06e-c9fb-44fb-be91-d9d4ca6f6739</t>
+  </si>
+  <si>
+    <t>relationship--85d74a25-2849-44c5-be0e-0b95c58d05f8</t>
+  </si>
+  <si>
+    <t>relationship--5601426d-de66-4843-a720-640c317e943a</t>
+  </si>
+  <si>
+    <t>relationship--6b8df6aa-2628-49da-9686-9f4ce8ca52b4</t>
+  </si>
+  <si>
+    <t>relationship--02fbe54f-4fe3-4152-9a95-e00d089ad2d0</t>
+  </si>
+  <si>
+    <t>relationship--b74dbe90-0bd4-44ca-9b39-3217a14f9230</t>
+  </si>
+  <si>
+    <t>relationship--37b54435-8bbc-408e-80ac-ccb32adf9d74</t>
+  </si>
+  <si>
+    <t>relationship--e8277521-5c12-4beb-afa2-1d923b1370fa</t>
+  </si>
+  <si>
+    <t>relationship--aac62415-47fd-4339-998a-96774dc28e1a</t>
+  </si>
+  <si>
+    <t>relationship--d884d995-cb3e-42e1-a219-5b8593d7f55d</t>
+  </si>
+  <si>
+    <t>relationship--e63288e7-7429-4d44-93f8-fbae85b7d73c</t>
+  </si>
+  <si>
+    <t>relationship--88530d1b-75a5-40da-a530-138b7ed1bccb</t>
+  </si>
+  <si>
+    <t>relationship--9ff1122a-8920-4536-a6c9-b3651fe87a41</t>
+  </si>
+  <si>
+    <t>relationship--27d5e8cd-20cd-46d3-9497-57611e95e581</t>
+  </si>
+  <si>
+    <t>relationship--bbd6ac57-e29b-42c1-be57-9bbd7676104e</t>
+  </si>
+  <si>
+    <t>relationship--92239776-053f-40a0-aee3-5f0b9a1c07b5</t>
+  </si>
+  <si>
+    <t>relationship--8a3be6db-85c6-4603-a7fc-bb3acfabea88</t>
+  </si>
+  <si>
+    <t>relationship--5fb44550-4eee-4ab7-b478-d2805c2ba9b4</t>
+  </si>
+  <si>
+    <t>relationship--ca087af6-d503-43b8-abc2-10d6090c5a27</t>
+  </si>
+  <si>
+    <t>relationship--8f906083-a1b0-4547-96cc-b43ba604f276</t>
+  </si>
+  <si>
+    <t>relationship--8b2be964-dd7c-4e0b-82b6-6428d3bf1d42</t>
+  </si>
+  <si>
+    <t>relationship--80915558-dd86-465b-9b1a-e747fb99671c</t>
+  </si>
+  <si>
+    <t>relationship--edcf285d-1f1a-46ea-b28f-a4fcee5a385b</t>
+  </si>
+  <si>
+    <t>relationship--20245c10-e5f3-407c-a3b2-96c8c085b0f1</t>
+  </si>
+  <si>
+    <t>relationship--10e85415-c003-4ef7-a284-05708b6b72be</t>
+  </si>
+  <si>
+    <t>relationship--0fff1f96-3a68-42e4-8e4a-8c8fcb3ce386</t>
+  </si>
+  <si>
+    <t>relationship--5847e598-577d-463a-a3e9-5ca130dd4507</t>
+  </si>
+  <si>
+    <t>relationship--0352eb5f-1132-41ac-9206-b0e16b54436f</t>
+  </si>
+  <si>
+    <t>relationship--852117e1-8630-47eb-8e2e-e22cb2a1564a</t>
+  </si>
+  <si>
+    <t>relationship--5f4533c6-d5e7-41ed-8e89-ce7a3cb061bf</t>
+  </si>
+  <si>
+    <t>relationship--9707dd7d-b5a0-43e2-a6a5-6abce54b7edb</t>
+  </si>
+  <si>
+    <t>relationship--2398c8cc-88a5-4549-b19b-911958d2abe5</t>
+  </si>
+  <si>
+    <t>relationship--c7016342-e47b-4470-a344-672819c70b0d</t>
+  </si>
+  <si>
+    <t>relationship--34666ba1-5c30-4d83-bf2f-c127bb848dcb</t>
+  </si>
+  <si>
+    <t>relationship--5fbe8112-b86f-44db-b323-2f27083564e0</t>
+  </si>
+  <si>
+    <t>relationship--5e064122-2c0d-4930-bf68-fa20ec7fcdea</t>
+  </si>
+  <si>
+    <t>relationship--465dfbec-c935-48b8-ba7c-e8fe3561ca94</t>
+  </si>
+  <si>
+    <t>relationship--1604968c-dab0-43dc-8511-292fcd5575d9</t>
+  </si>
+  <si>
+    <t>relationship--be9a0880-9570-4610-93ec-e350f360d63f</t>
+  </si>
+  <si>
+    <t>relationship--c72b0b22-0cf9-4346-9637-60b6e5b705f9</t>
+  </si>
+  <si>
+    <t>relationship--1f637adc-e5b4-471d-8de1-d477966b1125</t>
+  </si>
+  <si>
+    <t>relationship--56625bef-dd57-4978-9a56-f155789ef3be</t>
+  </si>
+  <si>
+    <t>relationship--b791a492-2bf2-4995-b2d0-6910745d9754</t>
+  </si>
+  <si>
+    <t>relationship--623213a6-abdf-44df-a6fb-c086a684f8b2</t>
+  </si>
+  <si>
+    <t>relationship--468473e7-12c2-46de-88cc-734eafde2868</t>
+  </si>
+  <si>
+    <t>relationship--df901f67-e71f-4192-bcde-7f50d2d9373d</t>
+  </si>
+  <si>
+    <t>relationship--4f31c0bc-a24c-4193-bff2-3a66dae4772f</t>
+  </si>
+  <si>
+    <t>relationship--ec428e67-8568-4f37-a49e-cd580e5c38bd</t>
+  </si>
+  <si>
+    <t>relationship--4ec4ad3d-beca-450e-b6e9-5a93785c5bb0</t>
+  </si>
+  <si>
+    <t>relationship--6effb145-0cd4-4b9f-929f-4c4d89f84ef0</t>
+  </si>
+  <si>
+    <t>relationship--ad081b29-5c12-4d02-8bd1-046b674f4c7c</t>
+  </si>
+  <si>
+    <t>relationship--8f1b3d6f-23b6-4f9b-a8dd-9b3454bd2117</t>
+  </si>
+  <si>
+    <t>relationship--dc5bf458-56f0-43cb-a78d-8bb4bd127e99</t>
+  </si>
+  <si>
+    <t>relationship--9f863b15-ef76-4d35-a0a2-5d4c24c6e6f6</t>
+  </si>
+  <si>
+    <t>relationship--0a76fed9-efeb-4a8e-af6e-d874bc53f71d</t>
+  </si>
+  <si>
+    <t>relationship--465166f8-6a08-4320-aa5b-197bee427cfc</t>
+  </si>
+  <si>
+    <t>relationship--50d6da69-13b5-4383-9a4d-9e6af0892636</t>
+  </si>
+  <si>
+    <t>relationship--67b802bf-c650-4b6b-beac-08a3c96358c8</t>
+  </si>
+  <si>
+    <t>relationship--53719d9d-7011-4032-a70e-8c6138033d7e</t>
+  </si>
+  <si>
+    <t>relationship--5d155807-495a-48a4-be27-5ae299f1c38e</t>
+  </si>
+  <si>
+    <t>relationship--24d049ad-df50-41bf-ba64-070a5db3f232</t>
+  </si>
+  <si>
+    <t>relationship--1912344f-c2b1-497b-8c79-885dac85519f</t>
+  </si>
+  <si>
+    <t>relationship--66da841a-9ba5-4698-9434-a0716c584fcd</t>
+  </si>
+  <si>
+    <t>relationship--a0e26193-7b83-4fac-ba81-a14473696c12</t>
+  </si>
+  <si>
+    <t>relationship--e5ff6d58-7126-41d2-bffc-22be3e559d4c</t>
+  </si>
+  <si>
+    <t>relationship--87e28e8e-0c89-4acc-8d96-191a08c0c4ca</t>
+  </si>
+  <si>
+    <t>relationship--3fc53e7f-aabf-48b1-b1ca-92d9188c5fee</t>
+  </si>
+  <si>
+    <t>relationship--08f43466-659f-422c-be58-91c863e7b936</t>
+  </si>
+  <si>
+    <t>relationship--8160d9a6-4943-4736-a8aa-f256cb2628e3</t>
+  </si>
+  <si>
+    <t>relationship--0fd1b83a-0e8c-485a-9eea-9f1c28469003</t>
+  </si>
+  <si>
+    <t>relationship--955f1858-3345-4ba3-a027-ebbbdc018d52</t>
+  </si>
+  <si>
+    <t>relationship--5f967830-b2b4-4835-b8b3-78e3bb061c70</t>
+  </si>
+  <si>
+    <t>relationship--3662bcda-cf5d-4fd0-9313-620bd45d8adf</t>
+  </si>
+  <si>
+    <t>relationship--97eea6b0-abef-4c35-9150-15ffb0cfd642</t>
+  </si>
+  <si>
+    <t>relationship--4374b082-17aa-4a1e-9780-00373446507e</t>
+  </si>
+  <si>
+    <t>relationship--a38375ec-bc00-4e85-a5b2-013e20b1c61d</t>
+  </si>
+  <si>
+    <t>relationship--dd2f3bc2-fac5-4b98-a5ef-9687daaaa6fc</t>
+  </si>
+  <si>
+    <t>relationship--366d7ed8-a586-4109-9559-6c939ffd576a</t>
+  </si>
+  <si>
+    <t>relationship--402e6d4b-59c4-4e77-9b16-57a4076ae2d5</t>
+  </si>
+  <si>
+    <t>relationship--e9909627-4a7d-495a-834c-315541ab15fd</t>
+  </si>
+  <si>
+    <t>relationship--4b76cb9a-0bed-478d-b892-63357f2f24c9</t>
+  </si>
+  <si>
+    <t>relationship--a93a651a-ffac-4fc7-b9d4-6cc0d508089f</t>
+  </si>
+  <si>
+    <t>relationship--cc43e87c-69f3-4e15-a919-8898b8215090</t>
+  </si>
+  <si>
+    <t>relationship--83e6df16-07fe-41e5-a65b-6ed35c215cc2</t>
+  </si>
+  <si>
+    <t>relationship--5b878410-76cf-418c-b857-a2449022a172</t>
+  </si>
+  <si>
+    <t>relationship--1f29a6cf-c9bd-4e1a-af91-4490d00c1ea6</t>
+  </si>
+  <si>
+    <t>relationship--2cf31521-70c1-4491-a5ae-fe3c4bbc5246</t>
+  </si>
+  <si>
+    <t>relationship--157809ff-2ffb-485c-8b54-1a89d4dcb435</t>
+  </si>
+  <si>
+    <t>relationship--0461225b-8179-4aae-bc0f-d3b7851d4346</t>
+  </si>
+  <si>
+    <t>relationship--5e1ebc3e-adbb-46e4-afea-ca56f35aa3b8</t>
+  </si>
+  <si>
+    <t>relationship--20dfaeff-38ff-450e-b141-6512f93d479c</t>
+  </si>
+  <si>
+    <t>relationship--f6651003-cdfd-476e-964b-b9c1f9814aea</t>
+  </si>
+  <si>
+    <t>relationship--db030bae-c5f5-49ed-8ff4-af0e20ee225d</t>
+  </si>
+  <si>
+    <t>relationship--060b2bb4-62b6-4c64-9527-12b75f6856fb</t>
+  </si>
+  <si>
+    <t>relationship--f105b8ec-d05f-4968-b2d5-c5e5adff5a61</t>
+  </si>
+  <si>
+    <t>relationship--9de38fe8-f56c-4b6d-937c-b36b9e6b8972</t>
+  </si>
+  <si>
+    <t>relationship--f1e432e9-d627-42c5-8582-b9091113bb86</t>
+  </si>
+  <si>
+    <t>relationship--bc55738f-b0ed-416f-844b-6b1f22a7f345</t>
+  </si>
+  <si>
+    <t>relationship--4b753a57-ecd3-4fc6-a713-e0ad97968b62</t>
+  </si>
+  <si>
+    <t>relationship--4e0d7262-08ba-4fb5-bb63-dc30429b3fab</t>
+  </si>
+  <si>
+    <t>relationship--781b4bbf-8a2c-4057-baf5-1878ea619b0c</t>
+  </si>
+  <si>
+    <t>relationship--79f87c09-c697-4dd0-99f2-9fe176f8755c</t>
+  </si>
+  <si>
+    <t>relationship--badcf672-80b4-4756-bc72-46ed253671e1</t>
+  </si>
+  <si>
+    <t>relationship--77906d62-bf50-4cac-88ce-1dd773bab573</t>
+  </si>
+  <si>
+    <t>relationship--16eaf531-3997-47f0-a83e-7f32c635c0fc</t>
+  </si>
+  <si>
+    <t>relationship--8212aa70-f140-43d6-ba87-bfc75ec72e5f</t>
+  </si>
+  <si>
+    <t>relationship--aaa22663-967a-4b00-a539-b09ff557e821</t>
+  </si>
+  <si>
+    <t>relationship--fb30d154-83b6-4539-afb5-0c3888d3bec9</t>
+  </si>
+  <si>
+    <t>relationship--55aba2a5-f217-4d99-9c5b-5f3dac640b92</t>
+  </si>
+  <si>
+    <t>relationship--e8afeeaf-035c-4c76-b5bc-7e4af0f3395c</t>
+  </si>
+  <si>
+    <t>relationship--41a8b0a2-e56f-4893-9cd8-7c65ff389bf8</t>
+  </si>
+  <si>
+    <t>relationship--fb15b942-85d3-4fc7-991d-d9d2041a09e1</t>
+  </si>
+  <si>
+    <t>relationship--c5d8a571-ee0d-419d-8c01-bede9443b942</t>
+  </si>
+  <si>
+    <t>relationship--da556bf9-dba9-4c54-a5e8-c44cb6e48c3d</t>
+  </si>
+  <si>
+    <t>relationship--035189d5-3e56-41ed-98a6-a7efa1dda59a</t>
+  </si>
+  <si>
+    <t>relationship--ba7fc371-952e-4b6b-a61c-45b699357b3d</t>
+  </si>
+  <si>
+    <t>relationship--c35844cb-0555-42da-ba1f-cd933eebe624</t>
+  </si>
+  <si>
+    <t>relationship--4acd9755-b416-4b00-acc6-250ae9622465</t>
+  </si>
+  <si>
+    <t>relationship--0c0d5d6e-42fc-4d8e-902a-a19fe207848e</t>
+  </si>
+  <si>
+    <t>relationship--85e68b26-66be-4060-bc7e-a280bacd4e3a</t>
+  </si>
+  <si>
+    <t>relationship--a74700f2-597f-4f08-aeba-e87654802d35</t>
+  </si>
+  <si>
+    <t>relationship--47cbce4a-835a-4782-be3f-3f40fed7a3c8</t>
+  </si>
+  <si>
+    <t>relationship--03840c67-b080-459b-afa5-dabebcb4d44d</t>
+  </si>
+  <si>
+    <t>relationship--b7e30afc-7d74-4b1e-a1c5-653abf36c875</t>
+  </si>
+  <si>
+    <t>relationship--5f1bc6d9-5417-4f2c-9c50-d84caa46cb19</t>
+  </si>
+  <si>
+    <t>relationship--21c44f8f-68f3-4578-acb9-ef09c6722ab8</t>
+  </si>
+  <si>
+    <t>relationship--13e01f4c-8dd4-4b7d-9a30-3900d9fed55c</t>
+  </si>
+  <si>
+    <t>relationship--9702d5d0-42c1-46ce-b8dd-b0bfb6b33a3c</t>
+  </si>
+  <si>
+    <t>relationship--0a9ba803-afc5-414d-9159-cbe1dec86fdb</t>
+  </si>
+  <si>
+    <t>relationship--59db0a16-d7b1-472c-ba90-58d8e720dc4c</t>
+  </si>
+  <si>
+    <t>relationship--06e37dc0-aec3-40a5-9fdc-0a3900505d13</t>
+  </si>
+  <si>
+    <t>relationship--bffe6e07-ed4b-4734-aa19-1477f29364d2</t>
+  </si>
+  <si>
+    <t>relationship--1c36c5be-b13c-4f11-960f-9b03cbc87f8d</t>
+  </si>
+  <si>
+    <t>relationship--d3fd53b4-18fa-45e9-b69f-6a0d7520a5ca</t>
+  </si>
+  <si>
+    <t>relationship--756d0f2d-207e-4f7b-b0b2-b48292f01566</t>
+  </si>
+  <si>
+    <t>relationship--9a868a03-666e-4f64-b596-5c48bdee52c3</t>
+  </si>
+  <si>
+    <t>relationship--d7fc2066-edf6-47c6-a83c-7206850f0ab5</t>
+  </si>
+  <si>
+    <t>relationship--5d579a13-67d5-448a-adc5-83a4fafe6397</t>
+  </si>
+  <si>
+    <t>relationship--de480653-7c48-4149-8c94-9b269c7d47a4</t>
+  </si>
+  <si>
+    <t>relationship--6a67ff6b-94aa-4750-ab1b-fc32683bdef6</t>
+  </si>
+  <si>
+    <t>relationship--7d309686-d313-4099-bb16-28e1c507b4de</t>
+  </si>
+  <si>
+    <t>relationship--da8866ae-3f47-46eb-94b8-372a984469cd</t>
+  </si>
+  <si>
+    <t>relationship--3a5d6f95-14ab-46c5-b8da-032669b0bae2</t>
+  </si>
+  <si>
+    <t>relationship--024a7113-e248-4822-bea2-30f77d9a7a8f</t>
+  </si>
+  <si>
+    <t>relationship--00ca73d0-0387-42d0-84bc-936fda075d8d</t>
+  </si>
+  <si>
+    <t>relationship--1c8c0f26-e354-4f16-866b-c4ed7978e820</t>
+  </si>
+  <si>
+    <t>relationship--37ca5c6c-a8bd-4cc0-a94a-94c62380ad01</t>
+  </si>
+  <si>
+    <t>relationship--09ca5108-558b-4995-9467-494a354a918a</t>
+  </si>
+  <si>
+    <t>relationship--0e1317d3-00a0-4713-9781-766b42db644e</t>
+  </si>
+  <si>
+    <t>relationship--ba57efe2-3653-460c-a6d1-5293aa19b7ce</t>
+  </si>
+  <si>
+    <t>relationship--19a86362-7955-4dbf-bbb0-1c8de038abc9</t>
+  </si>
+  <si>
+    <t>relationship--105776f8-fb6e-40b1-90d5-51a56bacf1c1</t>
+  </si>
+  <si>
+    <t>relationship--26e34a40-646e-40bd-97fd-af7707fec87e</t>
+  </si>
+  <si>
+    <t>relationship--43674d3b-1755-45c6-be2c-b5e6b83dc1fd</t>
+  </si>
+  <si>
+    <t>relationship--56c13e79-da44-4855-abc6-d1119ccf296a</t>
+  </si>
+  <si>
+    <t>relationship--2b20ec1c-dcf1-4f91-abeb-ebe52c94ed06</t>
+  </si>
+  <si>
+    <t>relationship--7bb3178c-db31-4233-9649-cde63f598fde</t>
+  </si>
+  <si>
+    <t>relationship--8840ff74-0db6-4bb2-b7fb-90692fae5cf7</t>
+  </si>
+  <si>
+    <t>relationship--1abc678f-dce8-47c5-90b4-26b570e01f03</t>
+  </si>
+  <si>
+    <t>relationship--a10fcf23-dced-4c62-8b72-de9252e3dd3e</t>
+  </si>
+  <si>
+    <t>relationship--16744069-cca1-4a02-b485-33f838b5ab31</t>
+  </si>
+  <si>
+    <t>relationship--c4da07a0-ac6b-43bb-acb4-0e1eebb72e1d</t>
+  </si>
+  <si>
+    <t>relationship--b13c20bf-f6f3-496b-9bbc-756d27bcc338</t>
+  </si>
+  <si>
+    <t>relationship--ead18e3d-243e-4bfc-9e35-dcef978fa1a6</t>
+  </si>
+  <si>
+    <t>relationship--daa06fd4-7ec9-441c-9dad-d0b476425de6</t>
+  </si>
+  <si>
+    <t>relationship--efe698ab-5c0f-471e-965f-49902fb52ff3</t>
+  </si>
+  <si>
+    <t>relationship--bc99b34b-c89e-4a48-93d6-98e18c56bd9c</t>
+  </si>
+  <si>
+    <t>relationship--1c294501-8bda-4b29-b345-880b8d39a07c</t>
+  </si>
+  <si>
+    <t>relationship--1420dce4-e170-412c-8605-5ec9480fb9e2</t>
+  </si>
+  <si>
+    <t>relationship--a88ea7e3-49fd-4f48-a25f-2aa2a4cfda6c</t>
+  </si>
+  <si>
+    <t>relationship--4fde23f7-a081-497c-907b-a3499be478c1</t>
+  </si>
+  <si>
+    <t>relationship--c894f2d6-6b3d-43a9-ad2c-6d2c1c596045</t>
+  </si>
+  <si>
+    <t>relationship--01673386-068e-4501-ac11-1263c9fe485e</t>
+  </si>
+  <si>
+    <t>relationship--2c5dfe88-33fb-44bb-9dbc-b2430f5b1ecf</t>
+  </si>
+  <si>
+    <t>relationship--34bf02af-e6fa-4c0e-ad5c-d45c46d77832</t>
+  </si>
+  <si>
+    <t>relationship--52bddd02-b48a-4510-910a-094c4433eb2d</t>
+  </si>
+  <si>
+    <t>relationship--5506c3cf-59c7-46bb-9bf2-902908d87126</t>
+  </si>
+  <si>
+    <t>relationship--3984cea3-d47b-4481-8888-c0b1f35969c1</t>
   </si>
   <si>
     <t>C0009</t>
@@ -2933,310 +2933,310 @@
     <t>Юридическое поглощение через создание СССР (1922–1924)</t>
   </si>
   <si>
-    <t>campaign--84bc21e9-f278-45cd-8acb-817742dcff21</t>
-  </si>
-  <si>
-    <t>campaign--4bf56bd2-d5ca-438b-a3aa-5cbc36381133</t>
-  </si>
-  <si>
-    <t>campaign--3bd127a5-73b3-4aac-8fd7-982a95669434</t>
-  </si>
-  <si>
-    <t>campaign--1b611c93-e848-4ee1-8527-8bbbdf2e62a5</t>
-  </si>
-  <si>
-    <t>campaign--09a157f6-2eda-4e89-85e1-0705374ca9ee</t>
-  </si>
-  <si>
-    <t>campaign--d2e92b25-7923-452d-8885-6245a64315da</t>
-  </si>
-  <si>
-    <t>campaign--20b4d9b6-86c9-414d-b7c2-ba45639bfae6</t>
-  </si>
-  <si>
-    <t>campaign--dbcf8329-be72-43a6-9503-bd3b5f80e167</t>
-  </si>
-  <si>
-    <t>campaign--06e4cf4f-1d7a-4669-bfe2-46cf114cf71f</t>
-  </si>
-  <si>
-    <t>campaign--21b1b148-99e1-447f-863e-5f179ec7aac7</t>
-  </si>
-  <si>
-    <t>campaign--d1a75343-e6bc-456b-af9c-67abfebd8778</t>
-  </si>
-  <si>
-    <t>campaign--a1253a3a-9d62-49e1-acc7-7430a198b8bc</t>
-  </si>
-  <si>
-    <t>campaign--7c61ae27-c860-4b7d-9dbc-12b393680025</t>
-  </si>
-  <si>
-    <t>campaign--0c5ea36b-4e12-47ff-8d99-a4a35e4327b0</t>
-  </si>
-  <si>
-    <t>campaign--8ba7050c-642b-4ab9-9ce1-6ca4a4676ab5</t>
-  </si>
-  <si>
-    <t>campaign--6232bf9b-bb63-402d-b03e-9a0515ee09d8</t>
-  </si>
-  <si>
-    <t>campaign--9f962768-2e42-4c2e-a172-9291db92461b</t>
-  </si>
-  <si>
-    <t>campaign--2e0766ba-2d5c-4bab-a68b-5fe011747831</t>
-  </si>
-  <si>
-    <t>campaign--4a0448c0-0001-4134-acd4-941aa1379172</t>
-  </si>
-  <si>
-    <t>campaign--eedf404e-3e21-4116-be4d-0d7601599b91</t>
-  </si>
-  <si>
-    <t>campaign--e62f4c80-a205-4fe1-91c4-85256ac37f31</t>
-  </si>
-  <si>
-    <t>campaign--6ceef077-03f6-482f-8e76-a98491db2913</t>
-  </si>
-  <si>
-    <t>campaign--2248df9e-ba27-43a8-98d8-9026a6b9de03</t>
-  </si>
-  <si>
-    <t>campaign--05daf063-815a-43c4-bdef-868e86a89149</t>
-  </si>
-  <si>
-    <t>campaign--584843e9-c5e0-4087-a142-c385deeb2bdf</t>
-  </si>
-  <si>
-    <t>campaign--a657f3f9-0df3-4ed7-a7a4-a5412ea7ecb6</t>
-  </si>
-  <si>
-    <t>campaign--8f323bf8-3b9b-4bf4-97ad-3d61fc33fd82</t>
-  </si>
-  <si>
-    <t>campaign--6e5202d1-fbbe-422b-84d5-246cb35c0b2d</t>
-  </si>
-  <si>
-    <t>campaign--8ba3d669-f614-429f-9b77-a9cf527ff71d</t>
-  </si>
-  <si>
-    <t>campaign--7ce1e89d-a9af-4fb3-81ee-15ea23718846</t>
-  </si>
-  <si>
-    <t>campaign--6c24cbbb-4ce2-45a1-981a-cf0fd9c34d97</t>
-  </si>
-  <si>
-    <t>campaign--b9baf1bc-a3fa-4050-8722-e4ac1d29b0aa</t>
-  </si>
-  <si>
-    <t>campaign--eb1f4e4b-b946-449e-8752-60b5a41d8094</t>
-  </si>
-  <si>
-    <t>campaign--fa1c9409-7b35-48bb-8f3f-1de992f2a9fe</t>
-  </si>
-  <si>
-    <t>campaign--485bc4b1-d6a0-4262-b92b-de60846a3cc2</t>
-  </si>
-  <si>
-    <t>campaign--f98d27b7-b9b2-4ee5-968d-2242b9fed57d</t>
-  </si>
-  <si>
-    <t>campaign--d9246b40-5b51-4294-bcd6-dba876074271</t>
-  </si>
-  <si>
-    <t>campaign--c084e1db-0f03-44c2-8697-12757be14ecf</t>
-  </si>
-  <si>
-    <t>campaign--78366146-c147-4bca-adbc-91cf59affa19</t>
-  </si>
-  <si>
-    <t>campaign--c4b1a1bd-5808-4f82-8404-cb671321f0b8</t>
-  </si>
-  <si>
-    <t>campaign--4cb4ba5f-3257-4a64-99a7-89c1c8584ea3</t>
-  </si>
-  <si>
-    <t>campaign--bb5621a4-0317-4a72-9557-a3309369a148</t>
-  </si>
-  <si>
-    <t>campaign--c00efded-d911-444c-8743-89ddb7c2a25b</t>
-  </si>
-  <si>
-    <t>campaign--33e7df73-0ba4-4031-911d-d9a34f23381e</t>
-  </si>
-  <si>
-    <t>campaign--398bbef2-59b4-4eae-b7fb-2ddb4325a3db</t>
-  </si>
-  <si>
-    <t>campaign--5e9e3ee9-0edc-47b8-b51f-27d825c93ba6</t>
-  </si>
-  <si>
-    <t>campaign--a928c5b5-bd92-4716-bd4b-8e2e42e22ee8</t>
-  </si>
-  <si>
-    <t>campaign--13a5e084-1143-4c42-82a1-97c7cc060f9c</t>
-  </si>
-  <si>
-    <t>campaign--2f03ada1-afc9-4e6a-b822-aa65414b1b02</t>
-  </si>
-  <si>
-    <t>campaign--6d1a46e6-ac73-4930-aabd-a8f533a687cf</t>
-  </si>
-  <si>
-    <t>campaign--5f6c1d2e-8b43-49f7-9d3f-f3a0c3ae48b1</t>
-  </si>
-  <si>
-    <t>campaign--2e2bed38-682c-4d2f-ad6c-e2bb4c4cfdd0</t>
-  </si>
-  <si>
-    <t>campaign--fcb45d3f-14e8-4834-8b2c-d18b4c8f5273</t>
-  </si>
-  <si>
-    <t>campaign--c86c2f91-e10d-4e8b-b767-78378e15121e</t>
-  </si>
-  <si>
-    <t>campaign--0ba3a916-5b43-4183-b453-0927882dba85</t>
-  </si>
-  <si>
-    <t>campaign--e0cc83b8-2a5f-42f8-8537-a7a3e72ee650</t>
-  </si>
-  <si>
-    <t>campaign--4fa7d988-4c1c-4971-84cf-ca0467775997</t>
-  </si>
-  <si>
-    <t>campaign--49d099af-a6dc-4afe-8188-c064ef26fde7</t>
-  </si>
-  <si>
-    <t>campaign--007f466b-7682-4d8a-b195-22c21ff3e565</t>
-  </si>
-  <si>
-    <t>campaign--8f1d796b-636c-4cd1-86b4-37c3ece5165a</t>
-  </si>
-  <si>
-    <t>campaign--3d806c36-94c1-487f-b65e-9ff91c2a9abb</t>
-  </si>
-  <si>
-    <t>campaign--f2ebdc18-4134-4740-9f13-2c482064e83a</t>
-  </si>
-  <si>
-    <t>campaign--c4507383-caba-4152-b825-48578038d866</t>
-  </si>
-  <si>
-    <t>campaign--127d73b7-ad29-4bc6-bae2-aec0c43bad66</t>
-  </si>
-  <si>
-    <t>campaign--b67d3570-8e41-417e-8f8e-7d5ecb7e1d31</t>
-  </si>
-  <si>
-    <t>campaign--7b0b746d-42c4-4b10-aa04-8bfec1343821</t>
-  </si>
-  <si>
-    <t>campaign--d00c3e48-4826-4f1e-bfb7-118f00d84861</t>
-  </si>
-  <si>
-    <t>campaign--51b9d6b1-568b-4d68-8f9c-19a0b548272b</t>
-  </si>
-  <si>
-    <t>campaign--ce760399-e985-4e95-bb41-7d3b796dd18b</t>
-  </si>
-  <si>
-    <t>campaign--4e66eed7-56a9-48ac-8a18-99a559927eb6</t>
-  </si>
-  <si>
-    <t>campaign--152cca2d-a341-45fd-a306-6690c012f021</t>
-  </si>
-  <si>
-    <t>campaign--387e09ec-bf7a-447c-a918-bcff0ee9da8b</t>
-  </si>
-  <si>
-    <t>campaign--beeb4667-4ab9-4028-94c4-b6b19eefabeb</t>
-  </si>
-  <si>
-    <t>campaign--40524974-ff86-4741-bc58-ccfb35d10bc7</t>
-  </si>
-  <si>
-    <t>campaign--d5059819-4fb3-4b0e-9e0a-5784b854386c</t>
-  </si>
-  <si>
-    <t>campaign--0dca3871-e3fd-47d7-a07f-e9ea15919c0d</t>
-  </si>
-  <si>
-    <t>campaign--d6da9526-4dd6-4eb9-abfd-44a5e1879d41</t>
-  </si>
-  <si>
-    <t>campaign--b1e8059c-3914-414e-8a6d-0fb74549bec8</t>
-  </si>
-  <si>
-    <t>campaign--2660323c-96cd-4d12-920b-3ca598fbdb74</t>
-  </si>
-  <si>
-    <t>campaign--a51dfeb5-c6ce-44b2-9bc5-c4c6687bd2f0</t>
-  </si>
-  <si>
-    <t>campaign--f3a217be-13bd-488e-b046-33d4a55b2cf3</t>
-  </si>
-  <si>
-    <t>campaign--5424b97c-0790-47c0-bc6a-99fda22a8e9d</t>
-  </si>
-  <si>
-    <t>campaign--6733da7e-2f67-4c13-97a6-00b05a549f10</t>
-  </si>
-  <si>
-    <t>campaign--ce5cc518-cbce-4e92-b8ff-30e504c15c2c</t>
-  </si>
-  <si>
-    <t>campaign--2907649b-fd94-42fa-8784-f18f4584d71a</t>
-  </si>
-  <si>
-    <t>campaign--dddb4201-585e-47c1-95e9-425b0730fb90</t>
-  </si>
-  <si>
-    <t>campaign--cf6632c9-6e3d-4cbc-9dce-724891b573c7</t>
-  </si>
-  <si>
-    <t>campaign--e7ee89b0-2cb6-4b84-948c-7057dd523852</t>
-  </si>
-  <si>
-    <t>campaign--eddd1738-28fd-4da0-b6f4-7c44a32152b7</t>
-  </si>
-  <si>
-    <t>campaign--5fa57ffc-7b8e-49c1-82da-60712fe1a716</t>
-  </si>
-  <si>
-    <t>campaign--466f1dd3-c4d2-4076-b0d7-d52a41e7bc83</t>
-  </si>
-  <si>
-    <t>campaign--11dce568-2d19-4c59-bdfd-64ec6fced3e6</t>
-  </si>
-  <si>
-    <t>campaign--0356e86e-0974-45cf-b41d-6997de20ba10</t>
-  </si>
-  <si>
-    <t>campaign--0956db31-89c5-43f3-aaa6-f6d9b3b7ff12</t>
-  </si>
-  <si>
-    <t>campaign--5177f321-68a6-4d63-a678-c5265f63243b</t>
-  </si>
-  <si>
-    <t>campaign--7402cc4a-618b-4851-8075-cb883379e3c0</t>
-  </si>
-  <si>
-    <t>campaign--b5ce00ca-7682-4ce8-9c4c-8be0c65df490</t>
-  </si>
-  <si>
-    <t>campaign--af98cd78-ddfd-4a73-8ab2-5b920e8221ac</t>
-  </si>
-  <si>
-    <t>campaign--9f187028-927d-4536-ba2f-3f2177c0e164</t>
-  </si>
-  <si>
-    <t>campaign--66970f35-4e71-491e-932e-1fee6b188e71</t>
-  </si>
-  <si>
-    <t>campaign--d419efc6-e0ba-4f5e-83a2-46e1d38cd231</t>
-  </si>
-  <si>
-    <t>campaign--09ffe87c-9f1c-4a9e-9879-3648aa2d3535</t>
+    <t>campaign--d5d3608b-1e2e-4e8e-9e3e-172b7ae8783f</t>
+  </si>
+  <si>
+    <t>campaign--da1bd8ae-397a-4c07-81d5-4ee62243c68b</t>
+  </si>
+  <si>
+    <t>campaign--6ba841e9-a6e2-4de1-ae16-ca96739e35ed</t>
+  </si>
+  <si>
+    <t>campaign--d25e87a6-7133-4e11-8e93-259d4f2bd994</t>
+  </si>
+  <si>
+    <t>campaign--327371af-9be7-44c2-8b57-7e51eea988c4</t>
+  </si>
+  <si>
+    <t>campaign--e31b1ed6-33c7-4d93-a2c6-a9b1dac0ac8c</t>
+  </si>
+  <si>
+    <t>campaign--000c635b-27f2-43b1-b98d-ff81a4105054</t>
+  </si>
+  <si>
+    <t>campaign--13625203-0aca-405b-9409-d6bb04dedcc2</t>
+  </si>
+  <si>
+    <t>campaign--c89888d0-b5d3-4947-b33d-d1d066710b8d</t>
+  </si>
+  <si>
+    <t>campaign--5b0cdeff-e761-4c3f-ba0c-feaec1ead563</t>
+  </si>
+  <si>
+    <t>campaign--cbda1a24-f09e-414b-ab6c-1177afcf6579</t>
+  </si>
+  <si>
+    <t>campaign--477d33b8-e868-4f14-994c-3ff87914d154</t>
+  </si>
+  <si>
+    <t>campaign--d07a6a51-42fd-4fca-9e60-9f47a2f3d55b</t>
+  </si>
+  <si>
+    <t>campaign--6dc22dba-186d-44f2-b8e5-932b3d3ae163</t>
+  </si>
+  <si>
+    <t>campaign--30e8ed62-d3e8-4143-9e5e-632bd7aa23cc</t>
+  </si>
+  <si>
+    <t>campaign--5a248622-bb69-496e-b7a9-6563aebba048</t>
+  </si>
+  <si>
+    <t>campaign--35ebb683-a8d6-4486-b3b2-f449826b17ce</t>
+  </si>
+  <si>
+    <t>campaign--9d8a0b71-9771-4b85-a072-eb7f2ebaaa79</t>
+  </si>
+  <si>
+    <t>campaign--04b69ccd-9489-447b-99a2-77765d33a863</t>
+  </si>
+  <si>
+    <t>campaign--e29a7c8b-78d8-4200-a28e-b29c47fd3db4</t>
+  </si>
+  <si>
+    <t>campaign--bee06f63-5b9a-40ee-8ded-3807e18b2794</t>
+  </si>
+  <si>
+    <t>campaign--12a31509-f6b1-4af2-ba71-d0d3f1a7e55c</t>
+  </si>
+  <si>
+    <t>campaign--cfd8e869-e600-4d3e-ab87-ab274a92891e</t>
+  </si>
+  <si>
+    <t>campaign--6569f13e-42ba-41d7-a075-7940b2fa7c53</t>
+  </si>
+  <si>
+    <t>campaign--b375cce2-197a-4d61-84e5-bc95c4f061aa</t>
+  </si>
+  <si>
+    <t>campaign--d1be4871-85b3-4161-b768-fcbdd3f3d268</t>
+  </si>
+  <si>
+    <t>campaign--b4a7dd59-002b-4a93-b13c-ab142a60073b</t>
+  </si>
+  <si>
+    <t>campaign--a06fac12-cd5a-4e5a-b61a-efbc0cd5c005</t>
+  </si>
+  <si>
+    <t>campaign--380516f0-c58a-4738-90e3-693af3883357</t>
+  </si>
+  <si>
+    <t>campaign--20b012fa-ab52-4e32-8992-ea76da37110f</t>
+  </si>
+  <si>
+    <t>campaign--d726fa7f-7c1c-4924-88a6-74444222bd9f</t>
+  </si>
+  <si>
+    <t>campaign--0a86d435-8e69-4f3a-bc96-b3ac668c82bc</t>
+  </si>
+  <si>
+    <t>campaign--fa5a41c0-90cb-4caf-860d-a3428108338f</t>
+  </si>
+  <si>
+    <t>campaign--93b9db3d-54e0-4cd1-a73d-8da9102e4009</t>
+  </si>
+  <si>
+    <t>campaign--2e5633ce-2d35-42b6-9ef4-0bf9c8b1bf35</t>
+  </si>
+  <si>
+    <t>campaign--cb207683-dcc4-4b73-ac2f-0be500edc74f</t>
+  </si>
+  <si>
+    <t>campaign--afb7bd59-6c2a-440a-a21d-5961efba5eff</t>
+  </si>
+  <si>
+    <t>campaign--43bcd15c-cf4f-4445-acbd-65ae81877442</t>
+  </si>
+  <si>
+    <t>campaign--d81de34f-47cd-428a-a41a-09a6f56a9da7</t>
+  </si>
+  <si>
+    <t>campaign--034fab01-25ca-406a-af72-18424cd8865e</t>
+  </si>
+  <si>
+    <t>campaign--65f10cf2-b7b9-4bba-99bd-850bd647691e</t>
+  </si>
+  <si>
+    <t>campaign--5a7b9428-869c-4411-836b-ac68418c3e88</t>
+  </si>
+  <si>
+    <t>campaign--993b7232-af60-4415-a814-7856a5aac9b0</t>
+  </si>
+  <si>
+    <t>campaign--adcbb713-6625-4bb2-bbdb-ca95dce75216</t>
+  </si>
+  <si>
+    <t>campaign--fc8f6110-efac-4b90-b548-1454dac7a19b</t>
+  </si>
+  <si>
+    <t>campaign--5c62e27c-a9a5-4f3d-8c9b-c9e0b90a244b</t>
+  </si>
+  <si>
+    <t>campaign--4ef7374d-4184-4e74-8a4d-61459b26d02f</t>
+  </si>
+  <si>
+    <t>campaign--cfee05cb-c034-4971-a531-902e845ccef3</t>
+  </si>
+  <si>
+    <t>campaign--34f93fca-7d2a-4e55-bc81-7f5697e97ef5</t>
+  </si>
+  <si>
+    <t>campaign--6664b694-3b86-465b-9e27-aea2b4bb1daa</t>
+  </si>
+  <si>
+    <t>campaign--3f943474-7a02-49f9-95d4-6284c13fcf28</t>
+  </si>
+  <si>
+    <t>campaign--8260bb29-de17-4c6d-8152-bcfe4b2b99ab</t>
+  </si>
+  <si>
+    <t>campaign--249316b5-9848-4974-bb96-36f491ad2ff3</t>
+  </si>
+  <si>
+    <t>campaign--51f52048-db4e-4bb3-a9d3-9c3ef5a7efdf</t>
+  </si>
+  <si>
+    <t>campaign--62d59075-a1be-4fc3-bb73-dfbba3d9890f</t>
+  </si>
+  <si>
+    <t>campaign--620a3478-b534-42fe-ae16-eef44729927d</t>
+  </si>
+  <si>
+    <t>campaign--33d73442-ef8e-4272-9b52-8409285e64d4</t>
+  </si>
+  <si>
+    <t>campaign--dde6e95d-8a5e-4d08-9cec-a7ff943a6316</t>
+  </si>
+  <si>
+    <t>campaign--451c6e51-6fd7-493b-82dd-f5b2d321469c</t>
+  </si>
+  <si>
+    <t>campaign--999f0ed3-c7f6-4cbe-b1a2-d7d8d6eedf7b</t>
+  </si>
+  <si>
+    <t>campaign--324dfd0b-8bb9-4e73-b770-c4878fa141b3</t>
+  </si>
+  <si>
+    <t>campaign--e48baa05-e5ad-4906-b269-18674c9abe58</t>
+  </si>
+  <si>
+    <t>campaign--5ac2c3e0-9d38-426d-81e5-09cf5a941ae2</t>
+  </si>
+  <si>
+    <t>campaign--b98a9b9a-6b83-45f6-b65e-38d9bffe4df7</t>
+  </si>
+  <si>
+    <t>campaign--71c8fe9d-7933-4793-8688-8ab211e64903</t>
+  </si>
+  <si>
+    <t>campaign--f8715c92-b16d-427b-8db4-e3a8d3c8f294</t>
+  </si>
+  <si>
+    <t>campaign--4d0ec18b-c72b-4515-9f5d-4246894f9414</t>
+  </si>
+  <si>
+    <t>campaign--d55f729d-5ef5-4b86-a509-1a176d91bbf5</t>
+  </si>
+  <si>
+    <t>campaign--5f5df72e-1fe1-43dd-82d6-8d828a183ff5</t>
+  </si>
+  <si>
+    <t>campaign--6c70c6bf-d458-4a42-a588-2d462edf232e</t>
+  </si>
+  <si>
+    <t>campaign--3e59ca2e-eae8-41fa-b2ec-cb039c9b4210</t>
+  </si>
+  <si>
+    <t>campaign--89ab3728-120a-41b6-b6f8-eee58aa5bf75</t>
+  </si>
+  <si>
+    <t>campaign--15dd6c2c-0e8f-4497-8d49-119a63052355</t>
+  </si>
+  <si>
+    <t>campaign--f5969a82-f450-48d2-a83f-31c2c2fcfc5a</t>
+  </si>
+  <si>
+    <t>campaign--8df71303-011a-488a-a3d5-cfabdf43a3bc</t>
+  </si>
+  <si>
+    <t>campaign--d59baa17-740d-4701-ac73-c8a740a1902e</t>
+  </si>
+  <si>
+    <t>campaign--bb2e0c40-4185-4a26-9a4a-843f0f42fb91</t>
+  </si>
+  <si>
+    <t>campaign--1c942e99-7fdf-43c2-a1c7-0c036960d550</t>
+  </si>
+  <si>
+    <t>campaign--2587cdb8-4685-4f49-ad80-4cf1673de499</t>
+  </si>
+  <si>
+    <t>campaign--4850b46c-5052-41fe-8b42-439a1d32be7b</t>
+  </si>
+  <si>
+    <t>campaign--160fbc62-8a4d-4576-86c8-bb6e8212b355</t>
+  </si>
+  <si>
+    <t>campaign--f726e55f-ac4b-4710-9b09-6b1bd5d7aca3</t>
+  </si>
+  <si>
+    <t>campaign--b12ec413-1bd9-46dd-b084-f775d59555ce</t>
+  </si>
+  <si>
+    <t>campaign--4b166b15-a737-4bfc-a873-ce378b04442b</t>
+  </si>
+  <si>
+    <t>campaign--7f39ffcb-c876-4ac1-97c7-77225d687cf7</t>
+  </si>
+  <si>
+    <t>campaign--c6287a90-fda2-414b-9536-7e8d7b333225</t>
+  </si>
+  <si>
+    <t>campaign--bfff8349-9b26-4bec-993e-4d3fb7792a21</t>
+  </si>
+  <si>
+    <t>campaign--a88279c6-8e3a-4610-98b4-61afdf9b1b00</t>
+  </si>
+  <si>
+    <t>campaign--a7923c48-f560-4ecf-99f5-9b6a59a4c658</t>
+  </si>
+  <si>
+    <t>campaign--bf2d7f34-0a40-4a70-8642-f68ef8dae022</t>
+  </si>
+  <si>
+    <t>campaign--86b88822-1271-4a0b-b652-bac9d6c1e4e8</t>
+  </si>
+  <si>
+    <t>campaign--ab434fb0-c7d3-4c1c-bcbd-c4c4498cf657</t>
+  </si>
+  <si>
+    <t>campaign--a156a043-c7da-45b0-aa0a-5299ead941bb</t>
+  </si>
+  <si>
+    <t>campaign--0cfea08d-0a35-4a62-a6b8-66a75b949383</t>
+  </si>
+  <si>
+    <t>campaign--8a97f881-3742-4d79-9bf1-0d2b3f8bacfe</t>
+  </si>
+  <si>
+    <t>campaign--b12ceb44-a32c-43df-82b7-e817321bdc3c</t>
+  </si>
+  <si>
+    <t>campaign--9c6d7b3b-bfe7-43c5-9b32-9928bf384cb3</t>
+  </si>
+  <si>
+    <t>campaign--2df6168b-6e9d-456f-a84a-30638a365400</t>
+  </si>
+  <si>
+    <t>campaign--d10ef172-c6c8-4f61-9f6c-4be1a77043ec</t>
+  </si>
+  <si>
+    <t>campaign--eecb9861-e70e-403d-bf70-88d38775c3b5</t>
+  </si>
+  <si>
+    <t>campaign--9a356b3e-0022-416c-bda6-336376c7b0f7</t>
+  </si>
+  <si>
+    <t>campaign--3b1dfe61-fc96-495a-92c1-e9617744d5b3</t>
   </si>
   <si>
     <t>campaign</t>
@@ -3410,313 +3410,313 @@
     <t>Указ Александра II: «Заборона ввозити українські книги з-за кордону, заборона підписувати українські тексти під нотами, заборона українських вистав» (Citation: Русифікація України — Вікіпедія 2026).</t>
   </si>
   <si>
-    <t>relationship--12bc8904-99bc-4a55-a768-c6d397e1a829</t>
-  </si>
-  <si>
-    <t>relationship--f69b368a-adad-48c6-8f60-0c29f400c102</t>
-  </si>
-  <si>
-    <t>relationship--18c6088c-8841-4ec9-aac2-46a007ebcc21</t>
-  </si>
-  <si>
-    <t>relationship--a963ff2b-070c-4db6-a06d-e5e88f4f3325</t>
-  </si>
-  <si>
-    <t>relationship--797f6d6f-ef9f-4e5e-ae50-0adf72381d8d</t>
-  </si>
-  <si>
-    <t>relationship--aac285db-9b35-40f3-850d-3879630f39b0</t>
-  </si>
-  <si>
-    <t>relationship--01b73e42-a773-4c1d-ae11-0261602aa1d5</t>
-  </si>
-  <si>
-    <t>relationship--fd3683f7-5961-46fb-a76a-82b65e3a5b73</t>
-  </si>
-  <si>
-    <t>relationship--70eb29ba-2799-438a-823e-c446df6bb1c3</t>
-  </si>
-  <si>
-    <t>relationship--3034bb38-cc9e-4fe3-9842-ae672d1b5536</t>
-  </si>
-  <si>
-    <t>relationship--386bf42f-4150-4986-9814-edbe336dfe55</t>
-  </si>
-  <si>
-    <t>relationship--284bb962-aeb3-442f-b754-228c2dd8867e</t>
-  </si>
-  <si>
-    <t>relationship--d05d0b21-357b-4498-bc88-e7c4cc4f9f9f</t>
-  </si>
-  <si>
-    <t>relationship--d2022ffe-3862-4f2c-9b89-19cb8f674ff3</t>
-  </si>
-  <si>
-    <t>relationship--44935fe7-597d-4305-8969-7d4193d4937e</t>
-  </si>
-  <si>
-    <t>relationship--b237bf26-ef58-44ce-884b-12d24cef4ebc</t>
-  </si>
-  <si>
-    <t>relationship--78f059a7-2d33-49be-9c65-b63c987a69e8</t>
-  </si>
-  <si>
-    <t>relationship--6cd0cf96-c86f-49ec-8146-9ffbe9e15ab1</t>
-  </si>
-  <si>
-    <t>relationship--eb81fea3-4753-4b73-893f-16fd43321646</t>
-  </si>
-  <si>
-    <t>relationship--170c807a-1fe8-4130-977a-13bd8e119f56</t>
-  </si>
-  <si>
-    <t>relationship--cdf4555b-3027-4c26-8582-bdb5ea5f869a</t>
-  </si>
-  <si>
-    <t>relationship--53131930-c0c4-4d4b-9c82-ee16de54ce19</t>
-  </si>
-  <si>
-    <t>relationship--4821fa4d-5f4d-4bfb-8bd6-4a0299575b5b</t>
-  </si>
-  <si>
-    <t>relationship--37cfc5df-0284-43b0-8c9f-621300de40cb</t>
-  </si>
-  <si>
-    <t>relationship--31c52698-3b14-4ed3-b949-6f20a9f44ea9</t>
-  </si>
-  <si>
-    <t>relationship--b392a5a2-6f29-4155-b30e-c35d6e81164a</t>
-  </si>
-  <si>
-    <t>relationship--10b967cf-5d22-49ba-9593-7586cfb25d57</t>
-  </si>
-  <si>
-    <t>relationship--9a4cfe1d-243b-4da7-8f85-a5a234c0de46</t>
-  </si>
-  <si>
-    <t>relationship--229bc6e3-bd6e-4f00-920a-bf0b75aeb3ce</t>
-  </si>
-  <si>
-    <t>relationship--3b64a530-ee75-43af-ad56-3f7be087f2b6</t>
-  </si>
-  <si>
-    <t>relationship--24417c43-3986-4157-a47b-138ce21c1586</t>
-  </si>
-  <si>
-    <t>relationship--d2f3847c-ea68-485c-9b5c-5489b3c02399</t>
-  </si>
-  <si>
-    <t>relationship--243e8e41-8775-4d04-8cf5-4270b8f00b87</t>
-  </si>
-  <si>
-    <t>relationship--1e9db859-18a1-4b08-bbd4-9c8cb097729b</t>
-  </si>
-  <si>
-    <t>relationship--05eb80d0-303e-4b3d-8974-3be40c5a6cdc</t>
-  </si>
-  <si>
-    <t>relationship--c1b7dbad-95fa-4b86-aa0b-f4847943206f</t>
-  </si>
-  <si>
-    <t>relationship--712355d5-0423-4efa-910b-56b77ad545fa</t>
-  </si>
-  <si>
-    <t>relationship--5fbfc696-714c-42dc-a387-89d2a7bb4132</t>
-  </si>
-  <si>
-    <t>relationship--9179dcc8-fd36-43e7-8ebc-45c9b2d0c555</t>
-  </si>
-  <si>
-    <t>relationship--e179b84d-4d95-4dce-a854-38c32b638bc9</t>
-  </si>
-  <si>
-    <t>relationship--d019a938-c6f0-42a3-b4c7-00fc1eac691c</t>
-  </si>
-  <si>
-    <t>relationship--fc05427b-b7ed-4a94-b62c-2bb9ef30d7ad</t>
-  </si>
-  <si>
-    <t>relationship--c5355ea4-9dd7-41b9-a281-58dfe58bacd2</t>
-  </si>
-  <si>
-    <t>relationship--e322551c-b3c2-40e8-9efa-d9fe5c984aab</t>
-  </si>
-  <si>
-    <t>relationship--6fabfad7-778f-461e-9d87-7d2f8192ddc4</t>
-  </si>
-  <si>
-    <t>relationship--1cada7a0-7e70-4c74-85aa-54969bd99f6d</t>
-  </si>
-  <si>
-    <t>relationship--464ccc93-dc4f-4050-bb8b-07a28cef790e</t>
-  </si>
-  <si>
-    <t>relationship--b6b6b49c-9491-4e42-a665-09884c32fa52</t>
-  </si>
-  <si>
-    <t>relationship--0e9d2f82-e202-4317-94cf-8932067cdd33</t>
-  </si>
-  <si>
-    <t>relationship--5b7b09b3-9a51-4d65-a86c-4befe3ab7fbc</t>
-  </si>
-  <si>
-    <t>relationship--f30be867-5cae-40b0-8c91-06f5c306ff2b</t>
-  </si>
-  <si>
-    <t>relationship--ca78e3f5-edc4-46ff-86f6-89fb3c35288e</t>
-  </si>
-  <si>
-    <t>relationship--7752b90a-82a7-4e9c-b827-c26959415840</t>
-  </si>
-  <si>
-    <t>relationship--ffa36b52-804f-4e4a-a467-aff1ccaeb8b2</t>
-  </si>
-  <si>
-    <t>relationship--b1dd4bc9-7ef5-4050-b0f8-f5fb9c2019e0</t>
-  </si>
-  <si>
-    <t>relationship--2ee3efa5-74c8-4255-94b2-ce1b5ff81142</t>
-  </si>
-  <si>
-    <t>relationship--fe6278dd-37ff-4ae0-aaa2-15e5deec1bad</t>
-  </si>
-  <si>
-    <t>relationship--e6bf0e77-c31d-42b9-8cd6-f52b8fb3d2db</t>
-  </si>
-  <si>
-    <t>relationship--5e841f9c-b382-44fc-b069-31d7ed86d613</t>
-  </si>
-  <si>
-    <t>relationship--26b24ed3-bab4-48b5-af20-473d37df73a1</t>
-  </si>
-  <si>
-    <t>relationship--5dc7f800-2702-41e3-a999-ec18d12bdb0b</t>
-  </si>
-  <si>
-    <t>relationship--bb205bd8-3105-49e8-a966-8a5a4b80ce4b</t>
-  </si>
-  <si>
-    <t>relationship--066eb730-edbb-4eb7-be95-30ee7a67bbad</t>
-  </si>
-  <si>
-    <t>relationship--997ffb23-24f9-4bf6-ae61-1773c568c2d6</t>
-  </si>
-  <si>
-    <t>relationship--90927691-a826-45b1-aa61-4b0253556a02</t>
-  </si>
-  <si>
-    <t>relationship--da285461-ab09-48e4-bac7-6e4b7f5c2e1d</t>
-  </si>
-  <si>
-    <t>relationship--ae5ce0c4-d70d-40a0-891a-6472f31c7fa3</t>
-  </si>
-  <si>
-    <t>relationship--a16aa153-ab2d-49f9-96bf-61989c058b71</t>
-  </si>
-  <si>
-    <t>relationship--64487f17-db95-46e3-adff-3d3d2629772b</t>
-  </si>
-  <si>
-    <t>relationship--5c1bd692-3e7e-43aa-907a-435464271bc7</t>
-  </si>
-  <si>
-    <t>relationship--c2595a81-92d7-404b-ad9f-1b290af8866b</t>
-  </si>
-  <si>
-    <t>relationship--bd9c2824-ba1b-4fc6-b7be-815d4341d76c</t>
-  </si>
-  <si>
-    <t>relationship--13d8371a-bd47-4e2d-9833-64256ea7236e</t>
-  </si>
-  <si>
-    <t>relationship--d4f3bacb-f6e3-44e1-948e-fb11cc9afcdb</t>
-  </si>
-  <si>
-    <t>relationship--c561afa2-ce06-447a-8c4c-be71f21480c7</t>
-  </si>
-  <si>
-    <t>relationship--28cf8d5f-6d6f-453c-a201-317c04dee34d</t>
-  </si>
-  <si>
-    <t>relationship--769341f9-ee3b-42c3-b2ab-3398313428ec</t>
-  </si>
-  <si>
-    <t>relationship--2d753309-a85e-415c-a222-0301ec963f66</t>
-  </si>
-  <si>
-    <t>relationship--cc65d3dc-fb26-4e54-b54f-9d2c812c7cff</t>
-  </si>
-  <si>
-    <t>relationship--1eb1a282-23cc-43ab-b857-0d11d636e2a5</t>
-  </si>
-  <si>
-    <t>relationship--2bbbd285-77d1-4fd6-91c9-5d028c72f098</t>
-  </si>
-  <si>
-    <t>relationship--a1492f55-f3d8-429c-8ec4-384c57f58821</t>
-  </si>
-  <si>
-    <t>relationship--c63d2783-b3b7-47a3-9be9-d1677fa6945c</t>
-  </si>
-  <si>
-    <t>relationship--0b4d5b99-7039-4ab0-a99d-094ceaa1cd91</t>
-  </si>
-  <si>
-    <t>relationship--c3b294ff-66a0-4e31-a6b4-12d7a648a472</t>
-  </si>
-  <si>
-    <t>relationship--4eef5b22-d5ab-478f-8fcc-018f34f58e25</t>
-  </si>
-  <si>
-    <t>relationship--40042475-a205-4c1b-97e7-7c76c7865cbb</t>
-  </si>
-  <si>
-    <t>relationship--c67c90d0-effd-43e6-84de-05d750e98fe0</t>
-  </si>
-  <si>
-    <t>relationship--b12bd32f-d8c0-47c2-a1f0-cfddf25000c1</t>
-  </si>
-  <si>
-    <t>relationship--ba3fd383-b77d-4c48-9eb4-506a4833f1f2</t>
-  </si>
-  <si>
-    <t>relationship--15c27931-d7a9-4b5c-9058-bf081b37a8a3</t>
-  </si>
-  <si>
-    <t>relationship--1ad4791e-261a-4512-8123-89fc26e12b25</t>
-  </si>
-  <si>
-    <t>relationship--17997574-a161-4f2d-81d7-a8ffc9343dcf</t>
-  </si>
-  <si>
-    <t>relationship--39edf99e-7601-4a47-ad39-8e3d080fba7d</t>
-  </si>
-  <si>
-    <t>relationship--5173a2ce-e76a-4bb7-8685-3d30657cf7bb</t>
-  </si>
-  <si>
-    <t>relationship--36eb1714-2670-44e7-b9cb-96d0eb426b72</t>
-  </si>
-  <si>
-    <t>relationship--3d4c10fe-6943-48fd-b897-e90c3158744f</t>
-  </si>
-  <si>
-    <t>relationship--78c6f40f-c64c-4681-9061-63acf50a4bd6</t>
-  </si>
-  <si>
-    <t>relationship--b24d5aea-09e9-41bc-85a0-240a7b69a591</t>
-  </si>
-  <si>
-    <t>relationship--2bb139e8-1edc-4db2-b8c1-482176975ad4</t>
-  </si>
-  <si>
-    <t>relationship--ca8c42ef-8ef1-4ccb-8237-f9206f58f733</t>
-  </si>
-  <si>
-    <t>relationship--fd974d03-b680-4744-85c5-8e1ac2ce7c31</t>
-  </si>
-  <si>
-    <t>relationship--d88929a7-dc71-49ce-b9a1-bfedc801e8a8</t>
+    <t>relationship--579007f9-28a0-48e4-9185-c1e2d0b17ae3</t>
+  </si>
+  <si>
+    <t>relationship--cbe422cd-9fe9-4132-84f1-96be195ac993</t>
+  </si>
+  <si>
+    <t>relationship--5667cd4d-ca36-46d4-a17a-9d54006f1f5b</t>
+  </si>
+  <si>
+    <t>relationship--f281ae66-2d30-4085-b524-194af26c8459</t>
+  </si>
+  <si>
+    <t>relationship--36dcc214-651c-4657-acdf-5a62bef3ec0f</t>
+  </si>
+  <si>
+    <t>relationship--13a0e8d5-cd26-41ad-989a-1ffb8a550016</t>
+  </si>
+  <si>
+    <t>relationship--2bf4f3c6-637c-41b5-b365-73fd8f1340fa</t>
+  </si>
+  <si>
+    <t>relationship--bc31601d-18b2-4aed-90e3-208e5d49b78a</t>
+  </si>
+  <si>
+    <t>relationship--9807e38f-6ad6-447a-ae60-a64f9f343370</t>
+  </si>
+  <si>
+    <t>relationship--8a514380-8a2d-4c81-9db0-93a248171fba</t>
+  </si>
+  <si>
+    <t>relationship--b2f79bb7-979e-4ea3-86ef-eebc886aaa6b</t>
+  </si>
+  <si>
+    <t>relationship--545039f1-fa7a-4f32-9e79-7584f9399a5a</t>
+  </si>
+  <si>
+    <t>relationship--bb7c01ba-b6d1-40f6-a6d0-3e4b0cdddbef</t>
+  </si>
+  <si>
+    <t>relationship--974dffe7-2fe4-45f0-bf21-5df9f49100d0</t>
+  </si>
+  <si>
+    <t>relationship--590d5394-a905-4b57-8ea4-38e941c36875</t>
+  </si>
+  <si>
+    <t>relationship--c76b1d3c-c2e5-45d1-a417-d580c9825105</t>
+  </si>
+  <si>
+    <t>relationship--3037be7e-2186-4f85-beb4-bfc477eef251</t>
+  </si>
+  <si>
+    <t>relationship--ceeb598f-298b-4fdd-aa06-06c66f75cb93</t>
+  </si>
+  <si>
+    <t>relationship--6e2eee1c-1d01-4aa2-b34b-1ce62806dae9</t>
+  </si>
+  <si>
+    <t>relationship--c347dbcd-3768-45bb-85b5-ee75069b5731</t>
+  </si>
+  <si>
+    <t>relationship--eacab9fe-e01f-49fc-a53a-bdbdacec0a5d</t>
+  </si>
+  <si>
+    <t>relationship--0a00c5e3-fc83-48cd-8ddb-09ef4bbedfe0</t>
+  </si>
+  <si>
+    <t>relationship--0ee2ab17-a17d-488c-a01f-4cc29fa47acc</t>
+  </si>
+  <si>
+    <t>relationship--72e5cce2-bbff-48a2-b689-589ad7bde2fb</t>
+  </si>
+  <si>
+    <t>relationship--d3b4874f-ecb2-4381-9b8d-7927f05858d0</t>
+  </si>
+  <si>
+    <t>relationship--ca5afe22-bac2-4077-b67b-337995a60f43</t>
+  </si>
+  <si>
+    <t>relationship--77b67bf7-363d-4a9d-9f8b-9742086db6c6</t>
+  </si>
+  <si>
+    <t>relationship--63fe6e4d-581d-431b-8116-9e090e8a745c</t>
+  </si>
+  <si>
+    <t>relationship--94908fc4-bb5b-4683-805a-dbd8dc5e4999</t>
+  </si>
+  <si>
+    <t>relationship--d9fe5d2b-3357-4241-901b-39166dd33941</t>
+  </si>
+  <si>
+    <t>relationship--035ae41a-01e9-4155-9738-28abee46fa01</t>
+  </si>
+  <si>
+    <t>relationship--22ee9109-c21a-4017-a011-8847cb95d8af</t>
+  </si>
+  <si>
+    <t>relationship--de151bf0-ed08-4e2c-924e-d1e4fcd66047</t>
+  </si>
+  <si>
+    <t>relationship--1b8dfcb3-509e-4b06-a3eb-15219d4b259f</t>
+  </si>
+  <si>
+    <t>relationship--d9c1c0f7-5386-45dd-90f5-cdcf145f2c40</t>
+  </si>
+  <si>
+    <t>relationship--a7369f3d-8b80-46e3-bb86-52408e4d0a70</t>
+  </si>
+  <si>
+    <t>relationship--924eeef7-4ac6-4094-a9d7-36befeac2c17</t>
+  </si>
+  <si>
+    <t>relationship--4135c852-a440-4feb-a662-d639156221ad</t>
+  </si>
+  <si>
+    <t>relationship--b50f9c63-ba9d-4a49-a4f7-45d9b53d8ef0</t>
+  </si>
+  <si>
+    <t>relationship--02f7b89f-53fa-478f-a1b5-7b61d8dcbff2</t>
+  </si>
+  <si>
+    <t>relationship--64360548-9a83-41f8-90e4-d73d3eb2c33a</t>
+  </si>
+  <si>
+    <t>relationship--8283b0e0-32c7-4708-9057-d42e6598176b</t>
+  </si>
+  <si>
+    <t>relationship--c1c921d9-699e-4928-8506-67dcd2061170</t>
+  </si>
+  <si>
+    <t>relationship--f2726f56-5487-4b4f-af8a-7031b19d1d76</t>
+  </si>
+  <si>
+    <t>relationship--d84105e6-4a04-4cf4-8a2c-c4a12e5dea08</t>
+  </si>
+  <si>
+    <t>relationship--3b452af0-3666-4c28-974e-a4fb53bbf295</t>
+  </si>
+  <si>
+    <t>relationship--f8ab7e5a-e300-48c9-b77c-8e67a4d7df27</t>
+  </si>
+  <si>
+    <t>relationship--40666857-41f2-4d46-bf70-47aa0c34dcc7</t>
+  </si>
+  <si>
+    <t>relationship--771548ba-7416-4cde-95d1-c788b08aaa71</t>
+  </si>
+  <si>
+    <t>relationship--779d583e-d222-4b26-956a-1e19ac4b77e2</t>
+  </si>
+  <si>
+    <t>relationship--d82e2525-0fdd-49cb-b3f1-1f2efa99ee08</t>
+  </si>
+  <si>
+    <t>relationship--31777070-381d-45d3-b313-00646e092c07</t>
+  </si>
+  <si>
+    <t>relationship--0f4de468-fd2f-4285-9db2-740ef8555069</t>
+  </si>
+  <si>
+    <t>relationship--24ad6afb-6426-413a-a29f-38668ad6ff90</t>
+  </si>
+  <si>
+    <t>relationship--946d5ae9-8056-4e22-9cd4-417de7f38d82</t>
+  </si>
+  <si>
+    <t>relationship--2a1f9d54-b16b-46ad-a923-604adfe79e1e</t>
+  </si>
+  <si>
+    <t>relationship--9a57978d-fe99-4297-8eb2-9746f0966990</t>
+  </si>
+  <si>
+    <t>relationship--366127f5-ecfd-431d-8baa-60078e576cef</t>
+  </si>
+  <si>
+    <t>relationship--835e8e03-39f2-4a00-a970-4f85d13ecae3</t>
+  </si>
+  <si>
+    <t>relationship--8a4a0c57-9338-42e3-8d0f-f04cc7e4970f</t>
+  </si>
+  <si>
+    <t>relationship--13eee957-a48f-466d-833c-b05db7b68537</t>
+  </si>
+  <si>
+    <t>relationship--5c8531a1-d41b-4b0b-8a4e-dfae8afcfa13</t>
+  </si>
+  <si>
+    <t>relationship--823a5587-50a0-40bc-9bde-70e3c2182300</t>
+  </si>
+  <si>
+    <t>relationship--293ad61a-8091-43f2-9fdc-e1adb4c75bc9</t>
+  </si>
+  <si>
+    <t>relationship--08e3ea95-b7f8-4937-b29c-4a1672614f9c</t>
+  </si>
+  <si>
+    <t>relationship--49edb497-7c42-44fc-bb53-870ca69c42d0</t>
+  </si>
+  <si>
+    <t>relationship--2051eeb2-4f36-497b-b503-5da4e20d78a0</t>
+  </si>
+  <si>
+    <t>relationship--30d0c38d-f5e6-4c94-a312-bb0202c53235</t>
+  </si>
+  <si>
+    <t>relationship--a372bff6-e803-4af7-ba39-d0996ef7de00</t>
+  </si>
+  <si>
+    <t>relationship--16bf97f2-e1ac-451b-93db-61a5ca25cfa5</t>
+  </si>
+  <si>
+    <t>relationship--b4456713-6f1a-423c-9417-3fd9318794b5</t>
+  </si>
+  <si>
+    <t>relationship--7368aac6-f55d-45e8-bcd2-0150164725c0</t>
+  </si>
+  <si>
+    <t>relationship--8fa92939-0395-495a-a2cc-25920befafd6</t>
+  </si>
+  <si>
+    <t>relationship--7f8c1d68-a431-4053-a40c-08397553d9f8</t>
+  </si>
+  <si>
+    <t>relationship--fe830b39-4d93-4844-92e9-630d112bb1cc</t>
+  </si>
+  <si>
+    <t>relationship--ba30d8c0-0a8a-43e3-884e-9ebc68c8b18b</t>
+  </si>
+  <si>
+    <t>relationship--a9ada7e1-57e6-4aba-95c7-33f97a61382d</t>
+  </si>
+  <si>
+    <t>relationship--4e5af6b1-7d02-4647-843f-917014cbfee5</t>
+  </si>
+  <si>
+    <t>relationship--a41e87ab-e2f0-472e-8b8b-b96ee2a8dbfb</t>
+  </si>
+  <si>
+    <t>relationship--7a731bc9-9092-4523-8921-dd7a3d94426f</t>
+  </si>
+  <si>
+    <t>relationship--b2beb81b-3b22-4e86-9770-beb7bcb9e418</t>
+  </si>
+  <si>
+    <t>relationship--eba89ba0-a62f-4d7a-aac2-58639ab713f8</t>
+  </si>
+  <si>
+    <t>relationship--cd2cd507-1be3-4d9a-b9fc-fcbddeac37be</t>
+  </si>
+  <si>
+    <t>relationship--0cfbf64b-f9a8-4961-bdcc-328c9364a656</t>
+  </si>
+  <si>
+    <t>relationship--3db40fe1-6e0d-4323-8da9-f0359cfa8be7</t>
+  </si>
+  <si>
+    <t>relationship--077d87d9-6da7-4b46-9cfc-4c84e7f788af</t>
+  </si>
+  <si>
+    <t>relationship--86e9c863-5ae5-46bf-b0e4-b02eaa185bd7</t>
+  </si>
+  <si>
+    <t>relationship--434ffa6e-8e3f-42bf-8887-3b685da7afe2</t>
+  </si>
+  <si>
+    <t>relationship--61560840-331e-4982-ab6f-90edf192c51f</t>
+  </si>
+  <si>
+    <t>relationship--5ed32bcc-ffac-41fb-ade7-6baf29882120</t>
+  </si>
+  <si>
+    <t>relationship--abce58d8-6877-4dcb-a877-9e213452f4b6</t>
+  </si>
+  <si>
+    <t>relationship--0b3c0a27-bbc5-4005-ac5d-bb05a255a1fd</t>
+  </si>
+  <si>
+    <t>relationship--9f3989ee-e8dd-48ba-a582-6a1fb2c277cf</t>
+  </si>
+  <si>
+    <t>relationship--5f947b73-c283-438a-b661-e922ef128815</t>
+  </si>
+  <si>
+    <t>relationship--f2028f92-96ba-481d-a719-e43200be30eb</t>
+  </si>
+  <si>
+    <t>relationship--9b0772cb-acd9-4f8a-82b1-c429efd3c3fc</t>
+  </si>
+  <si>
+    <t>relationship--cf2a8f50-c042-4978-8ac9-040f681a0902</t>
+  </si>
+  <si>
+    <t>relationship--dd0249b1-41cf-49f2-8b39-909edba54fbb</t>
+  </si>
+  <si>
+    <t>relationship--0863f965-e8ec-4d07-86db-37554adca29b</t>
+  </si>
+  <si>
+    <t>relationship--e86d43ec-a735-4d99-ad60-b0135dbfb42f</t>
+  </si>
+  <si>
+    <t>relationship--fc6c0597-d0d4-4933-8519-4d7a7c7297f6</t>
+  </si>
+  <si>
+    <t>relationship--27d3b66b-60c5-4691-884a-af621f775026</t>
+  </si>
+  <si>
+    <t>relationship--653d9b5d-056b-4633-8ccb-46dd884fe269</t>
   </si>
   <si>
     <t>reference</t>
@@ -3734,12 +3734,24 @@
     <t>Іван Мазепа — Вікіпедія 2026</t>
   </si>
   <si>
+    <t>Історія Донецької області — Вікіпедія 2026</t>
+  </si>
+  <si>
     <t>Історія України — Вікіпедія 2026</t>
   </si>
   <si>
+    <t>Андрусовское перемирие - Википедия 2026</t>
+  </si>
+  <si>
     <t>Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026</t>
   </si>
   <si>
+    <t>Батуринська трагедія — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>В ТЕНИ «БОЛЬШОГО БРАТА» ЗАПАДНЫЕ НАЦИОНАЛЬНЫЕ МЕНЬШИНСТВА В СССР 1917-1938 ГГ . 2011</t>
+  </si>
+  <si>
     <t>Война и наказание: Как Россия уничтожала Украину 2023</t>
   </si>
   <si>
@@ -3764,6 +3776,9 @@
     <t>ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011</t>
   </si>
   <si>
+    <t>Карательная психиатрия в России: назад в СССР? 2020</t>
+  </si>
+  <si>
     <t>Кенгирское восстание заключённых - Википедия 2026</t>
   </si>
   <si>
@@ -3785,6 +3800,9 @@
     <t>Мазепа 2007</t>
   </si>
   <si>
+    <t>Мазепа, Иван Степанович — Википедия 2026</t>
+  </si>
+  <si>
     <t>Малоросійське генерал-губернаторство — Вікіпедія 2026</t>
   </si>
   <si>
@@ -3857,12 +3875,24 @@
     <t>Вікіпедія. (2026). Іван Мазепа — Вікіпедія.</t>
   </si>
   <si>
+    <t>Вікіпедія. (2026). Історія Донецької області — Вікіпедія.</t>
+  </si>
+  <si>
     <t>Вікіпедія. (2026). Історія України — Вікіпедія.</t>
   </si>
   <si>
+    <t>Википедия. (2026). Андрусовское перемирие - Википедия.</t>
+  </si>
+  <si>
     <t>Вікіпедія. (2026). Анексія Київської митрополії Московським патріархатом — Вікіпедія.</t>
   </si>
   <si>
+    <t>Вікіпедія. (2026). Батуринська трагедія — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Виктор Дённингхаус. (2011). В ТЕНИ «БОЛЬШОГО БРАТА» ЗАПАДНЫЕ НАЦИОНАЛЬНЫЕ МЕНЬШИНСТВА В СССР 1917-1938 ГГ ..</t>
+  </si>
+  <si>
     <t>Михаил Зыгарь. (2023). Война и наказание: Как Россия уничтожала Украину.</t>
   </si>
   <si>
@@ -3887,6 +3917,9 @@
     <t>Татьяна Таирова-Яковлева. (2011). ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА».</t>
   </si>
   <si>
+    <t>Riddle Russia. (2020). Карательная психиатрия в России: назад в СССР?.</t>
+  </si>
+  <si>
     <t>Википедия. (2026). Кенгирское восстание заключённых - Википедия.</t>
   </si>
   <si>
@@ -3908,6 +3941,9 @@
     <t>Татьяна Таирова-Яковлева. (2007). Мазепа.</t>
   </si>
   <si>
+    <t>Википедия. (2026). Мазепа, Иван Степанович — Википедия.</t>
+  </si>
+  <si>
     <t>Вікіпедія. (2026). Малоросійське генерал-губернаторство — Вікіпедія.</t>
   </si>
   <si>
@@ -3980,12 +4016,21 @@
     <t>https://uk.wikipedia.org/wiki/%25D0%2586%25D0%25B2%25D0%25B0%25D0%25BD_%25D0%259C%25D0%25B0%25D0%25B7%25D0%25B5%25D0%25BF%25D0%25B0</t>
   </si>
   <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%2586%25D1%2581%25D1%2582%25D0%25BE%25D1%2580%25D1%2596%25D1%258F_%25D0%2594%25D0%25BE%25D0%25BD%25D0%25B5%25D1%2586%25D1%258C%25D0%25BA%25D0%25BE%25D1%2597_%25D0%25BE%25D0%25B1%25D0%25BB%25D0%25B0%25D1%2581%25D1%2582%25D1%2596</t>
+  </si>
+  <si>
     <t>https://uk.wikipedia.org/wiki/%25D0%2586%25D1%2581%25D1%2582%25D0%25BE%25D1%2580%25D1%2596%25D1%258F_%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D0%25B8</t>
   </si>
   <si>
+    <t>https://ru.wikipedia.org/wiki/%25D0%2590%25D0%25BD%25D0%25B4%25D1%2580%25D1%2583%25D1%2581%25D0%25BE%25D0%25B2%25D1%2581%25D0%25BA%25D0%25BE%25D0%25B5_%25D0%25BF%25D0%25B5%25D1%2580%25D0%25B5%25D0%25BC%25D0%25B8%25D1%2580%25D0%25B8%25D0%25B5</t>
+  </si>
+  <si>
     <t>https://uk.wikipedia.org/wiki/%25D0%2590%25D0%25BD%25D0%25B5%25D0%25BA%25D1%2581%25D1%2596%25D1%258F_%25D0%259A%25D0%25B8%25D1%2597%25D0%25B2%25D1%2581%25D1%258C%25D0%25BA%25D0%25BE%25D1%2597_%25D0%25BC%25D0%25B8%25D1%2582%25D1%2580%25D0%25BE%25D0%25BF%25D0%25BE%25D0%25BB%25D1%2596%25D1%2597_%25D0%259C%25D0%25BE%25D1%2581%25D0%25BA%25D0%25BE%25D0%25B2%25D1%2581%25D1%258C%25D0%25BA%25D0%25B8%25D0%25BC_%25D0%25BF%25D0%25B0%25D1%2582%25D1%2580%25D1%2596%25D0%25B0%25D1%2580%25D1%2585%25D0%25B0%25D1%2582%25D0%25BE%25D0%25BC</t>
   </si>
   <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%2591%25D0%25B0%25D1%2582%25D1%2583%25D1%2580%25D0%25B8%25D0%25BD%25D1%2581%25D1%258C%25D0%25BA%25D0%25B0_%25D1%2582%25D1%2580%25D0%25B0%25D0%25B3%25D0%25B5%25D0%25B4%25D1%2596%25D1%258F</t>
+  </si>
+  <si>
     <t>https://uk.wikipedia.org/wiki/%25D0%2592%25D1%2581%25D0%25B5%25D1%2581%25D0%25BE%25D1%258E%25D0%25B7%25D0%25BD%25D0%25B8%25D0%25B9_%25D1%2580%25D0%25B5%25D1%2584%25D0%25B5%25D1%2580%25D0%25B5%25D0%25BD%25D0%25B4%25D1%2583%25D0%25BC_%25D0%25BF%25D1%2580%25D0%25BE_%25D0%25B7%25D0%25B1%25D0%25B5%25D1%2580%25D0%25B5%25D0%25B6%25D0%25B5%25D0%25BD%25D0%25BD%25D1%258F_%25D0%25A1%25D0%25A0%25D0%25A1%25D0%25A0</t>
   </si>
   <si>
@@ -4004,6 +4049,9 @@
     <t>https://uk.wikipedia.org/wiki/%25D0%2597%25D0%25B0%25D0%25BF%25D0%25BE%25D1%2580%25D0%25BE%25D0%25B7%25D1%258C%25D0%25BA%25D0%25B0_%25D0%25A1%25D1%2596%25D1%2587</t>
   </si>
   <si>
+    <t>https://ridl.io/ru/karatelnaja-psihiatrija-v-rossii-nazad-v-sssr/</t>
+  </si>
+  <si>
     <t>https://ru.wikipedia.org/wiki/%25D0%259A%25D0%25B5%25D0%25BD%25D0%25B3%25D0%25B8%25D1%2580%25D1%2581%25D0%25BA%25D0%25BE%25D0%25B5_%25D0%25B2%25D0%25BE%25D1%2581%25D1%2581%25D1%2582%25D0%25B0%25D0%25BD%25D0%25B8%25D0%25B5_%25D0%25B7%25D0%25B0%25D0%25BA%25D0%25BB%25D1%258E%25D1%2587%25D1%2591%25D0%25BD%25D0%25BD%25D1%258B%25D1%2585</t>
   </si>
   <si>
@@ -4020,6 +4068,9 @@
   </si>
   <si>
     <t>https://uk.wikipedia.org/wiki/%25D0%259B%25D1%2596%25D0%25BA%25D0%25B2%25D1%2596%25D0%25B4%25D0%25B0%25D1%2586%25D1%2596%25D1%258F_%25D0%25B0%25D0%25B2%25D1%2582%25D0%25BE%25D0%25BD%25D0%25BE%25D0%25BC%25D1%2596%25D1%2597_%25D0%2593%25D0%25B5%25D1%2582%25D1%258C%25D0%25BC%25D0%25B0%25D0%25BD%25D1%2589%25D0%25B8%25D0%25BD%25D0%25B8</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%25D0%259C%25D0%25B0%25D0%25B7%25D0%25B5%25D0%25BF%25D0%25B0%2C_%25D0%2598%25D0%25B2%25D0%25B0%25D0%25BD_%25D0%25A1%25D1%2582%25D0%25B5%25D0%25BF%25D0%25B0%25D0%25BD%25D0%25BE%25D0%25B2%25D0%25B8%25D1%2587</t>
   </si>
   <si>
     <t>https://uk.wikipedia.org/wiki/%25D0%259C%25D0%25B0%25D0%25BB%25D0%25BE%25D1%2580%25D0%25BE%25D1%2581%25D1%2596%25D0%25B9%25D1%2581%25D1%258C%25D0%25BA%25D0%25B5_%25D0%25B3%25D0%25B5%25D0%25BD%25D0%25B5%25D1%2580%25D0%25B0%25D0%25BB-%25D0%25B3%25D1%2583%25D0%25B1%25D0%25B5%25D1%2580%25D0%25BD%25D0%25B0%25D1%2582%25D0%25BE%25D1%2580%25D1%2581%25D1%2582%25D0%25B2%25D0%25BE</t>
@@ -18185,7 +18236,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -18204,10 +18255,10 @@
         <v>1235</v>
       </c>
       <c r="B2" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1317</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -18215,10 +18266,10 @@
         <v>1236</v>
       </c>
       <c r="B3" t="s">
-        <v>1277</v>
+        <v>1283</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1318</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -18226,10 +18277,10 @@
         <v>1237</v>
       </c>
       <c r="B4" t="s">
-        <v>1278</v>
+        <v>1284</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>1319</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -18237,10 +18288,10 @@
         <v>1238</v>
       </c>
       <c r="B5" t="s">
-        <v>1279</v>
+        <v>1285</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>1320</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -18248,10 +18299,10 @@
         <v>1239</v>
       </c>
       <c r="B6" t="s">
-        <v>1280</v>
+        <v>1286</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1321</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -18259,7 +18310,10 @@
         <v>1240</v>
       </c>
       <c r="B7" t="s">
-        <v>1281</v>
+        <v>1287</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>1334</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -18267,10 +18321,10 @@
         <v>1241</v>
       </c>
       <c r="B8" t="s">
-        <v>1282</v>
+        <v>1288</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1322</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -18278,10 +18332,10 @@
         <v>1242</v>
       </c>
       <c r="B9" t="s">
-        <v>1283</v>
+        <v>1289</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>1323</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -18289,10 +18343,7 @@
         <v>1243</v>
       </c>
       <c r="B10" t="s">
-        <v>1284</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>1324</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -18300,10 +18351,7 @@
         <v>1244</v>
       </c>
       <c r="B11" t="s">
-        <v>1285</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>1325</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -18311,10 +18359,10 @@
         <v>1245</v>
       </c>
       <c r="B12" t="s">
-        <v>1286</v>
+        <v>1292</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>1326</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -18322,10 +18370,10 @@
         <v>1246</v>
       </c>
       <c r="B13" t="s">
-        <v>1287</v>
+        <v>1293</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>1327</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -18333,7 +18381,10 @@
         <v>1247</v>
       </c>
       <c r="B14" t="s">
-        <v>1288</v>
+        <v>1294</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>1339</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -18341,10 +18392,10 @@
         <v>1248</v>
       </c>
       <c r="B15" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>1328</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -18352,10 +18403,10 @@
         <v>1249</v>
       </c>
       <c r="B16" t="s">
-        <v>1290</v>
+        <v>1296</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>1329</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -18363,10 +18414,10 @@
         <v>1250</v>
       </c>
       <c r="B17" t="s">
-        <v>1291</v>
+        <v>1297</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>1330</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -18374,10 +18425,7 @@
         <v>1251</v>
       </c>
       <c r="B18" t="s">
-        <v>1292</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>1331</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -18385,10 +18433,10 @@
         <v>1252</v>
       </c>
       <c r="B19" t="s">
-        <v>1293</v>
+        <v>1299</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>1332</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -18396,10 +18444,10 @@
         <v>1253</v>
       </c>
       <c r="B20" t="s">
-        <v>1294</v>
+        <v>1300</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>1333</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -18407,7 +18455,10 @@
         <v>1254</v>
       </c>
       <c r="B21" t="s">
-        <v>1295</v>
+        <v>1301</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>1345</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -18415,10 +18466,10 @@
         <v>1255</v>
       </c>
       <c r="B22" t="s">
-        <v>1296</v>
+        <v>1302</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>1334</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -18426,10 +18477,10 @@
         <v>1256</v>
       </c>
       <c r="B23" t="s">
-        <v>1297</v>
+        <v>1303</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>1335</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -18437,10 +18488,10 @@
         <v>1257</v>
       </c>
       <c r="B24" t="s">
-        <v>1298</v>
+        <v>1304</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>1336</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -18448,10 +18499,10 @@
         <v>1258</v>
       </c>
       <c r="B25" t="s">
-        <v>1299</v>
+        <v>1305</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>1337</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -18459,10 +18510,7 @@
         <v>1259</v>
       </c>
       <c r="B26" t="s">
-        <v>1300</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>1338</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -18470,10 +18518,10 @@
         <v>1260</v>
       </c>
       <c r="B27" t="s">
-        <v>1301</v>
+        <v>1307</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>1339</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -18481,7 +18529,10 @@
         <v>1261</v>
       </c>
       <c r="B28" t="s">
-        <v>1302</v>
+        <v>1308</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>1351</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -18489,10 +18540,10 @@
         <v>1262</v>
       </c>
       <c r="B29" t="s">
-        <v>1303</v>
+        <v>1309</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>1340</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -18500,10 +18551,10 @@
         <v>1263</v>
       </c>
       <c r="B30" t="s">
-        <v>1304</v>
+        <v>1310</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>1341</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -18511,10 +18562,10 @@
         <v>1264</v>
       </c>
       <c r="B31" t="s">
-        <v>1305</v>
+        <v>1311</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>1342</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -18522,10 +18573,10 @@
         <v>1265</v>
       </c>
       <c r="B32" t="s">
-        <v>1306</v>
+        <v>1312</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>1343</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -18533,10 +18584,10 @@
         <v>1266</v>
       </c>
       <c r="B33" t="s">
-        <v>1307</v>
+        <v>1313</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>1344</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -18544,10 +18595,7 @@
         <v>1267</v>
       </c>
       <c r="B34" t="s">
-        <v>1308</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>1345</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -18555,10 +18603,10 @@
         <v>1268</v>
       </c>
       <c r="B35" t="s">
-        <v>1309</v>
+        <v>1315</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>1346</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -18566,10 +18614,10 @@
         <v>1269</v>
       </c>
       <c r="B36" t="s">
-        <v>1310</v>
+        <v>1316</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>1347</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -18577,10 +18625,10 @@
         <v>1270</v>
       </c>
       <c r="B37" t="s">
-        <v>1311</v>
+        <v>1317</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>1348</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -18588,10 +18636,10 @@
         <v>1271</v>
       </c>
       <c r="B38" t="s">
-        <v>1312</v>
+        <v>1318</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>1349</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -18599,10 +18647,10 @@
         <v>1272</v>
       </c>
       <c r="B39" t="s">
-        <v>1313</v>
+        <v>1319</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>1350</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -18610,10 +18658,10 @@
         <v>1273</v>
       </c>
       <c r="B40" t="s">
-        <v>1314</v>
+        <v>1320</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>1351</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -18621,10 +18669,10 @@
         <v>1274</v>
       </c>
       <c r="B41" t="s">
-        <v>1315</v>
+        <v>1321</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>1352</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -18632,10 +18680,76 @@
         <v>1275</v>
       </c>
       <c r="B42" t="s">
-        <v>1316</v>
+        <v>1322</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>1353</v>
+        <v>1364</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1323</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B44" t="s">
+        <v>1324</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B45" t="s">
+        <v>1325</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
+        <v>1279</v>
+      </c>
+      <c r="B46" t="s">
+        <v>1326</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B47" t="s">
+        <v>1327</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B48" t="s">
+        <v>1328</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>1370</v>
       </c>
     </row>
   </sheetData>
@@ -18645,38 +18759,43 @@
     <hyperlink ref="C4" r:id="rId3"/>
     <hyperlink ref="C5" r:id="rId4"/>
     <hyperlink ref="C6" r:id="rId5"/>
-    <hyperlink ref="C8" r:id="rId6"/>
-    <hyperlink ref="C9" r:id="rId7"/>
-    <hyperlink ref="C10" r:id="rId8"/>
-    <hyperlink ref="C11" r:id="rId9"/>
-    <hyperlink ref="C12" r:id="rId10"/>
-    <hyperlink ref="C13" r:id="rId11"/>
+    <hyperlink ref="C7" r:id="rId6"/>
+    <hyperlink ref="C8" r:id="rId7"/>
+    <hyperlink ref="C9" r:id="rId8"/>
+    <hyperlink ref="C12" r:id="rId9"/>
+    <hyperlink ref="C13" r:id="rId10"/>
+    <hyperlink ref="C14" r:id="rId11"/>
     <hyperlink ref="C15" r:id="rId12"/>
     <hyperlink ref="C16" r:id="rId13"/>
     <hyperlink ref="C17" r:id="rId14"/>
-    <hyperlink ref="C18" r:id="rId15"/>
-    <hyperlink ref="C19" r:id="rId16"/>
-    <hyperlink ref="C20" r:id="rId17"/>
+    <hyperlink ref="C19" r:id="rId15"/>
+    <hyperlink ref="C20" r:id="rId16"/>
+    <hyperlink ref="C21" r:id="rId17"/>
     <hyperlink ref="C22" r:id="rId18"/>
     <hyperlink ref="C23" r:id="rId19"/>
     <hyperlink ref="C24" r:id="rId20"/>
     <hyperlink ref="C25" r:id="rId21"/>
-    <hyperlink ref="C26" r:id="rId22"/>
-    <hyperlink ref="C27" r:id="rId23"/>
+    <hyperlink ref="C27" r:id="rId22"/>
+    <hyperlink ref="C28" r:id="rId23"/>
     <hyperlink ref="C29" r:id="rId24"/>
     <hyperlink ref="C30" r:id="rId25"/>
     <hyperlink ref="C31" r:id="rId26"/>
     <hyperlink ref="C32" r:id="rId27"/>
     <hyperlink ref="C33" r:id="rId28"/>
-    <hyperlink ref="C34" r:id="rId29"/>
-    <hyperlink ref="C35" r:id="rId30"/>
-    <hyperlink ref="C36" r:id="rId31"/>
-    <hyperlink ref="C37" r:id="rId32"/>
-    <hyperlink ref="C38" r:id="rId33"/>
-    <hyperlink ref="C39" r:id="rId34"/>
-    <hyperlink ref="C40" r:id="rId35"/>
-    <hyperlink ref="C41" r:id="rId36"/>
-    <hyperlink ref="C42" r:id="rId37"/>
+    <hyperlink ref="C35" r:id="rId29"/>
+    <hyperlink ref="C36" r:id="rId30"/>
+    <hyperlink ref="C37" r:id="rId31"/>
+    <hyperlink ref="C38" r:id="rId32"/>
+    <hyperlink ref="C39" r:id="rId33"/>
+    <hyperlink ref="C40" r:id="rId34"/>
+    <hyperlink ref="C41" r:id="rId35"/>
+    <hyperlink ref="C42" r:id="rId36"/>
+    <hyperlink ref="C43" r:id="rId37"/>
+    <hyperlink ref="C44" r:id="rId38"/>
+    <hyperlink ref="C45" r:id="rId39"/>
+    <hyperlink ref="C46" r:id="rId40"/>
+    <hyperlink ref="C47" r:id="rId41"/>
+    <hyperlink ref="C48" r:id="rId42"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-groups.xlsx
+++ b/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-groups.xlsx
@@ -68,22 +68,22 @@
     <t>G0013</t>
   </si>
   <si>
-    <t>intrusion-set--3642f171-4667-4b82-b3c5-73f7f518396b</t>
-  </si>
-  <si>
-    <t>intrusion-set--224aa639-ced9-4891-bc3c-72ee1592cf05</t>
-  </si>
-  <si>
-    <t>intrusion-set--e3bc6b24-7eb3-408b-af74-b5924d08cd07</t>
-  </si>
-  <si>
-    <t>intrusion-set--1be81b91-037a-46a1-8e5e-b282c40ea297</t>
-  </si>
-  <si>
-    <t>intrusion-set--243887eb-e4f8-4b0e-a6d2-843e9676f671</t>
-  </si>
-  <si>
-    <t>intrusion-set--8b5f0098-75af-4fcd-9c7f-88149768cd8b</t>
+    <t>intrusion-set--7b976569-98f0-4fa3-82fe-02d61389de3e</t>
+  </si>
+  <si>
+    <t>intrusion-set--d5113a56-7d11-4ccf-b29b-db0230a3deb5</t>
+  </si>
+  <si>
+    <t>intrusion-set--ccad1a64-f9f9-4595-8650-92f87954b4a0</t>
+  </si>
+  <si>
+    <t>intrusion-set--763a114d-2942-4a6d-9907-1170a64fae86</t>
+  </si>
+  <si>
+    <t>intrusion-set--efc55d3b-975e-4784-879d-5e1771bcdfb2</t>
+  </si>
+  <si>
+    <t>intrusion-set--d6cb53bb-bf87-46da-99d2-d218130dd4c9</t>
   </si>
   <si>
     <t>Белое движение (ВСЮР)</t>
@@ -149,22 +149,22 @@
     <t>1.0</t>
   </si>
   <si>
-    <t>(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.)</t>
-  </si>
-  <si>
-    <t>(Citation: Руїна — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Московсько-українська війна (1658—1659),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Руїна — Вікіпедія 2026),(Citation: Запорозька Січ — Вікіпедія 2026),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Московсько-українська війна (1658—1659),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Киевский синопсис — Википедия 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Переяславська рада — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Мазепа 2007),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Переяславські статті (1659),(Citation: Північна війна (1700—1721),(Citation: Малоросійський приказ — Вікіпедія 2026),(Citation: Решетилівські статті — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Запорозька Січ — Вікіпедія 2026),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Азовські походи (1695—1696),(Citation: Андрусовское перемирие - Википедия 2026),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Ліквідація козацтва на Правобережній Україні (1699),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Переяславська рада — Вікіпедія 2026),(Citation: Решетилівські статті — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Киевский синопсис — Википедия 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Московські статті (1665),(Citation: Мазепа 2007),(Citation: Малоросійський приказ — Вікіпедія 2026),(Citation: Переяславські статті (1659),(Citation: Конотопські статті — Вікіпедія 2026),(Citation: Руїна — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711)</t>
-  </si>
-  <si>
-    <t>(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Історія Донецької області — Вікіпедія 2026),(Citation: Чорносотенці — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Столипінська реформа — Вікіпедія 2026),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Друга Малоросійська колегія — Вікіпедія 2026),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026),(Citation: Повстання бузьких козаків (1817),(Citation: Історія України — Вікіпедія 2026),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: Листопадове повстання (1830—1831),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026),(Citation: Листопадове повстання (1830—1831),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Чорносотенці — Вікіпедія 2026),(Citation: Крымская война — Википедия 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Україна у війнах Наполеона — Вікіпедія 2026),(Citation: Російсько-турецька війна (1806—1812),(Citation: Русско-турецкая война (1768—1774),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Повстання бузьких козаків (1817),(Citation: Перепис населення Російської імперії (1897),(Citation: Смуга осілості — Вікіпедія 2026),(Citation: Польское восстание (1863—1864),(Citation: Правління гетьманського уряду — Вікіпедія 2026),(Citation: Малоросійське генерал-губернаторство — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Столипінська реформа — Вікіпедія 2026),(Citation: Антикріпосницький рух в Україні (1789-1861),(Citation: Кирило-Мефодіївське товариство — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026)</t>
-  </si>
-  <si>
-    <t>(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Рашизм: Звір з безодні 2023),(Citation: Дезінформація під час російсько-української війни — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: 2016 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Російсько-українська війна (з 2014),(Citation: Історія України — Вікіпедія 2026),(Citation: 2015 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023),(Citation: Российские удары по украинской энергосистеме — Википедия 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Хроника первой российской войны в Чечне 2026)</t>
-  </si>
-  <si>
-    <t>(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Карательная психиатрия в России: назад в СССР? 2020),(Citation: Історія України — Вікіпедія 2026),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Рашизм: Звір з безодні 2023),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Карательная психиатрия в России: назад в СССР? 2020),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: Котлета по-київськи (промова),(Citation: Історія України — Вікіпедія 2026),(Citation: Рашизм: Звір з безодні 2023),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: В ТЕНИ «БОЛЬШОГО БРАТА» ЗАПАДНЫЕ НАЦИОНАЛЬНЫЕ МЕНЬШИНСТВА В СССР 1917-1938 ГГ . 2011),(Citation: Всесоюзний референдум про збереження СРСР — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: ДИССИДЕНТСКОЕ ДВИЖЕНИЕ В УКРАИНЕ (1954 – 1987),(Citation: Історія України — Вікіпедія 2026),(Citation: Кенгирское восстание заключённых - Википедия 2026)</t>
-  </si>
-  <si>
-    <t>(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939)</t>
+    <t>(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.)</t>
+  </si>
+  <si>
+    <t>(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Руїна — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Московсько-українська війна (1658—1659),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Північна війна (1700—1721),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Руїна — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Решетилівські статті — Вікіпедія 2026),(Citation: Запорозька Січ — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Переяславські статті (1659),(Citation: Переяславська рада — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Московсько-українська війна (1658—1659),(Citation: Киевский синопсис — Википедия 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Малоросійський приказ — Вікіпедія 2026),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Мазепа 2007),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Решетилівські статті — Вікіпедія 2026),(Citation: Переяславська рада — Вікіпедія 2026),(Citation: Азовські походи (1695—1696),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Малоросійський приказ — Вікіпедія 2026),(Citation: Руїна — Вікіпедія 2026),(Citation: Ліквідація козацтва на Правобережній Україні (1699),(Citation: Андрусовское перемирие - Википедия 2026),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Мазепа 2007),(Citation: Конотопські статті — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Киевский синопсис — Википедия 2026),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Запорозька Січ — Вікіпедія 2026),(Citation: Переяславські статті (1659),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Московські статті (1665)</t>
+  </si>
+  <si>
+    <t>(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Повстання бузьких козаків (1817),(Citation: Листопадове повстання (1830—1831),(Citation: Чорносотенці — Вікіпедія 2026),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026),(Citation: Друга Малоросійська колегія — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Столипінська реформа — Вікіпедія 2026),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Історія Донецької області — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Крымская война — Википедия 2026),(Citation: Русско-турецкая война (1768—1774),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026),(Citation: Україна у війнах Наполеона — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Кирило-Мефодіївське товариство — Вікіпедія 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Російсько-турецька війна (1806—1812),(Citation: Правління гетьманського уряду — Вікіпедія 2026),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Смуга осілості — Вікіпедія 2026),(Citation: Малоросійське генерал-губернаторство — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Антикріпосницький рух в Україні (1789-1861),(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Столипінська реформа — Вікіпедія 2026),(Citation: Перепис населення Російської імперії (1897),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Повстання бузьких козаків (1817),(Citation: Листопадове повстання (1830—1831),(Citation: Чорносотенці — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Польское восстание (1863—1864)</t>
+  </si>
+  <si>
+    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Російсько-українська війна (з 2014),(Citation: Рашизм: Звір з безодні 2023),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Российские удары по украинской энергосистеме — Википедия 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Дезінформація під час російсько-української війни — Вікіпедія 2026),(Citation: 2015 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: 2016 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Русифікація України — Вікіпедія 2026)</t>
+  </si>
+  <si>
+    <t>(Citation: Історія України — Вікіпедія 2026),(Citation: Карательная психиатрия в России: назад в СССР? 2020),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Рашизм: Звір з безодні 2023),(Citation: Карательная психиатрия в России: назад в СССР? 2020),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Котлета по-київськи (промова),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: В ТЕНИ «БОЛЬШОГО БРАТА» ЗАПАДНЫЕ НАЦИОНАЛЬНЫЕ МЕНЬШИНСТВА В СССР 1917-1938 ГГ . 2011),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: ДИССИДЕНТСКОЕ ДВИЖЕНИЕ В УКРАИНЕ (1954 – 1987),(Citation: Рашизм: Звір з безодні 2023),(Citation: Кенгирское восстание заключённых - Википедия 2026),(Citation: Всесоюзний референдум про збереження СРСР — Вікіпедія 2026),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
+  </si>
+  <si>
+    <t>(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.)</t>
   </si>
   <si>
     <t>source ID</t>
@@ -281,43 +281,43 @@
     <t>Подконтрольная оппозиция</t>
   </si>
   <si>
-    <t>tool--b4c0d62c-b3f5-4069-a07d-c7e9a48427e5</t>
-  </si>
-  <si>
-    <t>tool--4ba8494b-f590-4308-868c-37a12508f6a3</t>
-  </si>
-  <si>
-    <t>tool--5ceff728-9a89-463d-b71b-79b952d31693</t>
-  </si>
-  <si>
-    <t>tool--d57519cc-1898-4106-8e8b-4798bf53d3b4</t>
-  </si>
-  <si>
-    <t>tool--4ebdeb25-4eb2-43cd-a70b-e019e1a4ef6c</t>
-  </si>
-  <si>
-    <t>tool--ff0e5cd8-b850-4df9-845a-ab14c6ba2104</t>
-  </si>
-  <si>
-    <t>tool--2de74860-9286-45c7-b350-d41ae6685351</t>
-  </si>
-  <si>
-    <t>tool--5c43501c-aa32-48a4-a151-6c6897e3b0dd</t>
-  </si>
-  <si>
-    <t>tool--5dcf4786-4e1a-44f2-8aa0-e4b5fdf1f93f</t>
-  </si>
-  <si>
-    <t>tool--af3c7286-be13-4569-ac9d-c96ebbac6a34</t>
-  </si>
-  <si>
-    <t>tool--413178e7-81d2-4bdd-ab53-c632febad570</t>
-  </si>
-  <si>
-    <t>tool--e5929876-f3ec-466c-90a8-ec4a16cd8ac7</t>
-  </si>
-  <si>
-    <t>tool--fd9d33aa-46ee-48a8-b37c-b5813b8dd7cb</t>
+    <t>tool--24a04dcd-846a-4c5b-bfcd-47828e9ddd57</t>
+  </si>
+  <si>
+    <t>tool--e8d0468c-8a92-4294-baa2-a91bcd6f19e4</t>
+  </si>
+  <si>
+    <t>tool--66dcf02c-a2aa-4a17-9e43-2e456ebdee31</t>
+  </si>
+  <si>
+    <t>tool--06c48a32-5cf5-4cef-8992-72c541bfdfac</t>
+  </si>
+  <si>
+    <t>tool--82bcdaea-f53f-45de-8281-b671db596090</t>
+  </si>
+  <si>
+    <t>tool--d0e502ca-3ba5-4364-b2ab-30d53b87c681</t>
+  </si>
+  <si>
+    <t>tool--e07eeae6-c3e5-45f1-b8f1-c3e50a179665</t>
+  </si>
+  <si>
+    <t>tool--fb5d65db-23c3-4502-8fd9-7b40965d2ed8</t>
+  </si>
+  <si>
+    <t>tool--634cf340-6e8c-49d7-b45f-c9fb4f722daa</t>
+  </si>
+  <si>
+    <t>tool--4d016c34-bb94-4b61-88bc-7e9cacc2185b</t>
+  </si>
+  <si>
+    <t>tool--2bf94bf0-b6e0-4e29-bef7-8745173179cb</t>
+  </si>
+  <si>
+    <t>tool--df0ba05b-fd65-4437-9c8f-5fbbf4498f51</t>
+  </si>
+  <si>
+    <t>tool--88d6ef27-a088-40e6-b97f-8a49b8c508e1</t>
   </si>
   <si>
     <t>software</t>
@@ -425,106 +425,106 @@
     <t>Провоцирование большевиками восстания рабочих завода «Арсенал» в самом Киеве для оттягивания резервов украинских властей прямо во время наступления красных войск. (Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
   </si>
   <si>
-    <t>relationship--ee1770df-945f-4564-9553-b1d84f490dcd</t>
-  </si>
-  <si>
-    <t>relationship--8bc54604-c986-43f2-a701-b12592389a95</t>
-  </si>
-  <si>
-    <t>relationship--653bfee4-8148-4228-b9ad-a0dd9f6fb024</t>
-  </si>
-  <si>
-    <t>relationship--8c5d41d1-9fc6-4849-a964-d4d4cd88d808</t>
-  </si>
-  <si>
-    <t>relationship--5be4de54-a976-41cf-9a3e-801a66dd4ab0</t>
-  </si>
-  <si>
-    <t>relationship--f005b199-111a-4b05-aefa-24a35febc482</t>
-  </si>
-  <si>
-    <t>relationship--0dbf3ce6-19bd-478e-adf9-32c6e80ed0ea</t>
-  </si>
-  <si>
-    <t>relationship--c208739a-827c-4d0e-bf28-61b916f15cfe</t>
-  </si>
-  <si>
-    <t>relationship--614fbc69-8cba-40a0-98f9-936eaac5419e</t>
-  </si>
-  <si>
-    <t>relationship--ca9d96ad-f282-4c8a-a7f1-c49268bc3a88</t>
-  </si>
-  <si>
-    <t>relationship--086b6153-43f4-47de-80df-44693f738943</t>
-  </si>
-  <si>
-    <t>relationship--8a4808c1-777c-40fc-aa35-f6cd68dc33c2</t>
-  </si>
-  <si>
-    <t>relationship--37a411b5-a9ad-4aa3-b275-64db44664d5d</t>
-  </si>
-  <si>
-    <t>relationship--aee80eb9-ab23-4760-8add-e0216bd30a05</t>
-  </si>
-  <si>
-    <t>relationship--ca3971ca-3608-4f4b-ba38-3b8e016ebf03</t>
-  </si>
-  <si>
-    <t>relationship--80974889-50af-4c79-93b8-102362fc0530</t>
-  </si>
-  <si>
-    <t>relationship--e6ca03f6-6ec1-4870-bcb9-a3c507268afb</t>
-  </si>
-  <si>
-    <t>relationship--2a6b0d1a-4fc7-40de-9362-c8eb8abcb9fa</t>
-  </si>
-  <si>
-    <t>relationship--df0ae14a-9167-4c70-bba9-d917ecd1bcbe</t>
-  </si>
-  <si>
-    <t>relationship--38cbf6e2-05be-4c93-9361-7c3355dec29f</t>
-  </si>
-  <si>
-    <t>relationship--eb3986b1-fecd-4d37-92dd-0c8250ef0740</t>
-  </si>
-  <si>
-    <t>relationship--388cb58a-f6b1-432c-aa19-57cc86f8713f</t>
-  </si>
-  <si>
-    <t>relationship--c6850c22-f194-48a1-b786-c5cf857b99cd</t>
-  </si>
-  <si>
-    <t>relationship--917fb287-22e5-452a-9dc2-8c5c8aca7d1b</t>
-  </si>
-  <si>
-    <t>relationship--34cf12dd-b962-4ebe-830a-d8f1c7ff5c4f</t>
-  </si>
-  <si>
-    <t>relationship--94711d8b-0578-438a-9d73-eafd0c1bc983</t>
-  </si>
-  <si>
-    <t>relationship--8045380f-5282-4b2f-ab8f-cb92ffd304a3</t>
-  </si>
-  <si>
-    <t>relationship--3536b790-3098-4639-9c74-ac882b5ab83e</t>
-  </si>
-  <si>
-    <t>relationship--c09a449b-0b73-4e67-abc0-922897a14e61</t>
-  </si>
-  <si>
-    <t>relationship--079404c8-fadc-4028-b464-f31ba21f9514</t>
-  </si>
-  <si>
-    <t>relationship--51aabffe-86e6-4eaa-bf10-1d5525e930ad</t>
-  </si>
-  <si>
-    <t>relationship--49567418-6145-460a-ab69-bcb7861395ac</t>
-  </si>
-  <si>
-    <t>relationship--69dc0331-617e-4089-ac23-257dbeee91a6</t>
-  </si>
-  <si>
-    <t>relationship--57e6a8bb-5b08-4144-8f3d-8b095b08d609</t>
+    <t>relationship--bb009c88-365d-4fab-bf01-19c7661e62af</t>
+  </si>
+  <si>
+    <t>relationship--77b46dc8-4a63-44dd-9bd7-031969ec253c</t>
+  </si>
+  <si>
+    <t>relationship--5bde57b1-9715-42f1-b049-e06f015a1772</t>
+  </si>
+  <si>
+    <t>relationship--a14a9035-fa57-4d41-89f7-891ac9fcf81f</t>
+  </si>
+  <si>
+    <t>relationship--1c1b685c-3181-4352-b249-432542879ed6</t>
+  </si>
+  <si>
+    <t>relationship--475161f8-6686-424b-9917-db6889a0fcf3</t>
+  </si>
+  <si>
+    <t>relationship--13ac5123-1a57-4b3a-8d5a-662c89bf41a2</t>
+  </si>
+  <si>
+    <t>relationship--f5209d1a-7895-4020-acae-5dc4e5d8bfc0</t>
+  </si>
+  <si>
+    <t>relationship--5ee5526e-96eb-41af-b8b8-c90b91e64049</t>
+  </si>
+  <si>
+    <t>relationship--3be37c13-b9bc-47bb-8653-fa401dabd4e7</t>
+  </si>
+  <si>
+    <t>relationship--b0c2c062-c89e-4085-8716-bad67e98026e</t>
+  </si>
+  <si>
+    <t>relationship--31fd82da-dfa8-42b5-95dd-f168e6627746</t>
+  </si>
+  <si>
+    <t>relationship--2c5e4520-1275-4ab3-a9a8-2e2b1e964c13</t>
+  </si>
+  <si>
+    <t>relationship--b55647cc-a783-4225-b64b-618bc0c73e2b</t>
+  </si>
+  <si>
+    <t>relationship--6014c6c0-0579-4b5e-a854-2e87b36442cf</t>
+  </si>
+  <si>
+    <t>relationship--9c8d906b-4588-4163-b779-c3b8321985df</t>
+  </si>
+  <si>
+    <t>relationship--1419cb9b-276d-4b72-a3f1-6788f5712c97</t>
+  </si>
+  <si>
+    <t>relationship--a0a599d6-96f3-46a9-8021-f95ca90c5c60</t>
+  </si>
+  <si>
+    <t>relationship--422caa87-ac34-4167-80a3-e3f294b52304</t>
+  </si>
+  <si>
+    <t>relationship--d95d1848-9eb8-41a1-9eb4-0dab6d9b048c</t>
+  </si>
+  <si>
+    <t>relationship--c8ddd7ea-ed8e-4c46-8d00-0188061a5430</t>
+  </si>
+  <si>
+    <t>relationship--b4237490-0e8a-46d4-95a6-1cdaa172bcc8</t>
+  </si>
+  <si>
+    <t>relationship--6d106e24-cb8f-42ae-8ea2-c24c3ac66a5e</t>
+  </si>
+  <si>
+    <t>relationship--d3e614da-a65e-49a8-b28c-1bda5c4ff9ad</t>
+  </si>
+  <si>
+    <t>relationship--673fe51c-7945-423e-9767-3b824d79a43f</t>
+  </si>
+  <si>
+    <t>relationship--b4b464b3-2e82-48ba-b3e5-8680a6803204</t>
+  </si>
+  <si>
+    <t>relationship--ec2419f7-91b8-4498-b50c-0deec7e9eed4</t>
+  </si>
+  <si>
+    <t>relationship--62fc2c5e-3c4f-4760-ba3a-320af5a52635</t>
+  </si>
+  <si>
+    <t>relationship--5c3c5267-b7aa-47e8-a640-d413fe3d0e2b</t>
+  </si>
+  <si>
+    <t>relationship--559bac5f-e601-4430-a4d1-3e40065ec036</t>
+  </si>
+  <si>
+    <t>relationship--aaed89ae-ca29-4a00-9e21-1cc9143a649e</t>
+  </si>
+  <si>
+    <t>relationship--acd4d015-7a92-4a60-8741-9e316340e075</t>
+  </si>
+  <si>
+    <t>relationship--3d963d7d-a454-4e0a-9940-35584a671824</t>
+  </si>
+  <si>
+    <t>relationship--e1c4bbc4-90c4-48de-8589-c0a639fef400</t>
   </si>
   <si>
     <t>T0019</t>
@@ -1025,253 +1025,253 @@
     <t>Поддержка подконтрольной оппозиции</t>
   </si>
   <si>
-    <t>attack-pattern--f60c3210-890a-4015-a4a9-e1966101ed5d</t>
-  </si>
-  <si>
-    <t>attack-pattern--c985b114-66f8-43e8-a9d5-09f7dcce76d2</t>
-  </si>
-  <si>
-    <t>attack-pattern--9d3f3422-f494-42ab-9385-bc4e8ef727ca</t>
-  </si>
-  <si>
-    <t>attack-pattern--67fd1251-9ad0-415e-94db-14c6fcda7c8c</t>
-  </si>
-  <si>
-    <t>attack-pattern--6819df95-06a3-4c71-874f-8daea090f07e</t>
-  </si>
-  <si>
-    <t>attack-pattern--22337eab-4ab5-4577-a766-4a514a636fe2</t>
-  </si>
-  <si>
-    <t>attack-pattern--ef5c8e81-c4de-408e-a0bb-eeba03e4ef41</t>
-  </si>
-  <si>
-    <t>attack-pattern--d71852a6-d08a-4937-b2b1-ccf143798754</t>
-  </si>
-  <si>
-    <t>attack-pattern--71b8603d-1b4a-45dd-bdc5-58df6fe6a1cb</t>
-  </si>
-  <si>
-    <t>attack-pattern--3953a646-ca74-4d27-bb4b-801773351821</t>
-  </si>
-  <si>
-    <t>attack-pattern--03024756-3f6a-42b3-b93e-2d31c7ce6b6b</t>
-  </si>
-  <si>
-    <t>attack-pattern--3d1653fe-5ea0-4eb0-8c78-f849ecc43e11</t>
-  </si>
-  <si>
-    <t>attack-pattern--9facc2a5-8243-49aa-96cb-a94ef85b25c9</t>
-  </si>
-  <si>
-    <t>attack-pattern--d38398cd-b820-4626-9510-465d56ba906c</t>
-  </si>
-  <si>
-    <t>attack-pattern--02964caf-d52a-4d68-abcc-cdd1ef5fa69d</t>
-  </si>
-  <si>
-    <t>attack-pattern--d5f24756-885a-43f1-a9f0-b0088651bbc3</t>
-  </si>
-  <si>
-    <t>attack-pattern--9162f78a-1b72-4adc-9f8b-0a6b6410a3a7</t>
-  </si>
-  <si>
-    <t>attack-pattern--0de3e487-7362-4416-91f8-3c71cc10d76d</t>
-  </si>
-  <si>
-    <t>attack-pattern--5e67abdd-9625-497c-8eed-591b2d0091a8</t>
-  </si>
-  <si>
-    <t>attack-pattern--9e90f9e3-ced7-476d-acac-467e8c865ca0</t>
-  </si>
-  <si>
-    <t>attack-pattern--f62f4a3e-70ad-4d66-978f-70460748790e</t>
-  </si>
-  <si>
-    <t>attack-pattern--9861afc3-113a-4f8e-ba90-12d851653a4c</t>
-  </si>
-  <si>
-    <t>attack-pattern--cc782e40-0ae3-4f6d-94cb-2828cb2d5005</t>
-  </si>
-  <si>
-    <t>attack-pattern--36fadd8e-e035-4c50-be0d-258be309a516</t>
-  </si>
-  <si>
-    <t>attack-pattern--9596e8a1-16fa-466f-b16e-b567018e83c6</t>
-  </si>
-  <si>
-    <t>attack-pattern--09059676-291f-4053-a7b5-17d93eb87d30</t>
-  </si>
-  <si>
-    <t>attack-pattern--8a804fba-621a-4868-b128-51cebf0ad2b2</t>
-  </si>
-  <si>
-    <t>attack-pattern--738e1811-a9a5-4407-be43-b726fd7e7589</t>
-  </si>
-  <si>
-    <t>attack-pattern--d4d22a9d-86be-4ed6-bb79-7792aad443f3</t>
-  </si>
-  <si>
-    <t>attack-pattern--63335f7f-c1d8-42d3-bab5-4055c59e6a1e</t>
-  </si>
-  <si>
-    <t>attack-pattern--c55f58f1-faf2-498e-84f2-59993e1ecbcc</t>
-  </si>
-  <si>
-    <t>attack-pattern--c7ccd834-4f08-4829-96ae-45e58d47945f</t>
-  </si>
-  <si>
-    <t>attack-pattern--c93829ec-d90f-41a9-9191-466a6365de51</t>
-  </si>
-  <si>
-    <t>attack-pattern--c671af96-e92c-44ff-820d-00bdb7de4fca</t>
-  </si>
-  <si>
-    <t>attack-pattern--4a811ffb-e200-4e7b-a48d-5dbb2e05d21b</t>
-  </si>
-  <si>
-    <t>attack-pattern--7ee9829e-072b-48f0-b801-b5b627c8bf1a</t>
-  </si>
-  <si>
-    <t>attack-pattern--ea9a2533-0faa-4b9d-bb0e-237ca902e1d7</t>
-  </si>
-  <si>
-    <t>attack-pattern--4b4499c1-7976-4838-ac5f-1b2503e91894</t>
-  </si>
-  <si>
-    <t>attack-pattern--b0851c83-e4d2-41c1-b5de-9115df406339</t>
-  </si>
-  <si>
-    <t>attack-pattern--137a55c1-3751-4f3e-b038-0a8a31ae7b53</t>
-  </si>
-  <si>
-    <t>attack-pattern--2bb142f3-19c9-4d2d-ab6b-e91a6d1eb45d</t>
-  </si>
-  <si>
-    <t>attack-pattern--09c9ca23-10d8-4f0f-a7dd-e99bb022299a</t>
-  </si>
-  <si>
-    <t>attack-pattern--6a388bfd-b3f8-4136-a3d0-3b6c92b62616</t>
-  </si>
-  <si>
-    <t>attack-pattern--e1c78d1f-6f07-4f4b-9220-6d455354bc64</t>
-  </si>
-  <si>
-    <t>attack-pattern--40f36bf9-2850-4992-b47f-4abe909a0e93</t>
-  </si>
-  <si>
-    <t>attack-pattern--b34ebb98-d962-4987-8399-890eef9c69fe</t>
-  </si>
-  <si>
-    <t>attack-pattern--cbff6b3a-8340-4986-9183-3c02b87fd1b2</t>
-  </si>
-  <si>
-    <t>attack-pattern--2f0e072e-5d5e-458e-a5c3-8efbaef46084</t>
-  </si>
-  <si>
-    <t>attack-pattern--41699f0f-f822-4dbc-b201-dca7ac3eddce</t>
-  </si>
-  <si>
-    <t>attack-pattern--07605117-d49e-4edb-b205-a42d341fbafe</t>
-  </si>
-  <si>
-    <t>attack-pattern--77c6e8eb-0074-49c8-90cd-9c830db4859f</t>
-  </si>
-  <si>
-    <t>attack-pattern--ed457228-1fd9-4a65-ac85-388ba6460f94</t>
-  </si>
-  <si>
-    <t>attack-pattern--12023694-fdfd-480d-990d-fefa0cc12655</t>
-  </si>
-  <si>
-    <t>attack-pattern--3eff3cd8-fbaf-4e5d-b38e-c72604acb3ce</t>
-  </si>
-  <si>
-    <t>attack-pattern--d984185b-2502-414b-969d-f165cdeedc31</t>
-  </si>
-  <si>
-    <t>attack-pattern--8a5da3da-67cf-4659-bb91-0b28685766a1</t>
-  </si>
-  <si>
-    <t>attack-pattern--76b6c6fb-ce17-427d-b717-16011ae54b6e</t>
-  </si>
-  <si>
-    <t>attack-pattern--6e962dbe-f818-407b-b5a6-3eec9fbe9ec2</t>
-  </si>
-  <si>
-    <t>attack-pattern--6f08f0ef-8704-4d0e-90f5-ad421918d899</t>
-  </si>
-  <si>
-    <t>attack-pattern--86f1c7c0-561e-4b45-97c0-faad41484e38</t>
-  </si>
-  <si>
-    <t>attack-pattern--36e1d7c1-2f0e-41c6-8aee-177df4bdbc61</t>
-  </si>
-  <si>
-    <t>attack-pattern--0d6e1a1e-2c33-4280-86f2-8a1d0049b089</t>
-  </si>
-  <si>
-    <t>attack-pattern--a882288f-98fe-4c75-859a-17d669c08376</t>
-  </si>
-  <si>
-    <t>attack-pattern--a87aa45d-2118-4e87-af92-e75e367453c9</t>
-  </si>
-  <si>
-    <t>attack-pattern--b3a3b655-dacd-4ee5-bae1-68801c3d15dc</t>
-  </si>
-  <si>
-    <t>attack-pattern--2d723928-4bb8-45b5-86d4-a6f2398ca02f</t>
-  </si>
-  <si>
-    <t>attack-pattern--5df092aa-9e0d-440d-8aa0-5f9988432ae3</t>
-  </si>
-  <si>
-    <t>attack-pattern--3c5f8bcd-ee2b-4396-9e79-3c99fcc96d81</t>
-  </si>
-  <si>
-    <t>attack-pattern--8861e444-81bb-468e-9fc5-8b7e401e8898</t>
-  </si>
-  <si>
-    <t>attack-pattern--da48c22f-a5e2-41e7-97e4-07bfc4156350</t>
-  </si>
-  <si>
-    <t>attack-pattern--c6da22a5-ceb4-4f40-a3bc-bcd6e655d591</t>
-  </si>
-  <si>
-    <t>attack-pattern--fef3fc3b-399c-41e0-8c76-a6eb1d014ada</t>
-  </si>
-  <si>
-    <t>attack-pattern--0b6448a8-18a4-4d48-bfcf-172a74724542</t>
-  </si>
-  <si>
-    <t>attack-pattern--edd49cde-2190-45a8-9277-0fafcda1502c</t>
-  </si>
-  <si>
-    <t>attack-pattern--8f3de97b-1ed5-4594-9889-41cd32d8adf5</t>
-  </si>
-  <si>
-    <t>attack-pattern--f2e939fc-283e-4bea-9fbf-f17acac31435</t>
-  </si>
-  <si>
-    <t>attack-pattern--1f8e90a1-2fa1-4e0c-9de7-2a6b61fc3412</t>
-  </si>
-  <si>
-    <t>attack-pattern--4b8920a8-f486-4065-aff8-4e7b6ee8b829</t>
-  </si>
-  <si>
-    <t>attack-pattern--b2df162e-6cd7-4286-8841-dbeff90a7e20</t>
-  </si>
-  <si>
-    <t>attack-pattern--02c5997b-a7da-48ac-96da-c4daa1aafc35</t>
-  </si>
-  <si>
-    <t>attack-pattern--5f90feb8-5507-456c-9d1d-0e0e3cce55de</t>
-  </si>
-  <si>
-    <t>attack-pattern--d051e585-aa48-4964-b54e-2e08adc472f9</t>
-  </si>
-  <si>
-    <t>attack-pattern--edcb13e5-fbb1-4396-9e8c-1e3fe9dde52c</t>
+    <t>attack-pattern--d8fec2ab-fe86-4530-9801-bbbe5c3baf44</t>
+  </si>
+  <si>
+    <t>attack-pattern--e06e27d3-c18f-4bac-9bb6-17121de4850b</t>
+  </si>
+  <si>
+    <t>attack-pattern--ab6eb169-9d35-462e-8540-e600dcfcc755</t>
+  </si>
+  <si>
+    <t>attack-pattern--11df0e1b-fb0b-495a-8517-fe9629386cc7</t>
+  </si>
+  <si>
+    <t>attack-pattern--d039ccb5-695e-4e9c-903d-4a25d80a5e91</t>
+  </si>
+  <si>
+    <t>attack-pattern--d67e92a1-567a-4443-b196-42eee7df7df9</t>
+  </si>
+  <si>
+    <t>attack-pattern--f8863479-abf3-40aa-909f-422ff587ef75</t>
+  </si>
+  <si>
+    <t>attack-pattern--f87361eb-4cc0-472a-9d20-d8814c3dcb83</t>
+  </si>
+  <si>
+    <t>attack-pattern--14ddac56-e61c-489c-9f2a-0ead47acab72</t>
+  </si>
+  <si>
+    <t>attack-pattern--ca19f909-8e73-4014-ab69-a521482caa77</t>
+  </si>
+  <si>
+    <t>attack-pattern--7b5e8502-6625-4bfb-becf-4701773fc345</t>
+  </si>
+  <si>
+    <t>attack-pattern--63e9746b-4223-4c4d-bb27-a4c2f724f832</t>
+  </si>
+  <si>
+    <t>attack-pattern--255d85ab-8ae5-4855-9d4d-398d57bfb428</t>
+  </si>
+  <si>
+    <t>attack-pattern--3c78bc06-b7d9-4d72-87cc-3896a83a79c1</t>
+  </si>
+  <si>
+    <t>attack-pattern--e1500254-a805-457b-9c9f-eaa7ed4441c2</t>
+  </si>
+  <si>
+    <t>attack-pattern--40ddc318-d9d7-4035-80a9-21f5de23c666</t>
+  </si>
+  <si>
+    <t>attack-pattern--bbbea8cd-eb4e-4314-abc8-2293225ab5e6</t>
+  </si>
+  <si>
+    <t>attack-pattern--7302168b-1756-4aa2-9831-57b042e5e79c</t>
+  </si>
+  <si>
+    <t>attack-pattern--23537b01-052d-4788-a1c5-ac64ea3a5440</t>
+  </si>
+  <si>
+    <t>attack-pattern--ba18aeed-1fa0-4221-b5c3-2951c695226d</t>
+  </si>
+  <si>
+    <t>attack-pattern--1c3cc896-6014-4a38-bb84-f755661f9f8a</t>
+  </si>
+  <si>
+    <t>attack-pattern--0f207f69-c49f-4bd9-a2c8-81d5903af798</t>
+  </si>
+  <si>
+    <t>attack-pattern--15b42e50-034b-48ec-a530-08f4da421ced</t>
+  </si>
+  <si>
+    <t>attack-pattern--0e9f8dfa-7044-47a4-99c4-b8108e0c3531</t>
+  </si>
+  <si>
+    <t>attack-pattern--541f9c2f-5e7e-40bd-8807-e27b27bf27f9</t>
+  </si>
+  <si>
+    <t>attack-pattern--d2982864-148c-45ed-9a9d-73124e552f59</t>
+  </si>
+  <si>
+    <t>attack-pattern--ce173a13-3838-4451-bcde-529c8c9cbf4d</t>
+  </si>
+  <si>
+    <t>attack-pattern--3c3ab581-f839-4439-bf70-a00298d8cbb7</t>
+  </si>
+  <si>
+    <t>attack-pattern--3d477757-3882-43e5-b3b5-5c453472af4e</t>
+  </si>
+  <si>
+    <t>attack-pattern--cfd09f3f-20c2-4148-a51e-c7533a4f6866</t>
+  </si>
+  <si>
+    <t>attack-pattern--69b5ecb8-ed59-476a-a8d0-692d61060065</t>
+  </si>
+  <si>
+    <t>attack-pattern--a67dba4e-5c9c-4a96-8564-cc1477847aa2</t>
+  </si>
+  <si>
+    <t>attack-pattern--3c2787d0-9bb3-4445-baf7-affe99ffc75d</t>
+  </si>
+  <si>
+    <t>attack-pattern--281cf3bf-8184-4148-8d26-8ae24ac5facd</t>
+  </si>
+  <si>
+    <t>attack-pattern--0a36cf96-d155-4205-badf-fce21153e3d3</t>
+  </si>
+  <si>
+    <t>attack-pattern--58aadf94-c0fc-45fe-b84d-86af05ac2a41</t>
+  </si>
+  <si>
+    <t>attack-pattern--f409ed58-993e-4cd3-816b-35cb16df5f13</t>
+  </si>
+  <si>
+    <t>attack-pattern--0f543b48-8526-45f6-9f4c-c0aabf08b950</t>
+  </si>
+  <si>
+    <t>attack-pattern--2665c1bf-c793-4ff8-81e1-8cdfb042a050</t>
+  </si>
+  <si>
+    <t>attack-pattern--d1450cbb-9ca9-4637-a3d4-415897d678b3</t>
+  </si>
+  <si>
+    <t>attack-pattern--f7a7642e-6431-4d94-8930-784669743a6e</t>
+  </si>
+  <si>
+    <t>attack-pattern--2eccd110-1bf6-4854-a82c-0a45775e907f</t>
+  </si>
+  <si>
+    <t>attack-pattern--77f583b6-9202-4712-9a61-f28cba87bf1b</t>
+  </si>
+  <si>
+    <t>attack-pattern--b9b7420d-58cf-49d6-9884-18e4d72f0a38</t>
+  </si>
+  <si>
+    <t>attack-pattern--31403032-89b6-4a29-af26-bdb2c907f869</t>
+  </si>
+  <si>
+    <t>attack-pattern--59e9ef1f-3d12-4523-a3ac-0b4c11c35573</t>
+  </si>
+  <si>
+    <t>attack-pattern--3b7ebd5a-2989-4a5f-8187-7dcbb6319ecd</t>
+  </si>
+  <si>
+    <t>attack-pattern--47a73afc-602e-4840-98f7-559a0583a02f</t>
+  </si>
+  <si>
+    <t>attack-pattern--b6ab653b-b93b-46b8-9fc3-d24ccf9a86a1</t>
+  </si>
+  <si>
+    <t>attack-pattern--cfe0ba66-044c-4fae-899d-2776ecd25970</t>
+  </si>
+  <si>
+    <t>attack-pattern--faf29c5e-51f3-4afd-9b72-70769986b561</t>
+  </si>
+  <si>
+    <t>attack-pattern--9f4aa723-88b2-42d4-b7f0-58bfc3f42435</t>
+  </si>
+  <si>
+    <t>attack-pattern--39c46a2f-f777-48c7-b903-20ce80bca89b</t>
+  </si>
+  <si>
+    <t>attack-pattern--0c6b2071-1b00-4c4e-ad42-c086fe85e44d</t>
+  </si>
+  <si>
+    <t>attack-pattern--20e9f442-a9aa-49d2-86e7-10b3677d2b71</t>
+  </si>
+  <si>
+    <t>attack-pattern--01cef48e-e90c-42c2-b99f-c6ce6b48b026</t>
+  </si>
+  <si>
+    <t>attack-pattern--df7b78e3-6709-4b71-ae0c-08ed1a47de6b</t>
+  </si>
+  <si>
+    <t>attack-pattern--661bd189-a8b3-42ff-bf5b-33de03ae6136</t>
+  </si>
+  <si>
+    <t>attack-pattern--7ef5f9c4-8044-44bc-88a6-9395e47e160a</t>
+  </si>
+  <si>
+    <t>attack-pattern--b7f8cff2-87c7-48c1-aeb7-5cf9187b1090</t>
+  </si>
+  <si>
+    <t>attack-pattern--3ec89812-91d7-48b1-aa07-b78e44175f91</t>
+  </si>
+  <si>
+    <t>attack-pattern--1a21e55e-d799-41ce-a799-461e1995bd5a</t>
+  </si>
+  <si>
+    <t>attack-pattern--5ba903c1-2421-4964-8ca4-f56dcc96a1c3</t>
+  </si>
+  <si>
+    <t>attack-pattern--50e11ffa-fd63-4200-af97-d723ceb03f87</t>
+  </si>
+  <si>
+    <t>attack-pattern--954103ab-7172-4bc3-80d2-6eda761140c7</t>
+  </si>
+  <si>
+    <t>attack-pattern--d4ba7ff5-0107-437e-853c-b8c4d37ea441</t>
+  </si>
+  <si>
+    <t>attack-pattern--f6f80852-da09-4571-bd87-ab371a289296</t>
+  </si>
+  <si>
+    <t>attack-pattern--c69305fb-035a-4c61-8929-2e22cea42d61</t>
+  </si>
+  <si>
+    <t>attack-pattern--b1ae5e87-2d91-4460-ab24-a874f71d0aa3</t>
+  </si>
+  <si>
+    <t>attack-pattern--3408f6b9-9851-47a8-8c46-591cab11c267</t>
+  </si>
+  <si>
+    <t>attack-pattern--9a46e5ee-7093-4048-9d7e-501463c0424d</t>
+  </si>
+  <si>
+    <t>attack-pattern--f2121d22-b6ab-4c8d-b1a6-a65df30bd836</t>
+  </si>
+  <si>
+    <t>attack-pattern--01660591-eff8-4002-8b86-edbc8ddcff75</t>
+  </si>
+  <si>
+    <t>attack-pattern--1337b0db-4d5f-447f-83d1-3682c83da1be</t>
+  </si>
+  <si>
+    <t>attack-pattern--2685f739-43ca-4258-8e7f-0cf545de3477</t>
+  </si>
+  <si>
+    <t>attack-pattern--5da8aa0b-7c9c-4638-bc17-9ed6bf1aafa6</t>
+  </si>
+  <si>
+    <t>attack-pattern--b1616020-3221-457d-9111-770be3da803f</t>
+  </si>
+  <si>
+    <t>attack-pattern--60789ba9-9b1e-4a2d-804d-b16342fe5f3d</t>
+  </si>
+  <si>
+    <t>attack-pattern--9b1b420b-4d1a-4108-a086-73ba81138b1a</t>
+  </si>
+  <si>
+    <t>attack-pattern--1a522e5a-e65b-443f-8aae-2bc39534e85e</t>
+  </si>
+  <si>
+    <t>attack-pattern--3c07dbf7-3e3e-47d9-b439-53989a64f430</t>
+  </si>
+  <si>
+    <t>attack-pattern--948886a4-efe9-40cc-8153-3370afff323e</t>
+  </si>
+  <si>
+    <t>attack-pattern--c21a61e0-99df-4c01-abf2-5e46d8345613</t>
   </si>
   <si>
     <t>technique</t>
@@ -1754,571 +1754,571 @@
     <t>Введение государственной монополии на торговлю хлебом и централизованный контроль над распределением товаров. (Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.) 2013)</t>
   </si>
   <si>
-    <t>relationship--e51c177b-f601-47d5-9ae9-f6adb3dc397d</t>
-  </si>
-  <si>
-    <t>relationship--baecff7e-dc21-44ea-b863-ca8da3c62424</t>
-  </si>
-  <si>
-    <t>relationship--19d3a78f-c438-41f5-a55e-42a419a860ed</t>
-  </si>
-  <si>
-    <t>relationship--1cff25ec-e815-4f02-a656-6f61d9b4302b</t>
-  </si>
-  <si>
-    <t>relationship--574346d1-3eca-43c0-804a-6a49b0fedfbc</t>
-  </si>
-  <si>
-    <t>relationship--e0c46f26-e4dc-44f2-931a-3de7a380d82c</t>
-  </si>
-  <si>
-    <t>relationship--13b93f7a-eceb-4ba1-985b-9f182d1f8959</t>
-  </si>
-  <si>
-    <t>relationship--c094c5e2-4681-47c6-b649-aac2e30ef63e</t>
-  </si>
-  <si>
-    <t>relationship--6b756697-3af1-4921-8afa-de43e8494726</t>
-  </si>
-  <si>
-    <t>relationship--7cd3a274-997e-4fd8-96bd-ed11dbd871ae</t>
-  </si>
-  <si>
-    <t>relationship--e5064444-57d6-4ead-9e9f-a9797549b00a</t>
-  </si>
-  <si>
-    <t>relationship--a977d06e-c9fb-44fb-be91-d9d4ca6f6739</t>
-  </si>
-  <si>
-    <t>relationship--85d74a25-2849-44c5-be0e-0b95c58d05f8</t>
-  </si>
-  <si>
-    <t>relationship--5601426d-de66-4843-a720-640c317e943a</t>
-  </si>
-  <si>
-    <t>relationship--6b8df6aa-2628-49da-9686-9f4ce8ca52b4</t>
-  </si>
-  <si>
-    <t>relationship--02fbe54f-4fe3-4152-9a95-e00d089ad2d0</t>
-  </si>
-  <si>
-    <t>relationship--b74dbe90-0bd4-44ca-9b39-3217a14f9230</t>
-  </si>
-  <si>
-    <t>relationship--37b54435-8bbc-408e-80ac-ccb32adf9d74</t>
-  </si>
-  <si>
-    <t>relationship--e8277521-5c12-4beb-afa2-1d923b1370fa</t>
-  </si>
-  <si>
-    <t>relationship--aac62415-47fd-4339-998a-96774dc28e1a</t>
-  </si>
-  <si>
-    <t>relationship--d884d995-cb3e-42e1-a219-5b8593d7f55d</t>
-  </si>
-  <si>
-    <t>relationship--e63288e7-7429-4d44-93f8-fbae85b7d73c</t>
-  </si>
-  <si>
-    <t>relationship--88530d1b-75a5-40da-a530-138b7ed1bccb</t>
-  </si>
-  <si>
-    <t>relationship--9ff1122a-8920-4536-a6c9-b3651fe87a41</t>
-  </si>
-  <si>
-    <t>relationship--27d5e8cd-20cd-46d3-9497-57611e95e581</t>
-  </si>
-  <si>
-    <t>relationship--bbd6ac57-e29b-42c1-be57-9bbd7676104e</t>
-  </si>
-  <si>
-    <t>relationship--92239776-053f-40a0-aee3-5f0b9a1c07b5</t>
-  </si>
-  <si>
-    <t>relationship--8a3be6db-85c6-4603-a7fc-bb3acfabea88</t>
-  </si>
-  <si>
-    <t>relationship--5fb44550-4eee-4ab7-b478-d2805c2ba9b4</t>
-  </si>
-  <si>
-    <t>relationship--ca087af6-d503-43b8-abc2-10d6090c5a27</t>
-  </si>
-  <si>
-    <t>relationship--8f906083-a1b0-4547-96cc-b43ba604f276</t>
-  </si>
-  <si>
-    <t>relationship--8b2be964-dd7c-4e0b-82b6-6428d3bf1d42</t>
-  </si>
-  <si>
-    <t>relationship--80915558-dd86-465b-9b1a-e747fb99671c</t>
-  </si>
-  <si>
-    <t>relationship--edcf285d-1f1a-46ea-b28f-a4fcee5a385b</t>
-  </si>
-  <si>
-    <t>relationship--20245c10-e5f3-407c-a3b2-96c8c085b0f1</t>
-  </si>
-  <si>
-    <t>relationship--10e85415-c003-4ef7-a284-05708b6b72be</t>
-  </si>
-  <si>
-    <t>relationship--0fff1f96-3a68-42e4-8e4a-8c8fcb3ce386</t>
-  </si>
-  <si>
-    <t>relationship--5847e598-577d-463a-a3e9-5ca130dd4507</t>
-  </si>
-  <si>
-    <t>relationship--0352eb5f-1132-41ac-9206-b0e16b54436f</t>
-  </si>
-  <si>
-    <t>relationship--852117e1-8630-47eb-8e2e-e22cb2a1564a</t>
-  </si>
-  <si>
-    <t>relationship--5f4533c6-d5e7-41ed-8e89-ce7a3cb061bf</t>
-  </si>
-  <si>
-    <t>relationship--9707dd7d-b5a0-43e2-a6a5-6abce54b7edb</t>
-  </si>
-  <si>
-    <t>relationship--2398c8cc-88a5-4549-b19b-911958d2abe5</t>
-  </si>
-  <si>
-    <t>relationship--c7016342-e47b-4470-a344-672819c70b0d</t>
-  </si>
-  <si>
-    <t>relationship--34666ba1-5c30-4d83-bf2f-c127bb848dcb</t>
-  </si>
-  <si>
-    <t>relationship--5fbe8112-b86f-44db-b323-2f27083564e0</t>
-  </si>
-  <si>
-    <t>relationship--5e064122-2c0d-4930-bf68-fa20ec7fcdea</t>
-  </si>
-  <si>
-    <t>relationship--465dfbec-c935-48b8-ba7c-e8fe3561ca94</t>
-  </si>
-  <si>
-    <t>relationship--1604968c-dab0-43dc-8511-292fcd5575d9</t>
-  </si>
-  <si>
-    <t>relationship--be9a0880-9570-4610-93ec-e350f360d63f</t>
-  </si>
-  <si>
-    <t>relationship--c72b0b22-0cf9-4346-9637-60b6e5b705f9</t>
-  </si>
-  <si>
-    <t>relationship--1f637adc-e5b4-471d-8de1-d477966b1125</t>
-  </si>
-  <si>
-    <t>relationship--56625bef-dd57-4978-9a56-f155789ef3be</t>
-  </si>
-  <si>
-    <t>relationship--b791a492-2bf2-4995-b2d0-6910745d9754</t>
-  </si>
-  <si>
-    <t>relationship--623213a6-abdf-44df-a6fb-c086a684f8b2</t>
-  </si>
-  <si>
-    <t>relationship--468473e7-12c2-46de-88cc-734eafde2868</t>
-  </si>
-  <si>
-    <t>relationship--df901f67-e71f-4192-bcde-7f50d2d9373d</t>
-  </si>
-  <si>
-    <t>relationship--4f31c0bc-a24c-4193-bff2-3a66dae4772f</t>
-  </si>
-  <si>
-    <t>relationship--ec428e67-8568-4f37-a49e-cd580e5c38bd</t>
-  </si>
-  <si>
-    <t>relationship--4ec4ad3d-beca-450e-b6e9-5a93785c5bb0</t>
-  </si>
-  <si>
-    <t>relationship--6effb145-0cd4-4b9f-929f-4c4d89f84ef0</t>
-  </si>
-  <si>
-    <t>relationship--ad081b29-5c12-4d02-8bd1-046b674f4c7c</t>
-  </si>
-  <si>
-    <t>relationship--8f1b3d6f-23b6-4f9b-a8dd-9b3454bd2117</t>
-  </si>
-  <si>
-    <t>relationship--dc5bf458-56f0-43cb-a78d-8bb4bd127e99</t>
-  </si>
-  <si>
-    <t>relationship--9f863b15-ef76-4d35-a0a2-5d4c24c6e6f6</t>
-  </si>
-  <si>
-    <t>relationship--0a76fed9-efeb-4a8e-af6e-d874bc53f71d</t>
-  </si>
-  <si>
-    <t>relationship--465166f8-6a08-4320-aa5b-197bee427cfc</t>
-  </si>
-  <si>
-    <t>relationship--50d6da69-13b5-4383-9a4d-9e6af0892636</t>
-  </si>
-  <si>
-    <t>relationship--67b802bf-c650-4b6b-beac-08a3c96358c8</t>
-  </si>
-  <si>
-    <t>relationship--53719d9d-7011-4032-a70e-8c6138033d7e</t>
-  </si>
-  <si>
-    <t>relationship--5d155807-495a-48a4-be27-5ae299f1c38e</t>
-  </si>
-  <si>
-    <t>relationship--24d049ad-df50-41bf-ba64-070a5db3f232</t>
-  </si>
-  <si>
-    <t>relationship--1912344f-c2b1-497b-8c79-885dac85519f</t>
-  </si>
-  <si>
-    <t>relationship--66da841a-9ba5-4698-9434-a0716c584fcd</t>
-  </si>
-  <si>
-    <t>relationship--a0e26193-7b83-4fac-ba81-a14473696c12</t>
-  </si>
-  <si>
-    <t>relationship--e5ff6d58-7126-41d2-bffc-22be3e559d4c</t>
-  </si>
-  <si>
-    <t>relationship--87e28e8e-0c89-4acc-8d96-191a08c0c4ca</t>
-  </si>
-  <si>
-    <t>relationship--3fc53e7f-aabf-48b1-b1ca-92d9188c5fee</t>
-  </si>
-  <si>
-    <t>relationship--08f43466-659f-422c-be58-91c863e7b936</t>
-  </si>
-  <si>
-    <t>relationship--8160d9a6-4943-4736-a8aa-f256cb2628e3</t>
-  </si>
-  <si>
-    <t>relationship--0fd1b83a-0e8c-485a-9eea-9f1c28469003</t>
-  </si>
-  <si>
-    <t>relationship--955f1858-3345-4ba3-a027-ebbbdc018d52</t>
-  </si>
-  <si>
-    <t>relationship--5f967830-b2b4-4835-b8b3-78e3bb061c70</t>
-  </si>
-  <si>
-    <t>relationship--3662bcda-cf5d-4fd0-9313-620bd45d8adf</t>
-  </si>
-  <si>
-    <t>relationship--97eea6b0-abef-4c35-9150-15ffb0cfd642</t>
-  </si>
-  <si>
-    <t>relationship--4374b082-17aa-4a1e-9780-00373446507e</t>
-  </si>
-  <si>
-    <t>relationship--a38375ec-bc00-4e85-a5b2-013e20b1c61d</t>
-  </si>
-  <si>
-    <t>relationship--dd2f3bc2-fac5-4b98-a5ef-9687daaaa6fc</t>
-  </si>
-  <si>
-    <t>relationship--366d7ed8-a586-4109-9559-6c939ffd576a</t>
-  </si>
-  <si>
-    <t>relationship--402e6d4b-59c4-4e77-9b16-57a4076ae2d5</t>
-  </si>
-  <si>
-    <t>relationship--e9909627-4a7d-495a-834c-315541ab15fd</t>
-  </si>
-  <si>
-    <t>relationship--4b76cb9a-0bed-478d-b892-63357f2f24c9</t>
-  </si>
-  <si>
-    <t>relationship--a93a651a-ffac-4fc7-b9d4-6cc0d508089f</t>
-  </si>
-  <si>
-    <t>relationship--cc43e87c-69f3-4e15-a919-8898b8215090</t>
-  </si>
-  <si>
-    <t>relationship--83e6df16-07fe-41e5-a65b-6ed35c215cc2</t>
-  </si>
-  <si>
-    <t>relationship--5b878410-76cf-418c-b857-a2449022a172</t>
-  </si>
-  <si>
-    <t>relationship--1f29a6cf-c9bd-4e1a-af91-4490d00c1ea6</t>
-  </si>
-  <si>
-    <t>relationship--2cf31521-70c1-4491-a5ae-fe3c4bbc5246</t>
-  </si>
-  <si>
-    <t>relationship--157809ff-2ffb-485c-8b54-1a89d4dcb435</t>
-  </si>
-  <si>
-    <t>relationship--0461225b-8179-4aae-bc0f-d3b7851d4346</t>
-  </si>
-  <si>
-    <t>relationship--5e1ebc3e-adbb-46e4-afea-ca56f35aa3b8</t>
-  </si>
-  <si>
-    <t>relationship--20dfaeff-38ff-450e-b141-6512f93d479c</t>
-  </si>
-  <si>
-    <t>relationship--f6651003-cdfd-476e-964b-b9c1f9814aea</t>
-  </si>
-  <si>
-    <t>relationship--db030bae-c5f5-49ed-8ff4-af0e20ee225d</t>
-  </si>
-  <si>
-    <t>relationship--060b2bb4-62b6-4c64-9527-12b75f6856fb</t>
-  </si>
-  <si>
-    <t>relationship--f105b8ec-d05f-4968-b2d5-c5e5adff5a61</t>
-  </si>
-  <si>
-    <t>relationship--9de38fe8-f56c-4b6d-937c-b36b9e6b8972</t>
-  </si>
-  <si>
-    <t>relationship--f1e432e9-d627-42c5-8582-b9091113bb86</t>
-  </si>
-  <si>
-    <t>relationship--bc55738f-b0ed-416f-844b-6b1f22a7f345</t>
-  </si>
-  <si>
-    <t>relationship--4b753a57-ecd3-4fc6-a713-e0ad97968b62</t>
-  </si>
-  <si>
-    <t>relationship--4e0d7262-08ba-4fb5-bb63-dc30429b3fab</t>
-  </si>
-  <si>
-    <t>relationship--781b4bbf-8a2c-4057-baf5-1878ea619b0c</t>
-  </si>
-  <si>
-    <t>relationship--79f87c09-c697-4dd0-99f2-9fe176f8755c</t>
-  </si>
-  <si>
-    <t>relationship--badcf672-80b4-4756-bc72-46ed253671e1</t>
-  </si>
-  <si>
-    <t>relationship--77906d62-bf50-4cac-88ce-1dd773bab573</t>
-  </si>
-  <si>
-    <t>relationship--16eaf531-3997-47f0-a83e-7f32c635c0fc</t>
-  </si>
-  <si>
-    <t>relationship--8212aa70-f140-43d6-ba87-bfc75ec72e5f</t>
-  </si>
-  <si>
-    <t>relationship--aaa22663-967a-4b00-a539-b09ff557e821</t>
-  </si>
-  <si>
-    <t>relationship--fb30d154-83b6-4539-afb5-0c3888d3bec9</t>
-  </si>
-  <si>
-    <t>relationship--55aba2a5-f217-4d99-9c5b-5f3dac640b92</t>
-  </si>
-  <si>
-    <t>relationship--e8afeeaf-035c-4c76-b5bc-7e4af0f3395c</t>
-  </si>
-  <si>
-    <t>relationship--41a8b0a2-e56f-4893-9cd8-7c65ff389bf8</t>
-  </si>
-  <si>
-    <t>relationship--fb15b942-85d3-4fc7-991d-d9d2041a09e1</t>
-  </si>
-  <si>
-    <t>relationship--c5d8a571-ee0d-419d-8c01-bede9443b942</t>
-  </si>
-  <si>
-    <t>relationship--da556bf9-dba9-4c54-a5e8-c44cb6e48c3d</t>
-  </si>
-  <si>
-    <t>relationship--035189d5-3e56-41ed-98a6-a7efa1dda59a</t>
-  </si>
-  <si>
-    <t>relationship--ba7fc371-952e-4b6b-a61c-45b699357b3d</t>
-  </si>
-  <si>
-    <t>relationship--c35844cb-0555-42da-ba1f-cd933eebe624</t>
-  </si>
-  <si>
-    <t>relationship--4acd9755-b416-4b00-acc6-250ae9622465</t>
-  </si>
-  <si>
-    <t>relationship--0c0d5d6e-42fc-4d8e-902a-a19fe207848e</t>
-  </si>
-  <si>
-    <t>relationship--85e68b26-66be-4060-bc7e-a280bacd4e3a</t>
-  </si>
-  <si>
-    <t>relationship--a74700f2-597f-4f08-aeba-e87654802d35</t>
-  </si>
-  <si>
-    <t>relationship--47cbce4a-835a-4782-be3f-3f40fed7a3c8</t>
-  </si>
-  <si>
-    <t>relationship--03840c67-b080-459b-afa5-dabebcb4d44d</t>
-  </si>
-  <si>
-    <t>relationship--b7e30afc-7d74-4b1e-a1c5-653abf36c875</t>
-  </si>
-  <si>
-    <t>relationship--5f1bc6d9-5417-4f2c-9c50-d84caa46cb19</t>
-  </si>
-  <si>
-    <t>relationship--21c44f8f-68f3-4578-acb9-ef09c6722ab8</t>
-  </si>
-  <si>
-    <t>relationship--13e01f4c-8dd4-4b7d-9a30-3900d9fed55c</t>
-  </si>
-  <si>
-    <t>relationship--9702d5d0-42c1-46ce-b8dd-b0bfb6b33a3c</t>
-  </si>
-  <si>
-    <t>relationship--0a9ba803-afc5-414d-9159-cbe1dec86fdb</t>
-  </si>
-  <si>
-    <t>relationship--59db0a16-d7b1-472c-ba90-58d8e720dc4c</t>
-  </si>
-  <si>
-    <t>relationship--06e37dc0-aec3-40a5-9fdc-0a3900505d13</t>
-  </si>
-  <si>
-    <t>relationship--bffe6e07-ed4b-4734-aa19-1477f29364d2</t>
-  </si>
-  <si>
-    <t>relationship--1c36c5be-b13c-4f11-960f-9b03cbc87f8d</t>
-  </si>
-  <si>
-    <t>relationship--d3fd53b4-18fa-45e9-b69f-6a0d7520a5ca</t>
-  </si>
-  <si>
-    <t>relationship--756d0f2d-207e-4f7b-b0b2-b48292f01566</t>
-  </si>
-  <si>
-    <t>relationship--9a868a03-666e-4f64-b596-5c48bdee52c3</t>
-  </si>
-  <si>
-    <t>relationship--d7fc2066-edf6-47c6-a83c-7206850f0ab5</t>
-  </si>
-  <si>
-    <t>relationship--5d579a13-67d5-448a-adc5-83a4fafe6397</t>
-  </si>
-  <si>
-    <t>relationship--de480653-7c48-4149-8c94-9b269c7d47a4</t>
-  </si>
-  <si>
-    <t>relationship--6a67ff6b-94aa-4750-ab1b-fc32683bdef6</t>
-  </si>
-  <si>
-    <t>relationship--7d309686-d313-4099-bb16-28e1c507b4de</t>
-  </si>
-  <si>
-    <t>relationship--da8866ae-3f47-46eb-94b8-372a984469cd</t>
-  </si>
-  <si>
-    <t>relationship--3a5d6f95-14ab-46c5-b8da-032669b0bae2</t>
-  </si>
-  <si>
-    <t>relationship--024a7113-e248-4822-bea2-30f77d9a7a8f</t>
-  </si>
-  <si>
-    <t>relationship--00ca73d0-0387-42d0-84bc-936fda075d8d</t>
-  </si>
-  <si>
-    <t>relationship--1c8c0f26-e354-4f16-866b-c4ed7978e820</t>
-  </si>
-  <si>
-    <t>relationship--37ca5c6c-a8bd-4cc0-a94a-94c62380ad01</t>
-  </si>
-  <si>
-    <t>relationship--09ca5108-558b-4995-9467-494a354a918a</t>
-  </si>
-  <si>
-    <t>relationship--0e1317d3-00a0-4713-9781-766b42db644e</t>
-  </si>
-  <si>
-    <t>relationship--ba57efe2-3653-460c-a6d1-5293aa19b7ce</t>
-  </si>
-  <si>
-    <t>relationship--19a86362-7955-4dbf-bbb0-1c8de038abc9</t>
-  </si>
-  <si>
-    <t>relationship--105776f8-fb6e-40b1-90d5-51a56bacf1c1</t>
-  </si>
-  <si>
-    <t>relationship--26e34a40-646e-40bd-97fd-af7707fec87e</t>
-  </si>
-  <si>
-    <t>relationship--43674d3b-1755-45c6-be2c-b5e6b83dc1fd</t>
-  </si>
-  <si>
-    <t>relationship--56c13e79-da44-4855-abc6-d1119ccf296a</t>
-  </si>
-  <si>
-    <t>relationship--2b20ec1c-dcf1-4f91-abeb-ebe52c94ed06</t>
-  </si>
-  <si>
-    <t>relationship--7bb3178c-db31-4233-9649-cde63f598fde</t>
-  </si>
-  <si>
-    <t>relationship--8840ff74-0db6-4bb2-b7fb-90692fae5cf7</t>
-  </si>
-  <si>
-    <t>relationship--1abc678f-dce8-47c5-90b4-26b570e01f03</t>
-  </si>
-  <si>
-    <t>relationship--a10fcf23-dced-4c62-8b72-de9252e3dd3e</t>
-  </si>
-  <si>
-    <t>relationship--16744069-cca1-4a02-b485-33f838b5ab31</t>
-  </si>
-  <si>
-    <t>relationship--c4da07a0-ac6b-43bb-acb4-0e1eebb72e1d</t>
-  </si>
-  <si>
-    <t>relationship--b13c20bf-f6f3-496b-9bbc-756d27bcc338</t>
-  </si>
-  <si>
-    <t>relationship--ead18e3d-243e-4bfc-9e35-dcef978fa1a6</t>
-  </si>
-  <si>
-    <t>relationship--daa06fd4-7ec9-441c-9dad-d0b476425de6</t>
-  </si>
-  <si>
-    <t>relationship--efe698ab-5c0f-471e-965f-49902fb52ff3</t>
-  </si>
-  <si>
-    <t>relationship--bc99b34b-c89e-4a48-93d6-98e18c56bd9c</t>
-  </si>
-  <si>
-    <t>relationship--1c294501-8bda-4b29-b345-880b8d39a07c</t>
-  </si>
-  <si>
-    <t>relationship--1420dce4-e170-412c-8605-5ec9480fb9e2</t>
-  </si>
-  <si>
-    <t>relationship--a88ea7e3-49fd-4f48-a25f-2aa2a4cfda6c</t>
-  </si>
-  <si>
-    <t>relationship--4fde23f7-a081-497c-907b-a3499be478c1</t>
-  </si>
-  <si>
-    <t>relationship--c894f2d6-6b3d-43a9-ad2c-6d2c1c596045</t>
-  </si>
-  <si>
-    <t>relationship--01673386-068e-4501-ac11-1263c9fe485e</t>
-  </si>
-  <si>
-    <t>relationship--2c5dfe88-33fb-44bb-9dbc-b2430f5b1ecf</t>
-  </si>
-  <si>
-    <t>relationship--34bf02af-e6fa-4c0e-ad5c-d45c46d77832</t>
-  </si>
-  <si>
-    <t>relationship--52bddd02-b48a-4510-910a-094c4433eb2d</t>
-  </si>
-  <si>
-    <t>relationship--5506c3cf-59c7-46bb-9bf2-902908d87126</t>
-  </si>
-  <si>
-    <t>relationship--3984cea3-d47b-4481-8888-c0b1f35969c1</t>
+    <t>relationship--14ff5c13-bd58-4f3e-8847-116ab3781971</t>
+  </si>
+  <si>
+    <t>relationship--b8a1efd8-c26a-40b5-aee5-821ce44b4e16</t>
+  </si>
+  <si>
+    <t>relationship--8b9ecf43-5f5e-4e27-b61d-4fceafa47b81</t>
+  </si>
+  <si>
+    <t>relationship--2280f18d-76c9-4ede-885e-1f9f023d5edf</t>
+  </si>
+  <si>
+    <t>relationship--8b5ce05d-0dc5-44bb-a980-427c816728fd</t>
+  </si>
+  <si>
+    <t>relationship--84a726d6-aa58-4936-b16d-e720c1b9a864</t>
+  </si>
+  <si>
+    <t>relationship--f1d4c82a-9578-4e69-8a56-31829df9fbe5</t>
+  </si>
+  <si>
+    <t>relationship--b04fb82c-ac5f-488a-8dcd-fee6bb377ac3</t>
+  </si>
+  <si>
+    <t>relationship--21ab8f08-5ff9-4e53-8833-b03519bd6cd1</t>
+  </si>
+  <si>
+    <t>relationship--c86a5336-5315-4098-aa83-cd2f97e64823</t>
+  </si>
+  <si>
+    <t>relationship--803320d8-15ba-4348-8c32-bccf3db9f530</t>
+  </si>
+  <si>
+    <t>relationship--b413164f-24a7-4fc4-8ea9-138b0044ce12</t>
+  </si>
+  <si>
+    <t>relationship--f5b536e6-69d1-4bbe-83d9-1ba923dfcb36</t>
+  </si>
+  <si>
+    <t>relationship--7039355e-000e-46d0-8e30-1f7d9dfb4f5e</t>
+  </si>
+  <si>
+    <t>relationship--0efafd8f-ad20-4211-94bd-b94e514a4f77</t>
+  </si>
+  <si>
+    <t>relationship--95b25427-2e1f-495c-a35f-4da450c13301</t>
+  </si>
+  <si>
+    <t>relationship--a6e2c789-2ec6-48f4-bdef-117bd254f13a</t>
+  </si>
+  <si>
+    <t>relationship--af609251-5be4-4f65-90c8-fb3cc9a3dbb4</t>
+  </si>
+  <si>
+    <t>relationship--5cd48454-813b-4331-9c08-66ab490f7c61</t>
+  </si>
+  <si>
+    <t>relationship--0c4c43ea-624a-44d5-ba8b-7758a90422b9</t>
+  </si>
+  <si>
+    <t>relationship--9cf98d26-dcde-4e15-9b77-f531dfaaa42c</t>
+  </si>
+  <si>
+    <t>relationship--d62fcf47-1ed7-4e8e-89ae-ae2b35893e89</t>
+  </si>
+  <si>
+    <t>relationship--a3a14ae4-5efd-4ab9-95b0-7fe445ebaba9</t>
+  </si>
+  <si>
+    <t>relationship--02467645-18f1-44b3-9807-2febf2484815</t>
+  </si>
+  <si>
+    <t>relationship--bf8dd70b-311f-4582-b644-bef5c2fb33b6</t>
+  </si>
+  <si>
+    <t>relationship--dd9311f1-d090-402e-95ba-563ab46c7d70</t>
+  </si>
+  <si>
+    <t>relationship--f2d6a2cf-89d4-471d-954f-85ebca68df09</t>
+  </si>
+  <si>
+    <t>relationship--16305f31-01fb-4769-adda-fb68bdb5bdf5</t>
+  </si>
+  <si>
+    <t>relationship--f2506c16-b956-47b5-8994-61403315d62f</t>
+  </si>
+  <si>
+    <t>relationship--287fce25-2f71-4417-86e4-73d207d621d4</t>
+  </si>
+  <si>
+    <t>relationship--0cd1d9f5-1b62-4894-9c7a-887333274daa</t>
+  </si>
+  <si>
+    <t>relationship--bcfcbe09-5315-4558-a202-b0c3549f574c</t>
+  </si>
+  <si>
+    <t>relationship--72c5aa19-3333-497c-bc10-22276193dbe0</t>
+  </si>
+  <si>
+    <t>relationship--15c9a760-9071-47c3-8b86-207c651c3f9d</t>
+  </si>
+  <si>
+    <t>relationship--4834d7b9-4aad-4db8-b067-793cae286279</t>
+  </si>
+  <si>
+    <t>relationship--fc84144f-1d31-45d5-a091-7122aeffdb3a</t>
+  </si>
+  <si>
+    <t>relationship--ab5fb347-4be5-47d7-ac92-a21f54383f24</t>
+  </si>
+  <si>
+    <t>relationship--2fa33b37-bbe4-4bd4-8235-b137f4579659</t>
+  </si>
+  <si>
+    <t>relationship--c2dc6232-da70-47d5-8e03-23c22d15201e</t>
+  </si>
+  <si>
+    <t>relationship--69b5a3eb-88ee-4898-b5eb-bf99882e755a</t>
+  </si>
+  <si>
+    <t>relationship--8f834fe2-1ea9-4f4e-904e-03480b71fc0c</t>
+  </si>
+  <si>
+    <t>relationship--4c910602-8a1f-4a1b-ae96-78ff77141c32</t>
+  </si>
+  <si>
+    <t>relationship--bb2fb6c6-2082-4128-9aa2-6fd397d4b077</t>
+  </si>
+  <si>
+    <t>relationship--6217bbde-7bd4-4ff9-8084-1bb50aa35f0a</t>
+  </si>
+  <si>
+    <t>relationship--ae394320-962d-4311-a23d-f02679fc432f</t>
+  </si>
+  <si>
+    <t>relationship--5e9166c6-f3f3-4067-b9fb-81ac58ccea57</t>
+  </si>
+  <si>
+    <t>relationship--a77f7b5f-7b61-4700-8fda-341ffc586aa3</t>
+  </si>
+  <si>
+    <t>relationship--17249a22-d960-4c98-bd73-2176cff9a66d</t>
+  </si>
+  <si>
+    <t>relationship--2a6b25b3-2106-4cc5-9daf-69080545023a</t>
+  </si>
+  <si>
+    <t>relationship--7b1b9159-5728-4caa-b025-e233988eed18</t>
+  </si>
+  <si>
+    <t>relationship--bc9dae11-ee8d-437a-a5f2-151aad2a22b9</t>
+  </si>
+  <si>
+    <t>relationship--957f013b-288a-43a5-9b47-0b8ae24ecf5a</t>
+  </si>
+  <si>
+    <t>relationship--aa2e1b37-5b37-49f7-aa1b-6ae619b5c0f4</t>
+  </si>
+  <si>
+    <t>relationship--3f22a8b4-118a-4f55-9a26-b1ba62fa35b2</t>
+  </si>
+  <si>
+    <t>relationship--bcddaa91-a8a1-47ba-885d-b9525a1001aa</t>
+  </si>
+  <si>
+    <t>relationship--ef01b363-58f1-4d39-83d0-99ac81ffc65b</t>
+  </si>
+  <si>
+    <t>relationship--5e7fd20e-84e5-4350-b635-8cbfe36923cb</t>
+  </si>
+  <si>
+    <t>relationship--68d4e642-f528-4420-abae-afc75e93414f</t>
+  </si>
+  <si>
+    <t>relationship--aafb6322-5c65-4a69-831f-ce7c553efb7a</t>
+  </si>
+  <si>
+    <t>relationship--d5f27e9e-a55f-43aa-9040-20018524f869</t>
+  </si>
+  <si>
+    <t>relationship--3f9d7bd8-83c9-4fd9-9aa4-3b54a80bdb79</t>
+  </si>
+  <si>
+    <t>relationship--ec6b5a74-c9d6-4d5d-851d-4340a2c1e77a</t>
+  </si>
+  <si>
+    <t>relationship--1bd2d7ca-6d0d-45b7-aa5c-92d1af9ab047</t>
+  </si>
+  <si>
+    <t>relationship--1788c4e6-bd1e-42f4-bc4c-53a28ea72247</t>
+  </si>
+  <si>
+    <t>relationship--d1bd8bf5-4e79-47ca-bcd8-cb3ceed828ed</t>
+  </si>
+  <si>
+    <t>relationship--9707a4a3-85fc-4326-b941-6e3f4ba3d66e</t>
+  </si>
+  <si>
+    <t>relationship--ce616361-b9c6-41d7-9fa1-c6800c8569b7</t>
+  </si>
+  <si>
+    <t>relationship--c16c1d51-00c9-42e2-a472-267146714a16</t>
+  </si>
+  <si>
+    <t>relationship--8be9daf3-3283-4014-bb07-58b184b74d93</t>
+  </si>
+  <si>
+    <t>relationship--1e810079-efd1-4437-8550-e46be0afa71e</t>
+  </si>
+  <si>
+    <t>relationship--23db1a49-8cfc-4e88-baa9-6cdc44a115a2</t>
+  </si>
+  <si>
+    <t>relationship--cd711de5-eeb1-4125-b828-3b8a8f1b07f3</t>
+  </si>
+  <si>
+    <t>relationship--349ef81a-2f99-4a9c-9c81-e57f79f07d82</t>
+  </si>
+  <si>
+    <t>relationship--60c11da2-7800-43b7-8d1f-76c8aa05a5c9</t>
+  </si>
+  <si>
+    <t>relationship--98c02793-243e-4135-9a39-882178ad8a96</t>
+  </si>
+  <si>
+    <t>relationship--55ff4a91-8661-475f-8ad7-0f09f83c5e85</t>
+  </si>
+  <si>
+    <t>relationship--f198baec-e5e1-4737-8a14-de81017b8eea</t>
+  </si>
+  <si>
+    <t>relationship--d6938961-a091-45b1-bffc-87c242cf25a2</t>
+  </si>
+  <si>
+    <t>relationship--4cfdc688-c4fc-4bb4-a16d-fe39a1f133f7</t>
+  </si>
+  <si>
+    <t>relationship--4c8204a0-a1be-45e1-86b8-3f4cdd438ce7</t>
+  </si>
+  <si>
+    <t>relationship--7b3c83f1-d4d5-48b3-aadf-dceaea68b4ed</t>
+  </si>
+  <si>
+    <t>relationship--d9e0502c-e40e-4515-8c12-b3097dc7475a</t>
+  </si>
+  <si>
+    <t>relationship--33335b1d-f384-436a-9b2f-6977401616dd</t>
+  </si>
+  <si>
+    <t>relationship--563da1b2-2363-4bca-a36f-9427fbb0eeb1</t>
+  </si>
+  <si>
+    <t>relationship--d513bfcd-ce05-438e-ae32-b2aa913d07c8</t>
+  </si>
+  <si>
+    <t>relationship--26a2ccda-f08b-4248-a25b-0e55035acef5</t>
+  </si>
+  <si>
+    <t>relationship--74fd0492-7a79-4dda-8c2d-24e17c4bdab3</t>
+  </si>
+  <si>
+    <t>relationship--c249bddd-af15-4cad-90ed-82cdbeb66aa8</t>
+  </si>
+  <si>
+    <t>relationship--a73dab7a-cba3-4295-9a68-163953884ba6</t>
+  </si>
+  <si>
+    <t>relationship--43501e8a-b825-42ec-b6ec-e295e5cc2e08</t>
+  </si>
+  <si>
+    <t>relationship--bcbf16b1-48cf-4bc1-bb2f-5c361772e1f1</t>
+  </si>
+  <si>
+    <t>relationship--42d0b716-8699-4628-a8d2-d043f5334d2f</t>
+  </si>
+  <si>
+    <t>relationship--e91bf280-5cb2-4f22-973d-ca790c6a9765</t>
+  </si>
+  <si>
+    <t>relationship--1a85808f-513b-446c-8752-4b2ec5da5ee5</t>
+  </si>
+  <si>
+    <t>relationship--b89f2f86-e815-40bd-a82f-3bb6a732125d</t>
+  </si>
+  <si>
+    <t>relationship--fe71a8b2-0517-4fd7-bfec-9e1cd4b701c0</t>
+  </si>
+  <si>
+    <t>relationship--c0561e87-1c03-480c-86ee-6e8e79673848</t>
+  </si>
+  <si>
+    <t>relationship--3542d62b-9969-4f15-87ec-f94b5e6b4405</t>
+  </si>
+  <si>
+    <t>relationship--d217853a-a549-41ec-b95b-00caca3410b2</t>
+  </si>
+  <si>
+    <t>relationship--a2bab682-f3ac-4992-a542-5cecc03e0074</t>
+  </si>
+  <si>
+    <t>relationship--431f4e5a-5596-4a39-b84d-cd1f38d861b3</t>
+  </si>
+  <si>
+    <t>relationship--48ffcfbb-741a-478a-baa6-a36149793de8</t>
+  </si>
+  <si>
+    <t>relationship--827e00b3-a532-4a87-82e5-77f4de601e05</t>
+  </si>
+  <si>
+    <t>relationship--65222228-0b79-420f-a997-9c20f99ecaa4</t>
+  </si>
+  <si>
+    <t>relationship--231fa5f0-a19b-44f4-bc6f-dfa148cc8679</t>
+  </si>
+  <si>
+    <t>relationship--01861179-0186-4305-a71f-27f5e670b04f</t>
+  </si>
+  <si>
+    <t>relationship--5324471d-3a9d-4dcd-989c-0d95bd2d23e9</t>
+  </si>
+  <si>
+    <t>relationship--137d4968-3b9a-4eac-845b-ba164af2867e</t>
+  </si>
+  <si>
+    <t>relationship--5f10c7ac-d87d-4407-add7-7166679dd1f5</t>
+  </si>
+  <si>
+    <t>relationship--e7163b63-492c-4886-9dc2-6e859aa6d034</t>
+  </si>
+  <si>
+    <t>relationship--fc01a550-6494-40e0-8c0d-5c380763303b</t>
+  </si>
+  <si>
+    <t>relationship--822f19d2-5f87-4880-afbe-f1a2b98a3dbf</t>
+  </si>
+  <si>
+    <t>relationship--93fa1b38-db1c-4c2c-aac4-835e21431a8b</t>
+  </si>
+  <si>
+    <t>relationship--9d405089-6db2-4242-9be1-901cd852b765</t>
+  </si>
+  <si>
+    <t>relationship--391c1305-e015-4bd7-bb03-22bfba33c82b</t>
+  </si>
+  <si>
+    <t>relationship--4a68d93b-f1da-4a51-812b-5bf2f0c60a7b</t>
+  </si>
+  <si>
+    <t>relationship--7a210575-716a-406f-9d8e-172a2dbba802</t>
+  </si>
+  <si>
+    <t>relationship--e8029807-08ca-48d9-8572-6a38d99bd2c2</t>
+  </si>
+  <si>
+    <t>relationship--1e9b5938-8fed-4bc2-8d92-9525edd34e24</t>
+  </si>
+  <si>
+    <t>relationship--5268dc98-c56e-46a9-9bef-63cf230d237b</t>
+  </si>
+  <si>
+    <t>relationship--5ea6892d-4b0d-4cbd-8020-6aed168df5a4</t>
+  </si>
+  <si>
+    <t>relationship--55780959-01ec-4069-844d-6df18f57da1f</t>
+  </si>
+  <si>
+    <t>relationship--c46122a2-0e53-4c4b-8b0c-21bfd5940873</t>
+  </si>
+  <si>
+    <t>relationship--6e256514-03e4-45c9-b522-525f27ce759d</t>
+  </si>
+  <si>
+    <t>relationship--87de8c02-0bc1-4b2a-b3a5-facabf410a9b</t>
+  </si>
+  <si>
+    <t>relationship--cfa25437-a45c-4215-891f-c88fb1c6854e</t>
+  </si>
+  <si>
+    <t>relationship--7672e7ae-da3c-4880-9317-481e88285ca7</t>
+  </si>
+  <si>
+    <t>relationship--8c84f972-8d80-4970-b47e-a43e07b700a3</t>
+  </si>
+  <si>
+    <t>relationship--ae23fbce-cefd-4b11-81e8-a74bed5bef7b</t>
+  </si>
+  <si>
+    <t>relationship--f2d91af3-aff9-4b74-a087-c4e8554811b8</t>
+  </si>
+  <si>
+    <t>relationship--eff280bc-ca08-449f-a941-43ea0f060726</t>
+  </si>
+  <si>
+    <t>relationship--c56e03d1-3287-4cde-95c6-23146e302c3e</t>
+  </si>
+  <si>
+    <t>relationship--c6a6164a-b374-493d-a404-68d7cfe61825</t>
+  </si>
+  <si>
+    <t>relationship--ad667537-8c1d-4601-8f6f-4b65f4440940</t>
+  </si>
+  <si>
+    <t>relationship--0071f400-1c99-437b-a1f1-e6433c057f6f</t>
+  </si>
+  <si>
+    <t>relationship--41366efa-5b40-4d9c-a10f-da330d4c22a0</t>
+  </si>
+  <si>
+    <t>relationship--ba8dc7cc-a4a7-495c-9492-90f49e8d1153</t>
+  </si>
+  <si>
+    <t>relationship--2f06cb0c-dcb4-4cd6-bb11-95526ecd709b</t>
+  </si>
+  <si>
+    <t>relationship--43bfb130-3a03-4742-885d-1a4958c7189b</t>
+  </si>
+  <si>
+    <t>relationship--a01766a1-519b-4338-8c88-0c0e2b937dd3</t>
+  </si>
+  <si>
+    <t>relationship--43545b6d-7cb5-463e-a53d-6528245de722</t>
+  </si>
+  <si>
+    <t>relationship--3ff9678f-3704-4082-a10b-9615cb64ce97</t>
+  </si>
+  <si>
+    <t>relationship--23f4ec20-2a56-48e3-9436-dc947eb85662</t>
+  </si>
+  <si>
+    <t>relationship--26d110af-bfc4-46bd-89a6-b25ec0077a25</t>
+  </si>
+  <si>
+    <t>relationship--749eab61-1c86-4133-8036-76b4667d387a</t>
+  </si>
+  <si>
+    <t>relationship--604c0228-a8aa-45ca-b3d9-009780cd0c93</t>
+  </si>
+  <si>
+    <t>relationship--b5f73c4d-eb9d-4ccc-8058-9891de23f8e6</t>
+  </si>
+  <si>
+    <t>relationship--82c4b68f-c4a9-4899-862a-20954adc01a3</t>
+  </si>
+  <si>
+    <t>relationship--5955053a-b87b-4b43-a152-f15bd6d5c523</t>
+  </si>
+  <si>
+    <t>relationship--2893c79c-adb3-4d67-a698-f859a0bbca0f</t>
+  </si>
+  <si>
+    <t>relationship--e5e199d4-6538-431c-94a2-85eabd8a9920</t>
+  </si>
+  <si>
+    <t>relationship--e1378deb-56c4-46c7-bf35-bcf7ab3a9ce2</t>
+  </si>
+  <si>
+    <t>relationship--9d5634ce-16b9-4d9b-a3d5-45a02d743968</t>
+  </si>
+  <si>
+    <t>relationship--c84a3b83-e414-4a18-b5ab-21d88156b13b</t>
+  </si>
+  <si>
+    <t>relationship--9a4aca14-a9a7-4761-90c4-a315313fa85f</t>
+  </si>
+  <si>
+    <t>relationship--07722c0c-5fc9-4dd0-86fd-06f3bdefc0b1</t>
+  </si>
+  <si>
+    <t>relationship--25b395e7-6c6b-43f4-a5ce-1a7c43a4c4a5</t>
+  </si>
+  <si>
+    <t>relationship--e8603dba-be2c-4d39-a158-05a34a8b2248</t>
+  </si>
+  <si>
+    <t>relationship--9f66288a-6101-45f1-a2e9-b6055dc72b7d</t>
+  </si>
+  <si>
+    <t>relationship--c6689428-236d-4e35-8f40-97343e6b4e4c</t>
+  </si>
+  <si>
+    <t>relationship--a7a247e1-e55c-4946-a6fe-8e89fff30460</t>
+  </si>
+  <si>
+    <t>relationship--bbd6f1fb-1697-4bf7-94eb-9bf778bd21fa</t>
+  </si>
+  <si>
+    <t>relationship--673687e5-33e3-4e10-853a-039ec9bbba0f</t>
+  </si>
+  <si>
+    <t>relationship--d8a80fd2-e649-403f-891a-f81e07386728</t>
+  </si>
+  <si>
+    <t>relationship--a182d298-ac49-4812-83d9-7c918bfdcff8</t>
+  </si>
+  <si>
+    <t>relationship--4e3d4cda-bc26-4e9a-944b-efcfa6e7dc78</t>
+  </si>
+  <si>
+    <t>relationship--89b24472-ef28-47d1-a136-9f156a129bf5</t>
+  </si>
+  <si>
+    <t>relationship--97230a5b-b9e5-4e98-a279-1afb93b1beeb</t>
+  </si>
+  <si>
+    <t>relationship--21b7fe4a-162a-4209-98d4-d360f5c94290</t>
+  </si>
+  <si>
+    <t>relationship--a03544ee-5257-4bc5-9f3d-941053278b0d</t>
+  </si>
+  <si>
+    <t>relationship--055c5491-8ec1-46ed-89bf-d00d10057a44</t>
+  </si>
+  <si>
+    <t>relationship--beff9c5d-311e-4dc5-810a-2898c3d5ef95</t>
+  </si>
+  <si>
+    <t>relationship--eb7f7d87-f0d9-415c-9d85-ec9d6995e371</t>
+  </si>
+  <si>
+    <t>relationship--d11d5a60-b488-4beb-b1e1-6cfeee9b512d</t>
+  </si>
+  <si>
+    <t>relationship--27449a60-290d-4640-9c7c-a4a87cb036d2</t>
+  </si>
+  <si>
+    <t>relationship--e4e82c07-b0d0-4fa0-b0ff-71a24ce8c031</t>
+  </si>
+  <si>
+    <t>relationship--f08aff09-5868-4f68-9056-fde79b6714e0</t>
+  </si>
+  <si>
+    <t>relationship--0eb3e9f8-ed56-49f9-961f-45b74f24d6b6</t>
+  </si>
+  <si>
+    <t>relationship--fe1ed08d-9a16-46e1-a211-946d17efabca</t>
+  </si>
+  <si>
+    <t>relationship--fddd4820-b3a3-42ab-8143-76a8a24e1e54</t>
+  </si>
+  <si>
+    <t>relationship--ad21a81f-9db2-419a-add3-717c177a80cb</t>
+  </si>
+  <si>
+    <t>relationship--3ccacaaf-c9c6-4bcf-8000-0f6f62ffe3a1</t>
+  </si>
+  <si>
+    <t>relationship--04df6efb-a4cd-4802-b309-fc2a7d94bdfa</t>
+  </si>
+  <si>
+    <t>relationship--52ba97a8-e66d-44a9-8e11-62a829dbb246</t>
+  </si>
+  <si>
+    <t>relationship--44b4500d-0d89-47da-aaed-e949cee74c3b</t>
+  </si>
+  <si>
+    <t>relationship--62164b6b-d164-41e7-9481-6223553cf173</t>
+  </si>
+  <si>
+    <t>relationship--50cd576b-7652-4699-b71f-0e4aa10e7538</t>
+  </si>
+  <si>
+    <t>relationship--858ee4ec-8c2e-4d81-a63a-6caaa3b1724e</t>
+  </si>
+  <si>
+    <t>relationship--956b8623-ce91-4d57-ab87-e214dcd8d1e6</t>
   </si>
   <si>
     <t>C0009</t>
@@ -2933,310 +2933,310 @@
     <t>Юридическое поглощение через создание СССР (1922–1924)</t>
   </si>
   <si>
-    <t>campaign--d5d3608b-1e2e-4e8e-9e3e-172b7ae8783f</t>
-  </si>
-  <si>
-    <t>campaign--da1bd8ae-397a-4c07-81d5-4ee62243c68b</t>
-  </si>
-  <si>
-    <t>campaign--6ba841e9-a6e2-4de1-ae16-ca96739e35ed</t>
-  </si>
-  <si>
-    <t>campaign--d25e87a6-7133-4e11-8e93-259d4f2bd994</t>
-  </si>
-  <si>
-    <t>campaign--327371af-9be7-44c2-8b57-7e51eea988c4</t>
-  </si>
-  <si>
-    <t>campaign--e31b1ed6-33c7-4d93-a2c6-a9b1dac0ac8c</t>
-  </si>
-  <si>
-    <t>campaign--000c635b-27f2-43b1-b98d-ff81a4105054</t>
-  </si>
-  <si>
-    <t>campaign--13625203-0aca-405b-9409-d6bb04dedcc2</t>
-  </si>
-  <si>
-    <t>campaign--c89888d0-b5d3-4947-b33d-d1d066710b8d</t>
-  </si>
-  <si>
-    <t>campaign--5b0cdeff-e761-4c3f-ba0c-feaec1ead563</t>
-  </si>
-  <si>
-    <t>campaign--cbda1a24-f09e-414b-ab6c-1177afcf6579</t>
-  </si>
-  <si>
-    <t>campaign--477d33b8-e868-4f14-994c-3ff87914d154</t>
-  </si>
-  <si>
-    <t>campaign--d07a6a51-42fd-4fca-9e60-9f47a2f3d55b</t>
-  </si>
-  <si>
-    <t>campaign--6dc22dba-186d-44f2-b8e5-932b3d3ae163</t>
-  </si>
-  <si>
-    <t>campaign--30e8ed62-d3e8-4143-9e5e-632bd7aa23cc</t>
-  </si>
-  <si>
-    <t>campaign--5a248622-bb69-496e-b7a9-6563aebba048</t>
-  </si>
-  <si>
-    <t>campaign--35ebb683-a8d6-4486-b3b2-f449826b17ce</t>
-  </si>
-  <si>
-    <t>campaign--9d8a0b71-9771-4b85-a072-eb7f2ebaaa79</t>
-  </si>
-  <si>
-    <t>campaign--04b69ccd-9489-447b-99a2-77765d33a863</t>
-  </si>
-  <si>
-    <t>campaign--e29a7c8b-78d8-4200-a28e-b29c47fd3db4</t>
-  </si>
-  <si>
-    <t>campaign--bee06f63-5b9a-40ee-8ded-3807e18b2794</t>
-  </si>
-  <si>
-    <t>campaign--12a31509-f6b1-4af2-ba71-d0d3f1a7e55c</t>
-  </si>
-  <si>
-    <t>campaign--cfd8e869-e600-4d3e-ab87-ab274a92891e</t>
-  </si>
-  <si>
-    <t>campaign--6569f13e-42ba-41d7-a075-7940b2fa7c53</t>
-  </si>
-  <si>
-    <t>campaign--b375cce2-197a-4d61-84e5-bc95c4f061aa</t>
-  </si>
-  <si>
-    <t>campaign--d1be4871-85b3-4161-b768-fcbdd3f3d268</t>
-  </si>
-  <si>
-    <t>campaign--b4a7dd59-002b-4a93-b13c-ab142a60073b</t>
-  </si>
-  <si>
-    <t>campaign--a06fac12-cd5a-4e5a-b61a-efbc0cd5c005</t>
-  </si>
-  <si>
-    <t>campaign--380516f0-c58a-4738-90e3-693af3883357</t>
-  </si>
-  <si>
-    <t>campaign--20b012fa-ab52-4e32-8992-ea76da37110f</t>
-  </si>
-  <si>
-    <t>campaign--d726fa7f-7c1c-4924-88a6-74444222bd9f</t>
-  </si>
-  <si>
-    <t>campaign--0a86d435-8e69-4f3a-bc96-b3ac668c82bc</t>
-  </si>
-  <si>
-    <t>campaign--fa5a41c0-90cb-4caf-860d-a3428108338f</t>
-  </si>
-  <si>
-    <t>campaign--93b9db3d-54e0-4cd1-a73d-8da9102e4009</t>
-  </si>
-  <si>
-    <t>campaign--2e5633ce-2d35-42b6-9ef4-0bf9c8b1bf35</t>
-  </si>
-  <si>
-    <t>campaign--cb207683-dcc4-4b73-ac2f-0be500edc74f</t>
-  </si>
-  <si>
-    <t>campaign--afb7bd59-6c2a-440a-a21d-5961efba5eff</t>
-  </si>
-  <si>
-    <t>campaign--43bcd15c-cf4f-4445-acbd-65ae81877442</t>
-  </si>
-  <si>
-    <t>campaign--d81de34f-47cd-428a-a41a-09a6f56a9da7</t>
-  </si>
-  <si>
-    <t>campaign--034fab01-25ca-406a-af72-18424cd8865e</t>
-  </si>
-  <si>
-    <t>campaign--65f10cf2-b7b9-4bba-99bd-850bd647691e</t>
-  </si>
-  <si>
-    <t>campaign--5a7b9428-869c-4411-836b-ac68418c3e88</t>
-  </si>
-  <si>
-    <t>campaign--993b7232-af60-4415-a814-7856a5aac9b0</t>
-  </si>
-  <si>
-    <t>campaign--adcbb713-6625-4bb2-bbdb-ca95dce75216</t>
-  </si>
-  <si>
-    <t>campaign--fc8f6110-efac-4b90-b548-1454dac7a19b</t>
-  </si>
-  <si>
-    <t>campaign--5c62e27c-a9a5-4f3d-8c9b-c9e0b90a244b</t>
-  </si>
-  <si>
-    <t>campaign--4ef7374d-4184-4e74-8a4d-61459b26d02f</t>
-  </si>
-  <si>
-    <t>campaign--cfee05cb-c034-4971-a531-902e845ccef3</t>
-  </si>
-  <si>
-    <t>campaign--34f93fca-7d2a-4e55-bc81-7f5697e97ef5</t>
-  </si>
-  <si>
-    <t>campaign--6664b694-3b86-465b-9e27-aea2b4bb1daa</t>
-  </si>
-  <si>
-    <t>campaign--3f943474-7a02-49f9-95d4-6284c13fcf28</t>
-  </si>
-  <si>
-    <t>campaign--8260bb29-de17-4c6d-8152-bcfe4b2b99ab</t>
-  </si>
-  <si>
-    <t>campaign--249316b5-9848-4974-bb96-36f491ad2ff3</t>
-  </si>
-  <si>
-    <t>campaign--51f52048-db4e-4bb3-a9d3-9c3ef5a7efdf</t>
-  </si>
-  <si>
-    <t>campaign--62d59075-a1be-4fc3-bb73-dfbba3d9890f</t>
-  </si>
-  <si>
-    <t>campaign--620a3478-b534-42fe-ae16-eef44729927d</t>
-  </si>
-  <si>
-    <t>campaign--33d73442-ef8e-4272-9b52-8409285e64d4</t>
-  </si>
-  <si>
-    <t>campaign--dde6e95d-8a5e-4d08-9cec-a7ff943a6316</t>
-  </si>
-  <si>
-    <t>campaign--451c6e51-6fd7-493b-82dd-f5b2d321469c</t>
-  </si>
-  <si>
-    <t>campaign--999f0ed3-c7f6-4cbe-b1a2-d7d8d6eedf7b</t>
-  </si>
-  <si>
-    <t>campaign--324dfd0b-8bb9-4e73-b770-c4878fa141b3</t>
-  </si>
-  <si>
-    <t>campaign--e48baa05-e5ad-4906-b269-18674c9abe58</t>
-  </si>
-  <si>
-    <t>campaign--5ac2c3e0-9d38-426d-81e5-09cf5a941ae2</t>
-  </si>
-  <si>
-    <t>campaign--b98a9b9a-6b83-45f6-b65e-38d9bffe4df7</t>
-  </si>
-  <si>
-    <t>campaign--71c8fe9d-7933-4793-8688-8ab211e64903</t>
-  </si>
-  <si>
-    <t>campaign--f8715c92-b16d-427b-8db4-e3a8d3c8f294</t>
-  </si>
-  <si>
-    <t>campaign--4d0ec18b-c72b-4515-9f5d-4246894f9414</t>
-  </si>
-  <si>
-    <t>campaign--d55f729d-5ef5-4b86-a509-1a176d91bbf5</t>
-  </si>
-  <si>
-    <t>campaign--5f5df72e-1fe1-43dd-82d6-8d828a183ff5</t>
-  </si>
-  <si>
-    <t>campaign--6c70c6bf-d458-4a42-a588-2d462edf232e</t>
-  </si>
-  <si>
-    <t>campaign--3e59ca2e-eae8-41fa-b2ec-cb039c9b4210</t>
-  </si>
-  <si>
-    <t>campaign--89ab3728-120a-41b6-b6f8-eee58aa5bf75</t>
-  </si>
-  <si>
-    <t>campaign--15dd6c2c-0e8f-4497-8d49-119a63052355</t>
-  </si>
-  <si>
-    <t>campaign--f5969a82-f450-48d2-a83f-31c2c2fcfc5a</t>
-  </si>
-  <si>
-    <t>campaign--8df71303-011a-488a-a3d5-cfabdf43a3bc</t>
-  </si>
-  <si>
-    <t>campaign--d59baa17-740d-4701-ac73-c8a740a1902e</t>
-  </si>
-  <si>
-    <t>campaign--bb2e0c40-4185-4a26-9a4a-843f0f42fb91</t>
-  </si>
-  <si>
-    <t>campaign--1c942e99-7fdf-43c2-a1c7-0c036960d550</t>
-  </si>
-  <si>
-    <t>campaign--2587cdb8-4685-4f49-ad80-4cf1673de499</t>
-  </si>
-  <si>
-    <t>campaign--4850b46c-5052-41fe-8b42-439a1d32be7b</t>
-  </si>
-  <si>
-    <t>campaign--160fbc62-8a4d-4576-86c8-bb6e8212b355</t>
-  </si>
-  <si>
-    <t>campaign--f726e55f-ac4b-4710-9b09-6b1bd5d7aca3</t>
-  </si>
-  <si>
-    <t>campaign--b12ec413-1bd9-46dd-b084-f775d59555ce</t>
-  </si>
-  <si>
-    <t>campaign--4b166b15-a737-4bfc-a873-ce378b04442b</t>
-  </si>
-  <si>
-    <t>campaign--7f39ffcb-c876-4ac1-97c7-77225d687cf7</t>
-  </si>
-  <si>
-    <t>campaign--c6287a90-fda2-414b-9536-7e8d7b333225</t>
-  </si>
-  <si>
-    <t>campaign--bfff8349-9b26-4bec-993e-4d3fb7792a21</t>
-  </si>
-  <si>
-    <t>campaign--a88279c6-8e3a-4610-98b4-61afdf9b1b00</t>
-  </si>
-  <si>
-    <t>campaign--a7923c48-f560-4ecf-99f5-9b6a59a4c658</t>
-  </si>
-  <si>
-    <t>campaign--bf2d7f34-0a40-4a70-8642-f68ef8dae022</t>
-  </si>
-  <si>
-    <t>campaign--86b88822-1271-4a0b-b652-bac9d6c1e4e8</t>
-  </si>
-  <si>
-    <t>campaign--ab434fb0-c7d3-4c1c-bcbd-c4c4498cf657</t>
-  </si>
-  <si>
-    <t>campaign--a156a043-c7da-45b0-aa0a-5299ead941bb</t>
-  </si>
-  <si>
-    <t>campaign--0cfea08d-0a35-4a62-a6b8-66a75b949383</t>
-  </si>
-  <si>
-    <t>campaign--8a97f881-3742-4d79-9bf1-0d2b3f8bacfe</t>
-  </si>
-  <si>
-    <t>campaign--b12ceb44-a32c-43df-82b7-e817321bdc3c</t>
-  </si>
-  <si>
-    <t>campaign--9c6d7b3b-bfe7-43c5-9b32-9928bf384cb3</t>
-  </si>
-  <si>
-    <t>campaign--2df6168b-6e9d-456f-a84a-30638a365400</t>
-  </si>
-  <si>
-    <t>campaign--d10ef172-c6c8-4f61-9f6c-4be1a77043ec</t>
-  </si>
-  <si>
-    <t>campaign--eecb9861-e70e-403d-bf70-88d38775c3b5</t>
-  </si>
-  <si>
-    <t>campaign--9a356b3e-0022-416c-bda6-336376c7b0f7</t>
-  </si>
-  <si>
-    <t>campaign--3b1dfe61-fc96-495a-92c1-e9617744d5b3</t>
+    <t>campaign--97185b62-b756-44d3-b841-c26ff2caa435</t>
+  </si>
+  <si>
+    <t>campaign--28368dc3-bac3-40ca-9be2-53cd5b18ae5a</t>
+  </si>
+  <si>
+    <t>campaign--3e7aca06-438d-4972-b481-5eef5dddab91</t>
+  </si>
+  <si>
+    <t>campaign--42c2db2c-bca8-4f4c-90a1-feed7ccb5499</t>
+  </si>
+  <si>
+    <t>campaign--0e489ab4-57c8-4ea9-b1c1-35a091e8dcf5</t>
+  </si>
+  <si>
+    <t>campaign--3951c130-926c-4354-b30a-d9b845e20711</t>
+  </si>
+  <si>
+    <t>campaign--5df5ab6d-110b-41b0-914c-d68a42814b3f</t>
+  </si>
+  <si>
+    <t>campaign--332047f3-d991-48d5-a8d0-d626d70b1520</t>
+  </si>
+  <si>
+    <t>campaign--35760d2a-4bf9-493b-ab94-fa67c4ff8fcd</t>
+  </si>
+  <si>
+    <t>campaign--780db662-7237-47c6-9d76-e0a9c213b1ca</t>
+  </si>
+  <si>
+    <t>campaign--d38fee72-8a5f-42cd-a0e6-08b3642e49e2</t>
+  </si>
+  <si>
+    <t>campaign--ae71667a-64b0-4a35-bd4b-2212af26d6f2</t>
+  </si>
+  <si>
+    <t>campaign--1063f60a-3894-4344-97eb-1a62a8d09e50</t>
+  </si>
+  <si>
+    <t>campaign--1f2bd0e1-55a3-4605-9910-a28c81b3aba4</t>
+  </si>
+  <si>
+    <t>campaign--21ac6d95-7b1e-4b4a-a039-c789d4ded516</t>
+  </si>
+  <si>
+    <t>campaign--7fc58166-effa-406a-8ca4-a7e4fb477a96</t>
+  </si>
+  <si>
+    <t>campaign--374ff3ac-7e13-4ceb-870a-1c25a5e81f45</t>
+  </si>
+  <si>
+    <t>campaign--2514ee85-51a9-477d-893a-bb45313d0bd5</t>
+  </si>
+  <si>
+    <t>campaign--89014d54-7b08-4fba-83ac-c8722773fad8</t>
+  </si>
+  <si>
+    <t>campaign--ba097673-a412-4203-bb06-447f860a51d3</t>
+  </si>
+  <si>
+    <t>campaign--a55ffc4f-129f-4d38-8324-fdd1ebbb5a4b</t>
+  </si>
+  <si>
+    <t>campaign--01e2f625-82e2-488e-8622-00ebde701e23</t>
+  </si>
+  <si>
+    <t>campaign--fd958d24-a4bf-4243-ae08-e860c13ea805</t>
+  </si>
+  <si>
+    <t>campaign--a6face44-139d-466a-a5ff-e8c3ff709ace</t>
+  </si>
+  <si>
+    <t>campaign--a413d1f2-8330-4668-b8bd-fd8086250234</t>
+  </si>
+  <si>
+    <t>campaign--48e3bbbf-203d-40a1-bc6d-aa8b18e5598e</t>
+  </si>
+  <si>
+    <t>campaign--08d1bb96-2342-4cdb-b6b9-55a161a88419</t>
+  </si>
+  <si>
+    <t>campaign--76935537-cdec-406c-9f4a-a4cbc121cc00</t>
+  </si>
+  <si>
+    <t>campaign--f4466bbc-027a-4e44-935a-035f903ef19e</t>
+  </si>
+  <si>
+    <t>campaign--c7e7bcde-9c6c-437b-ad59-5e5bd2d5c514</t>
+  </si>
+  <si>
+    <t>campaign--236b5c9a-15f6-43ce-9667-200af4732480</t>
+  </si>
+  <si>
+    <t>campaign--b8c59485-94d3-40a6-b0fc-23d338986d1f</t>
+  </si>
+  <si>
+    <t>campaign--167376d8-aab7-4cbb-b314-230969e6a7a3</t>
+  </si>
+  <si>
+    <t>campaign--b2510237-29ac-4193-8722-444a86b52190</t>
+  </si>
+  <si>
+    <t>campaign--c8bcfd3d-d39b-4d28-9b5c-c5f3e8e0728f</t>
+  </si>
+  <si>
+    <t>campaign--8432f3de-ec66-4e20-88e9-54ed4587df9b</t>
+  </si>
+  <si>
+    <t>campaign--5bf5d20e-3e8f-4b7f-beb9-1a3189e2cadf</t>
+  </si>
+  <si>
+    <t>campaign--5f5766b1-030a-4e87-b165-48a1f821e9a6</t>
+  </si>
+  <si>
+    <t>campaign--ac432357-fb30-4c0f-9123-ff894b2784de</t>
+  </si>
+  <si>
+    <t>campaign--4bc43f67-3dc2-4c2b-9539-a42ff3e48f8f</t>
+  </si>
+  <si>
+    <t>campaign--a89eb731-49da-49ec-94fd-10f7ec7e3212</t>
+  </si>
+  <si>
+    <t>campaign--db4a09bc-80d8-443b-8be6-9a04e643eab5</t>
+  </si>
+  <si>
+    <t>campaign--0c92bef0-ae48-4178-a4e8-2845fe5e43ba</t>
+  </si>
+  <si>
+    <t>campaign--1a54b369-cecd-4acf-aeeb-addc0eee2b65</t>
+  </si>
+  <si>
+    <t>campaign--fc415691-46e4-4d5b-88ef-568d20e2f82a</t>
+  </si>
+  <si>
+    <t>campaign--30bc8d41-e4ff-476d-a84a-d5435273ad2e</t>
+  </si>
+  <si>
+    <t>campaign--37aea0f8-0538-4f63-994d-621cd042cbe7</t>
+  </si>
+  <si>
+    <t>campaign--b9035652-ec19-498f-ad70-c1e7c3af8809</t>
+  </si>
+  <si>
+    <t>campaign--25c5110f-77ed-4932-b111-1dfc5e875a95</t>
+  </si>
+  <si>
+    <t>campaign--84ee7058-67a7-46ba-b6ee-a9087bb87634</t>
+  </si>
+  <si>
+    <t>campaign--75cf364b-6744-4d5a-bb26-0abd1753609f</t>
+  </si>
+  <si>
+    <t>campaign--192a1e9c-2e3d-43d2-b6a6-175a55e941b5</t>
+  </si>
+  <si>
+    <t>campaign--071a2be9-c5af-4201-9e25-71e6c6dc63cf</t>
+  </si>
+  <si>
+    <t>campaign--ed10ebb7-caaa-481f-8655-7cc6acbade91</t>
+  </si>
+  <si>
+    <t>campaign--dc27daac-0791-47f7-aaee-d0e5c7a16918</t>
+  </si>
+  <si>
+    <t>campaign--7c31c341-4948-4d76-bc9a-d602657f0db3</t>
+  </si>
+  <si>
+    <t>campaign--f136d4ca-d08c-4b0b-9e1d-368e30dbfa5b</t>
+  </si>
+  <si>
+    <t>campaign--3f35fe1f-00d3-4e41-98a9-2e406c219312</t>
+  </si>
+  <si>
+    <t>campaign--31aacef3-25a8-4fba-ac95-bae1bb0592fb</t>
+  </si>
+  <si>
+    <t>campaign--491b0716-9561-4ea6-a89b-4ba9e0953e3c</t>
+  </si>
+  <si>
+    <t>campaign--a4455377-a120-45a5-9089-99fb95fdb59a</t>
+  </si>
+  <si>
+    <t>campaign--ea61a171-fa35-4ed1-9287-41e3ca667409</t>
+  </si>
+  <si>
+    <t>campaign--7771ca5f-0b5b-4fbb-9f0b-f37801347fca</t>
+  </si>
+  <si>
+    <t>campaign--0b3c9ce1-a0be-4440-b0f0-c762880ed332</t>
+  </si>
+  <si>
+    <t>campaign--96ec7087-d1b0-4076-a568-5f8a779eef00</t>
+  </si>
+  <si>
+    <t>campaign--46077bfe-ce3a-4542-8b5c-b8b6d8d6fdef</t>
+  </si>
+  <si>
+    <t>campaign--1e47c887-315a-4c3d-bea5-d9632702b517</t>
+  </si>
+  <si>
+    <t>campaign--61012452-31df-4e70-80b3-74be0914a200</t>
+  </si>
+  <si>
+    <t>campaign--bf409339-c5e5-4ab8-8b1a-246071ed19b5</t>
+  </si>
+  <si>
+    <t>campaign--d0eb71bc-3823-42d6-b3e5-427e2a915763</t>
+  </si>
+  <si>
+    <t>campaign--9a0c9c17-48be-4239-ae4b-ba408248d9ba</t>
+  </si>
+  <si>
+    <t>campaign--6a3d44b3-9d73-4774-a015-293e5ff7c59f</t>
+  </si>
+  <si>
+    <t>campaign--6058b9a2-6422-4498-bc1f-466e8f5404d0</t>
+  </si>
+  <si>
+    <t>campaign--a3e43158-57aa-48a2-8b22-c4338061ebe6</t>
+  </si>
+  <si>
+    <t>campaign--556f85fe-e335-4694-aa72-2e4da45a572d</t>
+  </si>
+  <si>
+    <t>campaign--3fc52fc0-1fc8-40f8-99fe-daee0cafc351</t>
+  </si>
+  <si>
+    <t>campaign--dee519da-cbc0-4a3f-8f64-811927f8fa8a</t>
+  </si>
+  <si>
+    <t>campaign--fcb5345d-ae74-4a0d-8859-00654996201a</t>
+  </si>
+  <si>
+    <t>campaign--ca069712-0be3-42d8-a175-c8e568760aba</t>
+  </si>
+  <si>
+    <t>campaign--9fd8c082-9e7d-4657-b402-c6b5164ebb7c</t>
+  </si>
+  <si>
+    <t>campaign--62313c07-9360-40f3-9a67-f106b3a9901f</t>
+  </si>
+  <si>
+    <t>campaign--a92151c2-5f7d-4c2e-a659-7a10e298595d</t>
+  </si>
+  <si>
+    <t>campaign--e2dc6026-4b3e-4088-8687-ee5e8efc0fcc</t>
+  </si>
+  <si>
+    <t>campaign--b8913d57-e3f2-43cc-989e-b5dc2cd92219</t>
+  </si>
+  <si>
+    <t>campaign--771a290d-43a0-43fb-89a5-2aaf271da029</t>
+  </si>
+  <si>
+    <t>campaign--c29e446f-6d4f-4920-91d5-fc54dedf1f5f</t>
+  </si>
+  <si>
+    <t>campaign--0bd21e62-2023-485d-9c17-c2684d1bebdb</t>
+  </si>
+  <si>
+    <t>campaign--7c688b14-67e6-476e-8096-a44c3fb95db9</t>
+  </si>
+  <si>
+    <t>campaign--567e3204-7775-46bb-b5f9-874bfeaf0c6f</t>
+  </si>
+  <si>
+    <t>campaign--dbde897a-31a7-4684-a98d-5805601ba4c2</t>
+  </si>
+  <si>
+    <t>campaign--906ac28e-dbce-42ff-9e99-9b6cc4aaa5e3</t>
+  </si>
+  <si>
+    <t>campaign--ce2366df-0b95-4d79-8f46-07ffa76c4215</t>
+  </si>
+  <si>
+    <t>campaign--efaaf655-e666-48b6-b47f-c6778bee3360</t>
+  </si>
+  <si>
+    <t>campaign--00f784da-4f20-4b91-acbe-8f9b76ff9596</t>
+  </si>
+  <si>
+    <t>campaign--59c82e4e-f119-41db-98a0-42312fac19cb</t>
+  </si>
+  <si>
+    <t>campaign--5478a268-e577-4b91-8abc-920e07341e66</t>
+  </si>
+  <si>
+    <t>campaign--b7c7a3d4-e14e-4089-805e-0d6bd5d494c2</t>
+  </si>
+  <si>
+    <t>campaign--acd8df7a-c420-435e-a7c2-1b8fd5170fab</t>
+  </si>
+  <si>
+    <t>campaign--d36ba52b-faba-4013-81c1-bc5462725fe9</t>
+  </si>
+  <si>
+    <t>campaign--cec91334-cad3-439c-9fd6-a172aa9d1c68</t>
+  </si>
+  <si>
+    <t>campaign--487d3e61-633a-4a79-8421-e58f556d93e1</t>
+  </si>
+  <si>
+    <t>campaign--dffc0208-5ef6-47c3-99a3-57d880da041e</t>
   </si>
   <si>
     <t>campaign</t>
@@ -3410,313 +3410,313 @@
     <t>Указ Александра II: «Заборона ввозити українські книги з-за кордону, заборона підписувати українські тексти під нотами, заборона українських вистав» (Citation: Русифікація України — Вікіпедія 2026).</t>
   </si>
   <si>
-    <t>relationship--579007f9-28a0-48e4-9185-c1e2d0b17ae3</t>
-  </si>
-  <si>
-    <t>relationship--cbe422cd-9fe9-4132-84f1-96be195ac993</t>
-  </si>
-  <si>
-    <t>relationship--5667cd4d-ca36-46d4-a17a-9d54006f1f5b</t>
-  </si>
-  <si>
-    <t>relationship--f281ae66-2d30-4085-b524-194af26c8459</t>
-  </si>
-  <si>
-    <t>relationship--36dcc214-651c-4657-acdf-5a62bef3ec0f</t>
-  </si>
-  <si>
-    <t>relationship--13a0e8d5-cd26-41ad-989a-1ffb8a550016</t>
-  </si>
-  <si>
-    <t>relationship--2bf4f3c6-637c-41b5-b365-73fd8f1340fa</t>
-  </si>
-  <si>
-    <t>relationship--bc31601d-18b2-4aed-90e3-208e5d49b78a</t>
-  </si>
-  <si>
-    <t>relationship--9807e38f-6ad6-447a-ae60-a64f9f343370</t>
-  </si>
-  <si>
-    <t>relationship--8a514380-8a2d-4c81-9db0-93a248171fba</t>
-  </si>
-  <si>
-    <t>relationship--b2f79bb7-979e-4ea3-86ef-eebc886aaa6b</t>
-  </si>
-  <si>
-    <t>relationship--545039f1-fa7a-4f32-9e79-7584f9399a5a</t>
-  </si>
-  <si>
-    <t>relationship--bb7c01ba-b6d1-40f6-a6d0-3e4b0cdddbef</t>
-  </si>
-  <si>
-    <t>relationship--974dffe7-2fe4-45f0-bf21-5df9f49100d0</t>
-  </si>
-  <si>
-    <t>relationship--590d5394-a905-4b57-8ea4-38e941c36875</t>
-  </si>
-  <si>
-    <t>relationship--c76b1d3c-c2e5-45d1-a417-d580c9825105</t>
-  </si>
-  <si>
-    <t>relationship--3037be7e-2186-4f85-beb4-bfc477eef251</t>
-  </si>
-  <si>
-    <t>relationship--ceeb598f-298b-4fdd-aa06-06c66f75cb93</t>
-  </si>
-  <si>
-    <t>relationship--6e2eee1c-1d01-4aa2-b34b-1ce62806dae9</t>
-  </si>
-  <si>
-    <t>relationship--c347dbcd-3768-45bb-85b5-ee75069b5731</t>
-  </si>
-  <si>
-    <t>relationship--eacab9fe-e01f-49fc-a53a-bdbdacec0a5d</t>
-  </si>
-  <si>
-    <t>relationship--0a00c5e3-fc83-48cd-8ddb-09ef4bbedfe0</t>
-  </si>
-  <si>
-    <t>relationship--0ee2ab17-a17d-488c-a01f-4cc29fa47acc</t>
-  </si>
-  <si>
-    <t>relationship--72e5cce2-bbff-48a2-b689-589ad7bde2fb</t>
-  </si>
-  <si>
-    <t>relationship--d3b4874f-ecb2-4381-9b8d-7927f05858d0</t>
-  </si>
-  <si>
-    <t>relationship--ca5afe22-bac2-4077-b67b-337995a60f43</t>
-  </si>
-  <si>
-    <t>relationship--77b67bf7-363d-4a9d-9f8b-9742086db6c6</t>
-  </si>
-  <si>
-    <t>relationship--63fe6e4d-581d-431b-8116-9e090e8a745c</t>
-  </si>
-  <si>
-    <t>relationship--94908fc4-bb5b-4683-805a-dbd8dc5e4999</t>
-  </si>
-  <si>
-    <t>relationship--d9fe5d2b-3357-4241-901b-39166dd33941</t>
-  </si>
-  <si>
-    <t>relationship--035ae41a-01e9-4155-9738-28abee46fa01</t>
-  </si>
-  <si>
-    <t>relationship--22ee9109-c21a-4017-a011-8847cb95d8af</t>
-  </si>
-  <si>
-    <t>relationship--de151bf0-ed08-4e2c-924e-d1e4fcd66047</t>
-  </si>
-  <si>
-    <t>relationship--1b8dfcb3-509e-4b06-a3eb-15219d4b259f</t>
-  </si>
-  <si>
-    <t>relationship--d9c1c0f7-5386-45dd-90f5-cdcf145f2c40</t>
-  </si>
-  <si>
-    <t>relationship--a7369f3d-8b80-46e3-bb86-52408e4d0a70</t>
-  </si>
-  <si>
-    <t>relationship--924eeef7-4ac6-4094-a9d7-36befeac2c17</t>
-  </si>
-  <si>
-    <t>relationship--4135c852-a440-4feb-a662-d639156221ad</t>
-  </si>
-  <si>
-    <t>relationship--b50f9c63-ba9d-4a49-a4f7-45d9b53d8ef0</t>
-  </si>
-  <si>
-    <t>relationship--02f7b89f-53fa-478f-a1b5-7b61d8dcbff2</t>
-  </si>
-  <si>
-    <t>relationship--64360548-9a83-41f8-90e4-d73d3eb2c33a</t>
-  </si>
-  <si>
-    <t>relationship--8283b0e0-32c7-4708-9057-d42e6598176b</t>
-  </si>
-  <si>
-    <t>relationship--c1c921d9-699e-4928-8506-67dcd2061170</t>
-  </si>
-  <si>
-    <t>relationship--f2726f56-5487-4b4f-af8a-7031b19d1d76</t>
-  </si>
-  <si>
-    <t>relationship--d84105e6-4a04-4cf4-8a2c-c4a12e5dea08</t>
-  </si>
-  <si>
-    <t>relationship--3b452af0-3666-4c28-974e-a4fb53bbf295</t>
-  </si>
-  <si>
-    <t>relationship--f8ab7e5a-e300-48c9-b77c-8e67a4d7df27</t>
-  </si>
-  <si>
-    <t>relationship--40666857-41f2-4d46-bf70-47aa0c34dcc7</t>
-  </si>
-  <si>
-    <t>relationship--771548ba-7416-4cde-95d1-c788b08aaa71</t>
-  </si>
-  <si>
-    <t>relationship--779d583e-d222-4b26-956a-1e19ac4b77e2</t>
-  </si>
-  <si>
-    <t>relationship--d82e2525-0fdd-49cb-b3f1-1f2efa99ee08</t>
-  </si>
-  <si>
-    <t>relationship--31777070-381d-45d3-b313-00646e092c07</t>
-  </si>
-  <si>
-    <t>relationship--0f4de468-fd2f-4285-9db2-740ef8555069</t>
-  </si>
-  <si>
-    <t>relationship--24ad6afb-6426-413a-a29f-38668ad6ff90</t>
-  </si>
-  <si>
-    <t>relationship--946d5ae9-8056-4e22-9cd4-417de7f38d82</t>
-  </si>
-  <si>
-    <t>relationship--2a1f9d54-b16b-46ad-a923-604adfe79e1e</t>
-  </si>
-  <si>
-    <t>relationship--9a57978d-fe99-4297-8eb2-9746f0966990</t>
-  </si>
-  <si>
-    <t>relationship--366127f5-ecfd-431d-8baa-60078e576cef</t>
-  </si>
-  <si>
-    <t>relationship--835e8e03-39f2-4a00-a970-4f85d13ecae3</t>
-  </si>
-  <si>
-    <t>relationship--8a4a0c57-9338-42e3-8d0f-f04cc7e4970f</t>
-  </si>
-  <si>
-    <t>relationship--13eee957-a48f-466d-833c-b05db7b68537</t>
-  </si>
-  <si>
-    <t>relationship--5c8531a1-d41b-4b0b-8a4e-dfae8afcfa13</t>
-  </si>
-  <si>
-    <t>relationship--823a5587-50a0-40bc-9bde-70e3c2182300</t>
-  </si>
-  <si>
-    <t>relationship--293ad61a-8091-43f2-9fdc-e1adb4c75bc9</t>
-  </si>
-  <si>
-    <t>relationship--08e3ea95-b7f8-4937-b29c-4a1672614f9c</t>
-  </si>
-  <si>
-    <t>relationship--49edb497-7c42-44fc-bb53-870ca69c42d0</t>
-  </si>
-  <si>
-    <t>relationship--2051eeb2-4f36-497b-b503-5da4e20d78a0</t>
-  </si>
-  <si>
-    <t>relationship--30d0c38d-f5e6-4c94-a312-bb0202c53235</t>
-  </si>
-  <si>
-    <t>relationship--a372bff6-e803-4af7-ba39-d0996ef7de00</t>
-  </si>
-  <si>
-    <t>relationship--16bf97f2-e1ac-451b-93db-61a5ca25cfa5</t>
-  </si>
-  <si>
-    <t>relationship--b4456713-6f1a-423c-9417-3fd9318794b5</t>
-  </si>
-  <si>
-    <t>relationship--7368aac6-f55d-45e8-bcd2-0150164725c0</t>
-  </si>
-  <si>
-    <t>relationship--8fa92939-0395-495a-a2cc-25920befafd6</t>
-  </si>
-  <si>
-    <t>relationship--7f8c1d68-a431-4053-a40c-08397553d9f8</t>
-  </si>
-  <si>
-    <t>relationship--fe830b39-4d93-4844-92e9-630d112bb1cc</t>
-  </si>
-  <si>
-    <t>relationship--ba30d8c0-0a8a-43e3-884e-9ebc68c8b18b</t>
-  </si>
-  <si>
-    <t>relationship--a9ada7e1-57e6-4aba-95c7-33f97a61382d</t>
-  </si>
-  <si>
-    <t>relationship--4e5af6b1-7d02-4647-843f-917014cbfee5</t>
-  </si>
-  <si>
-    <t>relationship--a41e87ab-e2f0-472e-8b8b-b96ee2a8dbfb</t>
-  </si>
-  <si>
-    <t>relationship--7a731bc9-9092-4523-8921-dd7a3d94426f</t>
-  </si>
-  <si>
-    <t>relationship--b2beb81b-3b22-4e86-9770-beb7bcb9e418</t>
-  </si>
-  <si>
-    <t>relationship--eba89ba0-a62f-4d7a-aac2-58639ab713f8</t>
-  </si>
-  <si>
-    <t>relationship--cd2cd507-1be3-4d9a-b9fc-fcbddeac37be</t>
-  </si>
-  <si>
-    <t>relationship--0cfbf64b-f9a8-4961-bdcc-328c9364a656</t>
-  </si>
-  <si>
-    <t>relationship--3db40fe1-6e0d-4323-8da9-f0359cfa8be7</t>
-  </si>
-  <si>
-    <t>relationship--077d87d9-6da7-4b46-9cfc-4c84e7f788af</t>
-  </si>
-  <si>
-    <t>relationship--86e9c863-5ae5-46bf-b0e4-b02eaa185bd7</t>
-  </si>
-  <si>
-    <t>relationship--434ffa6e-8e3f-42bf-8887-3b685da7afe2</t>
-  </si>
-  <si>
-    <t>relationship--61560840-331e-4982-ab6f-90edf192c51f</t>
-  </si>
-  <si>
-    <t>relationship--5ed32bcc-ffac-41fb-ade7-6baf29882120</t>
-  </si>
-  <si>
-    <t>relationship--abce58d8-6877-4dcb-a877-9e213452f4b6</t>
-  </si>
-  <si>
-    <t>relationship--0b3c0a27-bbc5-4005-ac5d-bb05a255a1fd</t>
-  </si>
-  <si>
-    <t>relationship--9f3989ee-e8dd-48ba-a582-6a1fb2c277cf</t>
-  </si>
-  <si>
-    <t>relationship--5f947b73-c283-438a-b661-e922ef128815</t>
-  </si>
-  <si>
-    <t>relationship--f2028f92-96ba-481d-a719-e43200be30eb</t>
-  </si>
-  <si>
-    <t>relationship--9b0772cb-acd9-4f8a-82b1-c429efd3c3fc</t>
-  </si>
-  <si>
-    <t>relationship--cf2a8f50-c042-4978-8ac9-040f681a0902</t>
-  </si>
-  <si>
-    <t>relationship--dd0249b1-41cf-49f2-8b39-909edba54fbb</t>
-  </si>
-  <si>
-    <t>relationship--0863f965-e8ec-4d07-86db-37554adca29b</t>
-  </si>
-  <si>
-    <t>relationship--e86d43ec-a735-4d99-ad60-b0135dbfb42f</t>
-  </si>
-  <si>
-    <t>relationship--fc6c0597-d0d4-4933-8519-4d7a7c7297f6</t>
-  </si>
-  <si>
-    <t>relationship--27d3b66b-60c5-4691-884a-af621f775026</t>
-  </si>
-  <si>
-    <t>relationship--653d9b5d-056b-4633-8ccb-46dd884fe269</t>
+    <t>relationship--a95066fb-1718-46d3-8e6e-49e87d4751b7</t>
+  </si>
+  <si>
+    <t>relationship--e9a22d2b-cb0b-4938-9005-5533000e7b38</t>
+  </si>
+  <si>
+    <t>relationship--565adc13-b06e-47cd-ba71-049604f1c97e</t>
+  </si>
+  <si>
+    <t>relationship--1c284d41-421a-4be5-9678-bb2ac621c866</t>
+  </si>
+  <si>
+    <t>relationship--32210d72-5a5a-447f-bc97-012c21a9d180</t>
+  </si>
+  <si>
+    <t>relationship--48fe585f-60a2-4e8c-8063-2ef406ecabbc</t>
+  </si>
+  <si>
+    <t>relationship--1aa6f707-5ad2-4cee-9940-beb43e0bbd57</t>
+  </si>
+  <si>
+    <t>relationship--6810df1c-387a-422d-8a88-f1e5ac631c8c</t>
+  </si>
+  <si>
+    <t>relationship--ebf45aa9-ab01-471e-989c-cf1348b5d70a</t>
+  </si>
+  <si>
+    <t>relationship--4807f9f0-92c6-446d-9180-7913879270a1</t>
+  </si>
+  <si>
+    <t>relationship--2fd65693-90a1-4f44-8274-b473a3bb173f</t>
+  </si>
+  <si>
+    <t>relationship--a0e6d595-4668-4dda-806b-b016e035a696</t>
+  </si>
+  <si>
+    <t>relationship--d47a8fb4-6c97-4b93-a1d6-61eb3f535597</t>
+  </si>
+  <si>
+    <t>relationship--f5c06e1b-f14f-492b-95e0-e82889dcc877</t>
+  </si>
+  <si>
+    <t>relationship--11eee327-9c1f-4151-931a-fbeb9b35bb4c</t>
+  </si>
+  <si>
+    <t>relationship--e435b9fd-332a-4d75-9476-d406f9c37a61</t>
+  </si>
+  <si>
+    <t>relationship--c13f714f-67f4-4e3f-a5fb-410a7d86df85</t>
+  </si>
+  <si>
+    <t>relationship--34d5c786-e1a6-4953-8f03-d138258da3d4</t>
+  </si>
+  <si>
+    <t>relationship--ed0e4c1e-4a29-4e56-99b3-c40191c272cc</t>
+  </si>
+  <si>
+    <t>relationship--dc8be056-141e-4424-80c7-a593fb2736fb</t>
+  </si>
+  <si>
+    <t>relationship--7ba58dbe-7676-4d12-a9da-718738083fe5</t>
+  </si>
+  <si>
+    <t>relationship--fc74cc6a-7592-4289-985b-94d3f359ade3</t>
+  </si>
+  <si>
+    <t>relationship--5541fa16-864d-4d8f-bdd9-8f442103ea16</t>
+  </si>
+  <si>
+    <t>relationship--7d115ed9-39e7-4def-b4a0-79972420802d</t>
+  </si>
+  <si>
+    <t>relationship--1bca7e42-1da9-4ea3-bb66-afa4c1df3443</t>
+  </si>
+  <si>
+    <t>relationship--bbdcb1e8-692d-41fe-88e1-d1fc06f4a8d5</t>
+  </si>
+  <si>
+    <t>relationship--dfb42873-75dc-45b8-8abd-96f5da31a2fa</t>
+  </si>
+  <si>
+    <t>relationship--48aaa29f-ac3e-47ee-982c-8541c26117c5</t>
+  </si>
+  <si>
+    <t>relationship--30d03301-95c7-4a01-86ab-fc56fab12bd0</t>
+  </si>
+  <si>
+    <t>relationship--33c28a36-b522-4c5c-b33c-28d4390bd800</t>
+  </si>
+  <si>
+    <t>relationship--463bd61c-a8d3-40ab-ace9-4515dfa76476</t>
+  </si>
+  <si>
+    <t>relationship--32ff96a6-0b0a-4ca7-8f19-3ed9dce19f80</t>
+  </si>
+  <si>
+    <t>relationship--f743c22a-ebef-4a93-847b-3b6e3122b994</t>
+  </si>
+  <si>
+    <t>relationship--619ee101-358b-4aad-b5d0-14bced2f13c8</t>
+  </si>
+  <si>
+    <t>relationship--abf8a785-6875-4d28-8fe5-01247f5425d9</t>
+  </si>
+  <si>
+    <t>relationship--0eadb0af-59ea-46cf-929c-73d9b9764492</t>
+  </si>
+  <si>
+    <t>relationship--261854c3-1617-45ff-baa8-6dbe52976c77</t>
+  </si>
+  <si>
+    <t>relationship--b027ab64-92aa-4d21-af4e-2337894240b5</t>
+  </si>
+  <si>
+    <t>relationship--b58f403d-9810-45d5-86d3-41e89f270bcf</t>
+  </si>
+  <si>
+    <t>relationship--f56b40d8-819a-40bc-a68e-c60d01db7f0f</t>
+  </si>
+  <si>
+    <t>relationship--3ef446d6-bbb7-433b-af9a-46857a3bc555</t>
+  </si>
+  <si>
+    <t>relationship--0cfbc2d3-05dd-44a8-bc82-7887467e3928</t>
+  </si>
+  <si>
+    <t>relationship--646e8a40-ca48-4925-9031-204da00b650e</t>
+  </si>
+  <si>
+    <t>relationship--a5959dbf-f0f2-45a0-bb14-5e41bdb8e585</t>
+  </si>
+  <si>
+    <t>relationship--e634e455-5505-4898-b305-982f72306fc4</t>
+  </si>
+  <si>
+    <t>relationship--3ae42177-2839-483a-80ef-2f3a2d15803c</t>
+  </si>
+  <si>
+    <t>relationship--79f23e7a-d1dc-44a2-bc4c-6d7c0604d9d9</t>
+  </si>
+  <si>
+    <t>relationship--41d16cff-028a-45b7-9773-b7ed73ac0855</t>
+  </si>
+  <si>
+    <t>relationship--26683c7f-b18d-4f0b-8240-1474c128b1ed</t>
+  </si>
+  <si>
+    <t>relationship--1116351d-6972-444b-90a0-1f8e7e66d75e</t>
+  </si>
+  <si>
+    <t>relationship--8c0281e5-c7a7-4e8c-a340-f4c9c0e727e9</t>
+  </si>
+  <si>
+    <t>relationship--9cedb62b-574a-4771-bf01-3eb83d2c19e7</t>
+  </si>
+  <si>
+    <t>relationship--2c051a16-4463-4ce0-8045-05edbecdb96e</t>
+  </si>
+  <si>
+    <t>relationship--cb40224b-fde2-4bd9-b5f4-1c7fca7631b9</t>
+  </si>
+  <si>
+    <t>relationship--ce3e3dce-c741-4765-a1f3-44e4543d4b3d</t>
+  </si>
+  <si>
+    <t>relationship--58d301f9-9b44-47c3-8013-ae1ec11c5913</t>
+  </si>
+  <si>
+    <t>relationship--97129600-dfdc-46fc-87ea-0815c54c2726</t>
+  </si>
+  <si>
+    <t>relationship--bfea3bd1-1ce5-4d9e-b016-73478a483537</t>
+  </si>
+  <si>
+    <t>relationship--87f2faef-e5fd-49df-99d1-3d1b54ca7640</t>
+  </si>
+  <si>
+    <t>relationship--fab8f5da-e65c-435e-8311-720b6c9eeabf</t>
+  </si>
+  <si>
+    <t>relationship--3aa6ec34-f393-430c-9cbd-4841f9920f0e</t>
+  </si>
+  <si>
+    <t>relationship--31366991-d83e-4eaf-88ba-c26255847e3f</t>
+  </si>
+  <si>
+    <t>relationship--d87ce476-23f9-4fc6-b13c-047097357dcf</t>
+  </si>
+  <si>
+    <t>relationship--5badbe27-c263-478a-b68d-c0c28b4f8ef1</t>
+  </si>
+  <si>
+    <t>relationship--a351e0a9-ae44-4578-8b4d-c6b47da74308</t>
+  </si>
+  <si>
+    <t>relationship--a56ff3ba-96e6-4973-bcd0-c4bef23b5d38</t>
+  </si>
+  <si>
+    <t>relationship--0ce7bddd-50d5-48be-afb7-d3e06b285ef0</t>
+  </si>
+  <si>
+    <t>relationship--05e4c4c5-0966-4337-8275-c4907b8d4673</t>
+  </si>
+  <si>
+    <t>relationship--565130fe-3386-42b6-b475-f02f8474bd39</t>
+  </si>
+  <si>
+    <t>relationship--cef88e9a-6cb7-49e6-9b5b-ba08c8ca6b88</t>
+  </si>
+  <si>
+    <t>relationship--e1ac74fc-d530-4cc3-a105-56087b595c2c</t>
+  </si>
+  <si>
+    <t>relationship--516e3400-7942-4d72-b4b0-e3b39d62f9e7</t>
+  </si>
+  <si>
+    <t>relationship--df7ec859-d883-4c8f-8b0e-372570d2a736</t>
+  </si>
+  <si>
+    <t>relationship--da299c4e-9630-4b38-b717-b6583dbe26fc</t>
+  </si>
+  <si>
+    <t>relationship--c8edbb88-14ff-4d8e-9c74-b2712da0ab11</t>
+  </si>
+  <si>
+    <t>relationship--278b8d8c-0a20-4a8f-9bad-a72df718c17c</t>
+  </si>
+  <si>
+    <t>relationship--ed38512a-db10-4611-b123-d56d3b981c1e</t>
+  </si>
+  <si>
+    <t>relationship--83dd8b38-931f-40f7-bc4b-d56173bcfe73</t>
+  </si>
+  <si>
+    <t>relationship--7f6d56c5-6612-489c-9b18-8c24dc75af58</t>
+  </si>
+  <si>
+    <t>relationship--118c7ea5-f1e1-495b-a5a2-963b25933ac6</t>
+  </si>
+  <si>
+    <t>relationship--b7c59cd1-369f-4de9-a3a4-5b5cdae3d166</t>
+  </si>
+  <si>
+    <t>relationship--b907d83f-4982-4baa-b5f8-fc364e9b33cc</t>
+  </si>
+  <si>
+    <t>relationship--7c44d0bb-7378-48de-af57-28bbb3af8b8b</t>
+  </si>
+  <si>
+    <t>relationship--eda1dbd4-3b39-44ff-90c1-96e6046320fc</t>
+  </si>
+  <si>
+    <t>relationship--3b210ccc-f8be-470c-adc2-cd060d11ffbe</t>
+  </si>
+  <si>
+    <t>relationship--7bf4e691-2470-49cd-a172-5df8af2263c5</t>
+  </si>
+  <si>
+    <t>relationship--57227651-67a7-4ede-b3bd-9309c9dede53</t>
+  </si>
+  <si>
+    <t>relationship--692ea191-a544-4a50-9449-6ac7d09a1930</t>
+  </si>
+  <si>
+    <t>relationship--6e0c35a5-3a68-4c67-af6d-bd0866e51274</t>
+  </si>
+  <si>
+    <t>relationship--c4285b2d-5078-4331-9d59-fe17df33e8d0</t>
+  </si>
+  <si>
+    <t>relationship--c55f3f86-c5b9-4fc3-82f3-3ef59966c26b</t>
+  </si>
+  <si>
+    <t>relationship--a2a349c4-fcd3-47cf-913c-db97245ac089</t>
+  </si>
+  <si>
+    <t>relationship--d12e139d-c65a-4553-832b-62ec4ad574ca</t>
+  </si>
+  <si>
+    <t>relationship--80d2485a-1628-48d9-bb5f-e5b985c816ef</t>
+  </si>
+  <si>
+    <t>relationship--c0eb327a-d351-41c7-ad63-def80454e574</t>
+  </si>
+  <si>
+    <t>relationship--b8166e54-71e5-4ec9-b871-e2bfa18c5cbf</t>
+  </si>
+  <si>
+    <t>relationship--859a06b7-36a7-4ff8-bf25-dd0593d202f3</t>
+  </si>
+  <si>
+    <t>relationship--8c419d72-e7d3-43ef-abcc-b264990cc673</t>
+  </si>
+  <si>
+    <t>relationship--7eac7055-d3e2-4b34-9559-1360309757c9</t>
+  </si>
+  <si>
+    <t>relationship--cd9f0e86-64ce-438f-9767-6b4081d8079f</t>
+  </si>
+  <si>
+    <t>relationship--22ace871-0cc2-4b40-901d-51c4fd38aebd</t>
+  </si>
+  <si>
+    <t>relationship--2ebd7677-4776-4837-9240-39ff6493c0d9</t>
+  </si>
+  <si>
+    <t>relationship--123596cd-c28b-46e5-a300-7400a612cb67</t>
   </si>
   <si>
     <t>reference</t>

--- a/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-groups.xlsx
+++ b/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-groups.xlsx
@@ -149,22 +149,22 @@
     <t>1.0</t>
   </si>
   <si>
-    <t>(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.)</t>
-  </si>
-  <si>
-    <t>(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Руїна — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Московсько-українська війна (1658—1659),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Північна війна (1700—1721),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Руїна — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Решетилівські статті — Вікіпедія 2026),(Citation: Запорозька Січ — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Переяславські статті (1659),(Citation: Переяславська рада — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Московсько-українська війна (1658—1659),(Citation: Киевский синопсис — Википедия 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Малоросійський приказ — Вікіпедія 2026),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Мазепа 2007),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Решетилівські статті — Вікіпедія 2026),(Citation: Переяславська рада — Вікіпедія 2026),(Citation: Азовські походи (1695—1696),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Малоросійський приказ — Вікіпедія 2026),(Citation: Руїна — Вікіпедія 2026),(Citation: Ліквідація козацтва на Правобережній Україні (1699),(Citation: Андрусовское перемирие - Википедия 2026),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Мазепа 2007),(Citation: Конотопські статті — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Киевский синопсис — Википедия 2026),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Запорозька Січ — Вікіпедія 2026),(Citation: Переяславські статті (1659),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Московські статті (1665)</t>
-  </si>
-  <si>
-    <t>(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Повстання бузьких козаків (1817),(Citation: Листопадове повстання (1830—1831),(Citation: Чорносотенці — Вікіпедія 2026),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026),(Citation: Друга Малоросійська колегія — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Столипінська реформа — Вікіпедія 2026),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Історія Донецької області — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Крымская война — Википедия 2026),(Citation: Русско-турецкая война (1768—1774),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026),(Citation: Україна у війнах Наполеона — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Кирило-Мефодіївське товариство — Вікіпедія 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Російсько-турецька війна (1806—1812),(Citation: Правління гетьманського уряду — Вікіпедія 2026),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Смуга осілості — Вікіпедія 2026),(Citation: Малоросійське генерал-губернаторство — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Антикріпосницький рух в Україні (1789-1861),(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Столипінська реформа — Вікіпедія 2026),(Citation: Перепис населення Російської імперії (1897),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Повстання бузьких козаків (1817),(Citation: Листопадове повстання (1830—1831),(Citation: Чорносотенці — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Польское восстание (1863—1864)</t>
-  </si>
-  <si>
-    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Російсько-українська війна (з 2014),(Citation: Рашизм: Звір з безодні 2023),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Российские удары по украинской энергосистеме — Википедия 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Дезінформація під час російсько-української війни — Вікіпедія 2026),(Citation: 2015 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: 2016 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Русифікація України — Вікіпедія 2026)</t>
-  </si>
-  <si>
-    <t>(Citation: Історія України — Вікіпедія 2026),(Citation: Карательная психиатрия в России: назад в СССР? 2020),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Рашизм: Звір з безодні 2023),(Citation: Карательная психиатрия в России: назад в СССР? 2020),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Котлета по-київськи (промова),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: В ТЕНИ «БОЛЬШОГО БРАТА» ЗАПАДНЫЕ НАЦИОНАЛЬНЫЕ МЕНЬШИНСТВА В СССР 1917-1938 ГГ . 2011),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: ДИССИДЕНТСКОЕ ДВИЖЕНИЕ В УКРАИНЕ (1954 – 1987),(Citation: Рашизм: Звір з безодні 2023),(Citation: Кенгирское восстание заключённых - Википедия 2026),(Citation: Всесоюзний референдум про збереження СРСР — Вікіпедія 2026),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
-  </si>
-  <si>
-    <t>(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.)</t>
+    <t>(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.)</t>
+  </si>
+  <si>
+    <t>(Citation: Московсько-українська війна (1658—1659),(Citation: Руїна — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Киевский синопсис — Википедия 2026),(Citation: Московсько-українська війна (1658—1659),(Citation: Руїна — Вікіпедія 2026),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Північна війна (1700—1721),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Переяславська рада — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа 2007),(Citation: Решетилівські статті — Вікіпедія 2026),(Citation: Переяславські статті (1659),(Citation: Запорозька Січ — Вікіпедія 2026),(Citation: Малоросійський приказ — Вікіпедія 2026),(Citation: Киевский синопсис — Википедия 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Переяславська рада — Вікіпедія 2026),(Citation: Запорозька Січ — Вікіпедія 2026),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Московські статті (1665),(Citation: Переяславські статті (1659),(Citation: Андрусовское перемирие - Википедия 2026),(Citation: Азовські походи (1695—1696),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Мазепа 2007),(Citation: Ліквідація козацтва на Правобережній Україні (1699),(Citation: Руїна — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Решетилівські статті — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Конотопські статті — Вікіпедія 2026),(Citation: Малоросійський приказ — Вікіпедія 2026)</t>
+  </si>
+  <si>
+    <t>(Citation: Русифікація України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Чорносотенці — Вікіпедія 2026),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Столипінська реформа — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Історія України — Вікіпедія 2026),(Citation: Друга Малоросійська колегія — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Повстання бузьких козаків (1817),(Citation: Листопадове повстання (1830—1831),(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Історія Донецької області — Вікіпедія 2026),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Україна у війнах Наполеона — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Польское восстание (1863—1864),(Citation: Історія України — Вікіпедія 2026),(Citation: Правління гетьманського уряду — Вікіпедія 2026),(Citation: Перепис населення Російської імперії (1897),(Citation: Русско-турецкая война (1768—1774),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Кирило-Мефодіївське товариство — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Повстання бузьких козаків (1817),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Листопадове повстання (1830—1831),(Citation: Російсько-турецька війна (1806—1812),(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Антикріпосницький рух в Україні (1789-1861),(Citation: Смуга осілості — Вікіпедія 2026),(Citation: Чорносотенці — Вікіпедія 2026),(Citation: Столипінська реформа — Вікіпедія 2026),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Крымская война — Википедия 2026),(Citation: Малоросійське генерал-губернаторство — Вікіпедія 2026),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026)</t>
+  </si>
+  <si>
+    <t>(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Рашизм: Звір з безодні 2023),(Citation: Російсько-українська війна (з 2014),(Citation: Российские удары по украинской энергосистеме — Википедия 2026),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: 2015 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023),(Citation: 2016 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023),(Citation: Дезінформація під час російсько-української війни — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Хроника первой российской войны в Чечне 2026)</t>
+  </si>
+  <si>
+    <t>(Citation: Русифікація України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Карательная психиатрия в России: назад в СССР? 2020),(Citation: Рашизм: Звір з безодні 2023),(Citation: Котлета по-київськи (промова),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Карательная психиатрия в России: назад в СССР? 2020),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: Рашизм: Звір з безодні 2023),(Citation: В ТЕНИ «БОЛЬШОГО БРАТА» ЗАПАДНЫЕ НАЦИОНАЛЬНЫЕ МЕНЬШИНСТВА В СССР 1917-1938 ГГ . 2011),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Кенгирское восстание заключённых - Википедия 2026),(Citation: Всесоюзний референдум про збереження СРСР — Вікіпедія 2026),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: ДИССИДЕНТСКОЕ ДВИЖЕНИЕ В УКРАИНЕ (1954 – 1987)</t>
+  </si>
+  <si>
+    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.)</t>
   </si>
   <si>
     <t>source ID</t>

--- a/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-groups.xlsx
+++ b/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-groups.xlsx
@@ -68,22 +68,22 @@
     <t>G0013</t>
   </si>
   <si>
-    <t>intrusion-set--7b976569-98f0-4fa3-82fe-02d61389de3e</t>
-  </si>
-  <si>
-    <t>intrusion-set--d5113a56-7d11-4ccf-b29b-db0230a3deb5</t>
-  </si>
-  <si>
-    <t>intrusion-set--ccad1a64-f9f9-4595-8650-92f87954b4a0</t>
-  </si>
-  <si>
-    <t>intrusion-set--763a114d-2942-4a6d-9907-1170a64fae86</t>
-  </si>
-  <si>
-    <t>intrusion-set--efc55d3b-975e-4784-879d-5e1771bcdfb2</t>
-  </si>
-  <si>
-    <t>intrusion-set--d6cb53bb-bf87-46da-99d2-d218130dd4c9</t>
+    <t>intrusion-set--00d5aa42-725d-45ea-8815-ccc615a4d517</t>
+  </si>
+  <si>
+    <t>intrusion-set--3fb8da0b-6311-48dc-9b3e-0a6816345b77</t>
+  </si>
+  <si>
+    <t>intrusion-set--1f6d7249-6192-46e5-b1c5-793a60706469</t>
+  </si>
+  <si>
+    <t>intrusion-set--002e0782-6856-438e-bc83-3c5ebbcba18d</t>
+  </si>
+  <si>
+    <t>intrusion-set--f2a7d9cd-c26b-4ff1-a215-41d91c2ede51</t>
+  </si>
+  <si>
+    <t>intrusion-set--13896fcc-2d95-4d93-bb1e-073c354eab10</t>
   </si>
   <si>
     <t>Белое движение (ВСЮР)</t>
@@ -149,22 +149,22 @@
     <t>1.0</t>
   </si>
   <si>
-    <t>(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.)</t>
-  </si>
-  <si>
-    <t>(Citation: Московсько-українська війна (1658—1659),(Citation: Руїна — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Киевский синопсис — Википедия 2026),(Citation: Московсько-українська війна (1658—1659),(Citation: Руїна — Вікіпедія 2026),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Північна війна (1700—1721),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Переяславська рада — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа 2007),(Citation: Решетилівські статті — Вікіпедія 2026),(Citation: Переяславські статті (1659),(Citation: Запорозька Січ — Вікіпедія 2026),(Citation: Малоросійський приказ — Вікіпедія 2026),(Citation: Киевский синопсис — Википедия 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Переяславська рада — Вікіпедія 2026),(Citation: Запорозька Січ — Вікіпедія 2026),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Московські статті (1665),(Citation: Переяславські статті (1659),(Citation: Андрусовское перемирие - Википедия 2026),(Citation: Азовські походи (1695—1696),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Мазепа 2007),(Citation: Ліквідація козацтва на Правобережній Україні (1699),(Citation: Руїна — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Решетилівські статті — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Конотопські статті — Вікіпедія 2026),(Citation: Малоросійський приказ — Вікіпедія 2026)</t>
-  </si>
-  <si>
-    <t>(Citation: Русифікація України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Чорносотенці — Вікіпедія 2026),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Столипінська реформа — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Історія України — Вікіпедія 2026),(Citation: Друга Малоросійська колегія — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Повстання бузьких козаків (1817),(Citation: Листопадове повстання (1830—1831),(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Історія Донецької області — Вікіпедія 2026),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Україна у війнах Наполеона — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Польское восстание (1863—1864),(Citation: Історія України — Вікіпедія 2026),(Citation: Правління гетьманського уряду — Вікіпедія 2026),(Citation: Перепис населення Російської імперії (1897),(Citation: Русско-турецкая война (1768—1774),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Кирило-Мефодіївське товариство — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Повстання бузьких козаків (1817),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Листопадове повстання (1830—1831),(Citation: Російсько-турецька війна (1806—1812),(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Антикріпосницький рух в Україні (1789-1861),(Citation: Смуга осілості — Вікіпедія 2026),(Citation: Чорносотенці — Вікіпедія 2026),(Citation: Столипінська реформа — Вікіпедія 2026),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Крымская война — Википедия 2026),(Citation: Малоросійське генерал-губернаторство — Вікіпедія 2026),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026)</t>
-  </si>
-  <si>
-    <t>(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Рашизм: Звір з безодні 2023),(Citation: Російсько-українська війна (з 2014),(Citation: Российские удары по украинской энергосистеме — Википедия 2026),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: 2015 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023),(Citation: 2016 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023),(Citation: Дезінформація під час російсько-української війни — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Хроника первой российской войны в Чечне 2026)</t>
-  </si>
-  <si>
-    <t>(Citation: Русифікація України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Карательная психиатрия в России: назад в СССР? 2020),(Citation: Рашизм: Звір з безодні 2023),(Citation: Котлета по-київськи (промова),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Карательная психиатрия в России: назад в СССР? 2020),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: Рашизм: Звір з безодні 2023),(Citation: В ТЕНИ «БОЛЬШОГО БРАТА» ЗАПАДНЫЕ НАЦИОНАЛЬНЫЕ МЕНЬШИНСТВА В СССР 1917-1938 ГГ . 2011),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Кенгирское восстание заключённых - Википедия 2026),(Citation: Всесоюзний референдум про збереження СРСР — Вікіпедія 2026),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: ДИССИДЕНТСКОЕ ДВИЖЕНИЕ В УКРАИНЕ (1954 – 1987)</t>
-  </si>
-  <si>
-    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.)</t>
+    <t>(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.)</t>
+  </si>
+  <si>
+    <t>(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Руїна — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Московсько-українська війна (1658—1659),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Мазепа 2007),(Citation: Північна війна (1700—1721),(Citation: Решетилівські статті — Вікіпедія 2026),(Citation: Руїна — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Переяславські статті (1659),(Citation: Московсько-українська війна (1658—1659),(Citation: Запорозька Січ — Вікіпедія 2026),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Киевский синопсис — Википедия 2026),(Citation: Переяславська рада — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Малоросійський приказ — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Конотопські статті — Вікіпедія 2026),(Citation: Запорозька Січ — Вікіпедія 2026),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Киевский синопсис — Википедия 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Руїна — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Переяславська рада — Вікіпедія 2026),(Citation: Малоросійський приказ — Вікіпедія 2026),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Азовські походи (1695—1696),(Citation: Переяславські статті (1659),(Citation: Андрусовское перемирие - Википедия 2026),(Citation: Ліквідація козацтва на Правобережній Україні (1699),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Мазепа 2007),(Citation: Московські статті (1665),(Citation: Решетилівські статті — Вікіпедія 2026),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Іван Мазепа — Вікіпедія 2026)</t>
+  </si>
+  <si>
+    <t>(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Історія України — Вікіпедія 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Історія Донецької області — Вікіпедія 2026),(Citation: Чорносотенці — Вікіпедія 2026),(Citation: Листопадове повстання (1830—1831),(Citation: Друга Малоросійська колегія — Вікіпедія 2026),(Citation: Повстання бузьких козаків (1817),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Столипінська реформа — Вікіпедія 2026),(Citation: Крымская война — Википедия 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Столипінська реформа — Вікіпедія 2026),(Citation: Чорносотенці — Вікіпедія 2026),(Citation: Повстання бузьких козаків (1817),(Citation: Перепис населення Російської імперії (1897),(Citation: Русско-турецкая война (1768—1774),(Citation: Російсько-турецька війна (1806—1812),(Citation: Малоросійське генерал-губернаторство — Вікіпедія 2026),(Citation: Україна у війнах Наполеона — Вікіпедія 2026),(Citation: Кирило-Мефодіївське товариство — Вікіпедія 2026),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Антикріпосницький рух в Україні (1789-1861),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Листопадове повстання (1830—1831),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Правління гетьманського уряду — Вікіпедія 2026),(Citation: Смуга осілості — Вікіпедія 2026),(Citation: Польское восстание (1863—1864)</t>
+  </si>
+  <si>
+    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Российские удары по украинской энергосистеме — Википедия 2026),(Citation: Російсько-українська війна (з 2014),(Citation: 2016 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Історія України — Вікіпедія 2026),(Citation: 2015 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023),(Citation: Дезінформація під час російсько-української війни — Вікіпедія 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Рашизм: Звір з безодні 2023),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010)</t>
+  </si>
+  <si>
+    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Карательная психиатрия в России: назад в СССР? 2020),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Котлета по-київськи (промова),(Citation: Історія України — Вікіпедія 2026),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Рашизм: Звір з безодні 2023),(Citation: Карательная психиатрия в России: назад в СССР? 2020),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: В ТЕНИ «БОЛЬШОГО БРАТА» ЗАПАДНЫЕ НАЦИОНАЛЬНЫЕ МЕНЬШИНСТВА В СССР 1917-1938 ГГ . 2011),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Всесоюзний референдум про збереження СРСР — Вікіпедія 2026),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: ДИССИДЕНТСКОЕ ДВИЖЕНИЕ В УКРАИНЕ (1954 – 1987),(Citation: Історія України — Вікіпедія 2026),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Рашизм: Звір з безодні 2023),(Citation: Кенгирское восстание заключённых - Википедия 2026)</t>
+  </si>
+  <si>
+    <t>(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939)</t>
   </si>
   <si>
     <t>source ID</t>
@@ -281,43 +281,43 @@
     <t>Подконтрольная оппозиция</t>
   </si>
   <si>
-    <t>tool--24a04dcd-846a-4c5b-bfcd-47828e9ddd57</t>
-  </si>
-  <si>
-    <t>tool--e8d0468c-8a92-4294-baa2-a91bcd6f19e4</t>
-  </si>
-  <si>
-    <t>tool--66dcf02c-a2aa-4a17-9e43-2e456ebdee31</t>
-  </si>
-  <si>
-    <t>tool--06c48a32-5cf5-4cef-8992-72c541bfdfac</t>
-  </si>
-  <si>
-    <t>tool--82bcdaea-f53f-45de-8281-b671db596090</t>
-  </si>
-  <si>
-    <t>tool--d0e502ca-3ba5-4364-b2ab-30d53b87c681</t>
-  </si>
-  <si>
-    <t>tool--e07eeae6-c3e5-45f1-b8f1-c3e50a179665</t>
-  </si>
-  <si>
-    <t>tool--fb5d65db-23c3-4502-8fd9-7b40965d2ed8</t>
-  </si>
-  <si>
-    <t>tool--634cf340-6e8c-49d7-b45f-c9fb4f722daa</t>
-  </si>
-  <si>
-    <t>tool--4d016c34-bb94-4b61-88bc-7e9cacc2185b</t>
-  </si>
-  <si>
-    <t>tool--2bf94bf0-b6e0-4e29-bef7-8745173179cb</t>
-  </si>
-  <si>
-    <t>tool--df0ba05b-fd65-4437-9c8f-5fbbf4498f51</t>
-  </si>
-  <si>
-    <t>tool--88d6ef27-a088-40e6-b97f-8a49b8c508e1</t>
+    <t>tool--ceb165df-32e3-4d83-bdb6-db5ae496484d</t>
+  </si>
+  <si>
+    <t>tool--6cb97aa5-9ef0-4ccb-9e82-bbfc1ac6f9dc</t>
+  </si>
+  <si>
+    <t>tool--0f891574-2d64-4b40-959a-6822e47af301</t>
+  </si>
+  <si>
+    <t>tool--bc2f8deb-bfa4-4bfe-a514-08eaffbdace0</t>
+  </si>
+  <si>
+    <t>tool--6a1a7dc9-5d85-444a-b140-04e777c873f0</t>
+  </si>
+  <si>
+    <t>tool--2632cb38-aa7a-411c-a58d-f5ecef972484</t>
+  </si>
+  <si>
+    <t>tool--f00b45db-5e26-4a45-a418-6af97faa4a4d</t>
+  </si>
+  <si>
+    <t>tool--c245c447-66cb-48db-b15b-df8d8e0dd436</t>
+  </si>
+  <si>
+    <t>tool--065f9ef9-fbc6-40da-9537-1f0ba3d48637</t>
+  </si>
+  <si>
+    <t>tool--2ac13435-bb23-4791-b014-496ba930d1d1</t>
+  </si>
+  <si>
+    <t>tool--2d431e42-ef16-4d1a-9e90-7e5e0ffb410d</t>
+  </si>
+  <si>
+    <t>tool--1483b76f-f40e-4689-a9d1-55b8eac05837</t>
+  </si>
+  <si>
+    <t>tool--efbad242-63d3-40cf-9c6a-9ffe1578cc1e</t>
   </si>
   <si>
     <t>software</t>
@@ -425,106 +425,106 @@
     <t>Провоцирование большевиками восстания рабочих завода «Арсенал» в самом Киеве для оттягивания резервов украинских властей прямо во время наступления красных войск. (Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
   </si>
   <si>
-    <t>relationship--bb009c88-365d-4fab-bf01-19c7661e62af</t>
-  </si>
-  <si>
-    <t>relationship--77b46dc8-4a63-44dd-9bd7-031969ec253c</t>
-  </si>
-  <si>
-    <t>relationship--5bde57b1-9715-42f1-b049-e06f015a1772</t>
-  </si>
-  <si>
-    <t>relationship--a14a9035-fa57-4d41-89f7-891ac9fcf81f</t>
-  </si>
-  <si>
-    <t>relationship--1c1b685c-3181-4352-b249-432542879ed6</t>
-  </si>
-  <si>
-    <t>relationship--475161f8-6686-424b-9917-db6889a0fcf3</t>
-  </si>
-  <si>
-    <t>relationship--13ac5123-1a57-4b3a-8d5a-662c89bf41a2</t>
-  </si>
-  <si>
-    <t>relationship--f5209d1a-7895-4020-acae-5dc4e5d8bfc0</t>
-  </si>
-  <si>
-    <t>relationship--5ee5526e-96eb-41af-b8b8-c90b91e64049</t>
-  </si>
-  <si>
-    <t>relationship--3be37c13-b9bc-47bb-8653-fa401dabd4e7</t>
-  </si>
-  <si>
-    <t>relationship--b0c2c062-c89e-4085-8716-bad67e98026e</t>
-  </si>
-  <si>
-    <t>relationship--31fd82da-dfa8-42b5-95dd-f168e6627746</t>
-  </si>
-  <si>
-    <t>relationship--2c5e4520-1275-4ab3-a9a8-2e2b1e964c13</t>
-  </si>
-  <si>
-    <t>relationship--b55647cc-a783-4225-b64b-618bc0c73e2b</t>
-  </si>
-  <si>
-    <t>relationship--6014c6c0-0579-4b5e-a854-2e87b36442cf</t>
-  </si>
-  <si>
-    <t>relationship--9c8d906b-4588-4163-b779-c3b8321985df</t>
-  </si>
-  <si>
-    <t>relationship--1419cb9b-276d-4b72-a3f1-6788f5712c97</t>
-  </si>
-  <si>
-    <t>relationship--a0a599d6-96f3-46a9-8021-f95ca90c5c60</t>
-  </si>
-  <si>
-    <t>relationship--422caa87-ac34-4167-80a3-e3f294b52304</t>
-  </si>
-  <si>
-    <t>relationship--d95d1848-9eb8-41a1-9eb4-0dab6d9b048c</t>
-  </si>
-  <si>
-    <t>relationship--c8ddd7ea-ed8e-4c46-8d00-0188061a5430</t>
-  </si>
-  <si>
-    <t>relationship--b4237490-0e8a-46d4-95a6-1cdaa172bcc8</t>
-  </si>
-  <si>
-    <t>relationship--6d106e24-cb8f-42ae-8ea2-c24c3ac66a5e</t>
-  </si>
-  <si>
-    <t>relationship--d3e614da-a65e-49a8-b28c-1bda5c4ff9ad</t>
-  </si>
-  <si>
-    <t>relationship--673fe51c-7945-423e-9767-3b824d79a43f</t>
-  </si>
-  <si>
-    <t>relationship--b4b464b3-2e82-48ba-b3e5-8680a6803204</t>
-  </si>
-  <si>
-    <t>relationship--ec2419f7-91b8-4498-b50c-0deec7e9eed4</t>
-  </si>
-  <si>
-    <t>relationship--62fc2c5e-3c4f-4760-ba3a-320af5a52635</t>
-  </si>
-  <si>
-    <t>relationship--5c3c5267-b7aa-47e8-a640-d413fe3d0e2b</t>
-  </si>
-  <si>
-    <t>relationship--559bac5f-e601-4430-a4d1-3e40065ec036</t>
-  </si>
-  <si>
-    <t>relationship--aaed89ae-ca29-4a00-9e21-1cc9143a649e</t>
-  </si>
-  <si>
-    <t>relationship--acd4d015-7a92-4a60-8741-9e316340e075</t>
-  </si>
-  <si>
-    <t>relationship--3d963d7d-a454-4e0a-9940-35584a671824</t>
-  </si>
-  <si>
-    <t>relationship--e1c4bbc4-90c4-48de-8589-c0a639fef400</t>
+    <t>relationship--da050063-c065-4f64-b603-131c66564b27</t>
+  </si>
+  <si>
+    <t>relationship--7b77da04-ab8c-4853-ba78-ea68f918045f</t>
+  </si>
+  <si>
+    <t>relationship--d968e9cf-bac9-4fb8-bbac-8c2d02c54083</t>
+  </si>
+  <si>
+    <t>relationship--8a7e5e2f-2743-4768-bbc1-d3e89f312afa</t>
+  </si>
+  <si>
+    <t>relationship--daaa48ef-0c36-4443-b4a5-48114ee2269f</t>
+  </si>
+  <si>
+    <t>relationship--769748a7-f54a-4f41-9094-ad4f900591bf</t>
+  </si>
+  <si>
+    <t>relationship--ec87abc6-9641-4378-bc37-f1922bfa6e68</t>
+  </si>
+  <si>
+    <t>relationship--f123e402-c95a-4a58-a035-6769d33fba66</t>
+  </si>
+  <si>
+    <t>relationship--caa25457-ebc1-40b0-a2b4-774edffb669b</t>
+  </si>
+  <si>
+    <t>relationship--3e901e91-7d1a-4367-96d1-10be8c0b2df9</t>
+  </si>
+  <si>
+    <t>relationship--77cbf7e0-4ec3-4601-bfa7-e8e423f7ab0b</t>
+  </si>
+  <si>
+    <t>relationship--2c0a3765-6c13-410f-88d3-4fc78b67c0b4</t>
+  </si>
+  <si>
+    <t>relationship--bec6de6d-8e8d-4b94-a2c9-505039cde2e9</t>
+  </si>
+  <si>
+    <t>relationship--3a1ab7c1-8c43-48bd-94e3-915f6bde530f</t>
+  </si>
+  <si>
+    <t>relationship--68f9fe2a-e37e-44a7-a84f-197229636901</t>
+  </si>
+  <si>
+    <t>relationship--39580415-eb7f-4b71-b66a-b4e8f0df0f55</t>
+  </si>
+  <si>
+    <t>relationship--f49caced-62b5-4b68-b4dd-9fe6a7292e55</t>
+  </si>
+  <si>
+    <t>relationship--58b2abb6-02a7-45b3-8b5f-ec850122407a</t>
+  </si>
+  <si>
+    <t>relationship--d9035eff-e382-4c9d-aabc-937a7a051226</t>
+  </si>
+  <si>
+    <t>relationship--20d559c7-dba2-42fc-99f4-a6edaa1a32d4</t>
+  </si>
+  <si>
+    <t>relationship--6e948f4a-29cd-40a3-8f09-e0e70a92ec4e</t>
+  </si>
+  <si>
+    <t>relationship--0dfe276a-ab5f-4f02-8e44-434fa746e9ae</t>
+  </si>
+  <si>
+    <t>relationship--3f2d01b8-8530-4c17-8d6e-7d42d400a7e2</t>
+  </si>
+  <si>
+    <t>relationship--d9aec82b-c059-4c8a-bdf5-a7db19f9021c</t>
+  </si>
+  <si>
+    <t>relationship--8c5450b9-b74f-4d36-adf4-ac1da91a3111</t>
+  </si>
+  <si>
+    <t>relationship--532c2ae2-b015-410f-8ec4-63524e3e6c9f</t>
+  </si>
+  <si>
+    <t>relationship--dd7f3637-6aab-4fa1-95ad-c7004e880c76</t>
+  </si>
+  <si>
+    <t>relationship--b73f3df6-f349-49a0-85da-c9bb9849bfb0</t>
+  </si>
+  <si>
+    <t>relationship--8a035471-857e-40ba-953b-0aaa72176ee8</t>
+  </si>
+  <si>
+    <t>relationship--2328e2b4-4bc6-4432-afaf-43eaa9f10b9c</t>
+  </si>
+  <si>
+    <t>relationship--9c72f6da-453c-404e-87df-1a6c2b00e71c</t>
+  </si>
+  <si>
+    <t>relationship--8c006b00-a342-47c9-8e1b-2c6e44da94b5</t>
+  </si>
+  <si>
+    <t>relationship--dbd05fa7-67b6-402c-8c1c-1cd01026667b</t>
+  </si>
+  <si>
+    <t>relationship--82dfe3d2-cf42-4e0b-9d66-e20ec755ae3f</t>
   </si>
   <si>
     <t>T0019</t>
@@ -1025,253 +1025,253 @@
     <t>Поддержка подконтрольной оппозиции</t>
   </si>
   <si>
-    <t>attack-pattern--d8fec2ab-fe86-4530-9801-bbbe5c3baf44</t>
-  </si>
-  <si>
-    <t>attack-pattern--e06e27d3-c18f-4bac-9bb6-17121de4850b</t>
-  </si>
-  <si>
-    <t>attack-pattern--ab6eb169-9d35-462e-8540-e600dcfcc755</t>
-  </si>
-  <si>
-    <t>attack-pattern--11df0e1b-fb0b-495a-8517-fe9629386cc7</t>
-  </si>
-  <si>
-    <t>attack-pattern--d039ccb5-695e-4e9c-903d-4a25d80a5e91</t>
-  </si>
-  <si>
-    <t>attack-pattern--d67e92a1-567a-4443-b196-42eee7df7df9</t>
-  </si>
-  <si>
-    <t>attack-pattern--f8863479-abf3-40aa-909f-422ff587ef75</t>
-  </si>
-  <si>
-    <t>attack-pattern--f87361eb-4cc0-472a-9d20-d8814c3dcb83</t>
-  </si>
-  <si>
-    <t>attack-pattern--14ddac56-e61c-489c-9f2a-0ead47acab72</t>
-  </si>
-  <si>
-    <t>attack-pattern--ca19f909-8e73-4014-ab69-a521482caa77</t>
-  </si>
-  <si>
-    <t>attack-pattern--7b5e8502-6625-4bfb-becf-4701773fc345</t>
-  </si>
-  <si>
-    <t>attack-pattern--63e9746b-4223-4c4d-bb27-a4c2f724f832</t>
-  </si>
-  <si>
-    <t>attack-pattern--255d85ab-8ae5-4855-9d4d-398d57bfb428</t>
-  </si>
-  <si>
-    <t>attack-pattern--3c78bc06-b7d9-4d72-87cc-3896a83a79c1</t>
-  </si>
-  <si>
-    <t>attack-pattern--e1500254-a805-457b-9c9f-eaa7ed4441c2</t>
-  </si>
-  <si>
-    <t>attack-pattern--40ddc318-d9d7-4035-80a9-21f5de23c666</t>
-  </si>
-  <si>
-    <t>attack-pattern--bbbea8cd-eb4e-4314-abc8-2293225ab5e6</t>
-  </si>
-  <si>
-    <t>attack-pattern--7302168b-1756-4aa2-9831-57b042e5e79c</t>
-  </si>
-  <si>
-    <t>attack-pattern--23537b01-052d-4788-a1c5-ac64ea3a5440</t>
-  </si>
-  <si>
-    <t>attack-pattern--ba18aeed-1fa0-4221-b5c3-2951c695226d</t>
-  </si>
-  <si>
-    <t>attack-pattern--1c3cc896-6014-4a38-bb84-f755661f9f8a</t>
-  </si>
-  <si>
-    <t>attack-pattern--0f207f69-c49f-4bd9-a2c8-81d5903af798</t>
-  </si>
-  <si>
-    <t>attack-pattern--15b42e50-034b-48ec-a530-08f4da421ced</t>
-  </si>
-  <si>
-    <t>attack-pattern--0e9f8dfa-7044-47a4-99c4-b8108e0c3531</t>
-  </si>
-  <si>
-    <t>attack-pattern--541f9c2f-5e7e-40bd-8807-e27b27bf27f9</t>
-  </si>
-  <si>
-    <t>attack-pattern--d2982864-148c-45ed-9a9d-73124e552f59</t>
-  </si>
-  <si>
-    <t>attack-pattern--ce173a13-3838-4451-bcde-529c8c9cbf4d</t>
-  </si>
-  <si>
-    <t>attack-pattern--3c3ab581-f839-4439-bf70-a00298d8cbb7</t>
-  </si>
-  <si>
-    <t>attack-pattern--3d477757-3882-43e5-b3b5-5c453472af4e</t>
-  </si>
-  <si>
-    <t>attack-pattern--cfd09f3f-20c2-4148-a51e-c7533a4f6866</t>
-  </si>
-  <si>
-    <t>attack-pattern--69b5ecb8-ed59-476a-a8d0-692d61060065</t>
-  </si>
-  <si>
-    <t>attack-pattern--a67dba4e-5c9c-4a96-8564-cc1477847aa2</t>
-  </si>
-  <si>
-    <t>attack-pattern--3c2787d0-9bb3-4445-baf7-affe99ffc75d</t>
-  </si>
-  <si>
-    <t>attack-pattern--281cf3bf-8184-4148-8d26-8ae24ac5facd</t>
-  </si>
-  <si>
-    <t>attack-pattern--0a36cf96-d155-4205-badf-fce21153e3d3</t>
-  </si>
-  <si>
-    <t>attack-pattern--58aadf94-c0fc-45fe-b84d-86af05ac2a41</t>
-  </si>
-  <si>
-    <t>attack-pattern--f409ed58-993e-4cd3-816b-35cb16df5f13</t>
-  </si>
-  <si>
-    <t>attack-pattern--0f543b48-8526-45f6-9f4c-c0aabf08b950</t>
-  </si>
-  <si>
-    <t>attack-pattern--2665c1bf-c793-4ff8-81e1-8cdfb042a050</t>
-  </si>
-  <si>
-    <t>attack-pattern--d1450cbb-9ca9-4637-a3d4-415897d678b3</t>
-  </si>
-  <si>
-    <t>attack-pattern--f7a7642e-6431-4d94-8930-784669743a6e</t>
-  </si>
-  <si>
-    <t>attack-pattern--2eccd110-1bf6-4854-a82c-0a45775e907f</t>
-  </si>
-  <si>
-    <t>attack-pattern--77f583b6-9202-4712-9a61-f28cba87bf1b</t>
-  </si>
-  <si>
-    <t>attack-pattern--b9b7420d-58cf-49d6-9884-18e4d72f0a38</t>
-  </si>
-  <si>
-    <t>attack-pattern--31403032-89b6-4a29-af26-bdb2c907f869</t>
-  </si>
-  <si>
-    <t>attack-pattern--59e9ef1f-3d12-4523-a3ac-0b4c11c35573</t>
-  </si>
-  <si>
-    <t>attack-pattern--3b7ebd5a-2989-4a5f-8187-7dcbb6319ecd</t>
-  </si>
-  <si>
-    <t>attack-pattern--47a73afc-602e-4840-98f7-559a0583a02f</t>
-  </si>
-  <si>
-    <t>attack-pattern--b6ab653b-b93b-46b8-9fc3-d24ccf9a86a1</t>
-  </si>
-  <si>
-    <t>attack-pattern--cfe0ba66-044c-4fae-899d-2776ecd25970</t>
-  </si>
-  <si>
-    <t>attack-pattern--faf29c5e-51f3-4afd-9b72-70769986b561</t>
-  </si>
-  <si>
-    <t>attack-pattern--9f4aa723-88b2-42d4-b7f0-58bfc3f42435</t>
-  </si>
-  <si>
-    <t>attack-pattern--39c46a2f-f777-48c7-b903-20ce80bca89b</t>
-  </si>
-  <si>
-    <t>attack-pattern--0c6b2071-1b00-4c4e-ad42-c086fe85e44d</t>
-  </si>
-  <si>
-    <t>attack-pattern--20e9f442-a9aa-49d2-86e7-10b3677d2b71</t>
-  </si>
-  <si>
-    <t>attack-pattern--01cef48e-e90c-42c2-b99f-c6ce6b48b026</t>
-  </si>
-  <si>
-    <t>attack-pattern--df7b78e3-6709-4b71-ae0c-08ed1a47de6b</t>
-  </si>
-  <si>
-    <t>attack-pattern--661bd189-a8b3-42ff-bf5b-33de03ae6136</t>
-  </si>
-  <si>
-    <t>attack-pattern--7ef5f9c4-8044-44bc-88a6-9395e47e160a</t>
-  </si>
-  <si>
-    <t>attack-pattern--b7f8cff2-87c7-48c1-aeb7-5cf9187b1090</t>
-  </si>
-  <si>
-    <t>attack-pattern--3ec89812-91d7-48b1-aa07-b78e44175f91</t>
-  </si>
-  <si>
-    <t>attack-pattern--1a21e55e-d799-41ce-a799-461e1995bd5a</t>
-  </si>
-  <si>
-    <t>attack-pattern--5ba903c1-2421-4964-8ca4-f56dcc96a1c3</t>
-  </si>
-  <si>
-    <t>attack-pattern--50e11ffa-fd63-4200-af97-d723ceb03f87</t>
-  </si>
-  <si>
-    <t>attack-pattern--954103ab-7172-4bc3-80d2-6eda761140c7</t>
-  </si>
-  <si>
-    <t>attack-pattern--d4ba7ff5-0107-437e-853c-b8c4d37ea441</t>
-  </si>
-  <si>
-    <t>attack-pattern--f6f80852-da09-4571-bd87-ab371a289296</t>
-  </si>
-  <si>
-    <t>attack-pattern--c69305fb-035a-4c61-8929-2e22cea42d61</t>
-  </si>
-  <si>
-    <t>attack-pattern--b1ae5e87-2d91-4460-ab24-a874f71d0aa3</t>
-  </si>
-  <si>
-    <t>attack-pattern--3408f6b9-9851-47a8-8c46-591cab11c267</t>
-  </si>
-  <si>
-    <t>attack-pattern--9a46e5ee-7093-4048-9d7e-501463c0424d</t>
-  </si>
-  <si>
-    <t>attack-pattern--f2121d22-b6ab-4c8d-b1a6-a65df30bd836</t>
-  </si>
-  <si>
-    <t>attack-pattern--01660591-eff8-4002-8b86-edbc8ddcff75</t>
-  </si>
-  <si>
-    <t>attack-pattern--1337b0db-4d5f-447f-83d1-3682c83da1be</t>
-  </si>
-  <si>
-    <t>attack-pattern--2685f739-43ca-4258-8e7f-0cf545de3477</t>
-  </si>
-  <si>
-    <t>attack-pattern--5da8aa0b-7c9c-4638-bc17-9ed6bf1aafa6</t>
-  </si>
-  <si>
-    <t>attack-pattern--b1616020-3221-457d-9111-770be3da803f</t>
-  </si>
-  <si>
-    <t>attack-pattern--60789ba9-9b1e-4a2d-804d-b16342fe5f3d</t>
-  </si>
-  <si>
-    <t>attack-pattern--9b1b420b-4d1a-4108-a086-73ba81138b1a</t>
-  </si>
-  <si>
-    <t>attack-pattern--1a522e5a-e65b-443f-8aae-2bc39534e85e</t>
-  </si>
-  <si>
-    <t>attack-pattern--3c07dbf7-3e3e-47d9-b439-53989a64f430</t>
-  </si>
-  <si>
-    <t>attack-pattern--948886a4-efe9-40cc-8153-3370afff323e</t>
-  </si>
-  <si>
-    <t>attack-pattern--c21a61e0-99df-4c01-abf2-5e46d8345613</t>
+    <t>attack-pattern--18bfffe3-6edf-438e-a946-488affc66f7a</t>
+  </si>
+  <si>
+    <t>attack-pattern--b99f4011-58e6-451b-81a1-1ce712a80a70</t>
+  </si>
+  <si>
+    <t>attack-pattern--35b2816a-2fa1-429f-a041-5f6ffc581e69</t>
+  </si>
+  <si>
+    <t>attack-pattern--fb59974b-817d-48bb-81f3-4dd9873bd6b4</t>
+  </si>
+  <si>
+    <t>attack-pattern--8532007d-d463-45cc-958a-fe79d1d83608</t>
+  </si>
+  <si>
+    <t>attack-pattern--71fb05ba-3eab-4f5c-ba49-a67390e5fc13</t>
+  </si>
+  <si>
+    <t>attack-pattern--ab499b3c-40d3-4e5a-8de3-3ff1466362c7</t>
+  </si>
+  <si>
+    <t>attack-pattern--0f49883b-8f7f-45db-b962-d3017cc85771</t>
+  </si>
+  <si>
+    <t>attack-pattern--d974ffeb-b434-47fa-9665-cff3eb08afd7</t>
+  </si>
+  <si>
+    <t>attack-pattern--eb4e21e3-74e1-4c36-9847-f819d0da7468</t>
+  </si>
+  <si>
+    <t>attack-pattern--9482f472-eefe-4b92-b476-a9b5f3b343ff</t>
+  </si>
+  <si>
+    <t>attack-pattern--0d525dd4-9996-48c0-8b48-87019adce8e1</t>
+  </si>
+  <si>
+    <t>attack-pattern--1439ce66-b7a2-4db6-a8f7-d2ded55aa3b4</t>
+  </si>
+  <si>
+    <t>attack-pattern--6acaa0d2-b311-43d0-bf45-42f11350a821</t>
+  </si>
+  <si>
+    <t>attack-pattern--1bd02aba-634a-4588-9786-fc30696e70b5</t>
+  </si>
+  <si>
+    <t>attack-pattern--023c87b7-782d-4f6e-82f6-84485c8409be</t>
+  </si>
+  <si>
+    <t>attack-pattern--ccac8b90-d32e-4daa-b524-8c0134ff7d4e</t>
+  </si>
+  <si>
+    <t>attack-pattern--4f945941-64c6-443a-988b-7dd2bdbb0748</t>
+  </si>
+  <si>
+    <t>attack-pattern--9bb95249-6747-41c3-b711-7f5094e85ae7</t>
+  </si>
+  <si>
+    <t>attack-pattern--af62ced2-68d3-492b-98ce-c999c9827400</t>
+  </si>
+  <si>
+    <t>attack-pattern--4183c4e4-db10-432a-bca9-e1b23e3da61f</t>
+  </si>
+  <si>
+    <t>attack-pattern--107c88d2-2c1e-4f39-b5cc-0d909875c061</t>
+  </si>
+  <si>
+    <t>attack-pattern--5b69d1b6-c6dd-4f6d-8909-ee09462cfad8</t>
+  </si>
+  <si>
+    <t>attack-pattern--29ec00bf-fdfe-4900-bf0b-83e650136a16</t>
+  </si>
+  <si>
+    <t>attack-pattern--993fbcf3-8292-45af-817f-edd7d88c57ea</t>
+  </si>
+  <si>
+    <t>attack-pattern--7319913c-e3a4-4b03-a99c-3680896d81b7</t>
+  </si>
+  <si>
+    <t>attack-pattern--923f47cf-b68d-460e-9fe0-110a95077f6a</t>
+  </si>
+  <si>
+    <t>attack-pattern--3045e408-7cdd-45fa-b0e0-ac789bda69d1</t>
+  </si>
+  <si>
+    <t>attack-pattern--1346bbf5-d81b-4d05-b377-bdc659611dce</t>
+  </si>
+  <si>
+    <t>attack-pattern--c393033f-0d84-45b8-bf52-eb210a212208</t>
+  </si>
+  <si>
+    <t>attack-pattern--59e90492-d231-402a-a465-3f5bc479a1e8</t>
+  </si>
+  <si>
+    <t>attack-pattern--e9a7afa4-472f-45a0-9982-44652e7f5062</t>
+  </si>
+  <si>
+    <t>attack-pattern--68d98ee4-53c5-4745-9d7f-483114cc6999</t>
+  </si>
+  <si>
+    <t>attack-pattern--22b543df-dfb1-49fc-8d95-c374e058f540</t>
+  </si>
+  <si>
+    <t>attack-pattern--de25c05a-bf38-438b-927f-bc4dcb46653c</t>
+  </si>
+  <si>
+    <t>attack-pattern--80dfaadf-e59e-45e8-8ea6-1d438ac88184</t>
+  </si>
+  <si>
+    <t>attack-pattern--04898e9d-6eef-499f-8d56-bfd1c2af2c6b</t>
+  </si>
+  <si>
+    <t>attack-pattern--f4d219bd-ff07-431e-9ace-0021dc1336d1</t>
+  </si>
+  <si>
+    <t>attack-pattern--ef81761d-ca4c-4cf6-be70-349d2288f494</t>
+  </si>
+  <si>
+    <t>attack-pattern--336d16d8-fe0b-4c75-a34c-54fab8d76a2f</t>
+  </si>
+  <si>
+    <t>attack-pattern--49394ec7-2785-4aca-9975-684937954136</t>
+  </si>
+  <si>
+    <t>attack-pattern--ea37d3cc-2d42-45db-bad0-d7012841e93d</t>
+  </si>
+  <si>
+    <t>attack-pattern--f578e2ce-75c5-4a8c-8d47-63ce9a9138c0</t>
+  </si>
+  <si>
+    <t>attack-pattern--4b194f79-84f8-4b29-9ce9-cfa85642e44f</t>
+  </si>
+  <si>
+    <t>attack-pattern--7a0e5d1e-3983-4db9-b8e7-22aa583a2858</t>
+  </si>
+  <si>
+    <t>attack-pattern--e84b6176-a783-444d-8a2a-e5f1fd0d764c</t>
+  </si>
+  <si>
+    <t>attack-pattern--cd9deeb5-27a6-44c7-a11f-f5381bd4054a</t>
+  </si>
+  <si>
+    <t>attack-pattern--f9a845df-3e98-4ac7-9ef9-489dfd667aaf</t>
+  </si>
+  <si>
+    <t>attack-pattern--3f65d725-4c10-41c5-b822-f324cb8e9b5a</t>
+  </si>
+  <si>
+    <t>attack-pattern--261c27b8-7ad3-447b-bbc3-160ef90be57d</t>
+  </si>
+  <si>
+    <t>attack-pattern--d735ca35-037b-4a3a-b196-89833a86103d</t>
+  </si>
+  <si>
+    <t>attack-pattern--7aee84dc-e060-4d3c-ac28-c6defb82a28b</t>
+  </si>
+  <si>
+    <t>attack-pattern--c1d667b7-eee5-402c-a154-9dbbb2a23436</t>
+  </si>
+  <si>
+    <t>attack-pattern--52bef255-ae4c-4e58-b916-db73b8409467</t>
+  </si>
+  <si>
+    <t>attack-pattern--0f064151-346c-4c9a-9376-b7b632f1e384</t>
+  </si>
+  <si>
+    <t>attack-pattern--9d1eb227-fa81-4405-a0da-241f20f31dea</t>
+  </si>
+  <si>
+    <t>attack-pattern--a16626c3-d9fc-4781-a7d4-10c13bd9336f</t>
+  </si>
+  <si>
+    <t>attack-pattern--1fb1fa4c-bf4e-4fa8-a32f-a4896e48fef5</t>
+  </si>
+  <si>
+    <t>attack-pattern--3a5d809f-d5a5-49b8-8a87-adb7babcf139</t>
+  </si>
+  <si>
+    <t>attack-pattern--834b21dc-f1f6-4fc5-b05a-e75753a12b5e</t>
+  </si>
+  <si>
+    <t>attack-pattern--2c6e3672-d316-4467-8f4b-c5d2837957f0</t>
+  </si>
+  <si>
+    <t>attack-pattern--c0c319d3-3928-4843-9aeb-c57677814069</t>
+  </si>
+  <si>
+    <t>attack-pattern--1179ba8e-8da5-4aa9-8165-120b23ad1fec</t>
+  </si>
+  <si>
+    <t>attack-pattern--44563dbb-1be9-46bc-9a66-af5e19b2106d</t>
+  </si>
+  <si>
+    <t>attack-pattern--b1db6118-0a31-4730-bde2-8fac46c3e137</t>
+  </si>
+  <si>
+    <t>attack-pattern--257839c4-791b-4968-b2dc-23e6c882655c</t>
+  </si>
+  <si>
+    <t>attack-pattern--68303848-d811-444e-9c48-90bacb503e96</t>
+  </si>
+  <si>
+    <t>attack-pattern--b8de1150-a710-4046-ace7-5c0877fa0bff</t>
+  </si>
+  <si>
+    <t>attack-pattern--b661aaca-a287-468b-88df-878b68349563</t>
+  </si>
+  <si>
+    <t>attack-pattern--030bbee9-626f-4024-aa7f-05ef7fbb844f</t>
+  </si>
+  <si>
+    <t>attack-pattern--088dd75c-3d48-434e-95d2-19d0e3147c5a</t>
+  </si>
+  <si>
+    <t>attack-pattern--ed62c8ca-77f7-4c09-acb3-2258db6f7d60</t>
+  </si>
+  <si>
+    <t>attack-pattern--1bc0c743-4448-42f5-97f0-d4e107fab546</t>
+  </si>
+  <si>
+    <t>attack-pattern--944cf29d-d469-4233-aac4-379f43393faf</t>
+  </si>
+  <si>
+    <t>attack-pattern--0bb3bb16-2da8-4789-ba21-e514db2101f5</t>
+  </si>
+  <si>
+    <t>attack-pattern--aa1b9222-fcb9-447f-b977-fdfb30faa681</t>
+  </si>
+  <si>
+    <t>attack-pattern--137882c2-807a-40d3-b4b1-f6a204a18347</t>
+  </si>
+  <si>
+    <t>attack-pattern--7f0aa4ca-fe15-4b83-bab8-922d4698446f</t>
+  </si>
+  <si>
+    <t>attack-pattern--5a006ee6-b55d-4072-b4d2-92a59016f7f6</t>
+  </si>
+  <si>
+    <t>attack-pattern--97651d27-015f-4e58-b447-bc29c4569898</t>
+  </si>
+  <si>
+    <t>attack-pattern--ef572bf1-2a59-4459-856a-70d90d0d0395</t>
+  </si>
+  <si>
+    <t>attack-pattern--c56b38dd-5f25-422e-9698-d5bba69b683f</t>
+  </si>
+  <si>
+    <t>attack-pattern--24b1fa21-90c3-464f-833f-ac108ecc78d1</t>
   </si>
   <si>
     <t>technique</t>
@@ -1754,571 +1754,571 @@
     <t>Введение государственной монополии на торговлю хлебом и централизованный контроль над распределением товаров. (Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.) 2013)</t>
   </si>
   <si>
-    <t>relationship--14ff5c13-bd58-4f3e-8847-116ab3781971</t>
-  </si>
-  <si>
-    <t>relationship--b8a1efd8-c26a-40b5-aee5-821ce44b4e16</t>
-  </si>
-  <si>
-    <t>relationship--8b9ecf43-5f5e-4e27-b61d-4fceafa47b81</t>
-  </si>
-  <si>
-    <t>relationship--2280f18d-76c9-4ede-885e-1f9f023d5edf</t>
-  </si>
-  <si>
-    <t>relationship--8b5ce05d-0dc5-44bb-a980-427c816728fd</t>
-  </si>
-  <si>
-    <t>relationship--84a726d6-aa58-4936-b16d-e720c1b9a864</t>
-  </si>
-  <si>
-    <t>relationship--f1d4c82a-9578-4e69-8a56-31829df9fbe5</t>
-  </si>
-  <si>
-    <t>relationship--b04fb82c-ac5f-488a-8dcd-fee6bb377ac3</t>
-  </si>
-  <si>
-    <t>relationship--21ab8f08-5ff9-4e53-8833-b03519bd6cd1</t>
-  </si>
-  <si>
-    <t>relationship--c86a5336-5315-4098-aa83-cd2f97e64823</t>
-  </si>
-  <si>
-    <t>relationship--803320d8-15ba-4348-8c32-bccf3db9f530</t>
-  </si>
-  <si>
-    <t>relationship--b413164f-24a7-4fc4-8ea9-138b0044ce12</t>
-  </si>
-  <si>
-    <t>relationship--f5b536e6-69d1-4bbe-83d9-1ba923dfcb36</t>
-  </si>
-  <si>
-    <t>relationship--7039355e-000e-46d0-8e30-1f7d9dfb4f5e</t>
-  </si>
-  <si>
-    <t>relationship--0efafd8f-ad20-4211-94bd-b94e514a4f77</t>
-  </si>
-  <si>
-    <t>relationship--95b25427-2e1f-495c-a35f-4da450c13301</t>
-  </si>
-  <si>
-    <t>relationship--a6e2c789-2ec6-48f4-bdef-117bd254f13a</t>
-  </si>
-  <si>
-    <t>relationship--af609251-5be4-4f65-90c8-fb3cc9a3dbb4</t>
-  </si>
-  <si>
-    <t>relationship--5cd48454-813b-4331-9c08-66ab490f7c61</t>
-  </si>
-  <si>
-    <t>relationship--0c4c43ea-624a-44d5-ba8b-7758a90422b9</t>
-  </si>
-  <si>
-    <t>relationship--9cf98d26-dcde-4e15-9b77-f531dfaaa42c</t>
-  </si>
-  <si>
-    <t>relationship--d62fcf47-1ed7-4e8e-89ae-ae2b35893e89</t>
-  </si>
-  <si>
-    <t>relationship--a3a14ae4-5efd-4ab9-95b0-7fe445ebaba9</t>
-  </si>
-  <si>
-    <t>relationship--02467645-18f1-44b3-9807-2febf2484815</t>
-  </si>
-  <si>
-    <t>relationship--bf8dd70b-311f-4582-b644-bef5c2fb33b6</t>
-  </si>
-  <si>
-    <t>relationship--dd9311f1-d090-402e-95ba-563ab46c7d70</t>
-  </si>
-  <si>
-    <t>relationship--f2d6a2cf-89d4-471d-954f-85ebca68df09</t>
-  </si>
-  <si>
-    <t>relationship--16305f31-01fb-4769-adda-fb68bdb5bdf5</t>
-  </si>
-  <si>
-    <t>relationship--f2506c16-b956-47b5-8994-61403315d62f</t>
-  </si>
-  <si>
-    <t>relationship--287fce25-2f71-4417-86e4-73d207d621d4</t>
-  </si>
-  <si>
-    <t>relationship--0cd1d9f5-1b62-4894-9c7a-887333274daa</t>
-  </si>
-  <si>
-    <t>relationship--bcfcbe09-5315-4558-a202-b0c3549f574c</t>
-  </si>
-  <si>
-    <t>relationship--72c5aa19-3333-497c-bc10-22276193dbe0</t>
-  </si>
-  <si>
-    <t>relationship--15c9a760-9071-47c3-8b86-207c651c3f9d</t>
-  </si>
-  <si>
-    <t>relationship--4834d7b9-4aad-4db8-b067-793cae286279</t>
-  </si>
-  <si>
-    <t>relationship--fc84144f-1d31-45d5-a091-7122aeffdb3a</t>
-  </si>
-  <si>
-    <t>relationship--ab5fb347-4be5-47d7-ac92-a21f54383f24</t>
-  </si>
-  <si>
-    <t>relationship--2fa33b37-bbe4-4bd4-8235-b137f4579659</t>
-  </si>
-  <si>
-    <t>relationship--c2dc6232-da70-47d5-8e03-23c22d15201e</t>
-  </si>
-  <si>
-    <t>relationship--69b5a3eb-88ee-4898-b5eb-bf99882e755a</t>
-  </si>
-  <si>
-    <t>relationship--8f834fe2-1ea9-4f4e-904e-03480b71fc0c</t>
-  </si>
-  <si>
-    <t>relationship--4c910602-8a1f-4a1b-ae96-78ff77141c32</t>
-  </si>
-  <si>
-    <t>relationship--bb2fb6c6-2082-4128-9aa2-6fd397d4b077</t>
-  </si>
-  <si>
-    <t>relationship--6217bbde-7bd4-4ff9-8084-1bb50aa35f0a</t>
-  </si>
-  <si>
-    <t>relationship--ae394320-962d-4311-a23d-f02679fc432f</t>
-  </si>
-  <si>
-    <t>relationship--5e9166c6-f3f3-4067-b9fb-81ac58ccea57</t>
-  </si>
-  <si>
-    <t>relationship--a77f7b5f-7b61-4700-8fda-341ffc586aa3</t>
-  </si>
-  <si>
-    <t>relationship--17249a22-d960-4c98-bd73-2176cff9a66d</t>
-  </si>
-  <si>
-    <t>relationship--2a6b25b3-2106-4cc5-9daf-69080545023a</t>
-  </si>
-  <si>
-    <t>relationship--7b1b9159-5728-4caa-b025-e233988eed18</t>
-  </si>
-  <si>
-    <t>relationship--bc9dae11-ee8d-437a-a5f2-151aad2a22b9</t>
-  </si>
-  <si>
-    <t>relationship--957f013b-288a-43a5-9b47-0b8ae24ecf5a</t>
-  </si>
-  <si>
-    <t>relationship--aa2e1b37-5b37-49f7-aa1b-6ae619b5c0f4</t>
-  </si>
-  <si>
-    <t>relationship--3f22a8b4-118a-4f55-9a26-b1ba62fa35b2</t>
-  </si>
-  <si>
-    <t>relationship--bcddaa91-a8a1-47ba-885d-b9525a1001aa</t>
-  </si>
-  <si>
-    <t>relationship--ef01b363-58f1-4d39-83d0-99ac81ffc65b</t>
-  </si>
-  <si>
-    <t>relationship--5e7fd20e-84e5-4350-b635-8cbfe36923cb</t>
-  </si>
-  <si>
-    <t>relationship--68d4e642-f528-4420-abae-afc75e93414f</t>
-  </si>
-  <si>
-    <t>relationship--aafb6322-5c65-4a69-831f-ce7c553efb7a</t>
-  </si>
-  <si>
-    <t>relationship--d5f27e9e-a55f-43aa-9040-20018524f869</t>
-  </si>
-  <si>
-    <t>relationship--3f9d7bd8-83c9-4fd9-9aa4-3b54a80bdb79</t>
-  </si>
-  <si>
-    <t>relationship--ec6b5a74-c9d6-4d5d-851d-4340a2c1e77a</t>
-  </si>
-  <si>
-    <t>relationship--1bd2d7ca-6d0d-45b7-aa5c-92d1af9ab047</t>
-  </si>
-  <si>
-    <t>relationship--1788c4e6-bd1e-42f4-bc4c-53a28ea72247</t>
-  </si>
-  <si>
-    <t>relationship--d1bd8bf5-4e79-47ca-bcd8-cb3ceed828ed</t>
-  </si>
-  <si>
-    <t>relationship--9707a4a3-85fc-4326-b941-6e3f4ba3d66e</t>
-  </si>
-  <si>
-    <t>relationship--ce616361-b9c6-41d7-9fa1-c6800c8569b7</t>
-  </si>
-  <si>
-    <t>relationship--c16c1d51-00c9-42e2-a472-267146714a16</t>
-  </si>
-  <si>
-    <t>relationship--8be9daf3-3283-4014-bb07-58b184b74d93</t>
-  </si>
-  <si>
-    <t>relationship--1e810079-efd1-4437-8550-e46be0afa71e</t>
-  </si>
-  <si>
-    <t>relationship--23db1a49-8cfc-4e88-baa9-6cdc44a115a2</t>
-  </si>
-  <si>
-    <t>relationship--cd711de5-eeb1-4125-b828-3b8a8f1b07f3</t>
-  </si>
-  <si>
-    <t>relationship--349ef81a-2f99-4a9c-9c81-e57f79f07d82</t>
-  </si>
-  <si>
-    <t>relationship--60c11da2-7800-43b7-8d1f-76c8aa05a5c9</t>
-  </si>
-  <si>
-    <t>relationship--98c02793-243e-4135-9a39-882178ad8a96</t>
-  </si>
-  <si>
-    <t>relationship--55ff4a91-8661-475f-8ad7-0f09f83c5e85</t>
-  </si>
-  <si>
-    <t>relationship--f198baec-e5e1-4737-8a14-de81017b8eea</t>
-  </si>
-  <si>
-    <t>relationship--d6938961-a091-45b1-bffc-87c242cf25a2</t>
-  </si>
-  <si>
-    <t>relationship--4cfdc688-c4fc-4bb4-a16d-fe39a1f133f7</t>
-  </si>
-  <si>
-    <t>relationship--4c8204a0-a1be-45e1-86b8-3f4cdd438ce7</t>
-  </si>
-  <si>
-    <t>relationship--7b3c83f1-d4d5-48b3-aadf-dceaea68b4ed</t>
-  </si>
-  <si>
-    <t>relationship--d9e0502c-e40e-4515-8c12-b3097dc7475a</t>
-  </si>
-  <si>
-    <t>relationship--33335b1d-f384-436a-9b2f-6977401616dd</t>
-  </si>
-  <si>
-    <t>relationship--563da1b2-2363-4bca-a36f-9427fbb0eeb1</t>
-  </si>
-  <si>
-    <t>relationship--d513bfcd-ce05-438e-ae32-b2aa913d07c8</t>
-  </si>
-  <si>
-    <t>relationship--26a2ccda-f08b-4248-a25b-0e55035acef5</t>
-  </si>
-  <si>
-    <t>relationship--74fd0492-7a79-4dda-8c2d-24e17c4bdab3</t>
-  </si>
-  <si>
-    <t>relationship--c249bddd-af15-4cad-90ed-82cdbeb66aa8</t>
-  </si>
-  <si>
-    <t>relationship--a73dab7a-cba3-4295-9a68-163953884ba6</t>
-  </si>
-  <si>
-    <t>relationship--43501e8a-b825-42ec-b6ec-e295e5cc2e08</t>
-  </si>
-  <si>
-    <t>relationship--bcbf16b1-48cf-4bc1-bb2f-5c361772e1f1</t>
-  </si>
-  <si>
-    <t>relationship--42d0b716-8699-4628-a8d2-d043f5334d2f</t>
-  </si>
-  <si>
-    <t>relationship--e91bf280-5cb2-4f22-973d-ca790c6a9765</t>
-  </si>
-  <si>
-    <t>relationship--1a85808f-513b-446c-8752-4b2ec5da5ee5</t>
-  </si>
-  <si>
-    <t>relationship--b89f2f86-e815-40bd-a82f-3bb6a732125d</t>
-  </si>
-  <si>
-    <t>relationship--fe71a8b2-0517-4fd7-bfec-9e1cd4b701c0</t>
-  </si>
-  <si>
-    <t>relationship--c0561e87-1c03-480c-86ee-6e8e79673848</t>
-  </si>
-  <si>
-    <t>relationship--3542d62b-9969-4f15-87ec-f94b5e6b4405</t>
-  </si>
-  <si>
-    <t>relationship--d217853a-a549-41ec-b95b-00caca3410b2</t>
-  </si>
-  <si>
-    <t>relationship--a2bab682-f3ac-4992-a542-5cecc03e0074</t>
-  </si>
-  <si>
-    <t>relationship--431f4e5a-5596-4a39-b84d-cd1f38d861b3</t>
-  </si>
-  <si>
-    <t>relationship--48ffcfbb-741a-478a-baa6-a36149793de8</t>
-  </si>
-  <si>
-    <t>relationship--827e00b3-a532-4a87-82e5-77f4de601e05</t>
-  </si>
-  <si>
-    <t>relationship--65222228-0b79-420f-a997-9c20f99ecaa4</t>
-  </si>
-  <si>
-    <t>relationship--231fa5f0-a19b-44f4-bc6f-dfa148cc8679</t>
-  </si>
-  <si>
-    <t>relationship--01861179-0186-4305-a71f-27f5e670b04f</t>
-  </si>
-  <si>
-    <t>relationship--5324471d-3a9d-4dcd-989c-0d95bd2d23e9</t>
-  </si>
-  <si>
-    <t>relationship--137d4968-3b9a-4eac-845b-ba164af2867e</t>
-  </si>
-  <si>
-    <t>relationship--5f10c7ac-d87d-4407-add7-7166679dd1f5</t>
-  </si>
-  <si>
-    <t>relationship--e7163b63-492c-4886-9dc2-6e859aa6d034</t>
-  </si>
-  <si>
-    <t>relationship--fc01a550-6494-40e0-8c0d-5c380763303b</t>
-  </si>
-  <si>
-    <t>relationship--822f19d2-5f87-4880-afbe-f1a2b98a3dbf</t>
-  </si>
-  <si>
-    <t>relationship--93fa1b38-db1c-4c2c-aac4-835e21431a8b</t>
-  </si>
-  <si>
-    <t>relationship--9d405089-6db2-4242-9be1-901cd852b765</t>
-  </si>
-  <si>
-    <t>relationship--391c1305-e015-4bd7-bb03-22bfba33c82b</t>
-  </si>
-  <si>
-    <t>relationship--4a68d93b-f1da-4a51-812b-5bf2f0c60a7b</t>
-  </si>
-  <si>
-    <t>relationship--7a210575-716a-406f-9d8e-172a2dbba802</t>
-  </si>
-  <si>
-    <t>relationship--e8029807-08ca-48d9-8572-6a38d99bd2c2</t>
-  </si>
-  <si>
-    <t>relationship--1e9b5938-8fed-4bc2-8d92-9525edd34e24</t>
-  </si>
-  <si>
-    <t>relationship--5268dc98-c56e-46a9-9bef-63cf230d237b</t>
-  </si>
-  <si>
-    <t>relationship--5ea6892d-4b0d-4cbd-8020-6aed168df5a4</t>
-  </si>
-  <si>
-    <t>relationship--55780959-01ec-4069-844d-6df18f57da1f</t>
-  </si>
-  <si>
-    <t>relationship--c46122a2-0e53-4c4b-8b0c-21bfd5940873</t>
-  </si>
-  <si>
-    <t>relationship--6e256514-03e4-45c9-b522-525f27ce759d</t>
-  </si>
-  <si>
-    <t>relationship--87de8c02-0bc1-4b2a-b3a5-facabf410a9b</t>
-  </si>
-  <si>
-    <t>relationship--cfa25437-a45c-4215-891f-c88fb1c6854e</t>
-  </si>
-  <si>
-    <t>relationship--7672e7ae-da3c-4880-9317-481e88285ca7</t>
-  </si>
-  <si>
-    <t>relationship--8c84f972-8d80-4970-b47e-a43e07b700a3</t>
-  </si>
-  <si>
-    <t>relationship--ae23fbce-cefd-4b11-81e8-a74bed5bef7b</t>
-  </si>
-  <si>
-    <t>relationship--f2d91af3-aff9-4b74-a087-c4e8554811b8</t>
-  </si>
-  <si>
-    <t>relationship--eff280bc-ca08-449f-a941-43ea0f060726</t>
-  </si>
-  <si>
-    <t>relationship--c56e03d1-3287-4cde-95c6-23146e302c3e</t>
-  </si>
-  <si>
-    <t>relationship--c6a6164a-b374-493d-a404-68d7cfe61825</t>
-  </si>
-  <si>
-    <t>relationship--ad667537-8c1d-4601-8f6f-4b65f4440940</t>
-  </si>
-  <si>
-    <t>relationship--0071f400-1c99-437b-a1f1-e6433c057f6f</t>
-  </si>
-  <si>
-    <t>relationship--41366efa-5b40-4d9c-a10f-da330d4c22a0</t>
-  </si>
-  <si>
-    <t>relationship--ba8dc7cc-a4a7-495c-9492-90f49e8d1153</t>
-  </si>
-  <si>
-    <t>relationship--2f06cb0c-dcb4-4cd6-bb11-95526ecd709b</t>
-  </si>
-  <si>
-    <t>relationship--43bfb130-3a03-4742-885d-1a4958c7189b</t>
-  </si>
-  <si>
-    <t>relationship--a01766a1-519b-4338-8c88-0c0e2b937dd3</t>
-  </si>
-  <si>
-    <t>relationship--43545b6d-7cb5-463e-a53d-6528245de722</t>
-  </si>
-  <si>
-    <t>relationship--3ff9678f-3704-4082-a10b-9615cb64ce97</t>
-  </si>
-  <si>
-    <t>relationship--23f4ec20-2a56-48e3-9436-dc947eb85662</t>
-  </si>
-  <si>
-    <t>relationship--26d110af-bfc4-46bd-89a6-b25ec0077a25</t>
-  </si>
-  <si>
-    <t>relationship--749eab61-1c86-4133-8036-76b4667d387a</t>
-  </si>
-  <si>
-    <t>relationship--604c0228-a8aa-45ca-b3d9-009780cd0c93</t>
-  </si>
-  <si>
-    <t>relationship--b5f73c4d-eb9d-4ccc-8058-9891de23f8e6</t>
-  </si>
-  <si>
-    <t>relationship--82c4b68f-c4a9-4899-862a-20954adc01a3</t>
-  </si>
-  <si>
-    <t>relationship--5955053a-b87b-4b43-a152-f15bd6d5c523</t>
-  </si>
-  <si>
-    <t>relationship--2893c79c-adb3-4d67-a698-f859a0bbca0f</t>
-  </si>
-  <si>
-    <t>relationship--e5e199d4-6538-431c-94a2-85eabd8a9920</t>
-  </si>
-  <si>
-    <t>relationship--e1378deb-56c4-46c7-bf35-bcf7ab3a9ce2</t>
-  </si>
-  <si>
-    <t>relationship--9d5634ce-16b9-4d9b-a3d5-45a02d743968</t>
-  </si>
-  <si>
-    <t>relationship--c84a3b83-e414-4a18-b5ab-21d88156b13b</t>
-  </si>
-  <si>
-    <t>relationship--9a4aca14-a9a7-4761-90c4-a315313fa85f</t>
-  </si>
-  <si>
-    <t>relationship--07722c0c-5fc9-4dd0-86fd-06f3bdefc0b1</t>
-  </si>
-  <si>
-    <t>relationship--25b395e7-6c6b-43f4-a5ce-1a7c43a4c4a5</t>
-  </si>
-  <si>
-    <t>relationship--e8603dba-be2c-4d39-a158-05a34a8b2248</t>
-  </si>
-  <si>
-    <t>relationship--9f66288a-6101-45f1-a2e9-b6055dc72b7d</t>
-  </si>
-  <si>
-    <t>relationship--c6689428-236d-4e35-8f40-97343e6b4e4c</t>
-  </si>
-  <si>
-    <t>relationship--a7a247e1-e55c-4946-a6fe-8e89fff30460</t>
-  </si>
-  <si>
-    <t>relationship--bbd6f1fb-1697-4bf7-94eb-9bf778bd21fa</t>
-  </si>
-  <si>
-    <t>relationship--673687e5-33e3-4e10-853a-039ec9bbba0f</t>
-  </si>
-  <si>
-    <t>relationship--d8a80fd2-e649-403f-891a-f81e07386728</t>
-  </si>
-  <si>
-    <t>relationship--a182d298-ac49-4812-83d9-7c918bfdcff8</t>
-  </si>
-  <si>
-    <t>relationship--4e3d4cda-bc26-4e9a-944b-efcfa6e7dc78</t>
-  </si>
-  <si>
-    <t>relationship--89b24472-ef28-47d1-a136-9f156a129bf5</t>
-  </si>
-  <si>
-    <t>relationship--97230a5b-b9e5-4e98-a279-1afb93b1beeb</t>
-  </si>
-  <si>
-    <t>relationship--21b7fe4a-162a-4209-98d4-d360f5c94290</t>
-  </si>
-  <si>
-    <t>relationship--a03544ee-5257-4bc5-9f3d-941053278b0d</t>
-  </si>
-  <si>
-    <t>relationship--055c5491-8ec1-46ed-89bf-d00d10057a44</t>
-  </si>
-  <si>
-    <t>relationship--beff9c5d-311e-4dc5-810a-2898c3d5ef95</t>
-  </si>
-  <si>
-    <t>relationship--eb7f7d87-f0d9-415c-9d85-ec9d6995e371</t>
-  </si>
-  <si>
-    <t>relationship--d11d5a60-b488-4beb-b1e1-6cfeee9b512d</t>
-  </si>
-  <si>
-    <t>relationship--27449a60-290d-4640-9c7c-a4a87cb036d2</t>
-  </si>
-  <si>
-    <t>relationship--e4e82c07-b0d0-4fa0-b0ff-71a24ce8c031</t>
-  </si>
-  <si>
-    <t>relationship--f08aff09-5868-4f68-9056-fde79b6714e0</t>
-  </si>
-  <si>
-    <t>relationship--0eb3e9f8-ed56-49f9-961f-45b74f24d6b6</t>
-  </si>
-  <si>
-    <t>relationship--fe1ed08d-9a16-46e1-a211-946d17efabca</t>
-  </si>
-  <si>
-    <t>relationship--fddd4820-b3a3-42ab-8143-76a8a24e1e54</t>
-  </si>
-  <si>
-    <t>relationship--ad21a81f-9db2-419a-add3-717c177a80cb</t>
-  </si>
-  <si>
-    <t>relationship--3ccacaaf-c9c6-4bcf-8000-0f6f62ffe3a1</t>
-  </si>
-  <si>
-    <t>relationship--04df6efb-a4cd-4802-b309-fc2a7d94bdfa</t>
-  </si>
-  <si>
-    <t>relationship--52ba97a8-e66d-44a9-8e11-62a829dbb246</t>
-  </si>
-  <si>
-    <t>relationship--44b4500d-0d89-47da-aaed-e949cee74c3b</t>
-  </si>
-  <si>
-    <t>relationship--62164b6b-d164-41e7-9481-6223553cf173</t>
-  </si>
-  <si>
-    <t>relationship--50cd576b-7652-4699-b71f-0e4aa10e7538</t>
-  </si>
-  <si>
-    <t>relationship--858ee4ec-8c2e-4d81-a63a-6caaa3b1724e</t>
-  </si>
-  <si>
-    <t>relationship--956b8623-ce91-4d57-ab87-e214dcd8d1e6</t>
+    <t>relationship--94e1f217-42f2-459a-a545-6908dbcc290f</t>
+  </si>
+  <si>
+    <t>relationship--c5b0e284-95f9-484c-92a6-3c060abd3bb4</t>
+  </si>
+  <si>
+    <t>relationship--4bef2a92-999b-40f7-b07e-43f35b20d3e9</t>
+  </si>
+  <si>
+    <t>relationship--c74aea9a-311e-4db8-bb79-230d25ed68cf</t>
+  </si>
+  <si>
+    <t>relationship--04be9262-c441-4b42-b94d-14faaaebd38c</t>
+  </si>
+  <si>
+    <t>relationship--969b8098-2f06-4c38-8172-a89ec340e80b</t>
+  </si>
+  <si>
+    <t>relationship--abf89ac4-e487-46e2-af8f-d97fd28f9695</t>
+  </si>
+  <si>
+    <t>relationship--a78f2573-bbf4-4faa-9f9d-efd9b2eff2b4</t>
+  </si>
+  <si>
+    <t>relationship--30e23b40-3719-422e-8520-1098b0016763</t>
+  </si>
+  <si>
+    <t>relationship--f48a15c2-ca8b-406b-84c5-6a2b6d21e93e</t>
+  </si>
+  <si>
+    <t>relationship--68d08496-2634-4207-ad5b-6e899bf802c8</t>
+  </si>
+  <si>
+    <t>relationship--b81f5723-5eba-4b15-b4f6-ba50840ad359</t>
+  </si>
+  <si>
+    <t>relationship--20f8a015-6548-49f3-a4e7-ae8c18417d23</t>
+  </si>
+  <si>
+    <t>relationship--299ffd4d-f82f-400e-a5aa-111a2ed09a8e</t>
+  </si>
+  <si>
+    <t>relationship--fc089b4a-0138-40d6-9e18-8fb7f03754fe</t>
+  </si>
+  <si>
+    <t>relationship--94ece72b-0f70-4993-b29a-dc24e5911e26</t>
+  </si>
+  <si>
+    <t>relationship--4d66a077-ef73-4411-aa65-a000fc5271d6</t>
+  </si>
+  <si>
+    <t>relationship--a85e51c1-c058-48fe-9670-ccb343a427f7</t>
+  </si>
+  <si>
+    <t>relationship--42c06f0f-9fa8-42b2-958e-14c55d447edb</t>
+  </si>
+  <si>
+    <t>relationship--6d2a64e6-e6a8-4c2c-8466-9c794ab85ea3</t>
+  </si>
+  <si>
+    <t>relationship--48b3a397-9487-43c5-93be-840d9196be1d</t>
+  </si>
+  <si>
+    <t>relationship--14002f20-00de-43de-8846-9e4815c6e6cb</t>
+  </si>
+  <si>
+    <t>relationship--c57997d0-9295-450d-b1d5-ef17bb026f14</t>
+  </si>
+  <si>
+    <t>relationship--0b66ea38-98f1-4ded-92aa-a87c70f1456e</t>
+  </si>
+  <si>
+    <t>relationship--d215e283-3d59-40e6-8460-f6a5da0c3967</t>
+  </si>
+  <si>
+    <t>relationship--56987cf9-8e22-4398-b818-5e7e27a195a2</t>
+  </si>
+  <si>
+    <t>relationship--748c50e4-9e83-48d8-b5dc-e2b72bd60247</t>
+  </si>
+  <si>
+    <t>relationship--316fd0c6-cab7-458c-84fd-fc6221f0663d</t>
+  </si>
+  <si>
+    <t>relationship--5788d123-f09b-4def-b333-893909521114</t>
+  </si>
+  <si>
+    <t>relationship--87da0ac6-947a-4f13-ba8f-bf23651d0427</t>
+  </si>
+  <si>
+    <t>relationship--92b40284-268e-45ba-b499-59bfaec55a0d</t>
+  </si>
+  <si>
+    <t>relationship--a5a8f704-0810-4bc8-b776-cbf441cf5f34</t>
+  </si>
+  <si>
+    <t>relationship--376b9c98-bbe9-4576-a7d5-b88d5d27e52c</t>
+  </si>
+  <si>
+    <t>relationship--0c7ca6c4-073f-403b-b328-1ef45fbce413</t>
+  </si>
+  <si>
+    <t>relationship--cc188f87-1d9f-4bbf-85c6-65ca54bdb76e</t>
+  </si>
+  <si>
+    <t>relationship--aca7b73d-4397-49c6-ad6e-2dd43056b078</t>
+  </si>
+  <si>
+    <t>relationship--92c2486f-7771-4d54-a3d4-a3421a1f2862</t>
+  </si>
+  <si>
+    <t>relationship--72148f06-d607-4671-b336-5a1536c25116</t>
+  </si>
+  <si>
+    <t>relationship--130c2ac9-f262-45c6-b77d-a2d8065683ea</t>
+  </si>
+  <si>
+    <t>relationship--86ec4c0b-7618-4d32-b98b-611a70b99238</t>
+  </si>
+  <si>
+    <t>relationship--b5f35d59-43c2-4e81-a3ec-c1161e36756d</t>
+  </si>
+  <si>
+    <t>relationship--99f14310-68be-4f34-acd2-67392f36d34b</t>
+  </si>
+  <si>
+    <t>relationship--3e8ddd9f-eda0-4019-b81e-7d6e0d60d2f9</t>
+  </si>
+  <si>
+    <t>relationship--82e32f3e-a764-4f88-afe1-d73d333891c8</t>
+  </si>
+  <si>
+    <t>relationship--66dca3ec-bcc9-4ed2-85dc-db0ec33168d1</t>
+  </si>
+  <si>
+    <t>relationship--5f096b88-2f2c-448a-b3a3-02097ce270a6</t>
+  </si>
+  <si>
+    <t>relationship--7279c43e-1e6e-45bd-b7cd-e797a5a43d24</t>
+  </si>
+  <si>
+    <t>relationship--a29b2824-45ad-45db-9742-9732ea3157cc</t>
+  </si>
+  <si>
+    <t>relationship--8191fabf-06ec-4790-8c02-3ed087bd1233</t>
+  </si>
+  <si>
+    <t>relationship--800ed080-994d-40de-82c1-16acaf0780ef</t>
+  </si>
+  <si>
+    <t>relationship--b4d332cc-909c-49b4-9495-853695c6e489</t>
+  </si>
+  <si>
+    <t>relationship--5479e1aa-31ef-46a0-8c84-04a8c6334045</t>
+  </si>
+  <si>
+    <t>relationship--55aacf60-9343-4762-9ca2-f1773ee2dbcd</t>
+  </si>
+  <si>
+    <t>relationship--00596951-f6ae-40c9-97d7-51de0a6b565b</t>
+  </si>
+  <si>
+    <t>relationship--229059fd-4439-4e29-9463-17e8651b60c0</t>
+  </si>
+  <si>
+    <t>relationship--b20a86bf-287d-44b3-bd3e-dc4030002891</t>
+  </si>
+  <si>
+    <t>relationship--f59f0908-a79b-47ec-a443-28e4f9f953b4</t>
+  </si>
+  <si>
+    <t>relationship--d0c58f4e-6a94-48fa-bef4-95ec61771e85</t>
+  </si>
+  <si>
+    <t>relationship--670733a5-9130-456a-9a29-3e3600d71854</t>
+  </si>
+  <si>
+    <t>relationship--d8e97d51-3c1b-414f-a9a9-dc5b64a0fffe</t>
+  </si>
+  <si>
+    <t>relationship--5b7fd894-b2fd-4aa4-9032-4af292a067bd</t>
+  </si>
+  <si>
+    <t>relationship--2c99dc15-cc14-4132-a24b-bdacddbb235a</t>
+  </si>
+  <si>
+    <t>relationship--7ed2f4dd-e17e-41b2-bc15-3c562eb565d8</t>
+  </si>
+  <si>
+    <t>relationship--76697244-576a-4797-b6d3-5bd6c753160b</t>
+  </si>
+  <si>
+    <t>relationship--84a7c21b-4146-4b53-9fb1-ac91bfb7b2ee</t>
+  </si>
+  <si>
+    <t>relationship--09eee7ad-efd2-4e3b-ab1a-ff2d5b8245a1</t>
+  </si>
+  <si>
+    <t>relationship--4e7ccf87-166e-40b2-baf7-409667f91e97</t>
+  </si>
+  <si>
+    <t>relationship--9a726b46-0b15-4802-a454-931b29750f3b</t>
+  </si>
+  <si>
+    <t>relationship--0e881f78-62ee-436c-8548-f9c3ce45e1be</t>
+  </si>
+  <si>
+    <t>relationship--363efa53-2bc0-4a84-a2a2-642c4a154b99</t>
+  </si>
+  <si>
+    <t>relationship--9283d9e2-6fad-48e2-b81f-4791c4c918ad</t>
+  </si>
+  <si>
+    <t>relationship--f8dbb330-c03b-4d8b-8f09-f5eca322caa0</t>
+  </si>
+  <si>
+    <t>relationship--f85871a1-f01a-41ce-b0d5-6d7e5b6fc53c</t>
+  </si>
+  <si>
+    <t>relationship--2ea43e52-206a-4f84-997a-d1055440a2b8</t>
+  </si>
+  <si>
+    <t>relationship--f8488d36-b4db-4b51-b9db-a1fb22f47055</t>
+  </si>
+  <si>
+    <t>relationship--9e64984f-6623-44a1-958a-e1226e7db177</t>
+  </si>
+  <si>
+    <t>relationship--ca908ca9-1b02-438c-9233-fa17ce3950dd</t>
+  </si>
+  <si>
+    <t>relationship--51d72dd2-c0d4-4e6b-a926-deca764f5143</t>
+  </si>
+  <si>
+    <t>relationship--f16b12ff-361d-4554-b263-667f9b3dc56a</t>
+  </si>
+  <si>
+    <t>relationship--522fdb89-48f3-4736-9f85-a9d09be3c5f2</t>
+  </si>
+  <si>
+    <t>relationship--65b7e52d-99cc-45f4-af04-6757248b78b0</t>
+  </si>
+  <si>
+    <t>relationship--06d9c953-145a-4483-b984-94e089da5add</t>
+  </si>
+  <si>
+    <t>relationship--e2514085-8eee-4a3c-ba89-8455fc03c02b</t>
+  </si>
+  <si>
+    <t>relationship--bbed2f44-88a2-4dd4-a6c2-f10b83a66748</t>
+  </si>
+  <si>
+    <t>relationship--d4014cf0-2ae5-45f8-afdb-81ba5b2474f9</t>
+  </si>
+  <si>
+    <t>relationship--2ab71617-01d2-49c4-b3c0-4ffa82beea2d</t>
+  </si>
+  <si>
+    <t>relationship--e776d33f-87d3-4836-849f-4130197f473f</t>
+  </si>
+  <si>
+    <t>relationship--60cce790-bf5c-4690-bc5a-3ac63124aacb</t>
+  </si>
+  <si>
+    <t>relationship--05dde170-efe6-4def-908e-c6530f75c2b9</t>
+  </si>
+  <si>
+    <t>relationship--d646627e-6cb4-4875-8b83-73d90c69c5af</t>
+  </si>
+  <si>
+    <t>relationship--53fff489-b21c-4c86-8813-3f760348a14e</t>
+  </si>
+  <si>
+    <t>relationship--9e44cf99-695b-4716-b18d-796934094dab</t>
+  </si>
+  <si>
+    <t>relationship--f1265f46-e9f4-4ff7-a5fc-c077c5e98486</t>
+  </si>
+  <si>
+    <t>relationship--6f536c3e-03c0-4191-bc9f-ad9b2fc58b86</t>
+  </si>
+  <si>
+    <t>relationship--d9408c42-9534-4c31-9ed4-d1c2b408fce2</t>
+  </si>
+  <si>
+    <t>relationship--30f2ede4-96f1-443a-9238-ba6e6337dcc2</t>
+  </si>
+  <si>
+    <t>relationship--5e2c4902-c553-42fe-be38-65d2124b3a72</t>
+  </si>
+  <si>
+    <t>relationship--90ea2161-72d3-4e45-bdee-ff03cca959ad</t>
+  </si>
+  <si>
+    <t>relationship--9f6df441-2b5b-4e98-a769-4e01d473b561</t>
+  </si>
+  <si>
+    <t>relationship--d1faf29f-4646-4999-8612-238216e90c34</t>
+  </si>
+  <si>
+    <t>relationship--8f3cebb8-5a4c-40ad-bfda-eabc54424cdd</t>
+  </si>
+  <si>
+    <t>relationship--6fe997fb-a0ae-4c8c-a942-c25747c87864</t>
+  </si>
+  <si>
+    <t>relationship--0d3f2953-a543-448a-8e53-97420eda03cd</t>
+  </si>
+  <si>
+    <t>relationship--0df8f055-9e58-4a1d-b29c-0b66772ea766</t>
+  </si>
+  <si>
+    <t>relationship--633708db-156f-4b9f-a067-4752f8700b9c</t>
+  </si>
+  <si>
+    <t>relationship--a66260b8-c4ca-4462-bf3c-fcf19e787c9d</t>
+  </si>
+  <si>
+    <t>relationship--fc8cf2da-f266-443c-a83c-94c6ddd45fa8</t>
+  </si>
+  <si>
+    <t>relationship--2719f96e-0d89-4eec-b6da-4e7d5c973c7b</t>
+  </si>
+  <si>
+    <t>relationship--c9ab5858-9197-464a-8d00-8471cd67d48d</t>
+  </si>
+  <si>
+    <t>relationship--daf0a4d5-dea0-43cc-b1a6-fbc842dcbf02</t>
+  </si>
+  <si>
+    <t>relationship--bfcc0f69-d518-409c-9a96-46b635739144</t>
+  </si>
+  <si>
+    <t>relationship--d0a94c00-6142-4f67-b726-42723428e9e9</t>
+  </si>
+  <si>
+    <t>relationship--a8fac3b8-243e-4d5a-b4e7-67aa9b609767</t>
+  </si>
+  <si>
+    <t>relationship--6333146b-75b1-4448-b636-99e9d993ab8b</t>
+  </si>
+  <si>
+    <t>relationship--a338f362-f7f3-419a-b01e-1dbbab5cd5b2</t>
+  </si>
+  <si>
+    <t>relationship--5e15e7a8-f5ad-45f7-b3c7-ba394e55d1ee</t>
+  </si>
+  <si>
+    <t>relationship--7f128905-efc8-4d5d-9d2d-f1e3b184e62f</t>
+  </si>
+  <si>
+    <t>relationship--9c98a24f-1276-4b15-b335-19ce4e396590</t>
+  </si>
+  <si>
+    <t>relationship--8cfc4447-4b2f-4da9-9436-8294977035f8</t>
+  </si>
+  <si>
+    <t>relationship--9cce0756-e414-47b5-9ddb-fc35764061c4</t>
+  </si>
+  <si>
+    <t>relationship--3150b3ca-4a8e-4ba9-b61e-3571b75308e4</t>
+  </si>
+  <si>
+    <t>relationship--daa2b9cc-1867-43bb-8d89-9bf1e3088a9a</t>
+  </si>
+  <si>
+    <t>relationship--35c06343-36f8-4364-902c-5dffd8fdab30</t>
+  </si>
+  <si>
+    <t>relationship--fbe54f7b-dcf3-475f-ab52-d231e609a596</t>
+  </si>
+  <si>
+    <t>relationship--1eb9591f-0fba-4d0f-ae3a-7a9201d14a66</t>
+  </si>
+  <si>
+    <t>relationship--c7d8a464-a45c-4ef1-9891-731e41a36859</t>
+  </si>
+  <si>
+    <t>relationship--dc050f02-458f-4657-8d9b-5b3c21a5bb13</t>
+  </si>
+  <si>
+    <t>relationship--aa9eb727-03bb-4a54-955c-5f974856da12</t>
+  </si>
+  <si>
+    <t>relationship--3cd75a2d-d0e2-46c3-81ae-a1bbd37da6d2</t>
+  </si>
+  <si>
+    <t>relationship--efdf65fb-87d6-4f49-a218-0729cbeda7f2</t>
+  </si>
+  <si>
+    <t>relationship--f8dcd40e-1d06-4f44-a76e-7d5ba8546ce5</t>
+  </si>
+  <si>
+    <t>relationship--77c3d5b9-49bc-4bf2-b377-69e2481777a7</t>
+  </si>
+  <si>
+    <t>relationship--f7ba946e-3445-42c0-800c-384482de48f7</t>
+  </si>
+  <si>
+    <t>relationship--882c19c3-32a5-45ba-8d87-b7ae05464529</t>
+  </si>
+  <si>
+    <t>relationship--0c498660-baa4-4b56-9f9f-5da20757e52c</t>
+  </si>
+  <si>
+    <t>relationship--d8b6c99d-7ea9-4115-a161-58b8288517af</t>
+  </si>
+  <si>
+    <t>relationship--0370eab8-1f78-4e7e-9a43-5e854c096175</t>
+  </si>
+  <si>
+    <t>relationship--40e6e927-26d8-4a53-9a39-562850a77ae6</t>
+  </si>
+  <si>
+    <t>relationship--94f3c49d-188c-4725-8931-378a7c9bd42b</t>
+  </si>
+  <si>
+    <t>relationship--36a12f19-d0b9-4f59-9699-3be9def17e0d</t>
+  </si>
+  <si>
+    <t>relationship--5d53e412-ce44-4a3f-9e8e-ab2578741f04</t>
+  </si>
+  <si>
+    <t>relationship--711aa43b-6813-4fb9-9561-2a5475fed2dc</t>
+  </si>
+  <si>
+    <t>relationship--e9e8d50e-7d51-42a4-8312-700e58d90cc6</t>
+  </si>
+  <si>
+    <t>relationship--40ade569-6090-43f5-b71d-a73c6ee331d0</t>
+  </si>
+  <si>
+    <t>relationship--59b4d189-d57c-4c25-912c-da3eac3935d7</t>
+  </si>
+  <si>
+    <t>relationship--5dc280b6-ad46-4eb4-bd59-c0eec3938586</t>
+  </si>
+  <si>
+    <t>relationship--9f796ff7-1407-4783-be07-f9e77236376b</t>
+  </si>
+  <si>
+    <t>relationship--828c5a4e-c77e-46e9-a017-5afda757901d</t>
+  </si>
+  <si>
+    <t>relationship--22aa4145-ca0f-42d3-a693-0ccb175ca09c</t>
+  </si>
+  <si>
+    <t>relationship--83b819c1-7d01-44de-b61e-e8f32d4bd50c</t>
+  </si>
+  <si>
+    <t>relationship--082e12b3-5cac-4e3b-935a-b3f2aaedafe3</t>
+  </si>
+  <si>
+    <t>relationship--b50a765d-8def-4040-8c8c-ce25f592c050</t>
+  </si>
+  <si>
+    <t>relationship--e76bcde7-0d9d-4190-9819-4b77cd700714</t>
+  </si>
+  <si>
+    <t>relationship--b9c85a70-daa2-4e16-a294-1567f0898dd7</t>
+  </si>
+  <si>
+    <t>relationship--441033b7-c60c-4c3e-b4d3-e26d3ec6fb68</t>
+  </si>
+  <si>
+    <t>relationship--116af3a9-24e5-4886-894a-a91490a9a477</t>
+  </si>
+  <si>
+    <t>relationship--b1f65d92-35bc-46cb-998b-9c4f2cc6236f</t>
+  </si>
+  <si>
+    <t>relationship--216f04f8-646b-42b9-97a6-18dcf91c23d6</t>
+  </si>
+  <si>
+    <t>relationship--ea7b89a8-3a82-48af-95c4-fc0acda776c6</t>
+  </si>
+  <si>
+    <t>relationship--05aba7b5-d0cd-4fea-a518-04d20ee394bd</t>
+  </si>
+  <si>
+    <t>relationship--880bd43a-eb5c-4601-83a1-b14701b903d5</t>
+  </si>
+  <si>
+    <t>relationship--b1f54bc2-9e1f-46fc-81bf-6f1a639d314c</t>
+  </si>
+  <si>
+    <t>relationship--394f8a14-cd2b-40c7-8b99-377d117c91a0</t>
+  </si>
+  <si>
+    <t>relationship--2b9cfb6a-c6d3-475d-a2b8-32c382636825</t>
+  </si>
+  <si>
+    <t>relationship--068429d2-940b-4cc9-8e01-544e28d28140</t>
+  </si>
+  <si>
+    <t>relationship--2c197396-1567-4ba5-b652-ddcc53676c4b</t>
+  </si>
+  <si>
+    <t>relationship--000a7b7b-b69e-4e6b-8b11-825be421600e</t>
+  </si>
+  <si>
+    <t>relationship--6d7b6a67-ff04-41c7-aa81-0117620c0dc8</t>
+  </si>
+  <si>
+    <t>relationship--1cf1b7f4-3e14-4c4a-b328-1af6f2bf4dcd</t>
+  </si>
+  <si>
+    <t>relationship--2299e07f-541b-4421-bd11-4ffc91b977f5</t>
+  </si>
+  <si>
+    <t>relationship--47b73fa8-3f8f-4f25-8213-bf363e417d87</t>
+  </si>
+  <si>
+    <t>relationship--be02b2c4-4b58-436b-a726-3f377f5db0ad</t>
+  </si>
+  <si>
+    <t>relationship--7754990e-37eb-498c-91cd-c94018b1f4de</t>
+  </si>
+  <si>
+    <t>relationship--73fb2605-368d-4e7d-b76b-1b171bf6c428</t>
+  </si>
+  <si>
+    <t>relationship--cb354cd3-cc23-48c9-a933-b4592cbe36d1</t>
+  </si>
+  <si>
+    <t>relationship--7b89c335-642f-460c-a3c9-f184a722687f</t>
+  </si>
+  <si>
+    <t>relationship--32e32a50-83a8-4cae-933f-e7d0bc721672</t>
+  </si>
+  <si>
+    <t>relationship--671ec298-b979-419d-a141-8995a9f22cab</t>
+  </si>
+  <si>
+    <t>relationship--b73d6596-ff9a-4e10-9001-86645589ef80</t>
+  </si>
+  <si>
+    <t>relationship--17f4e651-2edc-40ae-b24a-2459922e2a05</t>
+  </si>
+  <si>
+    <t>relationship--8d658ebc-bf8f-4620-8630-b15943c990e5</t>
+  </si>
+  <si>
+    <t>relationship--2fe01f88-0caf-4125-8a5f-d2c56ed1c8e1</t>
+  </si>
+  <si>
+    <t>relationship--b5f12a30-4546-421d-896a-6ee9d8103cf8</t>
+  </si>
+  <si>
+    <t>relationship--6aac1e45-a96b-4357-91f2-a0ca8fe3b2d9</t>
+  </si>
+  <si>
+    <t>relationship--a0059280-c87e-4e5d-a68e-2ce66f9049dd</t>
+  </si>
+  <si>
+    <t>relationship--ed1f01db-1e4b-4333-aed8-8feb930cbd25</t>
+  </si>
+  <si>
+    <t>relationship--dcb15ec2-4ba3-45b3-bab6-d0a35b53efd5</t>
+  </si>
+  <si>
+    <t>relationship--bcf1261b-1d44-4642-bbb1-4e51ddb8ef2a</t>
+  </si>
+  <si>
+    <t>relationship--dbd00edc-0858-4977-a104-b41e28f12a0f</t>
   </si>
   <si>
     <t>C0009</t>
@@ -2933,310 +2933,310 @@
     <t>Юридическое поглощение через создание СССР (1922–1924)</t>
   </si>
   <si>
-    <t>campaign--97185b62-b756-44d3-b841-c26ff2caa435</t>
-  </si>
-  <si>
-    <t>campaign--28368dc3-bac3-40ca-9be2-53cd5b18ae5a</t>
-  </si>
-  <si>
-    <t>campaign--3e7aca06-438d-4972-b481-5eef5dddab91</t>
-  </si>
-  <si>
-    <t>campaign--42c2db2c-bca8-4f4c-90a1-feed7ccb5499</t>
-  </si>
-  <si>
-    <t>campaign--0e489ab4-57c8-4ea9-b1c1-35a091e8dcf5</t>
-  </si>
-  <si>
-    <t>campaign--3951c130-926c-4354-b30a-d9b845e20711</t>
-  </si>
-  <si>
-    <t>campaign--5df5ab6d-110b-41b0-914c-d68a42814b3f</t>
-  </si>
-  <si>
-    <t>campaign--332047f3-d991-48d5-a8d0-d626d70b1520</t>
-  </si>
-  <si>
-    <t>campaign--35760d2a-4bf9-493b-ab94-fa67c4ff8fcd</t>
-  </si>
-  <si>
-    <t>campaign--780db662-7237-47c6-9d76-e0a9c213b1ca</t>
-  </si>
-  <si>
-    <t>campaign--d38fee72-8a5f-42cd-a0e6-08b3642e49e2</t>
-  </si>
-  <si>
-    <t>campaign--ae71667a-64b0-4a35-bd4b-2212af26d6f2</t>
-  </si>
-  <si>
-    <t>campaign--1063f60a-3894-4344-97eb-1a62a8d09e50</t>
-  </si>
-  <si>
-    <t>campaign--1f2bd0e1-55a3-4605-9910-a28c81b3aba4</t>
-  </si>
-  <si>
-    <t>campaign--21ac6d95-7b1e-4b4a-a039-c789d4ded516</t>
-  </si>
-  <si>
-    <t>campaign--7fc58166-effa-406a-8ca4-a7e4fb477a96</t>
-  </si>
-  <si>
-    <t>campaign--374ff3ac-7e13-4ceb-870a-1c25a5e81f45</t>
-  </si>
-  <si>
-    <t>campaign--2514ee85-51a9-477d-893a-bb45313d0bd5</t>
-  </si>
-  <si>
-    <t>campaign--89014d54-7b08-4fba-83ac-c8722773fad8</t>
-  </si>
-  <si>
-    <t>campaign--ba097673-a412-4203-bb06-447f860a51d3</t>
-  </si>
-  <si>
-    <t>campaign--a55ffc4f-129f-4d38-8324-fdd1ebbb5a4b</t>
-  </si>
-  <si>
-    <t>campaign--01e2f625-82e2-488e-8622-00ebde701e23</t>
-  </si>
-  <si>
-    <t>campaign--fd958d24-a4bf-4243-ae08-e860c13ea805</t>
-  </si>
-  <si>
-    <t>campaign--a6face44-139d-466a-a5ff-e8c3ff709ace</t>
-  </si>
-  <si>
-    <t>campaign--a413d1f2-8330-4668-b8bd-fd8086250234</t>
-  </si>
-  <si>
-    <t>campaign--48e3bbbf-203d-40a1-bc6d-aa8b18e5598e</t>
-  </si>
-  <si>
-    <t>campaign--08d1bb96-2342-4cdb-b6b9-55a161a88419</t>
-  </si>
-  <si>
-    <t>campaign--76935537-cdec-406c-9f4a-a4cbc121cc00</t>
-  </si>
-  <si>
-    <t>campaign--f4466bbc-027a-4e44-935a-035f903ef19e</t>
-  </si>
-  <si>
-    <t>campaign--c7e7bcde-9c6c-437b-ad59-5e5bd2d5c514</t>
-  </si>
-  <si>
-    <t>campaign--236b5c9a-15f6-43ce-9667-200af4732480</t>
-  </si>
-  <si>
-    <t>campaign--b8c59485-94d3-40a6-b0fc-23d338986d1f</t>
-  </si>
-  <si>
-    <t>campaign--167376d8-aab7-4cbb-b314-230969e6a7a3</t>
-  </si>
-  <si>
-    <t>campaign--b2510237-29ac-4193-8722-444a86b52190</t>
-  </si>
-  <si>
-    <t>campaign--c8bcfd3d-d39b-4d28-9b5c-c5f3e8e0728f</t>
-  </si>
-  <si>
-    <t>campaign--8432f3de-ec66-4e20-88e9-54ed4587df9b</t>
-  </si>
-  <si>
-    <t>campaign--5bf5d20e-3e8f-4b7f-beb9-1a3189e2cadf</t>
-  </si>
-  <si>
-    <t>campaign--5f5766b1-030a-4e87-b165-48a1f821e9a6</t>
-  </si>
-  <si>
-    <t>campaign--ac432357-fb30-4c0f-9123-ff894b2784de</t>
-  </si>
-  <si>
-    <t>campaign--4bc43f67-3dc2-4c2b-9539-a42ff3e48f8f</t>
-  </si>
-  <si>
-    <t>campaign--a89eb731-49da-49ec-94fd-10f7ec7e3212</t>
-  </si>
-  <si>
-    <t>campaign--db4a09bc-80d8-443b-8be6-9a04e643eab5</t>
-  </si>
-  <si>
-    <t>campaign--0c92bef0-ae48-4178-a4e8-2845fe5e43ba</t>
-  </si>
-  <si>
-    <t>campaign--1a54b369-cecd-4acf-aeeb-addc0eee2b65</t>
-  </si>
-  <si>
-    <t>campaign--fc415691-46e4-4d5b-88ef-568d20e2f82a</t>
-  </si>
-  <si>
-    <t>campaign--30bc8d41-e4ff-476d-a84a-d5435273ad2e</t>
-  </si>
-  <si>
-    <t>campaign--37aea0f8-0538-4f63-994d-621cd042cbe7</t>
-  </si>
-  <si>
-    <t>campaign--b9035652-ec19-498f-ad70-c1e7c3af8809</t>
-  </si>
-  <si>
-    <t>campaign--25c5110f-77ed-4932-b111-1dfc5e875a95</t>
-  </si>
-  <si>
-    <t>campaign--84ee7058-67a7-46ba-b6ee-a9087bb87634</t>
-  </si>
-  <si>
-    <t>campaign--75cf364b-6744-4d5a-bb26-0abd1753609f</t>
-  </si>
-  <si>
-    <t>campaign--192a1e9c-2e3d-43d2-b6a6-175a55e941b5</t>
-  </si>
-  <si>
-    <t>campaign--071a2be9-c5af-4201-9e25-71e6c6dc63cf</t>
-  </si>
-  <si>
-    <t>campaign--ed10ebb7-caaa-481f-8655-7cc6acbade91</t>
-  </si>
-  <si>
-    <t>campaign--dc27daac-0791-47f7-aaee-d0e5c7a16918</t>
-  </si>
-  <si>
-    <t>campaign--7c31c341-4948-4d76-bc9a-d602657f0db3</t>
-  </si>
-  <si>
-    <t>campaign--f136d4ca-d08c-4b0b-9e1d-368e30dbfa5b</t>
-  </si>
-  <si>
-    <t>campaign--3f35fe1f-00d3-4e41-98a9-2e406c219312</t>
-  </si>
-  <si>
-    <t>campaign--31aacef3-25a8-4fba-ac95-bae1bb0592fb</t>
-  </si>
-  <si>
-    <t>campaign--491b0716-9561-4ea6-a89b-4ba9e0953e3c</t>
-  </si>
-  <si>
-    <t>campaign--a4455377-a120-45a5-9089-99fb95fdb59a</t>
-  </si>
-  <si>
-    <t>campaign--ea61a171-fa35-4ed1-9287-41e3ca667409</t>
-  </si>
-  <si>
-    <t>campaign--7771ca5f-0b5b-4fbb-9f0b-f37801347fca</t>
-  </si>
-  <si>
-    <t>campaign--0b3c9ce1-a0be-4440-b0f0-c762880ed332</t>
-  </si>
-  <si>
-    <t>campaign--96ec7087-d1b0-4076-a568-5f8a779eef00</t>
-  </si>
-  <si>
-    <t>campaign--46077bfe-ce3a-4542-8b5c-b8b6d8d6fdef</t>
-  </si>
-  <si>
-    <t>campaign--1e47c887-315a-4c3d-bea5-d9632702b517</t>
-  </si>
-  <si>
-    <t>campaign--61012452-31df-4e70-80b3-74be0914a200</t>
-  </si>
-  <si>
-    <t>campaign--bf409339-c5e5-4ab8-8b1a-246071ed19b5</t>
-  </si>
-  <si>
-    <t>campaign--d0eb71bc-3823-42d6-b3e5-427e2a915763</t>
-  </si>
-  <si>
-    <t>campaign--9a0c9c17-48be-4239-ae4b-ba408248d9ba</t>
-  </si>
-  <si>
-    <t>campaign--6a3d44b3-9d73-4774-a015-293e5ff7c59f</t>
-  </si>
-  <si>
-    <t>campaign--6058b9a2-6422-4498-bc1f-466e8f5404d0</t>
-  </si>
-  <si>
-    <t>campaign--a3e43158-57aa-48a2-8b22-c4338061ebe6</t>
-  </si>
-  <si>
-    <t>campaign--556f85fe-e335-4694-aa72-2e4da45a572d</t>
-  </si>
-  <si>
-    <t>campaign--3fc52fc0-1fc8-40f8-99fe-daee0cafc351</t>
-  </si>
-  <si>
-    <t>campaign--dee519da-cbc0-4a3f-8f64-811927f8fa8a</t>
-  </si>
-  <si>
-    <t>campaign--fcb5345d-ae74-4a0d-8859-00654996201a</t>
-  </si>
-  <si>
-    <t>campaign--ca069712-0be3-42d8-a175-c8e568760aba</t>
-  </si>
-  <si>
-    <t>campaign--9fd8c082-9e7d-4657-b402-c6b5164ebb7c</t>
-  </si>
-  <si>
-    <t>campaign--62313c07-9360-40f3-9a67-f106b3a9901f</t>
-  </si>
-  <si>
-    <t>campaign--a92151c2-5f7d-4c2e-a659-7a10e298595d</t>
-  </si>
-  <si>
-    <t>campaign--e2dc6026-4b3e-4088-8687-ee5e8efc0fcc</t>
-  </si>
-  <si>
-    <t>campaign--b8913d57-e3f2-43cc-989e-b5dc2cd92219</t>
-  </si>
-  <si>
-    <t>campaign--771a290d-43a0-43fb-89a5-2aaf271da029</t>
-  </si>
-  <si>
-    <t>campaign--c29e446f-6d4f-4920-91d5-fc54dedf1f5f</t>
-  </si>
-  <si>
-    <t>campaign--0bd21e62-2023-485d-9c17-c2684d1bebdb</t>
-  </si>
-  <si>
-    <t>campaign--7c688b14-67e6-476e-8096-a44c3fb95db9</t>
-  </si>
-  <si>
-    <t>campaign--567e3204-7775-46bb-b5f9-874bfeaf0c6f</t>
-  </si>
-  <si>
-    <t>campaign--dbde897a-31a7-4684-a98d-5805601ba4c2</t>
-  </si>
-  <si>
-    <t>campaign--906ac28e-dbce-42ff-9e99-9b6cc4aaa5e3</t>
-  </si>
-  <si>
-    <t>campaign--ce2366df-0b95-4d79-8f46-07ffa76c4215</t>
-  </si>
-  <si>
-    <t>campaign--efaaf655-e666-48b6-b47f-c6778bee3360</t>
-  </si>
-  <si>
-    <t>campaign--00f784da-4f20-4b91-acbe-8f9b76ff9596</t>
-  </si>
-  <si>
-    <t>campaign--59c82e4e-f119-41db-98a0-42312fac19cb</t>
-  </si>
-  <si>
-    <t>campaign--5478a268-e577-4b91-8abc-920e07341e66</t>
-  </si>
-  <si>
-    <t>campaign--b7c7a3d4-e14e-4089-805e-0d6bd5d494c2</t>
-  </si>
-  <si>
-    <t>campaign--acd8df7a-c420-435e-a7c2-1b8fd5170fab</t>
-  </si>
-  <si>
-    <t>campaign--d36ba52b-faba-4013-81c1-bc5462725fe9</t>
-  </si>
-  <si>
-    <t>campaign--cec91334-cad3-439c-9fd6-a172aa9d1c68</t>
-  </si>
-  <si>
-    <t>campaign--487d3e61-633a-4a79-8421-e58f556d93e1</t>
-  </si>
-  <si>
-    <t>campaign--dffc0208-5ef6-47c3-99a3-57d880da041e</t>
+    <t>campaign--beb3c204-bc97-4d59-9de6-ecdb0c1a8fa6</t>
+  </si>
+  <si>
+    <t>campaign--36718563-750c-4243-ac67-2afb9313199c</t>
+  </si>
+  <si>
+    <t>campaign--c0a083ff-f66b-4fe1-bbc2-eaf9c87ecafa</t>
+  </si>
+  <si>
+    <t>campaign--36b6cac5-68cd-44e9-948e-cdadfaeb03c0</t>
+  </si>
+  <si>
+    <t>campaign--931e85ed-d20f-4aab-ad0e-c481f9b6f9a4</t>
+  </si>
+  <si>
+    <t>campaign--aa92e9bb-c0c0-404b-b04e-cf449ba5e39d</t>
+  </si>
+  <si>
+    <t>campaign--618bc33c-2bd3-40a0-aecc-7d7b87050c1b</t>
+  </si>
+  <si>
+    <t>campaign--f62ceaad-15da-4759-8904-81880a93f161</t>
+  </si>
+  <si>
+    <t>campaign--81490a22-d3ad-4dac-a642-e2eba0016b14</t>
+  </si>
+  <si>
+    <t>campaign--9631e3bc-bab9-4043-bc04-c02749a194be</t>
+  </si>
+  <si>
+    <t>campaign--4a9d685a-9b20-4f1d-8915-4ada209c8cca</t>
+  </si>
+  <si>
+    <t>campaign--528c16c6-f91f-414a-8371-eab2292b3449</t>
+  </si>
+  <si>
+    <t>campaign--7b330b89-cb3c-4f20-a141-0e7d3be39898</t>
+  </si>
+  <si>
+    <t>campaign--eddeafb4-a875-4655-84a6-c63e89eeefd0</t>
+  </si>
+  <si>
+    <t>campaign--be2b48b0-daea-4dc8-b2be-24ebe5913dc5</t>
+  </si>
+  <si>
+    <t>campaign--7b32e63c-318e-4976-9a47-235504a9ebe1</t>
+  </si>
+  <si>
+    <t>campaign--6f93731b-4153-48bc-902d-f4e0ea897aa8</t>
+  </si>
+  <si>
+    <t>campaign--5d1e342a-8efe-4664-8157-4cc7ed55477a</t>
+  </si>
+  <si>
+    <t>campaign--dd4a2a03-d604-48f7-88b6-5a4fce5d3965</t>
+  </si>
+  <si>
+    <t>campaign--fc8f8fea-2e44-4409-a72b-e75ab314ec8a</t>
+  </si>
+  <si>
+    <t>campaign--f0c6054b-c01a-4747-b587-9903218358b2</t>
+  </si>
+  <si>
+    <t>campaign--2c6e0dec-e346-4ed4-b88f-5711faad6118</t>
+  </si>
+  <si>
+    <t>campaign--17e5ae14-9fa2-4925-bb28-0cdfc14fc1d7</t>
+  </si>
+  <si>
+    <t>campaign--5b639678-3921-474c-8c9e-4015ec9f949c</t>
+  </si>
+  <si>
+    <t>campaign--d1030d85-2e68-49b2-928c-2a14317de1bd</t>
+  </si>
+  <si>
+    <t>campaign--06927989-0878-4b74-9a28-35325dfa70f2</t>
+  </si>
+  <si>
+    <t>campaign--ea29169a-53a3-40d2-bd80-07873f4c7316</t>
+  </si>
+  <si>
+    <t>campaign--561a04bb-a336-4395-b343-c56073b71789</t>
+  </si>
+  <si>
+    <t>campaign--9707df54-95c3-4aa7-b931-57ee1a5c16f6</t>
+  </si>
+  <si>
+    <t>campaign--3dfcbbbc-e0ba-4b67-8bc2-810834ae08b3</t>
+  </si>
+  <si>
+    <t>campaign--f60fcbc2-4c94-4ef8-95b5-44d6aa0b3b8d</t>
+  </si>
+  <si>
+    <t>campaign--12b79d1c-2782-49d5-9a19-c40468968332</t>
+  </si>
+  <si>
+    <t>campaign--72bd14c6-9a8d-429e-8a8f-46ab0d667364</t>
+  </si>
+  <si>
+    <t>campaign--5fa83a2b-9405-4ea4-b37e-cd9d0ce57755</t>
+  </si>
+  <si>
+    <t>campaign--cc574bdf-4d55-47c1-b2fa-6bdb93755eea</t>
+  </si>
+  <si>
+    <t>campaign--27a779bf-b31d-4bbb-ace6-71f927cbde26</t>
+  </si>
+  <si>
+    <t>campaign--61a87e18-b207-448e-ba3a-c2a8d198974b</t>
+  </si>
+  <si>
+    <t>campaign--84ae7b7b-64d5-4093-a6a9-6dfacd6c66bf</t>
+  </si>
+  <si>
+    <t>campaign--67012817-6f85-428b-a010-93c08f2b76da</t>
+  </si>
+  <si>
+    <t>campaign--5dd1d621-c811-42cf-82c2-3406994dfde6</t>
+  </si>
+  <si>
+    <t>campaign--ace5b016-3d27-4b37-b2d2-d556647b00f1</t>
+  </si>
+  <si>
+    <t>campaign--4f18507b-2f69-46a9-85d5-40f17338779f</t>
+  </si>
+  <si>
+    <t>campaign--59f53554-bb3e-47d5-b876-5384f7e36329</t>
+  </si>
+  <si>
+    <t>campaign--5bcf32f4-e373-4f37-9efc-e49505e85e22</t>
+  </si>
+  <si>
+    <t>campaign--0aa91ac6-7a07-4d24-a072-994296a51cfa</t>
+  </si>
+  <si>
+    <t>campaign--9a502692-8621-4955-85ad-e7f7eb03cca2</t>
+  </si>
+  <si>
+    <t>campaign--a2171902-2718-49d1-b854-c8226a719312</t>
+  </si>
+  <si>
+    <t>campaign--592aa280-7cce-445b-b6e9-9abb88c52a90</t>
+  </si>
+  <si>
+    <t>campaign--19a08a71-50bd-429a-be2a-499c11fa5ccc</t>
+  </si>
+  <si>
+    <t>campaign--371756b0-4caf-470c-963c-a9cbaa8ee88b</t>
+  </si>
+  <si>
+    <t>campaign--4b25ef2f-6bb6-4d1d-a732-11a375521f54</t>
+  </si>
+  <si>
+    <t>campaign--a84dbd97-d0f4-4692-a0ab-e9d979d8a010</t>
+  </si>
+  <si>
+    <t>campaign--b767d548-72af-449a-adf8-63595a15dd6e</t>
+  </si>
+  <si>
+    <t>campaign--77beb7ac-80f5-4895-a7ea-b1dd56dacba4</t>
+  </si>
+  <si>
+    <t>campaign--06dfe566-0f1e-46bb-a5dc-ec4aff46135b</t>
+  </si>
+  <si>
+    <t>campaign--0975d9fe-1c4b-49ef-98ef-23d2b4210e88</t>
+  </si>
+  <si>
+    <t>campaign--b63c414e-aa3e-40c9-bb67-1f2d9ee5f71f</t>
+  </si>
+  <si>
+    <t>campaign--5478ddf2-476b-4d6c-a3aa-7096f3d5aca8</t>
+  </si>
+  <si>
+    <t>campaign--3574027e-078d-4e16-8484-b1dbe338ce61</t>
+  </si>
+  <si>
+    <t>campaign--1ddc10f7-4e18-404e-8910-5d8680bf7a82</t>
+  </si>
+  <si>
+    <t>campaign--39aac990-a61c-41dc-b9c5-b18f149b5cf8</t>
+  </si>
+  <si>
+    <t>campaign--3568c587-8fdb-4536-8de4-ebd3429b4cbd</t>
+  </si>
+  <si>
+    <t>campaign--e4ce65e2-37dd-4c97-98b8-c68fd507b4cc</t>
+  </si>
+  <si>
+    <t>campaign--0f94ee1d-db92-4fa1-9026-3308a6277f00</t>
+  </si>
+  <si>
+    <t>campaign--59491b04-3f44-42a9-bc41-7d0f175853c0</t>
+  </si>
+  <si>
+    <t>campaign--e509ef5e-b2d6-4520-8195-26f2931f56ff</t>
+  </si>
+  <si>
+    <t>campaign--dcf07b78-3dce-40f2-8c30-1e73ee27fb0a</t>
+  </si>
+  <si>
+    <t>campaign--e325f77e-16fc-4649-8dd9-ef74d4b8663c</t>
+  </si>
+  <si>
+    <t>campaign--fd91a053-f9b7-4cc1-879c-caa2f8a041f7</t>
+  </si>
+  <si>
+    <t>campaign--f4dffb8c-e664-4427-b25f-8a0f193c7649</t>
+  </si>
+  <si>
+    <t>campaign--e2f24cd2-ae30-4dcc-8c0e-6cbb3a0464a8</t>
+  </si>
+  <si>
+    <t>campaign--a48ef2d9-78c7-4412-830d-dfe17d102cc6</t>
+  </si>
+  <si>
+    <t>campaign--3396a968-9eeb-49ec-8dcd-18ff2d01b35b</t>
+  </si>
+  <si>
+    <t>campaign--02b7be7b-141b-4c27-a0c3-3a43f03219c9</t>
+  </si>
+  <si>
+    <t>campaign--b0acd87c-70ac-4d2d-a36b-2dec78583175</t>
+  </si>
+  <si>
+    <t>campaign--c0720a94-3178-4c69-8054-087ed0662c46</t>
+  </si>
+  <si>
+    <t>campaign--63c55fc1-e70c-4fdd-902a-14d4ca487812</t>
+  </si>
+  <si>
+    <t>campaign--40149032-0db8-4fbd-b5d4-a067b866c148</t>
+  </si>
+  <si>
+    <t>campaign--bfd071be-b1d5-44da-8f9d-e43041680ae7</t>
+  </si>
+  <si>
+    <t>campaign--bd6a4377-7f19-4732-a9f2-a3e0af5594a2</t>
+  </si>
+  <si>
+    <t>campaign--f1f67736-a37e-460d-8b05-49e59aad8ec3</t>
+  </si>
+  <si>
+    <t>campaign--696708cb-0055-44d8-99cb-f7fd2f15f721</t>
+  </si>
+  <si>
+    <t>campaign--2737ed0c-704b-422c-b4bd-d03d60ae1708</t>
+  </si>
+  <si>
+    <t>campaign--5a853b42-811c-495c-8cc3-4e44a8a1725c</t>
+  </si>
+  <si>
+    <t>campaign--87706f0a-efab-41dd-b40e-09d912b278fb</t>
+  </si>
+  <si>
+    <t>campaign--ee040f1e-7348-49a8-994b-429ea4f44ee9</t>
+  </si>
+  <si>
+    <t>campaign--627bf55a-42e0-4287-8113-35f4341ecab6</t>
+  </si>
+  <si>
+    <t>campaign--de98247a-897f-403e-9754-dae2fce2e39b</t>
+  </si>
+  <si>
+    <t>campaign--09020393-e2d9-4947-8e9e-0628160d3e3f</t>
+  </si>
+  <si>
+    <t>campaign--f5d8d5a7-70b7-4fc5-8971-e0eb43a47434</t>
+  </si>
+  <si>
+    <t>campaign--b6a88759-5300-4aaa-b49d-bf2236862685</t>
+  </si>
+  <si>
+    <t>campaign--b0168a30-f171-4142-9634-414781200ed4</t>
+  </si>
+  <si>
+    <t>campaign--c5d71421-e843-4a24-8444-46ebb0ad5b3e</t>
+  </si>
+  <si>
+    <t>campaign--97256eb3-cff9-433b-a6f2-48a15cbd9b9a</t>
+  </si>
+  <si>
+    <t>campaign--0d91cd39-b6e8-4cfe-adb1-cfc73904b0ab</t>
+  </si>
+  <si>
+    <t>campaign--44e766de-62fa-4407-8edc-b12167d3326c</t>
+  </si>
+  <si>
+    <t>campaign--bb6eedd8-fddb-409d-9b1f-c3a68aa615d5</t>
+  </si>
+  <si>
+    <t>campaign--674f47b9-9ec6-4c86-b3b7-63e25a43288e</t>
+  </si>
+  <si>
+    <t>campaign--fb281d58-2cc6-4a74-94c9-102105e35802</t>
+  </si>
+  <si>
+    <t>campaign--a4877dac-0e19-420c-87e8-e72f8806a3a5</t>
+  </si>
+  <si>
+    <t>campaign--1322fb40-8292-41fa-82bb-ea1743b9ce37</t>
+  </si>
+  <si>
+    <t>campaign--dcad1425-9259-44ad-a22e-bb1ba03156cb</t>
   </si>
   <si>
     <t>campaign</t>
@@ -3410,313 +3410,313 @@
     <t>Указ Александра II: «Заборона ввозити українські книги з-за кордону, заборона підписувати українські тексти під нотами, заборона українських вистав» (Citation: Русифікація України — Вікіпедія 2026).</t>
   </si>
   <si>
-    <t>relationship--a95066fb-1718-46d3-8e6e-49e87d4751b7</t>
-  </si>
-  <si>
-    <t>relationship--e9a22d2b-cb0b-4938-9005-5533000e7b38</t>
-  </si>
-  <si>
-    <t>relationship--565adc13-b06e-47cd-ba71-049604f1c97e</t>
-  </si>
-  <si>
-    <t>relationship--1c284d41-421a-4be5-9678-bb2ac621c866</t>
-  </si>
-  <si>
-    <t>relationship--32210d72-5a5a-447f-bc97-012c21a9d180</t>
-  </si>
-  <si>
-    <t>relationship--48fe585f-60a2-4e8c-8063-2ef406ecabbc</t>
-  </si>
-  <si>
-    <t>relationship--1aa6f707-5ad2-4cee-9940-beb43e0bbd57</t>
-  </si>
-  <si>
-    <t>relationship--6810df1c-387a-422d-8a88-f1e5ac631c8c</t>
-  </si>
-  <si>
-    <t>relationship--ebf45aa9-ab01-471e-989c-cf1348b5d70a</t>
-  </si>
-  <si>
-    <t>relationship--4807f9f0-92c6-446d-9180-7913879270a1</t>
-  </si>
-  <si>
-    <t>relationship--2fd65693-90a1-4f44-8274-b473a3bb173f</t>
-  </si>
-  <si>
-    <t>relationship--a0e6d595-4668-4dda-806b-b016e035a696</t>
-  </si>
-  <si>
-    <t>relationship--d47a8fb4-6c97-4b93-a1d6-61eb3f535597</t>
-  </si>
-  <si>
-    <t>relationship--f5c06e1b-f14f-492b-95e0-e82889dcc877</t>
-  </si>
-  <si>
-    <t>relationship--11eee327-9c1f-4151-931a-fbeb9b35bb4c</t>
-  </si>
-  <si>
-    <t>relationship--e435b9fd-332a-4d75-9476-d406f9c37a61</t>
-  </si>
-  <si>
-    <t>relationship--c13f714f-67f4-4e3f-a5fb-410a7d86df85</t>
-  </si>
-  <si>
-    <t>relationship--34d5c786-e1a6-4953-8f03-d138258da3d4</t>
-  </si>
-  <si>
-    <t>relationship--ed0e4c1e-4a29-4e56-99b3-c40191c272cc</t>
-  </si>
-  <si>
-    <t>relationship--dc8be056-141e-4424-80c7-a593fb2736fb</t>
-  </si>
-  <si>
-    <t>relationship--7ba58dbe-7676-4d12-a9da-718738083fe5</t>
-  </si>
-  <si>
-    <t>relationship--fc74cc6a-7592-4289-985b-94d3f359ade3</t>
-  </si>
-  <si>
-    <t>relationship--5541fa16-864d-4d8f-bdd9-8f442103ea16</t>
-  </si>
-  <si>
-    <t>relationship--7d115ed9-39e7-4def-b4a0-79972420802d</t>
-  </si>
-  <si>
-    <t>relationship--1bca7e42-1da9-4ea3-bb66-afa4c1df3443</t>
-  </si>
-  <si>
-    <t>relationship--bbdcb1e8-692d-41fe-88e1-d1fc06f4a8d5</t>
-  </si>
-  <si>
-    <t>relationship--dfb42873-75dc-45b8-8abd-96f5da31a2fa</t>
-  </si>
-  <si>
-    <t>relationship--48aaa29f-ac3e-47ee-982c-8541c26117c5</t>
-  </si>
-  <si>
-    <t>relationship--30d03301-95c7-4a01-86ab-fc56fab12bd0</t>
-  </si>
-  <si>
-    <t>relationship--33c28a36-b522-4c5c-b33c-28d4390bd800</t>
-  </si>
-  <si>
-    <t>relationship--463bd61c-a8d3-40ab-ace9-4515dfa76476</t>
-  </si>
-  <si>
-    <t>relationship--32ff96a6-0b0a-4ca7-8f19-3ed9dce19f80</t>
-  </si>
-  <si>
-    <t>relationship--f743c22a-ebef-4a93-847b-3b6e3122b994</t>
-  </si>
-  <si>
-    <t>relationship--619ee101-358b-4aad-b5d0-14bced2f13c8</t>
-  </si>
-  <si>
-    <t>relationship--abf8a785-6875-4d28-8fe5-01247f5425d9</t>
-  </si>
-  <si>
-    <t>relationship--0eadb0af-59ea-46cf-929c-73d9b9764492</t>
-  </si>
-  <si>
-    <t>relationship--261854c3-1617-45ff-baa8-6dbe52976c77</t>
-  </si>
-  <si>
-    <t>relationship--b027ab64-92aa-4d21-af4e-2337894240b5</t>
-  </si>
-  <si>
-    <t>relationship--b58f403d-9810-45d5-86d3-41e89f270bcf</t>
-  </si>
-  <si>
-    <t>relationship--f56b40d8-819a-40bc-a68e-c60d01db7f0f</t>
-  </si>
-  <si>
-    <t>relationship--3ef446d6-bbb7-433b-af9a-46857a3bc555</t>
-  </si>
-  <si>
-    <t>relationship--0cfbc2d3-05dd-44a8-bc82-7887467e3928</t>
-  </si>
-  <si>
-    <t>relationship--646e8a40-ca48-4925-9031-204da00b650e</t>
-  </si>
-  <si>
-    <t>relationship--a5959dbf-f0f2-45a0-bb14-5e41bdb8e585</t>
-  </si>
-  <si>
-    <t>relationship--e634e455-5505-4898-b305-982f72306fc4</t>
-  </si>
-  <si>
-    <t>relationship--3ae42177-2839-483a-80ef-2f3a2d15803c</t>
-  </si>
-  <si>
-    <t>relationship--79f23e7a-d1dc-44a2-bc4c-6d7c0604d9d9</t>
-  </si>
-  <si>
-    <t>relationship--41d16cff-028a-45b7-9773-b7ed73ac0855</t>
-  </si>
-  <si>
-    <t>relationship--26683c7f-b18d-4f0b-8240-1474c128b1ed</t>
-  </si>
-  <si>
-    <t>relationship--1116351d-6972-444b-90a0-1f8e7e66d75e</t>
-  </si>
-  <si>
-    <t>relationship--8c0281e5-c7a7-4e8c-a340-f4c9c0e727e9</t>
-  </si>
-  <si>
-    <t>relationship--9cedb62b-574a-4771-bf01-3eb83d2c19e7</t>
-  </si>
-  <si>
-    <t>relationship--2c051a16-4463-4ce0-8045-05edbecdb96e</t>
-  </si>
-  <si>
-    <t>relationship--cb40224b-fde2-4bd9-b5f4-1c7fca7631b9</t>
-  </si>
-  <si>
-    <t>relationship--ce3e3dce-c741-4765-a1f3-44e4543d4b3d</t>
-  </si>
-  <si>
-    <t>relationship--58d301f9-9b44-47c3-8013-ae1ec11c5913</t>
-  </si>
-  <si>
-    <t>relationship--97129600-dfdc-46fc-87ea-0815c54c2726</t>
-  </si>
-  <si>
-    <t>relationship--bfea3bd1-1ce5-4d9e-b016-73478a483537</t>
-  </si>
-  <si>
-    <t>relationship--87f2faef-e5fd-49df-99d1-3d1b54ca7640</t>
-  </si>
-  <si>
-    <t>relationship--fab8f5da-e65c-435e-8311-720b6c9eeabf</t>
-  </si>
-  <si>
-    <t>relationship--3aa6ec34-f393-430c-9cbd-4841f9920f0e</t>
-  </si>
-  <si>
-    <t>relationship--31366991-d83e-4eaf-88ba-c26255847e3f</t>
-  </si>
-  <si>
-    <t>relationship--d87ce476-23f9-4fc6-b13c-047097357dcf</t>
-  </si>
-  <si>
-    <t>relationship--5badbe27-c263-478a-b68d-c0c28b4f8ef1</t>
-  </si>
-  <si>
-    <t>relationship--a351e0a9-ae44-4578-8b4d-c6b47da74308</t>
-  </si>
-  <si>
-    <t>relationship--a56ff3ba-96e6-4973-bcd0-c4bef23b5d38</t>
-  </si>
-  <si>
-    <t>relationship--0ce7bddd-50d5-48be-afb7-d3e06b285ef0</t>
-  </si>
-  <si>
-    <t>relationship--05e4c4c5-0966-4337-8275-c4907b8d4673</t>
-  </si>
-  <si>
-    <t>relationship--565130fe-3386-42b6-b475-f02f8474bd39</t>
-  </si>
-  <si>
-    <t>relationship--cef88e9a-6cb7-49e6-9b5b-ba08c8ca6b88</t>
-  </si>
-  <si>
-    <t>relationship--e1ac74fc-d530-4cc3-a105-56087b595c2c</t>
-  </si>
-  <si>
-    <t>relationship--516e3400-7942-4d72-b4b0-e3b39d62f9e7</t>
-  </si>
-  <si>
-    <t>relationship--df7ec859-d883-4c8f-8b0e-372570d2a736</t>
-  </si>
-  <si>
-    <t>relationship--da299c4e-9630-4b38-b717-b6583dbe26fc</t>
-  </si>
-  <si>
-    <t>relationship--c8edbb88-14ff-4d8e-9c74-b2712da0ab11</t>
-  </si>
-  <si>
-    <t>relationship--278b8d8c-0a20-4a8f-9bad-a72df718c17c</t>
-  </si>
-  <si>
-    <t>relationship--ed38512a-db10-4611-b123-d56d3b981c1e</t>
-  </si>
-  <si>
-    <t>relationship--83dd8b38-931f-40f7-bc4b-d56173bcfe73</t>
-  </si>
-  <si>
-    <t>relationship--7f6d56c5-6612-489c-9b18-8c24dc75af58</t>
-  </si>
-  <si>
-    <t>relationship--118c7ea5-f1e1-495b-a5a2-963b25933ac6</t>
-  </si>
-  <si>
-    <t>relationship--b7c59cd1-369f-4de9-a3a4-5b5cdae3d166</t>
-  </si>
-  <si>
-    <t>relationship--b907d83f-4982-4baa-b5f8-fc364e9b33cc</t>
-  </si>
-  <si>
-    <t>relationship--7c44d0bb-7378-48de-af57-28bbb3af8b8b</t>
-  </si>
-  <si>
-    <t>relationship--eda1dbd4-3b39-44ff-90c1-96e6046320fc</t>
-  </si>
-  <si>
-    <t>relationship--3b210ccc-f8be-470c-adc2-cd060d11ffbe</t>
-  </si>
-  <si>
-    <t>relationship--7bf4e691-2470-49cd-a172-5df8af2263c5</t>
-  </si>
-  <si>
-    <t>relationship--57227651-67a7-4ede-b3bd-9309c9dede53</t>
-  </si>
-  <si>
-    <t>relationship--692ea191-a544-4a50-9449-6ac7d09a1930</t>
-  </si>
-  <si>
-    <t>relationship--6e0c35a5-3a68-4c67-af6d-bd0866e51274</t>
-  </si>
-  <si>
-    <t>relationship--c4285b2d-5078-4331-9d59-fe17df33e8d0</t>
-  </si>
-  <si>
-    <t>relationship--c55f3f86-c5b9-4fc3-82f3-3ef59966c26b</t>
-  </si>
-  <si>
-    <t>relationship--a2a349c4-fcd3-47cf-913c-db97245ac089</t>
-  </si>
-  <si>
-    <t>relationship--d12e139d-c65a-4553-832b-62ec4ad574ca</t>
-  </si>
-  <si>
-    <t>relationship--80d2485a-1628-48d9-bb5f-e5b985c816ef</t>
-  </si>
-  <si>
-    <t>relationship--c0eb327a-d351-41c7-ad63-def80454e574</t>
-  </si>
-  <si>
-    <t>relationship--b8166e54-71e5-4ec9-b871-e2bfa18c5cbf</t>
-  </si>
-  <si>
-    <t>relationship--859a06b7-36a7-4ff8-bf25-dd0593d202f3</t>
-  </si>
-  <si>
-    <t>relationship--8c419d72-e7d3-43ef-abcc-b264990cc673</t>
-  </si>
-  <si>
-    <t>relationship--7eac7055-d3e2-4b34-9559-1360309757c9</t>
-  </si>
-  <si>
-    <t>relationship--cd9f0e86-64ce-438f-9767-6b4081d8079f</t>
-  </si>
-  <si>
-    <t>relationship--22ace871-0cc2-4b40-901d-51c4fd38aebd</t>
-  </si>
-  <si>
-    <t>relationship--2ebd7677-4776-4837-9240-39ff6493c0d9</t>
-  </si>
-  <si>
-    <t>relationship--123596cd-c28b-46e5-a300-7400a612cb67</t>
+    <t>relationship--8dc2595a-ea3d-473a-a5ab-575d85961170</t>
+  </si>
+  <si>
+    <t>relationship--3c84583b-693a-411d-8a06-b9aab101e5c5</t>
+  </si>
+  <si>
+    <t>relationship--e8d1aab8-ede3-4533-8c27-28a8ab3a9367</t>
+  </si>
+  <si>
+    <t>relationship--13b55b19-53f2-4896-86bc-e1f50be71332</t>
+  </si>
+  <si>
+    <t>relationship--4679013f-4013-4366-aa96-58fb55a6aa34</t>
+  </si>
+  <si>
+    <t>relationship--b40e4178-b507-4dd4-af7e-a0d3edbfa984</t>
+  </si>
+  <si>
+    <t>relationship--26d306f5-3ef0-4f79-921b-0ed5b98c3c43</t>
+  </si>
+  <si>
+    <t>relationship--99bf693b-4903-48ad-ae82-4d5093e9f3f1</t>
+  </si>
+  <si>
+    <t>relationship--17d34dff-5105-4c32-8bd9-4a5c360275b2</t>
+  </si>
+  <si>
+    <t>relationship--6b18450a-0d29-4d28-a39e-211ed5c3e5e1</t>
+  </si>
+  <si>
+    <t>relationship--29fc4d48-e9a7-4d41-9350-759f35c10dc8</t>
+  </si>
+  <si>
+    <t>relationship--51826100-c689-4dfc-b952-79c064b32c09</t>
+  </si>
+  <si>
+    <t>relationship--85d5b58a-a850-44fa-a70b-565d0847df57</t>
+  </si>
+  <si>
+    <t>relationship--cb9711e4-244e-465f-9c39-1b1db3cec45f</t>
+  </si>
+  <si>
+    <t>relationship--f244205f-7f4f-4779-83cb-b5546f2907c6</t>
+  </si>
+  <si>
+    <t>relationship--486552f5-6661-4616-afbc-c9bb01a1ddea</t>
+  </si>
+  <si>
+    <t>relationship--e49c132f-0c7e-4890-89e3-9060f342daee</t>
+  </si>
+  <si>
+    <t>relationship--0a799f8f-4348-4756-ae8d-0053b35db49e</t>
+  </si>
+  <si>
+    <t>relationship--c0260409-7e77-4e21-b637-53e6b76e40a5</t>
+  </si>
+  <si>
+    <t>relationship--19add330-ac7a-4357-98af-9e1bc449b45a</t>
+  </si>
+  <si>
+    <t>relationship--98299ed0-aeee-4a24-b0f8-ac1ffb032879</t>
+  </si>
+  <si>
+    <t>relationship--2e08ea96-7302-4163-b951-a6992936f5d4</t>
+  </si>
+  <si>
+    <t>relationship--1282f430-f6a1-44c3-acd9-c6772a085e28</t>
+  </si>
+  <si>
+    <t>relationship--5b9db982-cb67-463e-99cb-b74e98983686</t>
+  </si>
+  <si>
+    <t>relationship--2e983734-e293-46fa-a3ca-59ab3e20acbc</t>
+  </si>
+  <si>
+    <t>relationship--206bd310-697b-48c8-9620-a8428c4b31b8</t>
+  </si>
+  <si>
+    <t>relationship--feb4f37f-6c5d-47eb-92bc-d9de34e5105c</t>
+  </si>
+  <si>
+    <t>relationship--effbdf3b-28c5-45ea-8c5a-a4aaad2d6684</t>
+  </si>
+  <si>
+    <t>relationship--dc15b305-bb0c-468e-bf55-29441ca02891</t>
+  </si>
+  <si>
+    <t>relationship--552815f9-b787-450b-b2f9-93f5e66a8957</t>
+  </si>
+  <si>
+    <t>relationship--d4bddd31-ce46-48f7-9213-fdc9abf9cab0</t>
+  </si>
+  <si>
+    <t>relationship--c2d442f7-36a3-4f01-85e9-74e5c228167b</t>
+  </si>
+  <si>
+    <t>relationship--efb14c78-9c3c-4b1a-8aa8-130ae785e59f</t>
+  </si>
+  <si>
+    <t>relationship--53ca7805-0a30-44fd-a9ed-80811c272e71</t>
+  </si>
+  <si>
+    <t>relationship--39b3a06e-b64a-48bd-8219-d1a340e8f8c8</t>
+  </si>
+  <si>
+    <t>relationship--8de2c20d-488f-44b0-a826-e2bf437c58f7</t>
+  </si>
+  <si>
+    <t>relationship--74b4b1c8-5505-4069-a9bb-b3aab4a59264</t>
+  </si>
+  <si>
+    <t>relationship--8d339651-b222-4255-89bc-21b1d1292935</t>
+  </si>
+  <si>
+    <t>relationship--cceeee86-4cc2-4d8d-a4c1-bb27c61204f7</t>
+  </si>
+  <si>
+    <t>relationship--26bd1c35-ea15-4ff8-b6f6-08ed46dfca86</t>
+  </si>
+  <si>
+    <t>relationship--67dcc9c5-8f7d-444b-b476-0a7bd878a900</t>
+  </si>
+  <si>
+    <t>relationship--b949ed45-ca02-48aa-b307-78dd8af7e422</t>
+  </si>
+  <si>
+    <t>relationship--4be45cec-a2bd-4f0a-a778-095b6752af02</t>
+  </si>
+  <si>
+    <t>relationship--f64fff70-eafe-460d-9157-da36af63b764</t>
+  </si>
+  <si>
+    <t>relationship--0fd6d8b1-cabd-4a84-8e9f-94e8957ab3c9</t>
+  </si>
+  <si>
+    <t>relationship--0b66b2f4-69a0-4687-a38d-5103d3a59aae</t>
+  </si>
+  <si>
+    <t>relationship--fb669914-1a8f-48cb-9d40-b4218be60472</t>
+  </si>
+  <si>
+    <t>relationship--bf2bf33b-0718-4a16-bc2d-39ee6fd50f41</t>
+  </si>
+  <si>
+    <t>relationship--ace8d8f7-f87c-45e9-a0c5-a6db13aaad67</t>
+  </si>
+  <si>
+    <t>relationship--47b11c13-c81d-4afd-bfef-2eec104a16bc</t>
+  </si>
+  <si>
+    <t>relationship--46c7972a-0170-46ee-a54e-00eac317d7c0</t>
+  </si>
+  <si>
+    <t>relationship--ff147538-2f19-48b9-b193-81bc3dad1108</t>
+  </si>
+  <si>
+    <t>relationship--333a50a3-d564-4dbe-849b-b11894b7ed79</t>
+  </si>
+  <si>
+    <t>relationship--0fa8a8c8-de1b-4c7a-ba1b-ddc747f84286</t>
+  </si>
+  <si>
+    <t>relationship--4a0cbdfe-b532-43ae-baeb-cf314aa4428b</t>
+  </si>
+  <si>
+    <t>relationship--cc0d240d-a816-453a-8188-cf45d9969879</t>
+  </si>
+  <si>
+    <t>relationship--720dea5e-74d9-42e5-857b-bda526769647</t>
+  </si>
+  <si>
+    <t>relationship--cc5c697e-b68b-4ee9-b89d-f6a0efd154e3</t>
+  </si>
+  <si>
+    <t>relationship--9aab33ce-0081-4870-a925-a592a1c665fa</t>
+  </si>
+  <si>
+    <t>relationship--de263284-c1a9-40e2-a6e8-7db444ed43a8</t>
+  </si>
+  <si>
+    <t>relationship--473d2c3f-29e4-4240-9378-75ef121e2fbf</t>
+  </si>
+  <si>
+    <t>relationship--5324c62e-3a35-4b7a-b14e-c89507d0ab29</t>
+  </si>
+  <si>
+    <t>relationship--9c280b9c-5ee6-4e79-8fce-a6090a5e6394</t>
+  </si>
+  <si>
+    <t>relationship--d558e7c7-08f3-41a3-8a0c-982ff50a56ce</t>
+  </si>
+  <si>
+    <t>relationship--1204277f-953e-461b-a56d-4e5a298da427</t>
+  </si>
+  <si>
+    <t>relationship--7c4d7b0e-bf38-4a39-8325-b770d26d6c2c</t>
+  </si>
+  <si>
+    <t>relationship--425d62f4-a51d-45f3-ad08-ccb9459a9c84</t>
+  </si>
+  <si>
+    <t>relationship--e99be189-029c-449f-934d-ff690bf7dcac</t>
+  </si>
+  <si>
+    <t>relationship--7624f845-91a7-4f63-80c5-88f7c0bdbcbb</t>
+  </si>
+  <si>
+    <t>relationship--2b6f8e15-69f6-4dc3-9806-553a5c2d5b38</t>
+  </si>
+  <si>
+    <t>relationship--6bda97d0-f843-4ec7-8b8d-edc2b40f02d6</t>
+  </si>
+  <si>
+    <t>relationship--7a886c7e-33be-4c26-ba00-dbc078e9cf62</t>
+  </si>
+  <si>
+    <t>relationship--065bf392-1be0-4866-b96e-3ccadf785266</t>
+  </si>
+  <si>
+    <t>relationship--c91fb938-45e3-409a-b405-61f05082eed3</t>
+  </si>
+  <si>
+    <t>relationship--c20014c6-540d-43bc-80c0-98cc844c9d15</t>
+  </si>
+  <si>
+    <t>relationship--44cfa7b6-235f-4b89-b41c-e254d74c2bc2</t>
+  </si>
+  <si>
+    <t>relationship--3eaac509-8079-41c1-84bc-679482ed864e</t>
+  </si>
+  <si>
+    <t>relationship--a5f04e72-b0a3-4439-b1b1-8a4b0e9a90d8</t>
+  </si>
+  <si>
+    <t>relationship--c387c4a8-3af7-44a3-994b-c633adf6179e</t>
+  </si>
+  <si>
+    <t>relationship--612fd961-d30f-4e77-a00e-3489d1eae79a</t>
+  </si>
+  <si>
+    <t>relationship--cbe02474-02b3-40cb-becd-610199c93a52</t>
+  </si>
+  <si>
+    <t>relationship--fa27ac74-f26e-45f6-97f6-6d221ce15f5a</t>
+  </si>
+  <si>
+    <t>relationship--f024e543-965f-4ece-91c8-34c5e94761ed</t>
+  </si>
+  <si>
+    <t>relationship--7a8d01c0-8c76-455b-94ce-7faf7a1a9ec0</t>
+  </si>
+  <si>
+    <t>relationship--9646f2db-0be1-412e-af35-3f7f8113555b</t>
+  </si>
+  <si>
+    <t>relationship--e84c607a-def4-471d-a7ef-fcdeaeb2ee9d</t>
+  </si>
+  <si>
+    <t>relationship--caf59a4b-f861-47d9-aac0-bf2f4e15b01f</t>
+  </si>
+  <si>
+    <t>relationship--69957228-a8d7-44a3-85b5-2ae21269762c</t>
+  </si>
+  <si>
+    <t>relationship--f88fa8c3-ef0b-4228-ac85-4d42e65e797f</t>
+  </si>
+  <si>
+    <t>relationship--b1497e6c-e2b6-4f63-b69a-0102358c2be6</t>
+  </si>
+  <si>
+    <t>relationship--a6563193-ff4a-4270-be28-c9b44647b975</t>
+  </si>
+  <si>
+    <t>relationship--0920fb2b-b2fe-4f8d-ac64-5f6c87f42a68</t>
+  </si>
+  <si>
+    <t>relationship--72f1a5a0-f043-4484-84c9-65cefa0f530a</t>
+  </si>
+  <si>
+    <t>relationship--447b159f-efe2-4684-a9b3-abee74d93d5c</t>
+  </si>
+  <si>
+    <t>relationship--e0fc9605-7703-469f-bb42-abfb0799181e</t>
+  </si>
+  <si>
+    <t>relationship--be80d057-d257-4b0f-a09b-f6221472a7af</t>
+  </si>
+  <si>
+    <t>relationship--f7dc890f-55e8-440d-979b-3f37dd3e16db</t>
+  </si>
+  <si>
+    <t>relationship--dbd117ad-c939-4d1a-a246-86d33f0f9b35</t>
+  </si>
+  <si>
+    <t>relationship--58dcff86-7f03-479a-af4d-3d632d0cf0d7</t>
+  </si>
+  <si>
+    <t>relationship--b5fad107-282d-4822-b74a-3ffbc0dbd25a</t>
+  </si>
+  <si>
+    <t>relationship--a0d19cd4-0b1f-4903-aba9-5ebb27785940</t>
+  </si>
+  <si>
+    <t>relationship--c242fcc7-9215-4e09-bdb1-db421f520abc</t>
+  </si>
+  <si>
+    <t>relationship--1f1f8692-7b1d-4c56-a805-b0a36e85dba1</t>
   </si>
   <si>
     <t>reference</t>
@@ -4013,124 +4013,124 @@
     <t>https://attack.mitre.org/campaigns/C0025/</t>
   </si>
   <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%2586%25D0%25B2%25D0%25B0%25D0%25BD_%25D0%259C%25D0%25B0%25D0%25B7%25D0%25B5%25D0%25BF%25D0%25B0</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%2586%25D1%2581%25D1%2582%25D0%25BE%25D1%2580%25D1%2596%25D1%258F_%25D0%2594%25D0%25BE%25D0%25BD%25D0%25B5%25D1%2586%25D1%258C%25D0%25BA%25D0%25BE%25D1%2597_%25D0%25BE%25D0%25B1%25D0%25BB%25D0%25B0%25D1%2581%25D1%2582%25D1%2596</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%2586%25D1%2581%25D1%2582%25D0%25BE%25D1%2580%25D1%2596%25D1%258F_%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D0%25B8</t>
-  </si>
-  <si>
-    <t>https://ru.wikipedia.org/wiki/%25D0%2590%25D0%25BD%25D0%25B4%25D1%2580%25D1%2583%25D1%2581%25D0%25BE%25D0%25B2%25D1%2581%25D0%25BA%25D0%25BE%25D0%25B5_%25D0%25BF%25D0%25B5%25D1%2580%25D0%25B5%25D0%25BC%25D0%25B8%25D1%2580%25D0%25B8%25D0%25B5</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%2590%25D0%25BD%25D0%25B5%25D0%25BA%25D1%2581%25D1%2596%25D1%258F_%25D0%259A%25D0%25B8%25D1%2597%25D0%25B2%25D1%2581%25D1%258C%25D0%25BA%25D0%25BE%25D1%2597_%25D0%25BC%25D0%25B8%25D1%2582%25D1%2580%25D0%25BE%25D0%25BF%25D0%25BE%25D0%25BB%25D1%2596%25D1%2597_%25D0%259C%25D0%25BE%25D1%2581%25D0%25BA%25D0%25BE%25D0%25B2%25D1%2581%25D1%258C%25D0%25BA%25D0%25B8%25D0%25BC_%25D0%25BF%25D0%25B0%25D1%2582%25D1%2580%25D1%2596%25D0%25B0%25D1%2580%25D1%2585%25D0%25B0%25D1%2582%25D0%25BE%25D0%25BC</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%2591%25D0%25B0%25D1%2582%25D1%2583%25D1%2580%25D0%25B8%25D0%25BD%25D1%2581%25D1%258C%25D0%25BA%25D0%25B0_%25D1%2582%25D1%2580%25D0%25B0%25D0%25B3%25D0%25B5%25D0%25B4%25D1%2596%25D1%258F</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%2592%25D1%2581%25D0%25B5%25D1%2581%25D0%25BE%25D1%258E%25D0%25B7%25D0%25BD%25D0%25B8%25D0%25B9_%25D1%2580%25D0%25B5%25D1%2584%25D0%25B5%25D1%2580%25D0%25B5%25D0%25BD%25D0%25B4%25D1%2583%25D0%25BC_%25D0%25BF%25D1%2580%25D0%25BE_%25D0%25B7%25D0%25B1%25D0%25B5%25D1%2580%25D0%25B5%25D0%25B6%25D0%25B5%25D0%25BD%25D0%25BD%25D1%258F_%25D0%25A1%25D0%25A0%25D0%25A1%25D0%25A0</t>
+    <t>https://uk.wikipedia.org/wiki/%D0%86%D0%B2%D0%B0%D0%BD_%D0%9C%D0%B0%D0%B7%D0%B5%D0%BF%D0%B0</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%86%D1%81%D1%82%D0%BE%D1%80%D1%96%D1%8F_%D0%94%D0%BE%D0%BD%D0%B5%D1%86%D1%8C%D0%BA%D0%BE%D1%97_%D0%BE%D0%B1%D0%BB%D0%B0%D1%81%D1%82%D1%96</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%86%D1%81%D1%82%D0%BE%D1%80%D1%96%D1%8F_%D0%A3%D0%BA%D1%80%D0%B0%D1%97%D0%BD%D0%B8</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%D0%90%D0%BD%D0%B4%D1%80%D1%83%D1%81%D0%BE%D0%B2%D1%81%D0%BA%D0%BE%D0%B5_%D0%BF%D0%B5%D1%80%D0%B5%D0%BC%D0%B8%D1%80%D0%B8%D0%B5</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%90%D0%BD%D0%B5%D0%BA%D1%81%D1%96%D1%8F_%D0%9A%D0%B8%D1%97%D0%B2%D1%81%D1%8C%D0%BA%D0%BE%D1%97_%D0%BC%D0%B8%D1%82%D1%80%D0%BE%D0%BF%D0%BE%D0%BB%D1%96%D1%97_%D0%9C%D0%BE%D1%81%D0%BA%D0%BE%D0%B2%D1%81%D1%8C%D0%BA%D0%B8%D0%BC_%D0%BF%D0%B0%D1%82%D1%80%D1%96%D0%B0%D1%80%D1%85%D0%B0%D1%82%D0%BE%D0%BC</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%91%D0%B0%D1%82%D1%83%D1%80%D0%B8%D0%BD%D1%81%D1%8C%D0%BA%D0%B0_%D1%82%D1%80%D0%B0%D0%B3%D0%B5%D0%B4%D1%96%D1%8F</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%92%D1%81%D0%B5%D1%81%D0%BE%D1%8E%D0%B7%D0%BD%D0%B8%D0%B9_%D1%80%D0%B5%D1%84%D0%B5%D1%80%D0%B5%D0%BD%D0%B4%D1%83%D0%BC_%D0%BF%D1%80%D0%BE_%D0%B7%D0%B1%D0%B5%D1%80%D0%B5%D0%B6%D0%B5%D0%BD%D0%BD%D1%8F_%D0%A1%D0%A0%D0%A1%D0%A0</t>
   </si>
   <si>
     <t>https://www.obozrevatel.com/novosti-obschestvo/dvojnoe-prestuplenie-sssr-kak-sovetyi-skryivali-chernobyilskuyu-katastrofu.htm</t>
   </si>
   <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%25A0%25D0%25BE%25D1%2581%25D1%2596%25D0%25B9%25D1%2581%25D1%258C%25D0%25BA%25D0%25B0_%25D0%25B4%25D0%25B5%25D0%25B7%25D1%2596%25D0%25BD%25D1%2584%25D0%25BE%25D1%2580%25D0%25BC%25D0%25B0%25D1%2586%25D1%2596%25D1%258F_%25D0%25BF%25D1%2596%25D0%25B4_%25D1%2587%25D0%25B0%25D1%2581_%25D1%2580%25D0%25BE%25D1%2581%25D1%2596%25D0%25B9%25D1%2581%25D1%258C%25D0%25BA%25D0%25BE-%25D1%2583%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D1%2581%25D1%258C%25D0%25BA%25D0%25BE%25D1%2597_%25D0%25B2%25D1%2596%25D0%25B9%25D0%25BD%25D0%25B8</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%2594%25D1%2580%25D1%2583%25D0%25B3%25D0%25B0_%25D0%259C%25D0%25B0%25D0%25BB%25D0%25BE%25D1%2580%25D0%25BE%25D1%2581%25D1%2596%25D0%25B9%25D1%2581%25D1%258C%25D0%25BA%25D0%25B0_%25D0%25BA%25D0%25BE%25D0%25BB%25D0%25B5%25D0%25B3%25D1%2596%25D1%258F</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%2597%25D0%25B0%25D0%25B4%25D1%2583%25D0%25BD%25D0%25B0%25D0%25B9%25D1%2581%25D1%258C%25D0%25BA%25D0%25B0_%25D0%25A1%25D1%2596%25D1%2587</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%2597%25D0%25B0%25D0%25BF%25D0%25BE%25D1%2580%25D0%25BE%25D0%25B7%25D1%258C%25D0%25BA%25D0%25B0_%25D0%25A1%25D1%2596%25D1%2587</t>
+    <t>https://uk.wikipedia.org/wiki/%D0%A0%D0%BE%D1%81%D1%96%D0%B9%D1%81%D1%8C%D0%BA%D0%B0_%D0%B4%D0%B5%D0%B7%D1%96%D0%BD%D1%84%D0%BE%D1%80%D0%BC%D0%B0%D1%86%D1%96%D1%8F_%D0%BF%D1%96%D0%B4_%D1%87%D0%B0%D1%81_%D1%80%D0%BE%D1%81%D1%96%D0%B9%D1%81%D1%8C%D0%BA%D0%BE-%D1%83%D0%BA%D1%80%D0%B0%D1%97%D0%BD%D1%81%D1%8C%D0%BA%D0%BE%D1%97_%D0%B2%D1%96%D0%B9%D0%BD%D0%B8</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%94%D1%80%D1%83%D0%B3%D0%B0_%D0%9C%D0%B0%D0%BB%D0%BE%D1%80%D0%BE%D1%81%D1%96%D0%B9%D1%81%D1%8C%D0%BA%D0%B0_%D0%BA%D0%BE%D0%BB%D0%B5%D0%B3%D1%96%D1%8F</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%97%D0%B0%D0%B4%D1%83%D0%BD%D0%B0%D0%B9%D1%81%D1%8C%D0%BA%D0%B0_%D0%A1%D1%96%D1%87</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%97%D0%B0%D0%BF%D0%BE%D1%80%D0%BE%D0%B7%D1%8C%D0%BA%D0%B0_%D0%A1%D1%96%D1%87</t>
   </si>
   <si>
     <t>https://ridl.io/ru/karatelnaja-psihiatrija-v-rossii-nazad-v-sssr/</t>
   </si>
   <si>
-    <t>https://ru.wikipedia.org/wiki/%25D0%259A%25D0%25B5%25D0%25BD%25D0%25B3%25D0%25B8%25D1%2580%25D1%2581%25D0%25BA%25D0%25BE%25D0%25B5_%25D0%25B2%25D0%25BE%25D1%2581%25D1%2581%25D1%2582%25D0%25B0%25D0%25BD%25D0%25B8%25D0%25B5_%25D0%25B7%25D0%25B0%25D0%25BA%25D0%25BB%25D1%258E%25D1%2587%25D1%2591%25D0%25BD%25D0%25BD%25D1%258B%25D1%2585</t>
+    <t>https://ru.wikipedia.org/wiki/%D0%9A%D0%B5%D0%BD%D0%B3%D0%B8%D1%80%D1%81%D0%BA%D0%BE%D0%B5_%D0%B2%D0%BE%D1%81%D1%81%D1%82%D0%B0%D0%BD%D0%B8%D0%B5_%D0%B7%D0%B0%D0%BA%D0%BB%D1%8E%D1%87%D1%91%D0%BD%D0%BD%D1%8B%D1%85</t>
   </si>
   <si>
     <t>https://ru.wikipedia.org/wiki/%D0%9A%D0%B8%D0%B5%D0%B2%D1%81%D0%BA%D0%B8%D0%B9_%D1%81%D0%B8%D0%BD%D0%BE%D0%BF%D1%81%D0%B8%D1%81</t>
   </si>
   <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%259A%25D0%25B8%25D1%2580%25D0%25B8%25D0%25BB%25D0%25BE-%25D0%259C%25D0%25B5%25D1%2584%25D0%25BE%25D0%25B4%25D1%2596%25D1%2597%25D0%25B2%25D1%2581%25D1%258C%25D0%25BA%25D0%25B5_%25D1%2582%25D0%25BE%25D0%25B2%25D0%25B0%25D1%2580%25D0%25B8%25D1%2581%25D1%2582%25D0%25B2%25D0%25BE</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%259A%25D0%25BE%25D0%25BD%25D0%25BE%25D1%2582%25D0%25BE%25D0%25BF%25D1%2581%25D1%258C%25D0%25BA%25D1%2596_%25D1%2581%25D1%2582%25D0%25B0%25D1%2582%25D1%2582%25D1%2596</t>
-  </si>
-  <si>
-    <t>https://ru.wikipedia.org/wiki/%25D0%259A%25D1%2580%25D1%258B%25D0%25BC%25D1%2581%25D0%25BA%25D0%25B0%25D1%258F_%25D0%25B2%25D0%25BE%25D0%25B9%25D0%25BD%25D0%25B0</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%259B%25D1%2596%25D0%25BA%25D0%25B2%25D1%2596%25D0%25B4%25D0%25B0%25D1%2586%25D1%2596%25D1%258F_%25D0%25B0%25D0%25B2%25D1%2582%25D0%25BE%25D0%25BD%25D0%25BE%25D0%25BC%25D1%2596%25D1%2597_%25D0%2593%25D0%25B5%25D1%2582%25D1%258C%25D0%25BC%25D0%25B0%25D0%25BD%25D1%2589%25D0%25B8%25D0%25BD%25D0%25B8</t>
-  </si>
-  <si>
-    <t>https://ru.wikipedia.org/wiki/%25D0%259C%25D0%25B0%25D0%25B7%25D0%25B5%25D0%25BF%25D0%25B0%2C_%25D0%2598%25D0%25B2%25D0%25B0%25D0%25BD_%25D0%25A1%25D1%2582%25D0%25B5%25D0%25BF%25D0%25B0%25D0%25BD%25D0%25BE%25D0%25B2%25D0%25B8%25D1%2587</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%259C%25D0%25B0%25D0%25BB%25D0%25BE%25D1%2580%25D0%25BE%25D1%2581%25D1%2596%25D0%25B9%25D1%2581%25D1%258C%25D0%25BA%25D0%25B5_%25D0%25B3%25D0%25B5%25D0%25BD%25D0%25B5%25D1%2580%25D0%25B0%25D0%25BB-%25D0%25B3%25D1%2583%25D0%25B1%25D0%25B5%25D1%2580%25D0%25BD%25D0%25B0%25D1%2582%25D0%25BE%25D1%2580%25D1%2581%25D1%2582%25D0%25B2%25D0%25BE</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%259C%25D0%25B0%25D0%25BB%25D0%25BE%25D1%2580%25D0%25BE%25D1%2581%25D1%2596%25D0%25B9%25D1%2581%25D1%258C%25D0%25BA%25D0%25B8%25D0%25B9_%25D0%25BF%25D1%2580%25D0%25B8%25D0%25BA%25D0%25B0%25D0%25B7</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%259D%25D0%25B0%25D1%2580%25D0%25BE%25D0%25B4%25D0%25BD%25D0%25B8%25D0%25B9_%25D1%2580%25D1%2583%25D1%2585_%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D0%25B8</t>
+    <t>https://uk.wikipedia.org/wiki/%D0%9A%D0%B8%D1%80%D0%B8%D0%BB%D0%BE-%D0%9C%D0%B5%D1%84%D0%BE%D0%B4%D1%96%D1%97%D0%B2%D1%81%D1%8C%D0%BA%D0%B5_%D1%82%D0%BE%D0%B2%D0%B0%D1%80%D0%B8%D1%81%D1%82%D0%B2%D0%BE</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%9A%D0%BE%D0%BD%D0%BE%D1%82%D0%BE%D0%BF%D1%81%D1%8C%D0%BA%D1%96_%D1%81%D1%82%D0%B0%D1%82%D1%82%D1%96</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%D0%9A%D1%80%D1%8B%D0%BC%D1%81%D0%BA%D0%B0%D1%8F_%D0%B2%D0%BE%D0%B9%D0%BD%D0%B0</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%9B%D1%96%D0%BA%D0%B2%D1%96%D0%B4%D0%B0%D1%86%D1%96%D1%8F_%D0%B0%D0%B2%D1%82%D0%BE%D0%BD%D0%BE%D0%BC%D1%96%D1%97_%D0%93%D0%B5%D1%82%D1%8C%D0%BC%D0%B0%D0%BD%D1%89%D0%B8%D0%BD%D0%B8</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%D0%9C%D0%B0%D0%B7%D0%B5%D0%BF%D0%B0%2C_%D0%98%D0%B2%D0%B0%D0%BD_%D0%A1%D1%82%D0%B5%D0%BF%D0%B0%D0%BD%D0%BE%D0%B2%D0%B8%D1%87</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%9C%D0%B0%D0%BB%D0%BE%D1%80%D0%BE%D1%81%D1%96%D0%B9%D1%81%D1%8C%D0%BA%D0%B5_%D0%B3%D0%B5%D0%BD%D0%B5%D1%80%D0%B0%D0%BB-%D0%B3%D1%83%D0%B1%D0%B5%D1%80%D0%BD%D0%B0%D1%82%D0%BE%D1%80%D1%81%D1%82%D0%B2%D0%BE</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%9C%D0%B0%D0%BB%D0%BE%D1%80%D0%BE%D1%81%D1%96%D0%B9%D1%81%D1%8C%D0%BA%D0%B8%D0%B9_%D0%BF%D1%80%D0%B8%D0%BA%D0%B0%D0%B7</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%9D%D0%B0%D1%80%D0%BE%D0%B4%D0%BD%D0%B8%D0%B9_%D1%80%D1%83%D1%85_%D0%A3%D0%BA%D1%80%D0%B0%D1%97%D0%BD%D0%B8</t>
   </si>
   <si>
     <t>https://uk.wikipedia.org/wiki/%D0%9F%D0%B5%D1%80%D0%B5%D1%8F%D1%81%D0%BB%D0%B0%D0%B2%D1%81%D1%8C%D0%BA%D0%B0_%D1%80%D0%B0%D0%B4%D0%B0</t>
   </si>
   <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%259F%25D0%25BE%25D0%25B4%25D1%2596%25D0%25BB%25D0%25B8_%25D0%25A0%25D0%25B5%25D1%2587%25D1%2596_%25D0%259F%25D0%25BE%25D1%2581%25D0%25BF%25D0%25BE%25D0%25BB%25D0%25B8%25D1%2582%25D0%25BE%25D1%2597</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%259F%25D1%2580%25D0%25B0%25D0%25B2%25D0%25BB%25D1%2596%25D0%25BD%25D0%25BD%25D1%258F_%25D0%25B3%25D0%25B5%25D1%2582%25D1%258C%25D0%25BC%25D0%25B0%25D0%25BD%25D1%2581%25D1%258C%25D0%25BA%25D0%25BE%25D0%25B3%25D0%25BE_%25D1%2583%25D1%2580%25D1%258F%25D0%25B4%25D1%2583</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%25A0%25D0%25B5%25D1%2588%25D0%25B5%25D1%2582%25D0%25B8%25D0%25BB%25D1%2596%25D0%25B2%25D1%2581%25D1%258C%25D0%25BA%25D1%2596_%25D1%2581%25D1%2582%25D0%25B0%25D1%2582%25D1%2582%25D1%2596</t>
-  </si>
-  <si>
-    <t>https://ru.wikipedia.org/wiki/%25D0%25A0%25D0%25BE%25D1%2581%25D1%2581%25D0%25B8%25D0%25B9%25D1%2581%25D0%25BA%25D0%25B8%25D0%25B5_%25D1%2583%25D0%25B4%25D0%25B0%25D1%2580%25D1%258B_%25D0%25BF%25D0%25BE_%25D1%2583%25D0%25BA%25D1%2580%25D0%25B0%25D0%25B8%25D0%25BD%25D1%2581%25D0%25BA%25D0%25BE%25D0%25B9_%25D1%258D%25D0%25BD%25D0%25B5%25D1%2580%25D0%25B3%25D0%25BE%25D1%2581%25D0%25B8%25D1%2581%25D1%2582%25D0%25B5%25D0%25BC%25D0%25B5</t>
+    <t>https://uk.wikipedia.org/wiki/%D0%9F%D0%BE%D0%B4%D1%96%D0%BB%D0%B8_%D0%A0%D0%B5%D1%87%D1%96_%D0%9F%D0%BE%D1%81%D0%BF%D0%BE%D0%BB%D0%B8%D1%82%D0%BE%D1%97</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%9F%D1%80%D0%B0%D0%B2%D0%BB%D1%96%D0%BD%D0%BD%D1%8F_%D0%B3%D0%B5%D1%82%D1%8C%D0%BC%D0%B0%D0%BD%D1%81%D1%8C%D0%BA%D0%BE%D0%B3%D0%BE_%D1%83%D1%80%D1%8F%D0%B4%D1%83</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%A0%D0%B5%D1%88%D0%B5%D1%82%D0%B8%D0%BB%D1%96%D0%B2%D1%81%D1%8C%D0%BA%D1%96_%D1%81%D1%82%D0%B0%D1%82%D1%82%D1%96</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%D0%A0%D0%BE%D1%81%D1%81%D0%B8%D0%B9%D1%81%D0%BA%D0%B8%D0%B5_%D1%83%D0%B4%D0%B0%D1%80%D1%8B_%D0%BF%D0%BE_%D1%83%D0%BA%D1%80%D0%B0%D0%B8%D0%BD%D1%81%D0%BA%D0%BE%D0%B9_%D1%8D%D0%BD%D0%B5%D1%80%D0%B3%D0%BE%D1%81%D0%B8%D1%81%D1%82%D0%B5%D0%BC%D0%B5</t>
   </si>
   <si>
     <t>https://web.archive.org/web/20160304195659/http%3A//www.memo.ru/2010/09/27/rch.pdf</t>
   </si>
   <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%25A0%25D1%2583%25D1%2581%25D0%25B8%25D1%2584%25D1%2596%25D0%25BA%25D0%25B0%25D1%2586%25D1%2596%25D1%258F_%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D0%25B8</t>
+    <t>https://uk.wikipedia.org/wiki/%D0%A0%D1%83%D1%81%D0%B8%D1%84%D1%96%D0%BA%D0%B0%D1%86%D1%96%D1%8F_%D0%A3%D0%BA%D1%80%D0%B0%D1%97%D0%BD%D0%B8</t>
   </si>
   <si>
     <t>https://uk.wikipedia.org/wiki/%D0%A0%D1%83%D1%97%D0%BD%D0%B0</t>
   </si>
   <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%25A0%25D1%2596%25D1%2588%25D0%25B8%25D1%2582%25D0%25B5%25D0%25BB%25D1%258C%25D0%25BD%25D1%2596_%25D0%25BF%25D1%2583%25D0%25BD%25D0%25BA%25D1%2582%25D0%25B8</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%25A1%25D0%25B5%25D1%2580%25D0%25BF%25D0%25BD%25D0%25B5%25D0%25B2%25D0%25B8%25D0%25B9_%25D0%25BF%25D1%2583%25D1%2582%25D1%2587</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%25A1%25D0%25BA%25D0%25B0%25D1%2581%25D1%2583%25D0%25B2%25D0%25B0%25D0%25BD%25D0%25BD%25D1%258F_%25D0%25BA%25D0%25BE%25D0%25B7%25D0%25B0%25D1%2586%25D1%258C%25D0%25BA%25D0%25BE%25D0%25B3%25D0%25BE_%25D1%2583%25D1%2581%25D1%2582%25D1%2580%25D0%25BE%25D1%258E_%25D0%25B2_%25D0%25A1%25D0%25BB%25D0%25BE%25D0%25B1%25D1%2596%25D0%25B4%25D1%2581%25D1%258C%25D0%25BA%25D1%2596%25D0%25B9_%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D1%2596</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%25A1%25D0%25BC%25D1%2583%25D0%25B3%25D0%25B0_%25D0%25BE%25D1%2581%25D1%2596%25D0%25BB%25D0%25BE%25D1%2581%25D1%2582%25D1%2596</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%25A1%25D1%2582%25D0%25BE%25D0%25BB%25D0%25B8%25D0%25BF%25D1%2596%25D0%25BD%25D1%2581%25D1%258C%25D0%25BA%25D0%25B0_%25D1%2580%25D0%25B5%25D1%2584%25D0%25BE%25D1%2580%25D0%25BC%25D0%25B0</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D0%25B0_%25D0%25B2_%25D0%259F%25D0%25B5%25D1%2580%25D1%2588%25D1%2596%25D0%25B9_%25D1%2581%25D0%25B2%25D1%2596%25D1%2582%25D0%25BE%25D0%25B2%25D1%2596%25D0%25B9_%25D0%25B2%25D1%2596%25D0%25B9%25D0%25BD%25D1%2596</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D0%25B0_%25D1%2583_%25D0%25B2%25D1%2596%25D0%25B9%25D0%25BD%25D0%25B0%25D1%2585_%25D0%259D%25D0%25B0%25D0%25BF%25D0%25BE%25D0%25BB%25D0%25B5%25D0%25BE%25D0%25BD%25D0%25B0</t>
+    <t>https://uk.wikipedia.org/wiki/%D0%A0%D1%96%D1%88%D0%B8%D1%82%D0%B5%D0%BB%D1%8C%D0%BD%D1%96_%D0%BF%D1%83%D0%BD%D0%BA%D1%82%D0%B8</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%A1%D0%B5%D1%80%D0%BF%D0%BD%D0%B5%D0%B2%D0%B8%D0%B9_%D0%BF%D1%83%D1%82%D1%87</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%A1%D0%BA%D0%B0%D1%81%D1%83%D0%B2%D0%B0%D0%BD%D0%BD%D1%8F_%D0%BA%D0%BE%D0%B7%D0%B0%D1%86%D1%8C%D0%BA%D0%BE%D0%B3%D0%BE_%D1%83%D1%81%D1%82%D1%80%D0%BE%D1%8E_%D0%B2_%D0%A1%D0%BB%D0%BE%D0%B1%D1%96%D0%B4%D1%81%D1%8C%D0%BA%D1%96%D0%B9_%D0%A3%D0%BA%D1%80%D0%B0%D1%97%D0%BD%D1%96</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%A1%D0%BC%D1%83%D0%B3%D0%B0_%D0%BE%D1%81%D1%96%D0%BB%D0%BE%D1%81%D1%82%D1%96</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%A1%D1%82%D0%BE%D0%BB%D0%B8%D0%BF%D1%96%D0%BD%D1%81%D1%8C%D0%BA%D0%B0_%D1%80%D0%B5%D1%84%D0%BE%D1%80%D0%BC%D0%B0</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%A3%D0%BA%D1%80%D0%B0%D1%97%D0%BD%D0%B0_%D0%B2_%D0%9F%D0%B5%D1%80%D1%88%D1%96%D0%B9_%D1%81%D0%B2%D1%96%D1%82%D0%BE%D0%B2%D1%96%D0%B9_%D0%B2%D1%96%D0%B9%D0%BD%D1%96</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%A3%D0%BA%D1%80%D0%B0%D1%97%D0%BD%D0%B0_%D1%83_%D0%B2%D1%96%D0%B9%D0%BD%D0%B0%D1%85_%D0%9D%D0%B0%D0%BF%D0%BE%D0%BB%D0%B5%D0%BE%D0%BD%D0%B0</t>
   </si>
   <si>
     <t>https://beda.media/ru/articles/war-in-chechnya-chronicle-part1-ru</t>
   </si>
   <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%25A7%25D0%25BE%25D1%2580%25D0%25BD%25D0%25BE%25D1%2581%25D0%25BE%25D1%2582%25D0%25B5%25D0%25BD%25D1%2586%25D1%2596</t>
+    <t>https://uk.wikipedia.org/wiki/%D0%A7%D0%BE%D1%80%D0%BD%D0%BE%D1%81%D0%BE%D1%82%D0%B5%D0%BD%D1%86%D1%96</t>
   </si>
 </sst>
 </file>
